--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
         <v>0.1</v>
@@ -541,16 +541,16 @@
         <v>71.8</v>
       </c>
       <c r="I2" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="J2" t="n">
-        <v>34.6</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
         <v>21.5</v>
       </c>
       <c r="L2" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>42.4</v>
       </c>
       <c r="D3" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="E3" t="n">
         <v>4.2</v>
@@ -595,22 +595,22 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.8</v>
+        <v>60.6</v>
       </c>
       <c r="I3" t="n">
-        <v>43.7</v>
+        <v>39.4</v>
       </c>
       <c r="J3" t="n">
-        <v>26.4</v>
+        <v>23.7</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>14.3</v>
       </c>
       <c r="L3" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -634,217 +634,217 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90.5</v>
+        <v>99.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>66.7</v>
+        <v>73</v>
       </c>
       <c r="I4" t="n">
-        <v>37.3</v>
+        <v>42.1</v>
       </c>
       <c r="J4" t="n">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
       <c r="K4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="L4" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1593.4</v>
+        <v>1577.2</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26.1</v>
+        <v>90.7</v>
       </c>
       <c r="D5" t="n">
-        <v>53.5</v>
+        <v>7.4</v>
       </c>
       <c r="E5" t="n">
-        <v>20.2</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
-        <v>97.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="H5" t="n">
-        <v>59.9</v>
+        <v>66.5</v>
       </c>
       <c r="I5" t="n">
-        <v>38.7</v>
+        <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>23.5</v>
+        <v>21.6</v>
       </c>
       <c r="K5" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="L5" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1560</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="R5" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>26.2</v>
       </c>
       <c r="D6" t="n">
-        <v>31.4</v>
+        <v>53.1</v>
       </c>
       <c r="E6" t="n">
-        <v>8.199999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" t="n">
-        <v>62.8</v>
+        <v>60.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>39.2</v>
       </c>
       <c r="J6" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="K6" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="L6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1582.5</v>
+        <v>1560</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="R6" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>59.8</v>
       </c>
       <c r="D7" t="n">
-        <v>32.4</v>
+        <v>31.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G7" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="H7" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="K7" t="n">
         <v>11.3</v>
@@ -858,17 +858,17 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1577.2</v>
+        <v>1582.5</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8">
@@ -883,34 +883,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.6</v>
+        <v>51.6</v>
       </c>
       <c r="D8" t="n">
-        <v>27.5</v>
+        <v>26.7</v>
       </c>
       <c r="E8" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="H8" t="n">
         <v>58.4</v>
       </c>
       <c r="I8" t="n">
-        <v>35.3</v>
+        <v>36.3</v>
       </c>
       <c r="J8" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="K8" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D9" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>64.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="J9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="K9" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1018,16 +1018,16 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>65.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="I10" t="n">
-        <v>35.9</v>
+        <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="K10" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>4.9</v>
@@ -1054,283 +1054,283 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56.4</v>
+        <v>37.3</v>
       </c>
       <c r="D11" t="n">
-        <v>25.2</v>
+        <v>50.9</v>
       </c>
       <c r="E11" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>44.2</v>
+        <v>52.4</v>
       </c>
       <c r="I11" t="n">
-        <v>28.4</v>
+        <v>31</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="K11" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>4.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1603.8</v>
+        <v>1575.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="R11" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.1</v>
+        <v>56.2</v>
       </c>
       <c r="D12" t="n">
-        <v>49.2</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="G12" t="n">
-        <v>97.8</v>
+        <v>91.3</v>
       </c>
       <c r="H12" t="n">
-        <v>55.9</v>
+        <v>44.1</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="J12" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="K12" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1556.1</v>
+        <v>1603.8</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.1</v>
+        <v>60.7</v>
       </c>
       <c r="D13" t="n">
-        <v>52.3</v>
+        <v>39.1</v>
       </c>
       <c r="E13" t="n">
-        <v>8.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>52.8</v>
+        <v>46.7</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="L13" t="n">
         <v>2.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1569.9</v>
+        <v>1571</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38.3</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>52.3</v>
       </c>
       <c r="E14" t="n">
-        <v>21.8</v>
+        <v>8.5</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>92.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="H14" t="n">
-        <v>43.3</v>
+        <v>56.9</v>
       </c>
       <c r="I14" t="n">
-        <v>22.1</v>
+        <v>26.9</v>
       </c>
       <c r="J14" t="n">
-        <v>10.7</v>
+        <v>12.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1575.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="R14" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.1</v>
+        <v>28.9</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>32.9</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>24.7</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="G15" t="n">
-        <v>99.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H15" t="n">
-        <v>57.7</v>
+        <v>49.2</v>
       </c>
       <c r="I15" t="n">
-        <v>27.6</v>
+        <v>22.4</v>
       </c>
       <c r="J15" t="n">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1338,59 +1338,59 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1545.2</v>
+        <v>1565</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>25.2</v>
       </c>
       <c r="D16" t="n">
-        <v>32.7</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>24.5</v>
+        <v>1.9</v>
       </c>
       <c r="F16" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>78.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>48.4</v>
+        <v>58.3</v>
       </c>
       <c r="I16" t="n">
-        <v>21.9</v>
+        <v>26.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1398,17 +1398,17 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1565</v>
+        <v>1545.2</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="17">
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="E17" t="n">
         <v>27.2</v>
@@ -1435,22 +1435,22 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>51.5</v>
+        <v>45.2</v>
       </c>
       <c r="I17" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1486,31 +1486,31 @@
         <v>52.6</v>
       </c>
       <c r="D18" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="E18" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="F18" t="n">
         <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H18" t="n">
-        <v>56.9</v>
+        <v>57.8</v>
       </c>
       <c r="I18" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="J18" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1534,58 +1534,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>63.2</v>
+        <v>13.8</v>
       </c>
       <c r="F19" t="n">
-        <v>15.6</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>62.9</v>
+        <v>94</v>
       </c>
       <c r="H19" t="n">
-        <v>31.7</v>
+        <v>44.5</v>
       </c>
       <c r="I19" t="n">
-        <v>17.6</v>
+        <v>19.9</v>
       </c>
       <c r="J19" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1573.4</v>
+        <v>1556.1</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="R19" t="n">
         <v>0.6899999999999999</v>
@@ -1594,118 +1594,118 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36.2</v>
+        <v>1.2</v>
       </c>
       <c r="D20" t="n">
-        <v>34.8</v>
+        <v>20.3</v>
       </c>
       <c r="E20" t="n">
-        <v>24.3</v>
+        <v>62.6</v>
       </c>
       <c r="F20" t="n">
-        <v>4.7</v>
+        <v>15.9</v>
       </c>
       <c r="G20" t="n">
-        <v>91.7</v>
+        <v>65.3</v>
       </c>
       <c r="H20" t="n">
-        <v>39</v>
+        <v>32.7</v>
       </c>
       <c r="I20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1571</v>
+        <v>1573.4</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>98.7</v>
+        <v>21.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3</v>
+        <v>24.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="H21" t="n">
-        <v>58.2</v>
+        <v>34.1</v>
       </c>
       <c r="I21" t="n">
-        <v>24.5</v>
+        <v>16.4</v>
       </c>
       <c r="J21" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1522.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.06</v>
+        <v>0.79</v>
       </c>
       <c r="R21" t="n">
         <v>0.61</v>
@@ -1714,58 +1714,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.9</v>
+        <v>98.7</v>
       </c>
       <c r="D22" t="n">
-        <v>24.4</v>
+        <v>1.3</v>
       </c>
       <c r="E22" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>63.2</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>33.8</v>
+        <v>60.4</v>
       </c>
       <c r="I22" t="n">
-        <v>16.1</v>
+        <v>25.3</v>
       </c>
       <c r="J22" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1546.8</v>
+        <v>1522.7</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="R22" t="n">
         <v>0.61</v>
@@ -1783,31 +1783,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="n">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="E23" t="n">
         <v>25.8</v>
       </c>
       <c r="F23" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="G23" t="n">
-        <v>75.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="I23" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.2</v>
@@ -1834,40 +1834,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.699999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="D24" t="n">
-        <v>21.7</v>
+        <v>30.4</v>
       </c>
       <c r="E24" t="n">
-        <v>67.7</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>84.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>33.9</v>
+        <v>35.3</v>
       </c>
       <c r="I24" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="J24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L24" t="n">
         <v>0.9</v>
@@ -1878,137 +1878,137 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1521.6</v>
+        <v>1537.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="R24" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>68.2</v>
+        <v>21.7</v>
       </c>
       <c r="E25" t="n">
-        <v>23.2</v>
+        <v>67.7</v>
       </c>
       <c r="F25" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="G25" t="n">
-        <v>89.5</v>
+        <v>89.2</v>
       </c>
       <c r="H25" t="n">
-        <v>37.4</v>
+        <v>32.6</v>
       </c>
       <c r="I25" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="J25" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1550.3</v>
+        <v>1521.6</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.3</v>
+        <v>3.9</v>
       </c>
       <c r="D26" t="n">
-        <v>30.1</v>
+        <v>68.2</v>
       </c>
       <c r="E26" t="n">
-        <v>33.4</v>
+        <v>23.3</v>
       </c>
       <c r="F26" t="n">
-        <v>21.2</v>
+        <v>4.6</v>
       </c>
       <c r="G26" t="n">
-        <v>68.2</v>
+        <v>91.3</v>
       </c>
       <c r="H26" t="n">
-        <v>34.8</v>
+        <v>38.3</v>
       </c>
       <c r="I26" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="J26" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>0.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1537.9</v>
+        <v>1550.3</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.89</v>
+        <v>1.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
@@ -2026,7 +2026,7 @@
         <v>1.2</v>
       </c>
       <c r="D27" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="E27" t="n">
         <v>25.3</v>
@@ -2035,16 +2035,16 @@
         <v>5.7</v>
       </c>
       <c r="G27" t="n">
-        <v>87.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>36.4</v>
+        <v>36.8</v>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K27" t="n">
         <v>1.7</v>
@@ -2074,280 +2074,280 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.5</v>
+        <v>22.1</v>
       </c>
       <c r="D28" t="n">
-        <v>15.2</v>
+        <v>37.9</v>
       </c>
       <c r="E28" t="n">
-        <v>61.1</v>
+        <v>21.7</v>
       </c>
       <c r="F28" t="n">
-        <v>22.3</v>
+        <v>18.3</v>
       </c>
       <c r="G28" t="n">
-        <v>57.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>24.2</v>
+        <v>22.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1544.1</v>
+        <v>1494.5</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="R28" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.2</v>
+        <v>1.5</v>
       </c>
       <c r="D29" t="n">
-        <v>37.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>57.2</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>30.2</v>
       </c>
       <c r="G29" t="n">
-        <v>76.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="H29" t="n">
-        <v>22.1</v>
+        <v>20.1</v>
       </c>
       <c r="I29" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L29" t="n">
         <v>0.4</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1494.5</v>
+        <v>1564.9</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="D30" t="n">
-        <v>11.3</v>
+        <v>45.1</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>25.9</v>
       </c>
       <c r="F30" t="n">
-        <v>30.1</v>
+        <v>26.2</v>
       </c>
       <c r="G30" t="n">
-        <v>46.5</v>
+        <v>66.5</v>
       </c>
       <c r="H30" t="n">
-        <v>18.1</v>
+        <v>27.1</v>
       </c>
       <c r="I30" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1564.9</v>
+        <v>1554.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="R30" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>44.9</v>
+        <v>4.9</v>
       </c>
       <c r="E31" t="n">
-        <v>26.2</v>
+        <v>72.3</v>
       </c>
       <c r="F31" t="n">
-        <v>26.1</v>
+        <v>22.7</v>
       </c>
       <c r="G31" t="n">
-        <v>65</v>
+        <v>23.2</v>
       </c>
       <c r="H31" t="n">
-        <v>26.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
         <v>0.3</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1554.9</v>
+        <v>1544.1</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.09</v>
+        <v>0.58</v>
       </c>
       <c r="R31" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>26.5</v>
+        <v>0.1</v>
       </c>
       <c r="D32" t="n">
-        <v>27.2</v>
+        <v>30.9</v>
       </c>
       <c r="E32" t="n">
-        <v>45.1</v>
+        <v>52.9</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2</v>
+        <v>16.1</v>
       </c>
       <c r="G32" t="n">
-        <v>95.8</v>
+        <v>71.8</v>
       </c>
       <c r="H32" t="n">
-        <v>27.6</v>
+        <v>23.1</v>
       </c>
       <c r="I32" t="n">
-        <v>9.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L32" t="n">
         <v>0.2</v>
@@ -2358,119 +2358,119 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1507.6</v>
+        <v>1519.6</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="R32" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>30.9</v>
+        <v>8.5</v>
       </c>
       <c r="E33" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="F33" t="n">
-        <v>16.1</v>
+        <v>39</v>
       </c>
       <c r="G33" t="n">
-        <v>69.09999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="H33" t="n">
-        <v>23.1</v>
+        <v>8.1</v>
       </c>
       <c r="I33" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1519.6</v>
+        <v>1534.2</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="R33" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="n">
-        <v>21.8</v>
+        <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>78.2</v>
+        <v>56.7</v>
       </c>
       <c r="G34" t="n">
-        <v>17</v>
+        <v>36.6</v>
       </c>
       <c r="H34" t="n">
-        <v>6.5</v>
+        <v>14.4</v>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K34" t="n">
         <v>0.4</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2478,53 +2478,53 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1578.2</v>
+        <v>1555</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>25.9</v>
+        <v>21.8</v>
       </c>
       <c r="F35" t="n">
-        <v>56.7</v>
+        <v>78.2</v>
       </c>
       <c r="G35" t="n">
-        <v>35.3</v>
+        <v>18.6</v>
       </c>
       <c r="H35" t="n">
-        <v>13.8</v>
+        <v>7.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
         <v>0.4</v>
@@ -2538,56 +2538,56 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1555</v>
+        <v>1578.2</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="R35" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="F36" t="n">
         <v>19.2</v>
       </c>
-      <c r="E36" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="F36" t="n">
-        <v>33.3</v>
-      </c>
       <c r="G36" t="n">
-        <v>45.3</v>
+        <v>56</v>
       </c>
       <c r="H36" t="n">
-        <v>11.1</v>
+        <v>17.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
         <v>1.3</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L36" t="n">
         <v>0.1</v>
@@ -2598,56 +2598,56 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1516.6</v>
+        <v>1514.3</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D37" t="n">
-        <v>8.5</v>
+        <v>19.1</v>
       </c>
       <c r="E37" t="n">
-        <v>52.5</v>
+        <v>35.4</v>
       </c>
       <c r="F37" t="n">
-        <v>39</v>
+        <v>33.5</v>
       </c>
       <c r="G37" t="n">
-        <v>20.3</v>
+        <v>45.9</v>
       </c>
       <c r="H37" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L37" t="n">
         <v>0.1</v>
@@ -2658,53 +2658,53 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1534.2</v>
+        <v>1516.6</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.15</v>
+        <v>0.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="R37" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="D38" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>23.9</v>
       </c>
       <c r="F38" t="n">
-        <v>19.2</v>
+        <v>62.4</v>
       </c>
       <c r="G38" t="n">
-        <v>55.8</v>
+        <v>31.4</v>
       </c>
       <c r="H38" t="n">
-        <v>17.4</v>
+        <v>12.1</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K38" t="n">
         <v>0.3</v>
@@ -2714,81 +2714,81 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1514.3</v>
+        <v>1544.8</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>24.2</v>
+        <v>88</v>
       </c>
       <c r="F39" t="n">
-        <v>61.9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>30.2</v>
+        <v>81.7</v>
       </c>
       <c r="H39" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L39" t="n">
         <v>0.1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1544.8</v>
+        <v>1507.6</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="R39" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="40">
@@ -2803,25 +2803,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="E40" t="n">
         <v>30.4</v>
       </c>
       <c r="F40" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="G40" t="n">
-        <v>40.1</v>
+        <v>41.3</v>
       </c>
       <c r="H40" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0.8</v>
@@ -2866,22 +2866,22 @@
         <v>5.7</v>
       </c>
       <c r="D41" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="F41" t="n">
-        <v>56.2</v>
+        <v>56.5</v>
       </c>
       <c r="G41" t="n">
-        <v>31.6</v>
+        <v>32.2</v>
       </c>
       <c r="H41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0.6</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="Q41" t="n">
         <v>1.13</v>
@@ -2935,16 +2935,16 @@
         <v>56.4</v>
       </c>
       <c r="G42" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="H42" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K42" t="n">
         <v>0.1</v>
@@ -2989,22 +2989,22 @@
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F43" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K43" t="n">
         <v>0.1</v>
@@ -3043,25 +3043,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="E44" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="F44" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="G44" t="n">
-        <v>65.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0.4</v>
@@ -3103,28 +3103,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>3.2</v>
+        <v>12.3</v>
       </c>
       <c r="E45" t="n">
-        <v>19.5</v>
+        <v>13.9</v>
       </c>
       <c r="F45" t="n">
-        <v>76.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G45" t="n">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
       <c r="H45" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3142,13 +3142,13 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="46">
@@ -3175,7 +3175,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H46" t="n">
         <v>0.1</v>
@@ -3229,19 +3229,19 @@
         <v>0.8</v>
       </c>
       <c r="E47" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F47" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="G47" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="H47" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         <v>80.8</v>
       </c>
       <c r="G48" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="H48" t="n">
         <v>2.7</v>
@@ -3325,7 +3325,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R48" t="n">
         <v>0.24</v>
@@ -3343,25 +3343,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>89.8</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3382,13 +3382,13 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -3487,13 +3487,13 @@
         <v>68.2</v>
       </c>
       <c r="E3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="F3" t="n">
         <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>89.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="4">
@@ -3520,7 +3520,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="5">
@@ -3547,7 +3547,7 @@
         <v>56.4</v>
       </c>
       <c r="G5" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D6" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="D7" t="n">
         <v>73</v>
@@ -3622,13 +3622,13 @@
         <v>1.9</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>19.2</v>
       </c>
       <c r="G8" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -3655,7 +3655,7 @@
         <v>80.8</v>
       </c>
       <c r="G9" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -3673,7 +3673,7 @@
         <v>42.4</v>
       </c>
       <c r="D10" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="E10" t="n">
         <v>4.2</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="E11" t="n">
         <v>27.2</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3736,7 +3736,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>84.8</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="13">
@@ -3763,7 +3763,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -3808,7 +3808,7 @@
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="E15" t="n">
         <v>25.3</v>
@@ -3817,7 +3817,7 @@
         <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>87.8</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3844,7 +3844,7 @@
         <v>16.1</v>
       </c>
       <c r="G16" t="n">
-        <v>69.09999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="17">
@@ -3871,7 +3871,7 @@
         <v>78.2</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="18">
@@ -3886,19 +3886,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>99.8</v>
       </c>
       <c r="D18" t="n">
-        <v>32.4</v>
+        <v>0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -3913,19 +3913,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40.1</v>
+        <v>0.2</v>
       </c>
       <c r="D19" t="n">
-        <v>49.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>10.1</v>
+        <v>13.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>97.8</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -3940,19 +3940,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>15.2</v>
+        <v>4.9</v>
       </c>
       <c r="E20" t="n">
-        <v>61.1</v>
+        <v>72.3</v>
       </c>
       <c r="F20" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="G20" t="n">
-        <v>57.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="21">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>12.3</v>
       </c>
       <c r="E21" t="n">
-        <v>19.5</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>76.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G21" t="n">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="22">
@@ -3994,19 +3994,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>50.9</v>
       </c>
       <c r="E22" t="n">
-        <v>21.8</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -4021,19 +4021,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36.2</v>
+        <v>60.7</v>
       </c>
       <c r="D23" t="n">
-        <v>34.8</v>
+        <v>39.1</v>
       </c>
       <c r="E23" t="n">
-        <v>24.3</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -4048,19 +4048,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.5</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>27.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>45.1</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>95.8</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="25">
@@ -4075,19 +4075,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>89.8</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4102,19 +4102,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50.6</v>
+        <v>51.6</v>
       </c>
       <c r="D26" t="n">
-        <v>27.5</v>
+        <v>26.7</v>
       </c>
       <c r="E26" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="F26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G26" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="27">
@@ -4129,19 +4129,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="D27" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="E27" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="G27" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D28" t="n">
-        <v>34.9</v>
+        <v>35.7</v>
       </c>
       <c r="E28" t="n">
         <v>25.8</v>
       </c>
       <c r="F28" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="G28" t="n">
-        <v>75.3</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -4186,16 +4186,16 @@
         <v>5.7</v>
       </c>
       <c r="D29" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="F29" t="n">
-        <v>56.2</v>
+        <v>56.5</v>
       </c>
       <c r="G29" t="n">
-        <v>31.6</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="30">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="D30" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="E30" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F30" t="n">
         <v>6.3</v>
       </c>
       <c r="G30" t="n">
-        <v>91</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="31">
@@ -4237,19 +4237,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D31" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="G31" t="n">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="D32" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="E32" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="F32" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="G32" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="33">
@@ -4291,19 +4291,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="E33" t="n">
         <v>30.4</v>
       </c>
       <c r="F33" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="G33" t="n">
-        <v>40.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="34">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="D34" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="E34" t="n">
         <v>8.199999999999999</v>
@@ -4330,7 +4330,7 @@
         <v>0.4</v>
       </c>
       <c r="G34" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="35">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="D35" t="n">
         <v>52.3</v>
       </c>
       <c r="E35" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F35" t="n">
         <v>0.9</v>
       </c>
       <c r="G35" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="36">
@@ -4372,19 +4372,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D36" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="n">
-        <v>57</v>
+        <v>57.2</v>
       </c>
       <c r="F36" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="G36" t="n">
-        <v>46.5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="37">
@@ -4405,13 +4405,13 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="38">
@@ -4426,13 +4426,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="D38" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F38" t="n">
         <v>0.1</v>
@@ -4453,19 +4453,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="D39" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="E39" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="F39" t="n">
         <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>97.40000000000001</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
@@ -4483,16 +4483,16 @@
         <v>1.2</v>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="E40" t="n">
-        <v>63.2</v>
+        <v>62.6</v>
       </c>
       <c r="F40" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="G40" t="n">
-        <v>62.9</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="41">
@@ -4513,13 +4513,13 @@
         <v>0.8</v>
       </c>
       <c r="E41" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="F41" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="G41" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="42">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="E42" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="G42" t="n">
-        <v>78.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="43">
@@ -4564,16 +4564,16 @@
         <v>52.6</v>
       </c>
       <c r="D43" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="E43" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="F43" t="n">
         <v>3.2</v>
       </c>
       <c r="G43" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="44">
@@ -4588,19 +4588,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="D44" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="E44" t="n">
-        <v>33.4</v>
+        <v>33</v>
       </c>
       <c r="F44" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="G44" t="n">
-        <v>68.2</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4621,13 +4621,13 @@
         <v>10.9</v>
       </c>
       <c r="E45" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F45" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="G45" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="46">
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
       <c r="D46" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="E46" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="47">
@@ -4672,16 +4672,16 @@
         <v>2.8</v>
       </c>
       <c r="D47" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="E47" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F47" t="n">
         <v>26.2</v>
       </c>
-      <c r="F47" t="n">
-        <v>26.1</v>
-      </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="48">
@@ -4702,13 +4702,13 @@
         <v>15.3</v>
       </c>
       <c r="E48" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
         <v>56.7</v>
       </c>
       <c r="G48" t="n">
-        <v>35.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="49">
@@ -4723,19 +4723,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D49" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="E49" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="F49" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="G49" t="n">
-        <v>65.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,82 +4836,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-20T19:00:00Z</t>
+          <t>2026-06-21T21:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.43</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>40.9</v>
+        <v>26.6</v>
       </c>
       <c r="J2" t="n">
-        <v>25.8</v>
+        <v>32.9</v>
       </c>
       <c r="K2" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="P2" t="n">
-        <v>33.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-20T23:00:00Z</t>
+          <t>2026-06-21T15:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,28 +4921,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="n">
-        <v>54.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>24.7</v>
+        <v>22.4</v>
       </c>
       <c r="K3" t="n">
-        <v>20.9</v>
+        <v>12.6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4951,33 +4951,33 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>24.2</v>
+        <v>104.6</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-20T16:00:00Z</t>
+          <t>2026-06-21T18:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4987,129 +4987,129 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="I4" t="n">
-        <v>53.6</v>
+        <v>48.6</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>23.6</v>
       </c>
       <c r="K4" t="n">
-        <v>25.4</v>
+        <v>27.8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>63.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>25.4</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00Z</t>
+          <t>2026-06-22T00:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="I5" t="n">
-        <v>8.699999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="J5" t="n">
-        <v>17.4</v>
+        <v>26.6</v>
       </c>
       <c r="K5" t="n">
-        <v>73.90000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>80.8</v>
+        <v>42.9</v>
       </c>
       <c r="P5" t="n">
-        <v>8.699999999999999</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-21T21:00:00Z</t>
+          <t>2026-06-22T23:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5119,63 +5119,63 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>2.01</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="I6" t="n">
-        <v>26.5</v>
+        <v>58.2</v>
       </c>
       <c r="J6" t="n">
-        <v>32.9</v>
+        <v>21.3</v>
       </c>
       <c r="K6" t="n">
-        <v>40.6</v>
+        <v>20.5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>22.1</v>
+        <v>17.6</v>
       </c>
       <c r="P6" t="n">
-        <v>40.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-21T15:00:00Z</t>
+          <t>2026-06-22T20:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5185,63 +5185,63 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>65.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="J7" t="n">
-        <v>22.3</v>
+        <v>20.5</v>
       </c>
       <c r="K7" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>104.6</v>
+        <v>35.2</v>
       </c>
       <c r="P7" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-21T18:00:00Z</t>
+          <t>2026-06-22T16:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5251,28 +5251,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="n">
-        <v>48.6</v>
+        <v>45.2</v>
       </c>
       <c r="J8" t="n">
-        <v>23.6</v>
+        <v>26.5</v>
       </c>
       <c r="K8" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -5281,99 +5281,99 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8.800000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00Z</t>
+          <t>2026-06-23T02:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H9" t="n">
-        <v>1.47</v>
+        <v>2.19</v>
       </c>
       <c r="I9" t="n">
-        <v>19.9</v>
+        <v>10.8</v>
       </c>
       <c r="J9" t="n">
-        <v>26.6</v>
+        <v>18.1</v>
       </c>
       <c r="K9" t="n">
-        <v>53.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>42.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>19.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-22T23:00:00Z</t>
+          <t>2026-06-23T19:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5383,129 +5383,129 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>0.52</v>
       </c>
       <c r="I10" t="n">
-        <v>58.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>21.3</v>
+        <v>14.5</v>
       </c>
       <c r="K10" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>17.6</v>
+        <v>125.7</v>
       </c>
       <c r="P10" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-22T20:00:00Z</t>
+          <t>2026-06-23T22:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>0.86</v>
+        <v>1.62</v>
       </c>
       <c r="I11" t="n">
-        <v>64.3</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>35.2</v>
+        <v>0.1</v>
       </c>
       <c r="P11" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-22T16:00:00Z</t>
+          <t>2026-06-23T16:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5515,129 +5515,129 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="I12" t="n">
-        <v>45.2</v>
+        <v>53.5</v>
       </c>
       <c r="J12" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
       <c r="K12" t="n">
-        <v>28.3</v>
+        <v>22.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>17.2</v>
+        <v>20.2</v>
       </c>
       <c r="P12" t="n">
-        <v>28.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00Z</t>
+          <t>2026-06-24T01:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.72</v>
+        <v>1.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.19</v>
+        <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>10.8</v>
+        <v>39.4</v>
       </c>
       <c r="J13" t="n">
-        <v>18</v>
+        <v>29.5</v>
       </c>
       <c r="K13" t="n">
-        <v>71.09999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>79.90000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>10.8</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-23T19:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5647,226 +5647,226 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>0.52</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="n">
-        <v>79.40000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="J14" t="n">
-        <v>14.4</v>
+        <v>25.7</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1</v>
+        <v>44</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>125.7</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>6.1</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-23T22:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>1.62</v>
+        <v>0.59</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>68</v>
       </c>
       <c r="J15" t="n">
-        <v>23.5</v>
+        <v>21.1</v>
       </c>
       <c r="K15" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.1</v>
+        <v>94.8</v>
       </c>
       <c r="P15" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-23T16:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="H16" t="n">
-        <v>0.99</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
-        <v>53.5</v>
+        <v>25.4</v>
       </c>
       <c r="J16" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="K16" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>20.2</v>
+        <v>0.6</v>
       </c>
       <c r="P16" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="H17" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>39.4</v>
+        <v>55.8</v>
       </c>
       <c r="J17" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
       <c r="K17" t="n">
-        <v>31.1</v>
+        <v>19</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -5875,231 +5875,231 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>31.1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I18" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
       <c r="J18" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>54.2</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>21.2</v>
+        <v>39.6</v>
       </c>
       <c r="P18" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>0.78</v>
       </c>
       <c r="H19" t="n">
-        <v>0.59</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>68</v>
+        <v>23.9</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>30.1</v>
       </c>
       <c r="K19" t="n">
-        <v>10.9</v>
+        <v>45.9</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>94.8</v>
+        <v>28.6</v>
       </c>
       <c r="P19" t="n">
-        <v>10.9</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="H20" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
-        <v>25.3</v>
+        <v>15.9</v>
       </c>
       <c r="J20" t="n">
-        <v>25.9</v>
+        <v>20.7</v>
       </c>
       <c r="K20" t="n">
-        <v>48.8</v>
+        <v>63.5</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.6</v>
+        <v>36.2</v>
       </c>
       <c r="P20" t="n">
-        <v>48.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6109,195 +6109,195 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.59</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="I21" t="n">
-        <v>55.9</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="K21" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="I22" t="n">
-        <v>19.2</v>
+        <v>72.2</v>
       </c>
       <c r="J22" t="n">
-        <v>26.6</v>
+        <v>15.9</v>
       </c>
       <c r="K22" t="n">
-        <v>54.3</v>
+        <v>11.9</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>39.6</v>
+        <v>68.2</v>
       </c>
       <c r="P22" t="n">
-        <v>19.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2</v>
+        <v>3.01</v>
       </c>
       <c r="I23" t="n">
-        <v>23.9</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>30.1</v>
+        <v>10.8</v>
       </c>
       <c r="K23" t="n">
-        <v>46</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>28.6</v>
+        <v>76</v>
       </c>
       <c r="P23" t="n">
-        <v>23.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6307,63 +6307,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.88</v>
+        <v>1.62</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="n">
-        <v>12.8</v>
+        <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>17.9</v>
+        <v>23.5</v>
       </c>
       <c r="K24" t="n">
-        <v>69.3</v>
+        <v>36.5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>36.2</v>
+        <v>55.5</v>
       </c>
       <c r="P24" t="n">
-        <v>12.8</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="H25" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="I25" t="n">
-        <v>22.9</v>
+        <v>30.8</v>
       </c>
       <c r="J25" t="n">
-        <v>26.4</v>
+        <v>29.3</v>
       </c>
       <c r="K25" t="n">
-        <v>50.7</v>
+        <v>39.9</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -6403,33 +6403,33 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>33.1</v>
+        <v>27.2</v>
       </c>
       <c r="P25" t="n">
-        <v>22.9</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6439,28 +6439,28 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H26" t="n">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="I26" t="n">
-        <v>56</v>
+        <v>47.1</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -6469,99 +6469,99 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>68.2</v>
+        <v>12.6</v>
       </c>
       <c r="P26" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="H27" t="n">
-        <v>2.37</v>
+        <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>9.699999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="J27" t="n">
-        <v>16.4</v>
+        <v>26.3</v>
       </c>
       <c r="K27" t="n">
-        <v>73.8</v>
+        <v>23.1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>76</v>
+        <v>30.2</v>
       </c>
       <c r="P27" t="n">
-        <v>9.699999999999999</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6571,129 +6571,129 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.63</v>
+        <v>0.99</v>
       </c>
       <c r="H28" t="n">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>40</v>
+        <v>31.6</v>
       </c>
       <c r="J28" t="n">
-        <v>23.5</v>
+        <v>29.7</v>
       </c>
       <c r="K28" t="n">
-        <v>36.5</v>
+        <v>38.7</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>55.5</v>
+        <v>14.1</v>
       </c>
       <c r="P28" t="n">
-        <v>36.5</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="H29" t="n">
-        <v>1.17</v>
+        <v>2.58</v>
       </c>
       <c r="I29" t="n">
-        <v>30.8</v>
+        <v>10.4</v>
       </c>
       <c r="J29" t="n">
-        <v>29.3</v>
+        <v>15.5</v>
       </c>
       <c r="K29" t="n">
-        <v>39.9</v>
+        <v>74.2</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>27.2</v>
+        <v>37.6</v>
       </c>
       <c r="P29" t="n">
-        <v>30.8</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6703,129 +6703,129 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="H30" t="n">
-        <v>1.51</v>
+        <v>0.78</v>
       </c>
       <c r="I30" t="n">
-        <v>47.1</v>
+        <v>44.6</v>
       </c>
       <c r="J30" t="n">
-        <v>22.1</v>
+        <v>30.7</v>
       </c>
       <c r="K30" t="n">
-        <v>30.8</v>
+        <v>24.7</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>12.6</v>
+        <v>4.7</v>
       </c>
       <c r="P30" t="n">
-        <v>30.8</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.49</v>
+        <v>0.61</v>
       </c>
       <c r="H31" t="n">
-        <v>0.91</v>
+        <v>1.55</v>
       </c>
       <c r="I31" t="n">
-        <v>50.6</v>
+        <v>14.4</v>
       </c>
       <c r="J31" t="n">
-        <v>26.3</v>
+        <v>25.3</v>
       </c>
       <c r="K31" t="n">
-        <v>23.1</v>
+        <v>60.3</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>30.2</v>
+        <v>87.2</v>
       </c>
       <c r="P31" t="n">
-        <v>23.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6835,129 +6835,129 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="H32" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="I32" t="n">
-        <v>31.6</v>
+        <v>15.3</v>
       </c>
       <c r="J32" t="n">
-        <v>29.7</v>
+        <v>20.4</v>
       </c>
       <c r="K32" t="n">
-        <v>38.7</v>
+        <v>64.3</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P32" t="n">
-        <v>38.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.87</v>
+        <v>1.91</v>
       </c>
       <c r="H33" t="n">
-        <v>2.58</v>
+        <v>0.91</v>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>60.8</v>
       </c>
       <c r="J33" t="n">
-        <v>15.5</v>
+        <v>21.8</v>
       </c>
       <c r="K33" t="n">
-        <v>74.2</v>
+        <v>17.5</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P33" t="n">
-        <v>10.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6967,129 +6967,129 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H34" t="n">
-        <v>0.78</v>
+        <v>1.46</v>
       </c>
       <c r="I34" t="n">
-        <v>44.7</v>
+        <v>27.5</v>
       </c>
       <c r="J34" t="n">
-        <v>30.7</v>
+        <v>26.2</v>
       </c>
       <c r="K34" t="n">
-        <v>24.7</v>
+        <v>46.3</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="P34" t="n">
-        <v>44.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="H35" t="n">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="I35" t="n">
-        <v>14.4</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
-        <v>25.3</v>
+        <v>10.2</v>
       </c>
       <c r="K35" t="n">
-        <v>60.3</v>
+        <v>85.7</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P35" t="n">
-        <v>14.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7099,63 +7099,63 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="I36" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
       <c r="J36" t="n">
-        <v>20.4</v>
+        <v>24.7</v>
       </c>
       <c r="K36" t="n">
-        <v>64.40000000000001</v>
+        <v>41.1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>38.4</v>
+        <v>23.3</v>
       </c>
       <c r="P36" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7165,28 +7165,28 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="H37" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="I37" t="n">
-        <v>60.8</v>
+        <v>41.1</v>
       </c>
       <c r="J37" t="n">
-        <v>21.8</v>
+        <v>31.4</v>
       </c>
       <c r="K37" t="n">
-        <v>17.4</v>
+        <v>27.5</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -7195,282 +7195,18 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P37" t="n">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>69</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I38" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>70</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P39" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>71</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I40" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K40" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P40" t="n">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>72</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I41" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P41" t="n">
         <v>41.1</v>
       </c>
     </row>
@@ -7592,17 +7328,17 @@
         <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1991</v>
+        <v>1.1983</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7496</v>
       </c>
       <c r="M2" t="n">
         <v>0.6884</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7374,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5382</v>
+        <v>1.5366</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -7648,7 +7384,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7420,7 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9692</v>
+        <v>0.9688</v>
       </c>
       <c r="L4" t="n">
         <v>0.7877</v>
@@ -7694,7 +7430,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7730,17 +7466,17 @@
         <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4479</v>
+        <v>1.4465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6569</v>
+        <v>0.6573</v>
       </c>
       <c r="M5" t="n">
         <v>0.8384</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7779,14 +7515,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7502</v>
+        <v>0.7503</v>
       </c>
       <c r="M6" t="n">
         <v>0.6801</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7822,17 +7558,17 @@
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9714</v>
+        <v>0.971</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0014</v>
+        <v>1.001</v>
       </c>
       <c r="M7" t="n">
         <v>0.384</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7604,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4399</v>
+        <v>1.4385</v>
       </c>
       <c r="L8" t="n">
         <v>0.8169999999999999</v>
@@ -7878,7 +7614,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7914,17 +7650,17 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2277</v>
+        <v>1.2268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5683</v>
+        <v>0.5687</v>
       </c>
       <c r="M9" t="n">
         <v>0.6276</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7960,17 +7696,17 @@
         <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0237</v>
+        <v>1.0233</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7467</v>
+        <v>0.747</v>
       </c>
       <c r="M10" t="n">
         <v>0.4983</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8006,17 +7742,17 @@
         <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3582</v>
+        <v>1.357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8558</v>
+        <v>0.8557</v>
       </c>
       <c r="M11" t="n">
         <v>0.6784</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8052,17 +7788,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.236</v>
+        <v>1.235</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0883</v>
+        <v>1.0877</v>
       </c>
       <c r="M12" t="n">
         <v>0.5662</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8083,32 +7819,32 @@
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" t="n">
         <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1904</v>
+        <v>1.0947</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4043</v>
+        <v>1.2966</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4031</v>
+        <v>0.3885</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8144,17 +7880,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1531</v>
+        <v>1.1524</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8667</v>
+        <v>0.8666</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8190,17 +7926,17 @@
         <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8949</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6375</v>
+        <v>0.6379</v>
       </c>
       <c r="M15" t="n">
         <v>0.5734</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8221,32 +7957,32 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8778</v>
+        <v>0.8045</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6262</v>
+        <v>0.5773</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5105</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8282,17 +8018,17 @@
         <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9528</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6782</v>
+        <v>0.6784</v>
       </c>
       <c r="M17" t="n">
         <v>0.5867</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8328,17 +8064,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4227</v>
+        <v>1.4213</v>
       </c>
       <c r="L18" t="n">
-        <v>0.642</v>
+        <v>0.6424</v>
       </c>
       <c r="M18" t="n">
         <v>0.8106</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8374,17 +8110,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4733</v>
+        <v>1.4718</v>
       </c>
       <c r="L19" t="n">
-        <v>0.861</v>
+        <v>0.8609</v>
       </c>
       <c r="M19" t="n">
         <v>0.7941</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8405,10 +8141,10 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -8417,20 +8153,20 @@
         <v>54</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8188</v>
+        <v>0.8064</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8718</v>
+        <v>0.8933</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8466,17 +8202,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.755</v>
+        <v>0.7553</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0836</v>
+        <v>1.0831</v>
       </c>
       <c r="M21" t="n">
         <v>0.2864</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8512,17 +8248,17 @@
         <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9529</v>
+        <v>0.9525</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9515</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0.3494</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8294,7 @@
         <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2942</v>
+        <v>1.2931</v>
       </c>
       <c r="L23" t="n">
         <v>0.785</v>
@@ -8568,7 +8304,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8607,14 +8343,14 @@
         <v>0.8138</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9741</v>
+        <v>0.9737</v>
       </c>
       <c r="M24" t="n">
         <v>0.5071</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8635,32 +8371,32 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1632</v>
+        <v>1.1255</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6138</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7893</v>
+        <v>0.6943</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8681,32 +8417,32 @@
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1633</v>
+        <v>1.3123</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6841</v>
+        <v>0.6249</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7426</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8742,17 +8478,17 @@
         <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8716</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2605</v>
+        <v>1.2595</v>
       </c>
       <c r="M27" t="n">
         <v>0.2044</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8524,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0785</v>
+        <v>1.0779</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -8798,7 +8534,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8570,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2988</v>
+        <v>1.2977</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -8844,7 +8580,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8865,32 +8601,32 @@
         <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.308</v>
+        <v>1.4971</v>
       </c>
       <c r="L30" t="n">
-        <v>0.842</v>
+        <v>0.8278</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6017</v>
+        <v>0.6559</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8926,17 +8662,17 @@
         <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9852</v>
+        <v>0.9848</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1295</v>
+        <v>1.1288</v>
       </c>
       <c r="M31" t="n">
         <v>0.2784</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8972,17 +8708,17 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>1.6335</v>
+        <v>1.6317</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7684</v>
+        <v>0.7685</v>
       </c>
       <c r="M32" t="n">
         <v>0.7295</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9018,17 +8754,17 @@
         <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1136</v>
+        <v>1.113</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0123</v>
+        <v>1.0118</v>
       </c>
       <c r="M33" t="n">
         <v>0.5132</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9064,17 +8800,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9996</v>
+        <v>0.9992</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9071</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0.5606</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9110,17 +8846,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3097</v>
+        <v>1.3086</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7849</v>
       </c>
       <c r="M35" t="n">
         <v>0.7025</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9156,17 +8892,17 @@
         <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6878</v>
+        <v>0.6881</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2658</v>
+        <v>1.2648</v>
       </c>
       <c r="M36" t="n">
         <v>0.2428</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9202,17 +8938,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8246</v>
+        <v>0.8245</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8872</v>
+        <v>0.887</v>
       </c>
       <c r="M37" t="n">
         <v>0.403</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9248,17 +8984,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>1.137</v>
+        <v>1.1363</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7558</v>
+        <v>0.7559</v>
       </c>
       <c r="M38" t="n">
         <v>0.5795</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9294,17 +9030,17 @@
         <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1501</v>
+        <v>1.1493</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9028</v>
+        <v>0.9025</v>
       </c>
       <c r="M39" t="n">
         <v>0.5076000000000001</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9340,17 +9076,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8088</v>
+        <v>0.8087</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8519</v>
+        <v>0.8518</v>
       </c>
       <c r="M40" t="n">
         <v>0.4009</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9122,7 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0441</v>
+        <v>1.0436</v>
       </c>
       <c r="L41" t="n">
         <v>0.791</v>
@@ -9396,7 +9132,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9432,17 +9168,17 @@
         <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>1.34</v>
+        <v>1.3388</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6772</v>
+        <v>0.6775</v>
       </c>
       <c r="M42" t="n">
         <v>0.6823</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9463,32 +9199,32 @@
         <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
         <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J43" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3885</v>
+        <v>1.3261</v>
       </c>
       <c r="L43" t="n">
-        <v>1.1473</v>
+        <v>1.3579</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5265</v>
+        <v>0.4537</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9524,17 +9260,17 @@
         <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4138</v>
+        <v>1.4125</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8357</v>
+        <v>0.8356</v>
       </c>
       <c r="M44" t="n">
         <v>0.6069</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9567,20 +9303,20 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7696</v>
+        <v>0.7145</v>
       </c>
       <c r="L45" t="n">
-        <v>1.2742</v>
+        <v>1.3994</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3094</v>
+        <v>0.2767</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9616,17 +9352,17 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1412</v>
+        <v>1.1405</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8515</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="M46" t="n">
         <v>0.63</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9662,17 +9398,17 @@
         <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3166</v>
+        <v>1.3155</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0621</v>
+        <v>1.0615</v>
       </c>
       <c r="M47" t="n">
         <v>0.6099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9708,17 +9444,17 @@
         <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7805</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7907</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0.4337</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9754,17 +9490,17 @@
         <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>1.0117</v>
+        <v>1.0112</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9379</v>
+        <v>0.9376</v>
       </c>
       <c r="M49" t="n">
         <v>0.4572</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-20T02:00:00+00:00</t>
+          <t>2026-06-21T03:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="D2" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="E2" t="n">
         <v>1.7</v>
@@ -535,22 +535,22 @@
         <v>0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>71.8</v>
+        <v>72.7</v>
       </c>
       <c r="I2" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="K2" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="L2" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>42.4</v>
       </c>
       <c r="D3" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="E3" t="n">
         <v>4.2</v>
@@ -598,13 +598,13 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="I3" t="n">
-        <v>39.4</v>
+        <v>39.8</v>
       </c>
       <c r="J3" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>14.3</v>
@@ -634,22 +634,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>99.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -658,157 +658,157 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>73</v>
+        <v>54.6</v>
       </c>
       <c r="I4" t="n">
-        <v>42.1</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="K4" t="n">
-        <v>13.3</v>
+        <v>14.7</v>
       </c>
       <c r="L4" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1577.2</v>
+        <v>1603.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90.7</v>
+        <v>99.8</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>66.5</v>
+        <v>73.2</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>41.8</v>
       </c>
       <c r="J5" t="n">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="K5" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="L5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1593.4</v>
+        <v>1577.2</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>53.1</v>
+        <v>7.6</v>
       </c>
       <c r="E6" t="n">
-        <v>20.4</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>60.2</v>
+        <v>66.5</v>
       </c>
       <c r="I6" t="n">
-        <v>39.2</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>23.6</v>
+        <v>21.3</v>
       </c>
       <c r="K6" t="n">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
         <v>6.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1560</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="R6" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -823,31 +823,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="E7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F7" t="n">
         <v>0.4</v>
       </c>
       <c r="G7" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="H7" t="n">
-        <v>65.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
         <v>20.1</v>
       </c>
       <c r="K7" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="L7" t="n">
         <v>5.9</v>
@@ -874,61 +874,61 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.6</v>
+        <v>25.9</v>
       </c>
       <c r="D8" t="n">
-        <v>26.7</v>
+        <v>53.4</v>
       </c>
       <c r="E8" t="n">
-        <v>14.3</v>
+        <v>20.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>90.2</v>
+        <v>98.3</v>
       </c>
       <c r="H8" t="n">
-        <v>58.4</v>
+        <v>55.4</v>
       </c>
       <c r="I8" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="J8" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1555.6</v>
+        <v>1560</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9">
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>65.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>40.7</v>
+        <v>39.8</v>
       </c>
       <c r="J9" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="K9" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="L9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -994,82 +994,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.09999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.9</v>
+        <v>54.9</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="H10" t="n">
-        <v>66.8</v>
+        <v>60.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>33.6</v>
       </c>
       <c r="J10" t="n">
-        <v>19.1</v>
+        <v>18.5</v>
       </c>
       <c r="K10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>4.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1573.8</v>
+        <v>1555.6</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>50.9</v>
+        <v>3.9</v>
       </c>
       <c r="E11" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1078,217 +1078,217 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>52.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="L11" t="n">
         <v>4.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1575.8</v>
+        <v>1573.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56.2</v>
+        <v>37.4</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>50.8</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>44.1</v>
+        <v>52.3</v>
       </c>
       <c r="I12" t="n">
-        <v>28.3</v>
+        <v>30.8</v>
       </c>
       <c r="J12" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="K12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>4.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1603.8</v>
+        <v>1575.8</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="R12" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60.7</v>
+        <v>38.5</v>
       </c>
       <c r="D13" t="n">
-        <v>39.1</v>
+        <v>52.1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>8.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>46.7</v>
+        <v>57</v>
       </c>
       <c r="I13" t="n">
-        <v>25.7</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="K13" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>2.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1571</v>
+        <v>1569.9</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="R13" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.3</v>
+        <v>60.6</v>
       </c>
       <c r="D14" t="n">
-        <v>52.3</v>
+        <v>39.1</v>
       </c>
       <c r="E14" t="n">
-        <v>8.5</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>56.9</v>
+        <v>46.6</v>
       </c>
       <c r="I14" t="n">
-        <v>26.9</v>
+        <v>25.7</v>
       </c>
       <c r="J14" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1569.9</v>
+        <v>1571</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="R14" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
@@ -1306,31 +1306,31 @@
         <v>28.9</v>
       </c>
       <c r="D15" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
         <v>24.7</v>
       </c>
       <c r="F15" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="G15" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="I15" t="n">
-        <v>22.4</v>
+        <v>21.3</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>1.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="R15" t="n">
         <v>0.7</v>
@@ -1375,22 +1375,22 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>58.3</v>
+        <v>58</v>
       </c>
       <c r="I16" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="J16" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1414,37 +1414,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47.9</v>
+        <v>54.3</v>
       </c>
       <c r="D17" t="n">
-        <v>24.9</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>45.2</v>
+        <v>51.3</v>
       </c>
       <c r="I17" t="n">
-        <v>22.4</v>
+        <v>26.6</v>
       </c>
       <c r="J17" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="K17" t="n">
         <v>4.7</v>
@@ -1458,53 +1458,53 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1542.8</v>
+        <v>1560.9</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52.6</v>
+        <v>47.9</v>
       </c>
       <c r="D18" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>18.4</v>
+        <v>27.2</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>57.8</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="n">
-        <v>24.5</v>
+        <v>22.1</v>
       </c>
       <c r="J18" t="n">
-        <v>10.6</v>
+        <v>9.9</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -1518,14 +1518,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1541.7</v>
+        <v>1542.8</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="R18" t="n">
         <v>0.68</v>
@@ -1534,37 +1534,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>52.5</v>
       </c>
       <c r="D19" t="n">
-        <v>82.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>13.8</v>
+        <v>18.2</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>44.5</v>
+        <v>57.9</v>
       </c>
       <c r="I19" t="n">
-        <v>19.9</v>
+        <v>23.7</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -1574,78 +1574,78 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1556.1</v>
+        <v>1541.7</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.68</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>20.3</v>
+        <v>82.5</v>
       </c>
       <c r="E20" t="n">
-        <v>62.6</v>
+        <v>13.8</v>
       </c>
       <c r="F20" t="n">
-        <v>15.9</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>65.3</v>
+        <v>94.3</v>
       </c>
       <c r="H20" t="n">
-        <v>32.7</v>
+        <v>44.7</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1573.4</v>
+        <v>1556.1</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="R20" t="n">
         <v>0.6899999999999999</v>
@@ -1654,181 +1654,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.2</v>
+        <v>1.3</v>
       </c>
       <c r="D21" t="n">
-        <v>24.6</v>
+        <v>20.2</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>62.2</v>
       </c>
       <c r="F21" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="G21" t="n">
-        <v>64</v>
+        <v>66.2</v>
       </c>
       <c r="H21" t="n">
-        <v>34.1</v>
+        <v>30.9</v>
       </c>
       <c r="I21" t="n">
-        <v>16.4</v>
+        <v>17.2</v>
       </c>
       <c r="J21" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1546.8</v>
+        <v>1573.4</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>98.7</v>
+        <v>17.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3</v>
+        <v>20.9</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>60.4</v>
+        <v>34.7</v>
       </c>
       <c r="I22" t="n">
-        <v>25.3</v>
+        <v>16.8</v>
       </c>
       <c r="J22" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1522.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="R22" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>98.7</v>
       </c>
       <c r="D23" t="n">
-        <v>35.7</v>
+        <v>1.3</v>
       </c>
       <c r="E23" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>76.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>38.8</v>
+        <v>60.3</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>25.9</v>
       </c>
       <c r="J23" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1560.9</v>
+        <v>1522.7</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="R23" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="24">
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="D24" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="G24" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="H24" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="I24" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="J24" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L24" t="n">
         <v>0.9</v>
@@ -1915,16 +1915,16 @@
         <v>0.9</v>
       </c>
       <c r="G25" t="n">
-        <v>89.2</v>
+        <v>90.2</v>
       </c>
       <c r="H25" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="I25" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="J25" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K25" t="n">
         <v>2.1</v>
@@ -1975,22 +1975,22 @@
         <v>4.6</v>
       </c>
       <c r="G26" t="n">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
       <c r="H26" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="I26" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="J26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2035,19 +2035,19 @@
         <v>5.7</v>
       </c>
       <c r="G27" t="n">
-        <v>89.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>36.8</v>
+        <v>33.8</v>
       </c>
       <c r="I27" t="n">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L27" t="n">
         <v>0.6</v>
@@ -2074,241 +2074,241 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.1</v>
+        <v>1.5</v>
       </c>
       <c r="D28" t="n">
-        <v>37.9</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="n">
-        <v>21.7</v>
+        <v>56.9</v>
       </c>
       <c r="F28" t="n">
-        <v>18.3</v>
+        <v>30.5</v>
       </c>
       <c r="G28" t="n">
-        <v>76.40000000000001</v>
+        <v>49.6</v>
       </c>
       <c r="H28" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="I28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1494.5</v>
+        <v>1564.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>67.5</v>
       </c>
       <c r="E29" t="n">
-        <v>57.2</v>
+        <v>15.6</v>
       </c>
       <c r="F29" t="n">
-        <v>30.2</v>
+        <v>13.7</v>
       </c>
       <c r="G29" t="n">
-        <v>48.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1564.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>45.1</v>
+        <v>4.9</v>
       </c>
       <c r="E30" t="n">
-        <v>25.9</v>
+        <v>72.3</v>
       </c>
       <c r="F30" t="n">
-        <v>26.2</v>
+        <v>22.8</v>
       </c>
       <c r="G30" t="n">
-        <v>66.5</v>
+        <v>23.2</v>
       </c>
       <c r="H30" t="n">
-        <v>27.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="L30" t="n">
         <v>0.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1554.9</v>
+        <v>1544.1</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>0.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.09</v>
+        <v>0.58</v>
       </c>
       <c r="R30" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="D31" t="n">
-        <v>4.9</v>
+        <v>44.6</v>
       </c>
       <c r="E31" t="n">
-        <v>72.3</v>
+        <v>26.2</v>
       </c>
       <c r="F31" t="n">
-        <v>22.7</v>
+        <v>26.3</v>
       </c>
       <c r="G31" t="n">
-        <v>23.2</v>
+        <v>66.7</v>
       </c>
       <c r="H31" t="n">
-        <v>9.699999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="I31" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1544.1</v>
+        <v>1554.9</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>1.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.58</v>
+        <v>1.09</v>
       </c>
       <c r="R31" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="32">
@@ -2335,16 +2335,16 @@
         <v>16.1</v>
       </c>
       <c r="G32" t="n">
-        <v>71.8</v>
+        <v>72.7</v>
       </c>
       <c r="H32" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="I32" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>0.6</v>
@@ -2374,34 +2374,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>52.5</v>
+        <v>21.8</v>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
+        <v>78.2</v>
       </c>
       <c r="G33" t="n">
-        <v>21.4</v>
+        <v>18.9</v>
       </c>
       <c r="H33" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>1.2</v>
@@ -2414,21 +2414,21 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1534.2</v>
+        <v>1578.2</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="34">
@@ -2446,19 +2446,19 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="E34" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="F34" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="G34" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
       <c r="H34" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="I34" t="n">
         <v>4.5</v>
@@ -2494,97 +2494,97 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E35" t="n">
-        <v>21.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>78.2</v>
+        <v>19.2</v>
       </c>
       <c r="G35" t="n">
-        <v>18.6</v>
+        <v>55.9</v>
       </c>
       <c r="H35" t="n">
-        <v>7.1</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L35" t="n">
         <v>0.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1578.2</v>
+        <v>1514.3</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0.63</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="D36" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="E36" t="n">
-        <v>78.90000000000001</v>
+        <v>24</v>
       </c>
       <c r="F36" t="n">
-        <v>19.2</v>
+        <v>62.2</v>
       </c>
       <c r="G36" t="n">
-        <v>56</v>
+        <v>31.8</v>
       </c>
       <c r="H36" t="n">
-        <v>17.3</v>
+        <v>12.1</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K36" t="n">
         <v>0.3</v>
@@ -2594,57 +2594,57 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1514.3</v>
+        <v>1544.8</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R36" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>19.1</v>
+        <v>8.5</v>
       </c>
       <c r="E37" t="n">
-        <v>35.4</v>
+        <v>52.5</v>
       </c>
       <c r="F37" t="n">
-        <v>33.5</v>
+        <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>45.9</v>
+        <v>21.5</v>
       </c>
       <c r="H37" t="n">
-        <v>11.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K37" t="n">
         <v>0.3</v>
@@ -2658,77 +2658,77 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1516.6</v>
+        <v>1534.2</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.78</v>
+        <v>1.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="R37" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.9</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>10.9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>23.9</v>
+        <v>75.3</v>
       </c>
       <c r="F38" t="n">
-        <v>62.4</v>
+        <v>7.7</v>
       </c>
       <c r="G38" t="n">
-        <v>31.4</v>
+        <v>36.9</v>
       </c>
       <c r="H38" t="n">
-        <v>12.1</v>
+        <v>9.5</v>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L38" t="n">
         <v>0.1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1544.8</v>
+        <v>1516.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1.01</v>
+        <v>0.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="R38" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="39">
@@ -2749,28 +2749,28 @@
         <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>81.7</v>
+        <v>83.3</v>
       </c>
       <c r="H39" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2794,43 +2794,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="D40" t="n">
-        <v>17.9</v>
+        <v>4.9</v>
       </c>
       <c r="E40" t="n">
-        <v>30.4</v>
+        <v>26.4</v>
       </c>
       <c r="F40" t="n">
-        <v>41.9</v>
+        <v>68.2</v>
       </c>
       <c r="G40" t="n">
-        <v>41.3</v>
+        <v>20.2</v>
       </c>
       <c r="H40" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2838,53 +2838,53 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1499.2</v>
+        <v>1534.7</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="R40" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>19.4</v>
       </c>
       <c r="E41" t="n">
-        <v>24.9</v>
+        <v>24.2</v>
       </c>
       <c r="F41" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="G41" t="n">
-        <v>32.2</v>
+        <v>23.9</v>
       </c>
       <c r="H41" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K41" t="n">
         <v>0.1</v>
@@ -2898,116 +2898,116 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1518</v>
+        <v>1521.7</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.13</v>
+        <v>0.85</v>
       </c>
       <c r="R41" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="D42" t="n">
-        <v>19.4</v>
+        <v>32.3</v>
       </c>
       <c r="E42" t="n">
-        <v>24.2</v>
+        <v>46.2</v>
       </c>
       <c r="F42" t="n">
-        <v>56.4</v>
+        <v>16.9</v>
       </c>
       <c r="G42" t="n">
-        <v>23.9</v>
+        <v>70.2</v>
       </c>
       <c r="H42" t="n">
-        <v>7.2</v>
+        <v>15.7</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1521.7</v>
+        <v>1467.7</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>18.3</v>
       </c>
       <c r="E43" t="n">
-        <v>26.2</v>
+        <v>3.1</v>
       </c>
       <c r="F43" t="n">
-        <v>68.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="H43" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3018,53 +3018,53 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1534.7</v>
+        <v>1499.2</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>12.4</v>
       </c>
       <c r="E44" t="n">
-        <v>46.5</v>
+        <v>13.9</v>
       </c>
       <c r="F44" t="n">
-        <v>16.8</v>
+        <v>73.8</v>
       </c>
       <c r="G44" t="n">
-        <v>69.09999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="H44" t="n">
-        <v>15.5</v>
+        <v>3.3</v>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3074,54 +3074,54 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1467.7</v>
+        <v>1519.9</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="R44" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>12.3</v>
+        <v>6.2</v>
       </c>
       <c r="E45" t="n">
-        <v>13.9</v>
+        <v>4.5</v>
       </c>
       <c r="F45" t="n">
-        <v>73.8</v>
+        <v>89.3</v>
       </c>
       <c r="G45" t="n">
-        <v>15.7</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0.1</v>
@@ -3138,17 +3138,17 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1519.9</v>
+        <v>1518</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="46">
@@ -3226,22 +3226,22 @@
         <v>0.1</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E47" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="F47" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3295,10 +3295,10 @@
         <v>80.8</v>
       </c>
       <c r="G48" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="H48" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I48" t="n">
         <v>0.4</v>
@@ -3493,7 +3493,7 @@
         <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="4">
@@ -3520,7 +3520,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="5">
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -3628,7 +3628,7 @@
         <v>19.2</v>
       </c>
       <c r="G8" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="9">
@@ -3655,7 +3655,7 @@
         <v>80.8</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="10">
@@ -3673,7 +3673,7 @@
         <v>42.4</v>
       </c>
       <c r="D10" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="E10" t="n">
         <v>4.2</v>
@@ -3700,7 +3700,7 @@
         <v>47.9</v>
       </c>
       <c r="D11" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>27.2</v>
@@ -3736,7 +3736,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>89.2</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="13">
@@ -3817,7 +3817,7 @@
         <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>89.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3844,7 +3844,7 @@
         <v>16.1</v>
       </c>
       <c r="G16" t="n">
-        <v>71.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="17">
@@ -3871,7 +3871,7 @@
         <v>78.2</v>
       </c>
       <c r="G17" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="18">
@@ -3916,7 +3916,7 @@
         <v>0.2</v>
       </c>
       <c r="D19" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="E19" t="n">
         <v>13.8</v>
@@ -3925,7 +3925,7 @@
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="20">
@@ -3949,7 +3949,7 @@
         <v>72.3</v>
       </c>
       <c r="F20" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="G20" t="n">
         <v>23.2</v>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="E21" t="n">
         <v>13.9</v>
@@ -3979,7 +3979,7 @@
         <v>73.8</v>
       </c>
       <c r="G21" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="22">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="D22" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="D23" t="n">
         <v>39.1</v>
@@ -4054,13 +4054,13 @@
         <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>81.7</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="25">
@@ -4102,19 +4102,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51.6</v>
+        <v>28.5</v>
       </c>
       <c r="D26" t="n">
-        <v>26.7</v>
+        <v>54.9</v>
       </c>
       <c r="E26" t="n">
-        <v>14.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F26" t="n">
         <v>7.4</v>
       </c>
       <c r="G26" t="n">
-        <v>90.2</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="27">
@@ -4125,23 +4125,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.2</v>
+        <v>54.3</v>
       </c>
       <c r="D27" t="n">
-        <v>24.6</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>27.8</v>
       </c>
       <c r="F27" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>64</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -4152,23 +4152,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21.6</v>
+        <v>17.2</v>
       </c>
       <c r="D28" t="n">
-        <v>35.7</v>
+        <v>20.9</v>
       </c>
       <c r="E28" t="n">
-        <v>25.8</v>
+        <v>58.5</v>
       </c>
       <c r="F28" t="n">
-        <v>16.9</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>76.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.9</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>56.5</v>
+        <v>89.3</v>
       </c>
       <c r="G29" t="n">
-        <v>32.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>56.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="E30" t="n">
-        <v>12.4</v>
+        <v>5.9</v>
       </c>
       <c r="F30" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>91.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -4237,19 +4237,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22.1</v>
+        <v>3.2</v>
       </c>
       <c r="D31" t="n">
-        <v>37.9</v>
+        <v>67.5</v>
       </c>
       <c r="E31" t="n">
-        <v>21.7</v>
+        <v>15.6</v>
       </c>
       <c r="F31" t="n">
-        <v>18.3</v>
+        <v>13.7</v>
       </c>
       <c r="G31" t="n">
-        <v>76.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>19.1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>35.4</v>
+        <v>75.3</v>
       </c>
       <c r="F32" t="n">
-        <v>33.5</v>
+        <v>7.7</v>
       </c>
       <c r="G32" t="n">
-        <v>45.9</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="33">
@@ -4291,19 +4291,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="E33" t="n">
-        <v>30.4</v>
+        <v>3.1</v>
       </c>
       <c r="F33" t="n">
-        <v>41.9</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>41.3</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="34">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="E34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="F34" t="n">
         <v>0.4</v>
       </c>
       <c r="G34" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="35">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="D35" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="E35" t="n">
         <v>8.5</v>
@@ -4357,7 +4357,7 @@
         <v>0.9</v>
       </c>
       <c r="G35" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -4378,13 +4378,13 @@
         <v>11.1</v>
       </c>
       <c r="E36" t="n">
-        <v>57.2</v>
+        <v>56.9</v>
       </c>
       <c r="F36" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="G36" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="37">
@@ -4402,16 +4402,16 @@
         <v>0.4</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="F37" t="n">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="G37" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="38">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="D38" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="E38" t="n">
         <v>1.7</v>
@@ -4438,7 +4438,7 @@
         <v>0.1</v>
       </c>
       <c r="G38" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -4453,19 +4453,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="D39" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="E39" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G39" t="n">
-        <v>98</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="40">
@@ -4480,19 +4480,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D40" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="E40" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="F40" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="G40" t="n">
-        <v>65.3</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="41">
@@ -4510,16 +4510,16 @@
         <v>0.1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E41" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="F41" t="n">
-        <v>83.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="42">
@@ -4537,16 +4537,16 @@
         <v>28.9</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E42" t="n">
         <v>24.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="G42" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="D43" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="E43" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="F43" t="n">
         <v>3.2</v>
       </c>
       <c r="G43" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -4588,19 +4588,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="D44" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="E44" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="G44" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="45">
@@ -4621,13 +4621,13 @@
         <v>10.9</v>
       </c>
       <c r="E45" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="G45" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="46">
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G46" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D47" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="E47" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="F47" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="G47" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="48">
@@ -4699,16 +4699,16 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="F48" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="G48" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="49">
@@ -4726,16 +4726,16 @@
         <v>4.6</v>
       </c>
       <c r="D49" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="E49" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="F49" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="G49" t="n">
-        <v>69.09999999999999</v>
+        <v>70.2</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,16 +4836,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21T21:00:00Z</t>
+          <t>2026-06-22T23:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4855,63 +4855,63 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>2.01</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>26.6</v>
+        <v>58.2</v>
       </c>
       <c r="J2" t="n">
-        <v>32.9</v>
+        <v>21.3</v>
       </c>
       <c r="K2" t="n">
-        <v>40.6</v>
+        <v>20.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>22.1</v>
+        <v>17.6</v>
       </c>
       <c r="P2" t="n">
-        <v>40.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-21T15:00:00Z</t>
+          <t>2026-06-22T20:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,63 +4921,63 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>65.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="J3" t="n">
-        <v>22.4</v>
+        <v>20.5</v>
       </c>
       <c r="K3" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>104.6</v>
+        <v>35.2</v>
       </c>
       <c r="P3" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-21T18:00:00Z</t>
+          <t>2026-06-22T16:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4987,28 +4987,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>48.6</v>
+        <v>45.2</v>
       </c>
       <c r="J4" t="n">
-        <v>23.6</v>
+        <v>26.5</v>
       </c>
       <c r="K4" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -5017,99 +5017,99 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>8.800000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="P4" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00Z</t>
+          <t>2026-06-23T02:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H5" t="n">
-        <v>1.47</v>
+        <v>2.19</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="J5" t="n">
-        <v>26.6</v>
+        <v>18.1</v>
       </c>
       <c r="K5" t="n">
-        <v>53.5</v>
+        <v>71</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>42.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-22T23:00:00Z</t>
+          <t>2026-06-23T19:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5119,129 +5119,129 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.11</v>
+        <v>0.52</v>
       </c>
       <c r="I6" t="n">
-        <v>58.2</v>
+        <v>79.3</v>
       </c>
       <c r="J6" t="n">
-        <v>21.3</v>
+        <v>14.5</v>
       </c>
       <c r="K6" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>17.6</v>
+        <v>125.7</v>
       </c>
       <c r="P6" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-22T20:00:00Z</t>
+          <t>2026-06-23T22:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>64.3</v>
+        <v>36.8</v>
       </c>
       <c r="J7" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>35.2</v>
+        <v>0.1</v>
       </c>
       <c r="P7" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-22T16:00:00Z</t>
+          <t>2026-06-23T16:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5251,129 +5251,129 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>45.2</v>
+        <v>53.4</v>
       </c>
       <c r="J8" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
       <c r="K8" t="n">
-        <v>28.2</v>
+        <v>22.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>20.2</v>
       </c>
       <c r="P8" t="n">
-        <v>28.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00Z</t>
+          <t>2026-06-24T01:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.72</v>
+        <v>1.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.19</v>
+        <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>10.8</v>
+        <v>39.4</v>
       </c>
       <c r="J9" t="n">
-        <v>18.1</v>
+        <v>29.5</v>
       </c>
       <c r="K9" t="n">
-        <v>71.09999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>79.90000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>10.8</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-23T19:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5383,226 +5383,226 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="H10" t="n">
-        <v>0.52</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>79.40000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="J10" t="n">
-        <v>14.5</v>
+        <v>25.7</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>125.7</v>
+        <v>21.2</v>
       </c>
       <c r="P10" t="n">
-        <v>6.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-23T22:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
-        <v>1.62</v>
+        <v>0.59</v>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>23.5</v>
+        <v>21.1</v>
       </c>
       <c r="K11" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.1</v>
+        <v>94.8</v>
       </c>
       <c r="P11" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-23T16:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="H12" t="n">
-        <v>0.98</v>
+        <v>1.51</v>
       </c>
       <c r="I12" t="n">
-        <v>53.5</v>
+        <v>25.4</v>
       </c>
       <c r="J12" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="K12" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>20.2</v>
+        <v>0.6</v>
       </c>
       <c r="P12" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>39.4</v>
+        <v>55.8</v>
       </c>
       <c r="J13" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
       <c r="K13" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -5611,231 +5611,231 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3.8</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="H14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I14" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
       <c r="J14" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>54.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>39.6</v>
       </c>
       <c r="P14" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>0.78</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59</v>
+        <v>1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>21.1</v>
+        <v>30.1</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>45.9</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>94.8</v>
+        <v>28.6</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="I16" t="n">
-        <v>25.4</v>
+        <v>15.9</v>
       </c>
       <c r="J16" t="n">
-        <v>25.9</v>
+        <v>20.7</v>
       </c>
       <c r="K16" t="n">
-        <v>48.7</v>
+        <v>63.4</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.6</v>
+        <v>36.2</v>
       </c>
       <c r="P16" t="n">
-        <v>48.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5845,195 +5845,195 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.59</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>55.8</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="P17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.75</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="I18" t="n">
-        <v>19.2</v>
+        <v>72.2</v>
       </c>
       <c r="J18" t="n">
-        <v>26.6</v>
+        <v>15.9</v>
       </c>
       <c r="K18" t="n">
-        <v>54.2</v>
+        <v>11.9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>39.6</v>
+        <v>68.2</v>
       </c>
       <c r="P18" t="n">
-        <v>19.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>3.01</v>
       </c>
       <c r="I19" t="n">
-        <v>23.9</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>30.1</v>
+        <v>10.8</v>
       </c>
       <c r="K19" t="n">
-        <v>45.9</v>
+        <v>83.8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>28.6</v>
+        <v>76</v>
       </c>
       <c r="P19" t="n">
-        <v>23.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6043,63 +6043,63 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.9</v>
+        <v>1.62</v>
       </c>
       <c r="H20" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="I20" t="n">
-        <v>15.9</v>
+        <v>39.9</v>
       </c>
       <c r="J20" t="n">
-        <v>20.7</v>
+        <v>23.6</v>
       </c>
       <c r="K20" t="n">
-        <v>63.5</v>
+        <v>36.5</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>36.2</v>
+        <v>55.5</v>
       </c>
       <c r="P20" t="n">
-        <v>15.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6109,28 +6109,28 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H21" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
       <c r="J21" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="K21" t="n">
-        <v>50.1</v>
+        <v>39.9</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -6139,33 +6139,33 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>33.1</v>
+        <v>27.2</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6175,129 +6175,129 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>0.97</v>
+        <v>1.51</v>
       </c>
       <c r="I22" t="n">
-        <v>72.2</v>
+        <v>47.1</v>
       </c>
       <c r="J22" t="n">
-        <v>15.9</v>
+        <v>22.2</v>
       </c>
       <c r="K22" t="n">
-        <v>11.9</v>
+        <v>30.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>68.2</v>
+        <v>12.6</v>
       </c>
       <c r="P22" t="n">
-        <v>11.9</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.66</v>
+        <v>1.48</v>
       </c>
       <c r="H23" t="n">
-        <v>3.01</v>
+        <v>0.91</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>50.5</v>
       </c>
       <c r="J23" t="n">
-        <v>10.8</v>
+        <v>26.3</v>
       </c>
       <c r="K23" t="n">
-        <v>83.90000000000001</v>
+        <v>23.1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>76</v>
+        <v>30.2</v>
       </c>
       <c r="P23" t="n">
-        <v>5.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6307,129 +6307,129 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>40</v>
+        <v>33.9</v>
       </c>
       <c r="J24" t="n">
-        <v>23.5</v>
+        <v>30.6</v>
       </c>
       <c r="K24" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>55.5</v>
+        <v>14.1</v>
       </c>
       <c r="P24" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="H25" t="n">
-        <v>1.17</v>
+        <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
       <c r="J25" t="n">
-        <v>29.3</v>
+        <v>15.2</v>
       </c>
       <c r="K25" t="n">
-        <v>39.9</v>
+        <v>75.7</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>27.2</v>
+        <v>37.6</v>
       </c>
       <c r="P25" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6439,129 +6439,129 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="H26" t="n">
-        <v>1.51</v>
+        <v>0.78</v>
       </c>
       <c r="I26" t="n">
-        <v>47.1</v>
+        <v>51.9</v>
       </c>
       <c r="J26" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="K26" t="n">
-        <v>30.8</v>
+        <v>20.8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>12.6</v>
+        <v>4.7</v>
       </c>
       <c r="P26" t="n">
-        <v>30.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.48</v>
+        <v>0.6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="I27" t="n">
-        <v>50.6</v>
+        <v>11.5</v>
       </c>
       <c r="J27" t="n">
-        <v>26.3</v>
+        <v>21.5</v>
       </c>
       <c r="K27" t="n">
-        <v>23.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>30.2</v>
+        <v>87.2</v>
       </c>
       <c r="P27" t="n">
-        <v>23.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6571,129 +6571,129 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="H28" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="I28" t="n">
-        <v>31.6</v>
+        <v>15.3</v>
       </c>
       <c r="J28" t="n">
-        <v>29.7</v>
+        <v>20.4</v>
       </c>
       <c r="K28" t="n">
-        <v>38.7</v>
+        <v>64.3</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P28" t="n">
-        <v>38.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.87</v>
+        <v>1.91</v>
       </c>
       <c r="H29" t="n">
-        <v>2.58</v>
+        <v>0.91</v>
       </c>
       <c r="I29" t="n">
-        <v>10.4</v>
+        <v>60.7</v>
       </c>
       <c r="J29" t="n">
-        <v>15.5</v>
+        <v>21.8</v>
       </c>
       <c r="K29" t="n">
-        <v>74.2</v>
+        <v>17.5</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P29" t="n">
-        <v>10.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6703,129 +6703,129 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H30" t="n">
-        <v>0.78</v>
+        <v>1.46</v>
       </c>
       <c r="I30" t="n">
-        <v>44.6</v>
+        <v>27.5</v>
       </c>
       <c r="J30" t="n">
-        <v>30.7</v>
+        <v>26.2</v>
       </c>
       <c r="K30" t="n">
-        <v>24.7</v>
+        <v>46.3</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="P30" t="n">
-        <v>44.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="H31" t="n">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="I31" t="n">
-        <v>14.4</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
-        <v>25.3</v>
+        <v>10.2</v>
       </c>
       <c r="K31" t="n">
-        <v>60.3</v>
+        <v>85.7</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P31" t="n">
-        <v>14.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6835,63 +6835,63 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="H32" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
       <c r="J32" t="n">
-        <v>20.4</v>
+        <v>24.7</v>
       </c>
       <c r="K32" t="n">
-        <v>64.3</v>
+        <v>41.1</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>38.4</v>
+        <v>23.3</v>
       </c>
       <c r="P32" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6901,28 +6901,28 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="H33" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I33" t="n">
-        <v>60.8</v>
+        <v>41.1</v>
       </c>
       <c r="J33" t="n">
-        <v>21.8</v>
+        <v>31.4</v>
       </c>
       <c r="K33" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -6931,282 +6931,18 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P33" t="n">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>69</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I34" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>70</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>71</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I36" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K36" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>72</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I37" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P37" t="n">
         <v>41.1</v>
       </c>
     </row>
@@ -7328,17 +7064,17 @@
         <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1983</v>
+        <v>1.1978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7496</v>
+        <v>0.7498</v>
       </c>
       <c r="M2" t="n">
         <v>0.6884</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7110,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5366</v>
+        <v>1.5355</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -7384,7 +7120,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7420,17 +7156,17 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9688</v>
+        <v>0.9687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7877</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.5422</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7466,17 +7202,17 @@
         <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4465</v>
+        <v>1.4456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6573</v>
+        <v>0.6577</v>
       </c>
       <c r="M5" t="n">
         <v>0.8384</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7500,29 +7236,29 @@
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.65</v>
+        <v>1.5192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7503</v>
+        <v>0.6832</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6801</v>
+        <v>0.6408</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7558,17 +7294,17 @@
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>0.971</v>
+        <v>0.9708</v>
       </c>
       <c r="L7" t="n">
-        <v>1.001</v>
+        <v>1.0008</v>
       </c>
       <c r="M7" t="n">
         <v>0.384</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7604,17 +7340,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4385</v>
+        <v>1.4376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8171</v>
       </c>
       <c r="M8" t="n">
         <v>0.6761</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7386,17 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2268</v>
+        <v>1.2263</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5687</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>0.6276</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7678,35 +7414,35 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0233</v>
+        <v>1.0611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.747</v>
+        <v>0.8111</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4983</v>
+        <v>0.4729</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7478,7 @@
         <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>1.357</v>
+        <v>1.3563</v>
       </c>
       <c r="L11" t="n">
         <v>0.8557</v>
@@ -7752,7 +7488,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7788,17 +7524,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.235</v>
+        <v>1.2345</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0877</v>
+        <v>1.0873</v>
       </c>
       <c r="M12" t="n">
         <v>0.5662</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7834,17 +7570,17 @@
         <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0947</v>
+        <v>1.0944</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2966</v>
+        <v>1.296</v>
       </c>
       <c r="M13" t="n">
         <v>0.3885</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7616,7 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1524</v>
+        <v>1.1519</v>
       </c>
       <c r="L14" t="n">
         <v>0.8666</v>
@@ -7890,7 +7626,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7929,14 +7665,14 @@
         <v>0.8947000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6379</v>
+        <v>0.6383</v>
       </c>
       <c r="M15" t="n">
         <v>0.5734</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7972,17 +7708,17 @@
         <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8045</v>
+        <v>0.8046</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5773</v>
+        <v>0.5777</v>
       </c>
       <c r="M16" t="n">
         <v>0.5105</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8012,23 +7748,23 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9528</v>
+        <v>1.0402</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6784</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5867</v>
+        <v>0.6263</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8064,17 +7800,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4213</v>
+        <v>1.4204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6424</v>
+        <v>0.6428</v>
       </c>
       <c r="M18" t="n">
         <v>0.8106</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8110,7 +7846,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4718</v>
+        <v>1.4709</v>
       </c>
       <c r="L19" t="n">
         <v>0.8609</v>
@@ -8120,7 +7856,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8159,14 +7895,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8064</v>
+        <v>0.8065</v>
       </c>
       <c r="M20" t="n">
         <v>0.8933</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8202,17 +7938,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7553</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0831</v>
+        <v>1.0827</v>
       </c>
       <c r="M21" t="n">
         <v>0.2864</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8248,17 +7984,17 @@
         <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9525</v>
+        <v>0.9524</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="M22" t="n">
         <v>0.3494</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8279,32 +8015,32 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2931</v>
+        <v>1.1764</v>
       </c>
       <c r="L23" t="n">
-        <v>0.785</v>
+        <v>0.7212</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6065</v>
+        <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8340,17 +8076,17 @@
         <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8138</v>
+        <v>0.8139</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9737</v>
+        <v>0.9736</v>
       </c>
       <c r="M24" t="n">
         <v>0.5071</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8386,17 +8122,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1255</v>
+        <v>1.1251</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6823</v>
       </c>
       <c r="M25" t="n">
         <v>0.6943</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8432,17 +8168,17 @@
         <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3123</v>
+        <v>1.3116</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6249</v>
+        <v>0.6253</v>
       </c>
       <c r="M26" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8481,14 +8217,14 @@
         <v>0.8715000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2595</v>
+        <v>1.2589</v>
       </c>
       <c r="M27" t="n">
         <v>0.2044</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8260,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0779</v>
+        <v>1.0775</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -8534,7 +8270,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8306,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2977</v>
+        <v>1.2971</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -8580,7 +8316,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8352,7 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4971</v>
+        <v>1.4962</v>
       </c>
       <c r="L30" t="n">
         <v>0.8278</v>
@@ -8626,7 +8362,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8650,29 +8386,29 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
         <v>45</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9848</v>
+        <v>0.9633</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1288</v>
+        <v>1.2166</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2784</v>
+        <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8444,17 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>1.6317</v>
+        <v>1.6305</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7685</v>
+        <v>0.7687</v>
       </c>
       <c r="M32" t="n">
         <v>0.7295</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8754,17 +8490,17 @@
         <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>1.113</v>
+        <v>1.1126</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0118</v>
+        <v>1.0116</v>
       </c>
       <c r="M33" t="n">
         <v>0.5132</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="L34" t="n">
         <v>0.9068000000000001</v>
@@ -8810,7 +8546,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8846,17 +8582,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3086</v>
+        <v>1.3079</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7849</v>
+        <v>0.785</v>
       </c>
       <c r="M35" t="n">
         <v>0.7025</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8892,17 +8628,17 @@
         <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6881</v>
+        <v>0.6884</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2648</v>
+        <v>1.2642</v>
       </c>
       <c r="M36" t="n">
         <v>0.2428</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8926,29 +8662,29 @@
         <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8245</v>
+        <v>0.7703</v>
       </c>
       <c r="L37" t="n">
-        <v>0.887</v>
+        <v>1.0483</v>
       </c>
       <c r="M37" t="n">
-        <v>0.403</v>
+        <v>0.3585</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8984,17 +8720,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1363</v>
+        <v>1.1359</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7559</v>
+        <v>0.7561</v>
       </c>
       <c r="M38" t="n">
         <v>0.5795</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9030,17 +8766,17 @@
         <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1493</v>
+        <v>1.1489</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9025</v>
+        <v>0.9024</v>
       </c>
       <c r="M39" t="n">
         <v>0.5076000000000001</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9076,7 +8812,7 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8087</v>
+        <v>0.8088</v>
       </c>
       <c r="L40" t="n">
         <v>0.8518</v>
@@ -9086,7 +8822,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9122,17 +8858,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0436</v>
+        <v>1.0433</v>
       </c>
       <c r="L41" t="n">
-        <v>0.791</v>
+        <v>0.7911</v>
       </c>
       <c r="M41" t="n">
         <v>0.6054</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9165,20 +8901,20 @@
         <v>53</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3388</v>
+        <v>1.4576</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6775</v>
+        <v>0.6204</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6823</v>
+        <v>0.7209</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9214,17 +8950,17 @@
         <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3261</v>
+        <v>1.3254</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3579</v>
+        <v>1.3571</v>
       </c>
       <c r="M43" t="n">
         <v>0.4537</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9260,7 +8996,7 @@
         <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4125</v>
+        <v>1.4117</v>
       </c>
       <c r="L44" t="n">
         <v>0.8356</v>
@@ -9270,7 +9006,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9306,17 +9042,17 @@
         <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7145</v>
+        <v>0.7147</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3994</v>
+        <v>1.3986</v>
       </c>
       <c r="M45" t="n">
         <v>0.2767</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9352,17 +9088,17 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1405</v>
+        <v>1.1401</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8514</v>
       </c>
       <c r="M46" t="n">
         <v>0.63</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9398,17 +9134,17 @@
         <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3155</v>
+        <v>1.3148</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0615</v>
+        <v>1.0612</v>
       </c>
       <c r="M47" t="n">
         <v>0.6099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9438,23 +9174,23 @@
         <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.8528</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4337</v>
+        <v>0.4187</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9490,17 +9226,17 @@
         <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>1.0112</v>
+        <v>1.011</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9376</v>
+        <v>0.9375</v>
       </c>
       <c r="M49" t="n">
         <v>0.4572</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-21T03:00:00+00:00</t>
+          <t>2026-06-22T00:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -523,38 +523,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>25.4</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>72.7</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
-        <v>50.6</v>
+        <v>53.9</v>
       </c>
       <c r="J2" t="n">
-        <v>34.5</v>
+        <v>35.9</v>
       </c>
       <c r="K2" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="L2" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -562,34 +562,34 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q2" t="n">
         <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.4</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>53.4</v>
+        <v>6.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -598,58 +598,58 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>60.9</v>
+        <v>60.3</v>
       </c>
       <c r="I3" t="n">
-        <v>39.8</v>
+        <v>41.8</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>14.3</v>
+        <v>16.2</v>
       </c>
       <c r="L3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1617.8</v>
+        <v>1603.8</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.90000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2</v>
+        <v>53.4</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -658,199 +658,199 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>38.9</v>
       </c>
       <c r="J4" t="n">
-        <v>25.1</v>
+        <v>23.6</v>
       </c>
       <c r="K4" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="L4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1603.8</v>
+        <v>1617.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>99.8</v>
+        <v>90.5</v>
       </c>
       <c r="D5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="H5" t="n">
-        <v>73.2</v>
+        <v>66.8</v>
       </c>
       <c r="I5" t="n">
-        <v>41.8</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>23.1</v>
+        <v>21.4</v>
       </c>
       <c r="K5" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1577.2</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="D6" t="n">
-        <v>7.6</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>66.5</v>
+        <v>73.2</v>
       </c>
       <c r="I6" t="n">
-        <v>37.1</v>
+        <v>41.5</v>
       </c>
       <c r="J6" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>13.3</v>
       </c>
       <c r="L6" t="n">
         <v>6.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1577.2</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>59.6</v>
+        <v>74.8</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9</v>
+        <v>25.2</v>
       </c>
       <c r="E7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>65.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>39.9</v>
       </c>
       <c r="J7" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="K7" t="n">
-        <v>11.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -858,59 +858,59 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1582.5</v>
+        <v>1544.6</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.9</v>
+        <v>28.5</v>
       </c>
       <c r="D8" t="n">
-        <v>53.4</v>
+        <v>54.9</v>
       </c>
       <c r="E8" t="n">
-        <v>20.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
-        <v>98.3</v>
+        <v>91.2</v>
       </c>
       <c r="H8" t="n">
-        <v>55.4</v>
+        <v>60.3</v>
       </c>
       <c r="I8" t="n">
-        <v>35.6</v>
+        <v>32.5</v>
       </c>
       <c r="J8" t="n">
-        <v>21.4</v>
+        <v>18.2</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -918,35 +918,35 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1560</v>
+        <v>1555.6</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.8</v>
+        <v>40.5</v>
       </c>
       <c r="D9" t="n">
-        <v>25.2</v>
+        <v>59.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,118 +958,118 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I9" t="n">
-        <v>39.8</v>
+        <v>33.8</v>
       </c>
       <c r="J9" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="K9" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1544.6</v>
+        <v>1582.5</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="R9" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>54.9</v>
+        <v>3.9</v>
       </c>
       <c r="E10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>60.4</v>
+        <v>67.2</v>
       </c>
       <c r="I10" t="n">
-        <v>33.6</v>
+        <v>37</v>
       </c>
       <c r="J10" t="n">
         <v>18.5</v>
       </c>
       <c r="K10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1555.6</v>
+        <v>1573.8</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>96.09999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3.9</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1078,58 +1078,58 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>66.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="K11" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1573.8</v>
+        <v>1575.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="R11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37.4</v>
+        <v>59.5</v>
       </c>
       <c r="D12" t="n">
-        <v>50.8</v>
+        <v>40.5</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1138,79 +1138,79 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>52.3</v>
+        <v>63.3</v>
       </c>
       <c r="I12" t="n">
-        <v>30.8</v>
+        <v>32.6</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="K12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1575.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="R12" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.5</v>
+        <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>52.1</v>
+        <v>65.8</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5</v>
+        <v>33.7</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G13" t="n">
-        <v>98.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="H13" t="n">
-        <v>57</v>
+        <v>43.3</v>
       </c>
       <c r="I13" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="J13" t="n">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1218,17 +1218,17 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1569.9</v>
+        <v>1560</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="R13" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="14">
@@ -1246,10 +1246,10 @@
         <v>60.6</v>
       </c>
       <c r="D14" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>46.6</v>
+        <v>47.1</v>
       </c>
       <c r="I14" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="J14" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
         <v>0.83</v>
@@ -1294,40 +1294,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.9</v>
+        <v>25.2</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>24.7</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>79.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>49.6</v>
+        <v>57.9</v>
       </c>
       <c r="I15" t="n">
-        <v>21.3</v>
+        <v>26.3</v>
       </c>
       <c r="J15" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>2.1</v>
@@ -1338,59 +1338,59 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1565</v>
+        <v>1545.2</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.2</v>
+        <v>29.2</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9</v>
+        <v>24.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>58</v>
+        <v>49.5</v>
       </c>
       <c r="I16" t="n">
-        <v>26.3</v>
+        <v>21.9</v>
       </c>
       <c r="J16" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1398,17 +1398,17 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1545.2</v>
+        <v>1565</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="R16" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -1438,16 +1438,16 @@
         <v>99.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="I17" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="J17" t="n">
         <v>11.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -1474,103 +1474,103 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>34.1</v>
       </c>
       <c r="E18" t="n">
-        <v>27.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>81.7</v>
       </c>
       <c r="H18" t="n">
-        <v>44.8</v>
+        <v>38</v>
       </c>
       <c r="I18" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="J18" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1542.8</v>
+        <v>1573.4</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>52.5</v>
+        <v>47.9</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="E19" t="n">
-        <v>18.2</v>
+        <v>27.2</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>57.9</v>
+        <v>44.5</v>
       </c>
       <c r="I19" t="n">
-        <v>23.7</v>
+        <v>21.6</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1541.7</v>
+        <v>1542.8</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="R19" t="n">
         <v>0.68</v>
@@ -1594,118 +1594,118 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2</v>
+        <v>52.6</v>
       </c>
       <c r="D20" t="n">
-        <v>82.5</v>
+        <v>26.1</v>
       </c>
       <c r="E20" t="n">
-        <v>13.8</v>
+        <v>18.1</v>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>94.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>44.7</v>
+        <v>58.1</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>24.5</v>
       </c>
       <c r="J20" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1556.1</v>
+        <v>1541.7</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="Q20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.68</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="D21" t="n">
-        <v>20.2</v>
+        <v>82.5</v>
       </c>
       <c r="E21" t="n">
-        <v>62.2</v>
+        <v>13.8</v>
       </c>
       <c r="F21" t="n">
-        <v>16.3</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>66.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>30.9</v>
+        <v>40.6</v>
       </c>
       <c r="I21" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="J21" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1573.4</v>
+        <v>1556.1</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="R21" t="n">
         <v>0.6899999999999999</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="D22" t="n">
         <v>20.9</v>
@@ -1735,10 +1735,10 @@
         <v>3.3</v>
       </c>
       <c r="G22" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="H22" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="I22" t="n">
         <v>16.8</v>
@@ -1750,7 +1750,7 @@
         <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1798,19 +1798,19 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>60.3</v>
+        <v>60.4</v>
       </c>
       <c r="I23" t="n">
-        <v>25.9</v>
+        <v>26.6</v>
       </c>
       <c r="J23" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="D24" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="E24" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="F24" t="n">
         <v>21.1</v>
       </c>
       <c r="G24" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="H24" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="I24" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="J24" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="L24" t="n">
         <v>0.9</v>
@@ -1894,121 +1894,121 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9.699999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="D25" t="n">
-        <v>21.7</v>
+        <v>68.2</v>
       </c>
       <c r="E25" t="n">
-        <v>67.7</v>
+        <v>23.3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="G25" t="n">
-        <v>90.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>33.2</v>
+        <v>38.6</v>
       </c>
       <c r="I25" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="J25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L25" t="n">
         <v>0.8</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1521.6</v>
+        <v>1550.3</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>68.2</v>
+        <v>21.7</v>
       </c>
       <c r="E26" t="n">
-        <v>23.3</v>
+        <v>67.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="G26" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="H26" t="n">
-        <v>38.4</v>
+        <v>33.3</v>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="J26" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1550.3</v>
+        <v>1521.6</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="27">
@@ -2029,28 +2029,28 @@
         <v>67.8</v>
       </c>
       <c r="E27" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="F27" t="n">
         <v>5.7</v>
       </c>
       <c r="G27" t="n">
-        <v>90.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="H27" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="I27" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2074,61 +2074,61 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>44.6</v>
       </c>
       <c r="E28" t="n">
-        <v>56.9</v>
+        <v>26.6</v>
       </c>
       <c r="F28" t="n">
-        <v>30.5</v>
+        <v>25.9</v>
       </c>
       <c r="G28" t="n">
-        <v>49.6</v>
+        <v>67.3</v>
       </c>
       <c r="H28" t="n">
-        <v>20.3</v>
+        <v>27.5</v>
       </c>
       <c r="I28" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1564.9</v>
+        <v>1554.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="R28" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="29">
@@ -2146,25 +2146,25 @@
         <v>3.2</v>
       </c>
       <c r="D29" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>15.6</v>
       </c>
       <c r="F29" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="G29" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="I29" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
         <v>0.9</v>
@@ -2215,16 +2215,16 @@
         <v>22.8</v>
       </c>
       <c r="G30" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K30" t="n">
         <v>0.6</v>
@@ -2254,37 +2254,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>44.6</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>26.2</v>
+        <v>79.3</v>
       </c>
       <c r="F31" t="n">
-        <v>26.3</v>
+        <v>20.7</v>
       </c>
       <c r="G31" t="n">
-        <v>66.7</v>
+        <v>49.8</v>
       </c>
       <c r="H31" t="n">
-        <v>27.4</v>
+        <v>18.4</v>
       </c>
       <c r="I31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="K31" t="n">
         <v>0.8</v>
@@ -2294,21 +2294,21 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1554.9</v>
+        <v>1564.9</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="R31" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
@@ -2326,7 +2326,7 @@
         <v>0.1</v>
       </c>
       <c r="D32" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
         <v>52.9</v>
@@ -2335,16 +2335,16 @@
         <v>16.1</v>
       </c>
       <c r="G32" t="n">
-        <v>72.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K32" t="n">
         <v>0.6</v>
@@ -2395,19 +2395,19 @@
         <v>78.2</v>
       </c>
       <c r="G33" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="H33" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
@@ -2446,25 +2446,25 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="E34" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="F34" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="G34" t="n">
         <v>37.5</v>
       </c>
       <c r="H34" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="I34" t="n">
         <v>4.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K34" t="n">
         <v>0.4</v>
@@ -2494,40 +2494,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="E35" t="n">
-        <v>78.90000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="F35" t="n">
-        <v>19.2</v>
+        <v>39</v>
       </c>
       <c r="G35" t="n">
-        <v>55.9</v>
+        <v>21.2</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>1.3</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L35" t="n">
         <v>0.1</v>
@@ -2538,53 +2538,53 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1514.3</v>
+        <v>1534.2</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="R35" t="n">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>62.2</v>
+        <v>19.2</v>
       </c>
       <c r="G36" t="n">
-        <v>31.8</v>
+        <v>55.8</v>
       </c>
       <c r="H36" t="n">
-        <v>12.1</v>
+        <v>17.3</v>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K36" t="n">
         <v>0.3</v>
@@ -2594,57 +2594,57 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1544.8</v>
+        <v>1514.3</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="E37" t="n">
-        <v>52.5</v>
+        <v>24.3</v>
       </c>
       <c r="F37" t="n">
-        <v>39</v>
+        <v>62.4</v>
       </c>
       <c r="G37" t="n">
-        <v>21.5</v>
+        <v>31.8</v>
       </c>
       <c r="H37" t="n">
-        <v>8.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K37" t="n">
         <v>0.3</v>
@@ -2654,57 +2654,57 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1534.2</v>
+        <v>1544.8</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>75.3</v>
+        <v>88</v>
       </c>
       <c r="F38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>36.9</v>
+        <v>85</v>
       </c>
       <c r="H38" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K38" t="n">
         <v>0.2</v>
@@ -2714,117 +2714,117 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1516.6</v>
+        <v>1507.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.84</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.85</v>
+        <v>1.36</v>
       </c>
       <c r="R38" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>87.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G39" t="n">
-        <v>83.3</v>
+        <v>36.5</v>
       </c>
       <c r="H39" t="n">
-        <v>18.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L39" t="n">
         <v>0.1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1507.6</v>
+        <v>1516.6</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="R39" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4.9</v>
+        <v>19.4</v>
       </c>
       <c r="E40" t="n">
-        <v>26.4</v>
+        <v>24.1</v>
       </c>
       <c r="F40" t="n">
-        <v>68.2</v>
+        <v>56.4</v>
       </c>
       <c r="G40" t="n">
-        <v>20.2</v>
+        <v>23.8</v>
       </c>
       <c r="H40" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K40" t="n">
         <v>0.1</v>
@@ -2838,113 +2838,113 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1534.7</v>
+        <v>1521.7</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="R40" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="D41" t="n">
-        <v>19.4</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>24.2</v>
+        <v>46.2</v>
       </c>
       <c r="F41" t="n">
-        <v>56.4</v>
+        <v>17.1</v>
       </c>
       <c r="G41" t="n">
-        <v>23.9</v>
+        <v>70.3</v>
       </c>
       <c r="H41" t="n">
-        <v>7.2</v>
+        <v>15.9</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1521.7</v>
+        <v>1467.7</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>32.3</v>
+        <v>12.4</v>
       </c>
       <c r="E42" t="n">
-        <v>46.2</v>
+        <v>13.9</v>
       </c>
       <c r="F42" t="n">
-        <v>16.9</v>
+        <v>73.7</v>
       </c>
       <c r="G42" t="n">
-        <v>70.2</v>
+        <v>15.8</v>
       </c>
       <c r="H42" t="n">
-        <v>15.7</v>
+        <v>2.7</v>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2954,57 +2954,57 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1467.7</v>
+        <v>1519.9</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="R42" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.1</v>
+        <v>20.7</v>
       </c>
       <c r="F43" t="n">
-        <v>78.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="G43" t="n">
-        <v>20.7</v>
+        <v>7.7</v>
       </c>
       <c r="H43" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3018,50 +3018,50 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1499.2</v>
+        <v>1534.7</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="R43" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>12.4</v>
+        <v>6.3</v>
       </c>
       <c r="E44" t="n">
-        <v>13.9</v>
+        <v>4.5</v>
       </c>
       <c r="F44" t="n">
-        <v>73.8</v>
+        <v>89.2</v>
       </c>
       <c r="G44" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0.1</v>
@@ -3078,50 +3078,50 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1519.9</v>
+        <v>1518</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R44" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>6.2</v>
+        <v>18.4</v>
       </c>
       <c r="E45" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="F45" t="n">
-        <v>89.3</v>
+        <v>78.5</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>20.7</v>
       </c>
       <c r="H45" t="n">
         <v>2.7</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0.1</v>
@@ -3138,17 +3138,17 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1518</v>
+        <v>1499.2</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="R45" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="46">
@@ -3223,25 +3223,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>15.6</v>
+        <v>1.9</v>
       </c>
       <c r="F47" t="n">
-        <v>83.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R47" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="48">
@@ -3295,13 +3295,13 @@
         <v>80.8</v>
       </c>
       <c r="G48" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="H48" t="n">
         <v>2.8</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>91.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3520,7 +3520,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="5">
@@ -3541,13 +3541,13 @@
         <v>19.4</v>
       </c>
       <c r="E5" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="F5" t="n">
         <v>56.4</v>
       </c>
       <c r="G5" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="6">
@@ -3595,7 +3595,7 @@
         <v>73</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>19.2</v>
       </c>
       <c r="G8" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="9">
@@ -3655,7 +3655,7 @@
         <v>80.8</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="10">
@@ -3700,7 +3700,7 @@
         <v>47.9</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="E11" t="n">
         <v>27.2</v>
@@ -3736,7 +3736,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>90.2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3811,13 +3811,13 @@
         <v>67.8</v>
       </c>
       <c r="E15" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="F15" t="n">
         <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>90.40000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="16">
@@ -3835,7 +3835,7 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
         <v>52.9</v>
@@ -3844,7 +3844,7 @@
         <v>16.1</v>
       </c>
       <c r="G16" t="n">
-        <v>72.7</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3871,7 +3871,7 @@
         <v>78.2</v>
       </c>
       <c r="G17" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="18">
@@ -3925,7 +3925,7 @@
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3952,7 +3952,7 @@
         <v>22.8</v>
       </c>
       <c r="G20" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -3976,7 +3976,7 @@
         <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="G21" t="n">
         <v>15.8</v>
@@ -4024,10 +4024,10 @@
         <v>60.6</v>
       </c>
       <c r="D23" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4054,13 +4054,13 @@
         <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>83.3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="D28" t="n">
         <v>20.9</v>
@@ -4168,7 +4168,7 @@
         <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="29">
@@ -4186,13 +4186,13 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="E29" t="n">
         <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>89.3</v>
+        <v>89.2</v>
       </c>
       <c r="G29" t="n">
         <v>9</v>
@@ -4240,13 +4240,13 @@
         <v>3.2</v>
       </c>
       <c r="D31" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>15.6</v>
       </c>
       <c r="F31" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="G31" t="n">
         <v>79.59999999999999</v>
@@ -4276,7 +4276,7 @@
         <v>7.7</v>
       </c>
       <c r="G32" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="33">
@@ -4294,13 +4294,13 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="E33" t="n">
         <v>3.1</v>
       </c>
       <c r="F33" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="G33" t="n">
         <v>20.7</v>
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.6</v>
+        <v>40.5</v>
       </c>
       <c r="D34" t="n">
-        <v>31.9</v>
+        <v>59.5</v>
       </c>
       <c r="E34" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.5</v>
+        <v>59.5</v>
       </c>
       <c r="D35" t="n">
-        <v>52.1</v>
+        <v>40.5</v>
       </c>
       <c r="E35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -4372,19 +4372,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>56.9</v>
+        <v>79.3</v>
       </c>
       <c r="F36" t="n">
-        <v>30.5</v>
+        <v>20.7</v>
       </c>
       <c r="G36" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="37">
@@ -4399,19 +4399,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>26.4</v>
+        <v>20.7</v>
       </c>
       <c r="F37" t="n">
-        <v>68.2</v>
+        <v>79.3</v>
       </c>
       <c r="G37" t="n">
-        <v>20.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="38">
@@ -4426,19 +4426,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>25.4</v>
+        <v>0.1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -4453,19 +4453,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>25.9</v>
+        <v>0.1</v>
       </c>
       <c r="D39" t="n">
-        <v>53.4</v>
+        <v>65.8</v>
       </c>
       <c r="E39" t="n">
-        <v>20.5</v>
+        <v>33.7</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G39" t="n">
-        <v>98.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
@@ -4480,19 +4480,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>20.2</v>
+        <v>34.1</v>
       </c>
       <c r="E40" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>16.3</v>
+        <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>66.2</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="41">
@@ -4507,19 +4507,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>15.6</v>
+        <v>1.9</v>
       </c>
       <c r="F41" t="n">
-        <v>83.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="D42" t="n">
         <v>33</v>
       </c>
       <c r="E42" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="F42" t="n">
         <v>13.4</v>
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="D43" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="E43" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G43" t="n">
-        <v>95.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4588,19 +4588,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="D44" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="E44" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="F44" t="n">
         <v>21.1</v>
       </c>
       <c r="G44" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="45">
@@ -4615,16 +4615,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D45" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="F45" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="G45" t="n">
         <v>31.8</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="D46" t="n">
         <v>7.6</v>
@@ -4651,10 +4651,10 @@
         <v>1.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="47">
@@ -4675,13 +4675,13 @@
         <v>44.6</v>
       </c>
       <c r="E47" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="F47" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="G47" t="n">
-        <v>66.7</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="48">
@@ -4699,13 +4699,13 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="E48" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="F48" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="G48" t="n">
         <v>37.5</v>
@@ -4726,16 +4726,16 @@
         <v>4.6</v>
       </c>
       <c r="D49" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="E49" t="n">
         <v>46.2</v>
       </c>
       <c r="F49" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="G49" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,16 +4836,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22T23:00:00Z</t>
+          <t>2026-06-23T19:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4855,129 +4855,129 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>58.2</v>
+        <v>79.3</v>
       </c>
       <c r="J2" t="n">
-        <v>21.3</v>
+        <v>14.5</v>
       </c>
       <c r="K2" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>17.6</v>
+        <v>125.7</v>
       </c>
       <c r="P2" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-22T20:00:00Z</t>
+          <t>2026-06-23T22:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>64.2</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="K3" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>35.2</v>
+        <v>0.1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-22T16:00:00Z</t>
+          <t>2026-06-23T16:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4987,129 +4987,129 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>45.2</v>
+        <v>53.4</v>
       </c>
       <c r="J4" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
       <c r="K4" t="n">
-        <v>28.2</v>
+        <v>22.3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>17.2</v>
+        <v>20.2</v>
       </c>
       <c r="P4" t="n">
-        <v>28.2</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00Z</t>
+          <t>2026-06-24T01:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.72</v>
+        <v>1.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.19</v>
+        <v>0.99</v>
       </c>
       <c r="I5" t="n">
-        <v>10.9</v>
+        <v>39.4</v>
       </c>
       <c r="J5" t="n">
-        <v>18.1</v>
+        <v>29.5</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>31.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>79.90000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="P5" t="n">
-        <v>10.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-23T19:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5119,226 +5119,226 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="H6" t="n">
-        <v>0.52</v>
+        <v>1.47</v>
       </c>
       <c r="I6" t="n">
-        <v>79.3</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
-        <v>14.5</v>
+        <v>25.8</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>125.7</v>
+        <v>21.2</v>
       </c>
       <c r="P6" t="n">
-        <v>6.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-23T22:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
-        <v>1.62</v>
+        <v>0.58</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>23.5</v>
+        <v>21.1</v>
       </c>
       <c r="K7" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.1</v>
+        <v>94.8</v>
       </c>
       <c r="P7" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-23T16:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="H8" t="n">
-        <v>0.98</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>53.4</v>
+        <v>25.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="K8" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>20.2</v>
+        <v>0.6</v>
       </c>
       <c r="P8" t="n">
-        <v>22.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>39.4</v>
+        <v>55.8</v>
       </c>
       <c r="J9" t="n">
-        <v>29.5</v>
+        <v>25.2</v>
       </c>
       <c r="K9" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -5347,231 +5347,231 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="H10" t="n">
         <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
       <c r="J10" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>54.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>21.2</v>
+        <v>39.6</v>
       </c>
       <c r="P10" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>0.78</v>
       </c>
       <c r="H11" t="n">
-        <v>0.59</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="n">
-        <v>67.90000000000001</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>21.1</v>
+        <v>30.1</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>45.9</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>94.8</v>
+        <v>28.6</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>25.4</v>
+        <v>15.9</v>
       </c>
       <c r="J12" t="n">
-        <v>25.9</v>
+        <v>20.7</v>
       </c>
       <c r="K12" t="n">
-        <v>48.7</v>
+        <v>63.4</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>36.2</v>
       </c>
       <c r="P12" t="n">
-        <v>48.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5581,195 +5581,195 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.59</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="I13" t="n">
-        <v>55.8</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
-        <v>25.1</v>
+        <v>27.8</v>
       </c>
       <c r="K13" t="n">
-        <v>19.1</v>
+        <v>50.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="P13" t="n">
-        <v>19.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.75</v>
+        <v>2.59</v>
       </c>
       <c r="H14" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="I14" t="n">
-        <v>19.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>26.6</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>54.2</v>
+        <v>11.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>39.6</v>
+        <v>68.2</v>
       </c>
       <c r="P14" t="n">
-        <v>19.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>30.1</v>
+        <v>10.9</v>
       </c>
       <c r="K15" t="n">
-        <v>45.9</v>
+        <v>83.8</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>28.6</v>
+        <v>76</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5779,63 +5779,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.9</v>
+        <v>1.62</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="I16" t="n">
-        <v>15.9</v>
+        <v>39.9</v>
       </c>
       <c r="J16" t="n">
-        <v>20.7</v>
+        <v>23.6</v>
       </c>
       <c r="K16" t="n">
-        <v>63.4</v>
+        <v>36.5</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>36.2</v>
+        <v>55.5</v>
       </c>
       <c r="P16" t="n">
-        <v>15.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5845,28 +5845,28 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H17" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
       <c r="J17" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="K17" t="n">
-        <v>50.1</v>
+        <v>39.9</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -5875,33 +5875,33 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>33.1</v>
+        <v>27.2</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5911,129 +5911,129 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="H18" t="n">
-        <v>0.97</v>
+        <v>1.69</v>
       </c>
       <c r="I18" t="n">
-        <v>72.2</v>
+        <v>40.8</v>
       </c>
       <c r="J18" t="n">
-        <v>15.9</v>
+        <v>22.3</v>
       </c>
       <c r="K18" t="n">
-        <v>11.9</v>
+        <v>36.9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>68.2</v>
+        <v>12.6</v>
       </c>
       <c r="P18" t="n">
-        <v>11.9</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.66</v>
+        <v>1.66</v>
       </c>
       <c r="H19" t="n">
-        <v>3.01</v>
+        <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>54.9</v>
       </c>
       <c r="J19" t="n">
-        <v>10.8</v>
+        <v>24.4</v>
       </c>
       <c r="K19" t="n">
-        <v>83.8</v>
+        <v>20.7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>76</v>
+        <v>30.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6043,129 +6043,129 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>39.9</v>
+        <v>33.9</v>
       </c>
       <c r="J20" t="n">
-        <v>23.6</v>
+        <v>30.6</v>
       </c>
       <c r="K20" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>55.5</v>
+        <v>14.1</v>
       </c>
       <c r="P20" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="H21" t="n">
-        <v>1.17</v>
+        <v>2.53</v>
       </c>
       <c r="I21" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
       <c r="J21" t="n">
-        <v>29.3</v>
+        <v>15.2</v>
       </c>
       <c r="K21" t="n">
-        <v>39.9</v>
+        <v>75.7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>27.2</v>
+        <v>37.6</v>
       </c>
       <c r="P21" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6175,129 +6175,129 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="H22" t="n">
-        <v>1.51</v>
+        <v>0.78</v>
       </c>
       <c r="I22" t="n">
-        <v>47.1</v>
+        <v>51.8</v>
       </c>
       <c r="J22" t="n">
-        <v>22.2</v>
+        <v>27.4</v>
       </c>
       <c r="K22" t="n">
-        <v>30.8</v>
+        <v>20.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>12.6</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>30.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.48</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="I23" t="n">
-        <v>50.5</v>
+        <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>26.3</v>
+        <v>21.5</v>
       </c>
       <c r="K23" t="n">
-        <v>23.1</v>
+        <v>67</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>30.2</v>
+        <v>87.2</v>
       </c>
       <c r="P23" t="n">
-        <v>23.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6307,129 +6307,129 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="H24" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="I24" t="n">
-        <v>33.9</v>
+        <v>15.3</v>
       </c>
       <c r="J24" t="n">
-        <v>30.6</v>
+        <v>20.4</v>
       </c>
       <c r="K24" t="n">
-        <v>35.5</v>
+        <v>64.2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P24" t="n">
-        <v>35.5</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.77</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
-        <v>2.54</v>
+        <v>0.91</v>
       </c>
       <c r="I25" t="n">
-        <v>9.1</v>
+        <v>60.7</v>
       </c>
       <c r="J25" t="n">
-        <v>15.2</v>
+        <v>21.8</v>
       </c>
       <c r="K25" t="n">
-        <v>75.7</v>
+        <v>17.5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P25" t="n">
-        <v>9.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6439,129 +6439,129 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.78</v>
+        <v>1.3</v>
       </c>
       <c r="I26" t="n">
-        <v>51.9</v>
+        <v>34.2</v>
       </c>
       <c r="J26" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="K26" t="n">
-        <v>20.8</v>
+        <v>38.8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="P26" t="n">
-        <v>51.9</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
-        <v>1.83</v>
+        <v>2.97</v>
       </c>
       <c r="I27" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>21.5</v>
+        <v>9.9</v>
       </c>
       <c r="K27" t="n">
-        <v>67.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P27" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6571,63 +6571,63 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.88</v>
+        <v>1.37</v>
       </c>
       <c r="H28" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="I28" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
       <c r="J28" t="n">
-        <v>20.4</v>
+        <v>24.7</v>
       </c>
       <c r="K28" t="n">
-        <v>64.3</v>
+        <v>41.1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>38.4</v>
+        <v>23.3</v>
       </c>
       <c r="P28" t="n">
-        <v>15.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6637,28 +6637,28 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="H29" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I29" t="n">
-        <v>60.7</v>
+        <v>41.1</v>
       </c>
       <c r="J29" t="n">
-        <v>21.8</v>
+        <v>31.4</v>
       </c>
       <c r="K29" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -6667,282 +6667,18 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P29" t="n">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>69</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I30" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>46.3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>70</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>71</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I32" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P32" t="n">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>72</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I33" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P33" t="n">
         <v>41.1</v>
       </c>
     </row>
@@ -7046,10 +6782,10 @@
         <v>82</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -7058,23 +6794,23 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1978</v>
+        <v>1.2164</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7498</v>
+        <v>0.7469</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6884</v>
+        <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7104,23 +6840,23 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J3" t="n">
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5355</v>
+        <v>1.5212</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9045</v>
+        <v>0.9166</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7156,17 +6892,17 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9687</v>
+        <v>0.9683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7879</v>
       </c>
       <c r="M4" t="n">
         <v>0.5422</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7190,29 +6926,29 @@
         <v>13</v>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
       <c r="I5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4456</v>
+        <v>1.3184</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6577</v>
+        <v>0.7271</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8384</v>
+        <v>0.7222</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7248,17 +6984,17 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5192</v>
+        <v>1.5176</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6832</v>
+        <v>0.6834</v>
       </c>
       <c r="M6" t="n">
         <v>0.6408</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7294,17 +7030,17 @@
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9708</v>
+        <v>0.9705</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="M7" t="n">
         <v>0.384</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7340,17 +7076,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4376</v>
+        <v>1.4363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8171</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>0.6761</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7386,17 +7122,17 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2263</v>
+        <v>1.2254</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5695</v>
       </c>
       <c r="M9" t="n">
         <v>0.6276</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7432,17 +7168,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0611</v>
+        <v>1.0606</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8111</v>
+        <v>0.8112</v>
       </c>
       <c r="M10" t="n">
         <v>0.4729</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7478,17 +7214,17 @@
         <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3563</v>
+        <v>1.355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8557</v>
+        <v>0.8556</v>
       </c>
       <c r="M11" t="n">
         <v>0.6784</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7260,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2345</v>
+        <v>1.2335</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0873</v>
+        <v>1.0867</v>
       </c>
       <c r="M12" t="n">
         <v>0.5662</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7570,17 +7306,17 @@
         <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0944</v>
+        <v>1.0937</v>
       </c>
       <c r="L13" t="n">
-        <v>1.296</v>
+        <v>1.2949</v>
       </c>
       <c r="M13" t="n">
         <v>0.3885</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7616,17 +7352,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1519</v>
+        <v>1.1512</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8666</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7398,17 @@
         <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8945</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6383</v>
+        <v>0.6387</v>
       </c>
       <c r="M15" t="n">
         <v>0.5734</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7711,14 +7447,14 @@
         <v>0.8046</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5777</v>
+        <v>0.5782</v>
       </c>
       <c r="M16" t="n">
         <v>0.5105</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7754,17 +7490,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0402</v>
+        <v>1.0396</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6852</v>
       </c>
       <c r="M17" t="n">
         <v>0.6263</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7800,17 +7536,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4204</v>
+        <v>1.4191</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6428</v>
+        <v>0.6432</v>
       </c>
       <c r="M18" t="n">
         <v>0.8106</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7840,23 +7576,23 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" t="n">
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4709</v>
+        <v>1.5266</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8609</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7941</v>
+        <v>0.8192</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7638,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7674,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7558</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0827</v>
+        <v>1.0822</v>
       </c>
       <c r="M21" t="n">
         <v>0.2864</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7984,17 +7720,17 @@
         <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9524</v>
+        <v>0.952</v>
       </c>
       <c r="L22" t="n">
-        <v>0.951</v>
+        <v>0.9507</v>
       </c>
       <c r="M22" t="n">
         <v>0.3494</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8030,17 +7766,17 @@
         <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1764</v>
+        <v>1.1756</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7212</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8064,29 +7800,29 @@
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8139</v>
+        <v>0.7523</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9736</v>
+        <v>1.0772</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5071</v>
+        <v>0.4447</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8122,17 +7858,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1251</v>
+        <v>1.1244</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6823</v>
+        <v>0.6825</v>
       </c>
       <c r="M25" t="n">
         <v>0.6943</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8168,17 +7904,17 @@
         <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3116</v>
+        <v>1.3105</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6253</v>
+        <v>0.6257</v>
       </c>
       <c r="M26" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8202,29 +7938,29 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
         <v>9</v>
       </c>
-      <c r="H27" t="n">
-        <v>8</v>
-      </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8645</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2589</v>
+        <v>1.2812</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2044</v>
+        <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8260,7 +7996,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0775</v>
+        <v>1.0769</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -8270,7 +8006,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8042,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2971</v>
+        <v>1.2961</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -8316,7 +8052,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8088,7 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4962</v>
+        <v>1.4947</v>
       </c>
       <c r="L30" t="n">
         <v>0.8278</v>
@@ -8362,7 +8098,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8398,17 +8134,17 @@
         <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9633</v>
+        <v>0.963</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2166</v>
+        <v>1.2157</v>
       </c>
       <c r="M31" t="n">
         <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8438,23 +8174,23 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.6305</v>
+        <v>1.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7687</v>
+        <v>0.8249</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7295</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8490,17 +8226,17 @@
         <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1126</v>
+        <v>1.1119</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0116</v>
+        <v>1.0111</v>
       </c>
       <c r="M33" t="n">
         <v>0.5132</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8536,17 +8272,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.999</v>
+        <v>0.9986</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9066</v>
       </c>
       <c r="M34" t="n">
         <v>0.5606</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8582,17 +8318,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3079</v>
+        <v>1.3068</v>
       </c>
       <c r="L35" t="n">
-        <v>0.785</v>
+        <v>0.7851</v>
       </c>
       <c r="M35" t="n">
         <v>0.7025</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8364,17 @@
         <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6884</v>
+        <v>0.6887</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2642</v>
+        <v>1.2631</v>
       </c>
       <c r="M36" t="n">
         <v>0.2428</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8677,14 +8413,14 @@
         <v>0.7703</v>
       </c>
       <c r="L37" t="n">
-        <v>1.0483</v>
+        <v>1.0478</v>
       </c>
       <c r="M37" t="n">
         <v>0.3585</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8720,17 +8456,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1359</v>
+        <v>1.1351</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7561</v>
+        <v>0.7562</v>
       </c>
       <c r="M38" t="n">
         <v>0.5795</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8754,29 +8490,29 @@
         <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1489</v>
+        <v>1.1745</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9024</v>
+        <v>0.9947</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4583</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8812,17 +8548,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8088</v>
+        <v>0.8087</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8518</v>
+        <v>0.8516</v>
       </c>
       <c r="M40" t="n">
         <v>0.4009</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8594,7 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0433</v>
+        <v>1.0428</v>
       </c>
       <c r="L41" t="n">
         <v>0.7911</v>
@@ -8868,7 +8604,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8904,17 +8640,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4576</v>
+        <v>1.4562</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6204</v>
+        <v>0.6208</v>
       </c>
       <c r="M42" t="n">
         <v>0.7209</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8950,17 +8686,17 @@
         <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3254</v>
+        <v>1.3243</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3571</v>
+        <v>1.3559</v>
       </c>
       <c r="M43" t="n">
         <v>0.4537</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8732,7 @@
         <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4117</v>
+        <v>1.4103</v>
       </c>
       <c r="L44" t="n">
         <v>0.8356</v>
@@ -9006,7 +8742,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9042,17 +8778,17 @@
         <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7147</v>
+        <v>0.7149</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3986</v>
+        <v>1.3974</v>
       </c>
       <c r="M45" t="n">
         <v>0.2767</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9088,17 +8824,17 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1401</v>
+        <v>1.1393</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8514</v>
+        <v>0.8512</v>
       </c>
       <c r="M46" t="n">
         <v>0.63</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9134,17 +8870,17 @@
         <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3148</v>
+        <v>1.3137</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0612</v>
+        <v>1.0607</v>
       </c>
       <c r="M47" t="n">
         <v>0.6099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9180,17 +8916,17 @@
         <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8436</v>
+        <v>0.8435</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8528</v>
+        <v>0.8527</v>
       </c>
       <c r="M48" t="n">
         <v>0.4187</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -9226,17 +8962,17 @@
         <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>1.011</v>
+        <v>1.0105</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9375</v>
+        <v>0.9372</v>
       </c>
       <c r="M49" t="n">
         <v>0.4572</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-22T00:00:00+00:00</t>
+          <t>2026-06-23T02:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,19 +538,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="J2" t="n">
-        <v>35.9</v>
+        <v>34.7</v>
       </c>
       <c r="K2" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="L2" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D3" t="n">
         <v>6.2</v>
@@ -598,19 +598,19 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="I3" t="n">
-        <v>41.8</v>
+        <v>38.2</v>
       </c>
       <c r="J3" t="n">
-        <v>28</v>
+        <v>25.3</v>
       </c>
       <c r="K3" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="L3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -655,22 +655,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="I4" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="J4" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="K4" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="L4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -694,82 +694,82 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90.5</v>
+        <v>99.8</v>
       </c>
       <c r="D5" t="n">
-        <v>7.6</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>66.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>41.9</v>
       </c>
       <c r="J5" t="n">
-        <v>21.4</v>
+        <v>23.2</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1593.4</v>
+        <v>1577.2</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>99.8</v>
+        <v>68.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>31.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,58 +778,58 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>73.2</v>
+        <v>63.9</v>
       </c>
       <c r="I6" t="n">
-        <v>41.5</v>
+        <v>35.2</v>
       </c>
       <c r="J6" t="n">
-        <v>23.3</v>
+        <v>20.3</v>
       </c>
       <c r="K6" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1577.2</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.8</v>
+        <v>46.7</v>
       </c>
       <c r="D7" t="n">
-        <v>25.2</v>
+        <v>53.1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -838,97 +838,97 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>64.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I7" t="n">
-        <v>39.9</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>19.5</v>
+        <v>20.6</v>
       </c>
       <c r="K7" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1544.6</v>
+        <v>1565</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>54.9</v>
+        <v>3.9</v>
       </c>
       <c r="E8" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>60.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>32.5</v>
+        <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1555.6</v>
+        <v>1573.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -961,13 +961,13 @@
         <v>64.2</v>
       </c>
       <c r="I9" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="J9" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="L9" t="n">
         <v>4.9</v>
@@ -985,7 +985,7 @@
         <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="R9" t="n">
         <v>0.76</v>
@@ -994,82 +994,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.09999999999999</v>
+        <v>28.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.9</v>
+        <v>54.9</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>67.2</v>
+        <v>60.5</v>
       </c>
       <c r="I10" t="n">
-        <v>37</v>
+        <v>32.9</v>
       </c>
       <c r="J10" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="K10" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1573.8</v>
+        <v>1555.6</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.4</v>
+        <v>74.8</v>
       </c>
       <c r="D11" t="n">
-        <v>50.8</v>
+        <v>25.2</v>
       </c>
       <c r="E11" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1078,58 +1078,58 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>52.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>30</v>
+        <v>38.6</v>
       </c>
       <c r="J11" t="n">
-        <v>16.2</v>
+        <v>18.6</v>
       </c>
       <c r="K11" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="L11" t="n">
         <v>4.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1575.8</v>
+        <v>1544.6</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.63</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59.5</v>
+        <v>37.4</v>
       </c>
       <c r="D12" t="n">
-        <v>40.5</v>
+        <v>50.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1138,97 +1138,97 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>63.3</v>
+        <v>52.3</v>
       </c>
       <c r="I12" t="n">
-        <v>32.6</v>
+        <v>30.2</v>
       </c>
       <c r="J12" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1569.9</v>
+        <v>1575.8</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="R12" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>59.5</v>
       </c>
       <c r="D13" t="n">
-        <v>65.8</v>
+        <v>40.5</v>
       </c>
       <c r="E13" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>43.3</v>
+        <v>63.4</v>
       </c>
       <c r="I13" t="n">
-        <v>25.8</v>
+        <v>32.3</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>16.9</v>
       </c>
       <c r="K13" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1560</v>
+        <v>1569.9</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="R13" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="14">
@@ -1249,7 +1249,7 @@
         <v>39.2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="I14" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="J14" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.83</v>
@@ -1294,43 +1294,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.2</v>
+        <v>0.1</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>65.7</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>33.7</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>57.9</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
-        <v>26.3</v>
+        <v>22.9</v>
       </c>
       <c r="J15" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1338,23 +1338,23 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1545.2</v>
+        <v>1560</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1363,112 +1363,112 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>53.3</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>46.7</v>
       </c>
       <c r="E16" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>79.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>49.5</v>
+        <v>65.2</v>
       </c>
       <c r="I16" t="n">
-        <v>21.9</v>
+        <v>28.2</v>
       </c>
       <c r="J16" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1565</v>
+        <v>1541.7</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54.3</v>
+        <v>25.2</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>27.8</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>51.2</v>
+        <v>57.8</v>
       </c>
       <c r="I17" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1560.9</v>
+        <v>1545.2</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="R17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="18">
@@ -1495,19 +1495,19 @@
         <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>81.7</v>
+        <v>82.5</v>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="I18" t="n">
-        <v>21.7</v>
+        <v>20.4</v>
       </c>
       <c r="J18" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1546,7 +1546,7 @@
         <v>47.9</v>
       </c>
       <c r="D19" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
         <v>27.2</v>
@@ -1555,22 +1555,22 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>44.5</v>
+        <v>45.2</v>
       </c>
       <c r="I19" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1594,43 +1594,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.6</v>
+        <v>54.2</v>
       </c>
       <c r="D20" t="n">
-        <v>26.1</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>18.1</v>
+        <v>27.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>58.1</v>
+        <v>51.3</v>
       </c>
       <c r="I20" t="n">
-        <v>24.5</v>
+        <v>25.7</v>
       </c>
       <c r="J20" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,17 +1638,17 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1541.7</v>
+        <v>1560.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
@@ -1669,28 +1669,28 @@
         <v>82.5</v>
       </c>
       <c r="E21" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="H21" t="n">
         <v>40.6</v>
       </c>
       <c r="I21" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="J21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q21" t="n">
         <v>0.68</v>
@@ -1726,31 +1726,31 @@
         <v>17.3</v>
       </c>
       <c r="D22" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="E22" t="n">
         <v>58.5</v>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="I22" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="J22" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1798,16 +1798,16 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>60.4</v>
+        <v>61.6</v>
       </c>
       <c r="I23" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="J23" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.1</v>
@@ -1834,37 +1834,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>30.3</v>
+        <v>21.7</v>
       </c>
       <c r="E24" t="n">
-        <v>33.2</v>
+        <v>67.7</v>
       </c>
       <c r="F24" t="n">
-        <v>21.1</v>
+        <v>0.9</v>
       </c>
       <c r="G24" t="n">
-        <v>69.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>35.6</v>
+        <v>33.1</v>
       </c>
       <c r="I24" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K24" t="n">
         <v>2.3</v>
@@ -1878,17 +1878,17 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1537.9</v>
+        <v>1521.6</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="R24" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="25">
@@ -1915,19 +1915,19 @@
         <v>4.6</v>
       </c>
       <c r="G25" t="n">
-        <v>92.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="H25" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="I25" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0.8</v>
@@ -1954,181 +1954,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="D26" t="n">
-        <v>21.7</v>
+        <v>67.7</v>
       </c>
       <c r="E26" t="n">
-        <v>67.7</v>
+        <v>25.3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="G26" t="n">
-        <v>91</v>
+        <v>90.5</v>
       </c>
       <c r="H26" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="I26" t="n">
-        <v>13.8</v>
+        <v>10.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1521.6</v>
+        <v>1546.8</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>21.7</v>
       </c>
       <c r="D27" t="n">
-        <v>67.8</v>
+        <v>37.5</v>
       </c>
       <c r="E27" t="n">
-        <v>25.4</v>
+        <v>38.3</v>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>90.8</v>
+        <v>94.5</v>
       </c>
       <c r="H27" t="n">
-        <v>33.9</v>
+        <v>36.1</v>
       </c>
       <c r="I27" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>1.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1546.8</v>
+        <v>1554.9</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>44.6</v>
+        <v>0.2</v>
       </c>
       <c r="E28" t="n">
-        <v>26.6</v>
+        <v>76.3</v>
       </c>
       <c r="F28" t="n">
-        <v>25.9</v>
+        <v>23.5</v>
       </c>
       <c r="G28" t="n">
-        <v>67.3</v>
+        <v>49.3</v>
       </c>
       <c r="H28" t="n">
-        <v>27.5</v>
+        <v>20.1</v>
       </c>
       <c r="I28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1554.9</v>
+        <v>1537.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.09</v>
+        <v>0.65</v>
       </c>
       <c r="R28" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
@@ -2149,22 +2149,22 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F29" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G29" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="H29" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.9</v>
@@ -2194,40 +2194,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>72.3</v>
+        <v>79.3</v>
       </c>
       <c r="F30" t="n">
-        <v>22.8</v>
+        <v>20.7</v>
       </c>
       <c r="G30" t="n">
-        <v>23</v>
+        <v>48.9</v>
       </c>
       <c r="H30" t="n">
-        <v>9.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L30" t="n">
         <v>0.3</v>
@@ -2238,137 +2238,137 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1544.1</v>
+        <v>1564.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
-        <v>79.3</v>
+        <v>52.8</v>
       </c>
       <c r="F31" t="n">
-        <v>20.7</v>
+        <v>16.1</v>
       </c>
       <c r="G31" t="n">
-        <v>49.8</v>
+        <v>73.7</v>
       </c>
       <c r="H31" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
       </c>
       <c r="I31" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L31" t="n">
         <v>0.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1564.9</v>
+        <v>1519.6</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="R31" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>4.9</v>
       </c>
       <c r="E32" t="n">
-        <v>52.9</v>
+        <v>72.3</v>
       </c>
       <c r="F32" t="n">
-        <v>16.1</v>
+        <v>22.8</v>
       </c>
       <c r="G32" t="n">
-        <v>73.09999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="H32" t="n">
-        <v>21.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L32" t="n">
         <v>0.2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1519.6</v>
+        <v>1544.1</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="R32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="33">
@@ -2395,19 +2395,19 @@
         <v>78.2</v>
       </c>
       <c r="G33" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>1.1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
@@ -2434,37 +2434,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>15.7</v>
+        <v>8.5</v>
       </c>
       <c r="E34" t="n">
-        <v>25.5</v>
+        <v>52.5</v>
       </c>
       <c r="F34" t="n">
-        <v>56.7</v>
+        <v>39</v>
       </c>
       <c r="G34" t="n">
-        <v>37.5</v>
+        <v>21.1</v>
       </c>
       <c r="H34" t="n">
-        <v>14.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K34" t="n">
         <v>0.4</v>
@@ -2474,60 +2474,60 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1555</v>
+        <v>1534.2</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="R34" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>39</v>
+        <v>19.2</v>
       </c>
       <c r="G35" t="n">
-        <v>21.2</v>
+        <v>55.8</v>
       </c>
       <c r="H35" t="n">
-        <v>8.199999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J35" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L35" t="n">
         <v>0.1</v>
@@ -2538,56 +2538,56 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1534.2</v>
+        <v>1514.3</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0.55</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="F36" t="n">
-        <v>19.2</v>
+        <v>7.7</v>
       </c>
       <c r="G36" t="n">
-        <v>55.8</v>
+        <v>36.3</v>
       </c>
       <c r="H36" t="n">
-        <v>17.3</v>
+        <v>9.9</v>
       </c>
       <c r="I36" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L36" t="n">
         <v>0.1</v>
@@ -2598,119 +2598,119 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1514.3</v>
+        <v>1516.6</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="R36" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="E37" t="n">
-        <v>24.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>62.4</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>31.8</v>
+        <v>84.8</v>
       </c>
       <c r="H37" t="n">
-        <v>12.1</v>
+        <v>18.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1544.8</v>
+        <v>1507.6</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="R37" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>31.1</v>
       </c>
       <c r="E38" t="n">
-        <v>88</v>
+        <v>58.9</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>85</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>18.6</v>
+        <v>19.7</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2718,116 +2718,116 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1507.6</v>
+        <v>1467.7</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>0.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.36</v>
+        <v>0.98</v>
       </c>
       <c r="R38" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="E39" t="n">
-        <v>75.3</v>
+        <v>24.2</v>
       </c>
       <c r="F39" t="n">
-        <v>7.7</v>
+        <v>56.3</v>
       </c>
       <c r="G39" t="n">
-        <v>36.5</v>
+        <v>23.7</v>
       </c>
       <c r="H39" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1516.6</v>
+        <v>1521.7</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q39" t="n">
         <v>0.85</v>
       </c>
       <c r="R39" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>19.4</v>
+        <v>12.4</v>
       </c>
       <c r="E40" t="n">
-        <v>24.1</v>
+        <v>13.9</v>
       </c>
       <c r="F40" t="n">
-        <v>56.4</v>
+        <v>73.7</v>
       </c>
       <c r="G40" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="H40" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2838,53 +2838,53 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1521.7</v>
+        <v>1519.9</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.85</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>46.2</v>
+        <v>20.7</v>
       </c>
       <c r="F41" t="n">
-        <v>17.1</v>
+        <v>79.3</v>
       </c>
       <c r="G41" t="n">
-        <v>70.3</v>
+        <v>8.5</v>
       </c>
       <c r="H41" t="n">
-        <v>15.9</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2894,54 +2894,54 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1467.7</v>
+        <v>1534.7</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="Q41" t="n">
         <v>1.08</v>
       </c>
       <c r="R41" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>12.4</v>
+        <v>6.3</v>
       </c>
       <c r="E42" t="n">
-        <v>13.9</v>
+        <v>4.5</v>
       </c>
       <c r="F42" t="n">
-        <v>73.7</v>
+        <v>89.2</v>
       </c>
       <c r="G42" t="n">
-        <v>15.8</v>
+        <v>8.9</v>
       </c>
       <c r="H42" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0.1</v>
@@ -2958,50 +2958,50 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1519.9</v>
+        <v>1518</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="R42" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="E43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G43" t="n">
         <v>20.7</v>
       </c>
-      <c r="F43" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="G43" t="n">
-        <v>7.7</v>
-      </c>
       <c r="H43" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0.1</v>
@@ -3018,47 +3018,47 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1534.7</v>
+        <v>1499.2</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="R43" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="F44" t="n">
-        <v>89.2</v>
+        <v>76.5</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="I44" t="n">
         <v>0.4</v>
@@ -3078,53 +3078,53 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1518</v>
+        <v>1544.8</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="R44" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="F45" t="n">
-        <v>78.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>20.7</v>
+        <v>0.6</v>
       </c>
       <c r="H45" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1499.2</v>
+        <v>1523</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="R45" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3169,16 +3169,16 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="F46" t="n">
-        <v>99.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1523</v>
+        <v>1493.5</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.95</v>
+        <v>1.28</v>
       </c>
       <c r="R46" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3229,20 +3229,20 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="F47" t="n">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="G47" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="H47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I47" t="n">
         <v>0.2</v>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
@@ -3258,17 +3258,17 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1493.5</v>
+        <v>1555</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="48">
@@ -3295,13 +3295,13 @@
         <v>80.8</v>
       </c>
       <c r="G48" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="H48" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="Q49" t="n">
         <v>1.4</v>
@@ -3493,7 +3493,7 @@
         <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>92.09999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="4">
@@ -3520,7 +3520,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="5">
@@ -3538,16 +3538,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="E5" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="F5" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
       <c r="G5" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="6">
@@ -3592,10 +3592,10 @@
         <v>25.2</v>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>80.8</v>
       </c>
       <c r="G9" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="10">
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3700,7 +3700,7 @@
         <v>47.9</v>
       </c>
       <c r="D11" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>27.2</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3736,7 +3736,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3808,16 +3808,16 @@
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>67.8</v>
+        <v>67.7</v>
       </c>
       <c r="E15" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="F15" t="n">
         <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>90.8</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="16">
@@ -3838,13 +3838,13 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="F16" t="n">
         <v>16.1</v>
       </c>
       <c r="G16" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="17">
@@ -3871,7 +3871,7 @@
         <v>78.2</v>
       </c>
       <c r="G17" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -3919,13 +3919,13 @@
         <v>82.5</v>
       </c>
       <c r="E19" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="20">
@@ -3952,7 +3952,7 @@
         <v>22.8</v>
       </c>
       <c r="G20" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="21">
@@ -4027,7 +4027,7 @@
         <v>39.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4051,16 +4051,16 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="25">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D26" t="n">
         <v>54.9</v>
@@ -4114,7 +4114,7 @@
         <v>7.4</v>
       </c>
       <c r="G26" t="n">
-        <v>91.2</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -4159,16 +4159,16 @@
         <v>17.3</v>
       </c>
       <c r="D28" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="E28" t="n">
         <v>58.5</v>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -4195,7 +4195,7 @@
         <v>89.2</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="30">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D30" t="n">
         <v>6.2</v>
@@ -4243,13 +4243,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F31" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G31" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="32">
@@ -4276,7 +4276,7 @@
         <v>7.7</v>
       </c>
       <c r="G32" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="33">
@@ -4384,7 +4384,7 @@
         <v>20.7</v>
       </c>
       <c r="G36" t="n">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="37">
@@ -4411,7 +4411,7 @@
         <v>79.3</v>
       </c>
       <c r="G37" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="38">
@@ -4456,7 +4456,7 @@
         <v>0.1</v>
       </c>
       <c r="D39" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="E39" t="n">
         <v>33.7</v>
@@ -4465,7 +4465,7 @@
         <v>0.4</v>
       </c>
       <c r="G39" t="n">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4492,7 +4492,7 @@
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>81.7</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="41">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>29.2</v>
+        <v>46.7</v>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>53.1</v>
       </c>
       <c r="E42" t="n">
-        <v>24.4</v>
+        <v>0.2</v>
       </c>
       <c r="F42" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>79.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52.6</v>
+        <v>53.3</v>
       </c>
       <c r="D43" t="n">
-        <v>26.1</v>
+        <v>46.7</v>
       </c>
       <c r="E43" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -4588,19 +4588,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>30.3</v>
+        <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>33.2</v>
+        <v>76.3</v>
       </c>
       <c r="F44" t="n">
-        <v>21.1</v>
+        <v>23.5</v>
       </c>
       <c r="G44" t="n">
-        <v>69.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="45">
@@ -4615,19 +4615,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="F45" t="n">
-        <v>62.4</v>
+        <v>76.5</v>
       </c>
       <c r="G45" t="n">
-        <v>31.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90.5</v>
+        <v>68.3</v>
       </c>
       <c r="D46" t="n">
-        <v>7.6</v>
+        <v>31.3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.9</v>
+        <v>21.7</v>
       </c>
       <c r="D47" t="n">
-        <v>44.6</v>
+        <v>37.5</v>
       </c>
       <c r="E47" t="n">
-        <v>26.6</v>
+        <v>38.3</v>
       </c>
       <c r="F47" t="n">
-        <v>25.9</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="n">
-        <v>67.3</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="48">
@@ -4692,23 +4692,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>15.7</v>
+        <v>31.1</v>
       </c>
       <c r="E48" t="n">
-        <v>25.5</v>
+        <v>58.9</v>
       </c>
       <c r="F48" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>37.5</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4719,23 +4719,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>46.2</v>
+        <v>2.5</v>
       </c>
       <c r="F49" t="n">
-        <v>17.1</v>
+        <v>97.5</v>
       </c>
       <c r="G49" t="n">
-        <v>70.3</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,16 +4836,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-23T19:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4855,226 +4855,226 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.52</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>79.3</v>
+        <v>30.3</v>
       </c>
       <c r="J2" t="n">
-        <v>14.5</v>
+        <v>25.7</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>125.7</v>
+        <v>21.2</v>
       </c>
       <c r="P2" t="n">
-        <v>6.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-23T22:00:00Z</t>
+          <t>2026-06-24T21:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>1.62</v>
+        <v>0.59</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>68</v>
       </c>
       <c r="J3" t="n">
-        <v>23.5</v>
+        <v>21.1</v>
       </c>
       <c r="K3" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.1</v>
+        <v>94.8</v>
       </c>
       <c r="P3" t="n">
-        <v>39.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-23T16:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="H4" t="n">
-        <v>0.98</v>
+        <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>53.4</v>
+        <v>25.4</v>
       </c>
       <c r="J4" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="K4" t="n">
-        <v>22.3</v>
+        <v>48.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>20.2</v>
+        <v>0.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00Z</t>
+          <t>2026-06-24T18:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>39.4</v>
+        <v>55.8</v>
       </c>
       <c r="J5" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
       <c r="K5" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -5083,231 +5083,231 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
-        <v>31.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
         <v>1.47</v>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
       <c r="J6" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>54.3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>21.2</v>
+        <v>39.6</v>
       </c>
       <c r="P6" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>0.78</v>
       </c>
       <c r="H7" t="n">
-        <v>0.58</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>67.90000000000001</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>21.1</v>
+        <v>30.1</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>45.9</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>94.8</v>
+        <v>28.6</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="I8" t="n">
-        <v>25.4</v>
+        <v>15.9</v>
       </c>
       <c r="J8" t="n">
-        <v>25.9</v>
+        <v>20.7</v>
       </c>
       <c r="K8" t="n">
-        <v>48.7</v>
+        <v>63.4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>36.2</v>
       </c>
       <c r="P8" t="n">
-        <v>48.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5317,195 +5317,195 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>55.8</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>25.2</v>
+        <v>27.8</v>
       </c>
       <c r="K9" t="n">
-        <v>19.1</v>
+        <v>50.2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>33.1</v>
       </c>
       <c r="P9" t="n">
-        <v>19.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>19.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>26.6</v>
+        <v>15.9</v>
       </c>
       <c r="K10" t="n">
-        <v>54.2</v>
+        <v>11.9</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>39.6</v>
+        <v>68.2</v>
       </c>
       <c r="P10" t="n">
-        <v>19.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>30.1</v>
+        <v>10.8</v>
       </c>
       <c r="K11" t="n">
-        <v>45.9</v>
+        <v>83.8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>28.6</v>
+        <v>76</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5515,63 +5515,63 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>15.9</v>
+        <v>39.9</v>
       </c>
       <c r="J12" t="n">
-        <v>20.7</v>
+        <v>23.5</v>
       </c>
       <c r="K12" t="n">
-        <v>63.4</v>
+        <v>36.5</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>36.2</v>
+        <v>55.5</v>
       </c>
       <c r="P12" t="n">
-        <v>15.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5581,28 +5581,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H13" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="K13" t="n">
-        <v>50.2</v>
+        <v>39.9</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -5611,33 +5611,33 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>33.1</v>
+        <v>27.2</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5647,129 +5647,129 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2.59</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
+        <v>1.69</v>
       </c>
       <c r="I14" t="n">
-        <v>72.09999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>22.3</v>
       </c>
       <c r="K14" t="n">
-        <v>11.9</v>
+        <v>36.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>68.2</v>
+        <v>12.6</v>
       </c>
       <c r="P14" t="n">
-        <v>11.9</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.67</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>54.9</v>
       </c>
       <c r="J15" t="n">
-        <v>10.9</v>
+        <v>24.4</v>
       </c>
       <c r="K15" t="n">
-        <v>83.8</v>
+        <v>20.7</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>76</v>
+        <v>30.2</v>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5779,28 +5779,28 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="I16" t="n">
-        <v>39.9</v>
+        <v>34</v>
       </c>
       <c r="J16" t="n">
-        <v>23.6</v>
+        <v>30.5</v>
       </c>
       <c r="K16" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -5809,99 +5809,99 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>55.5</v>
+        <v>14.1</v>
       </c>
       <c r="P16" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="H17" t="n">
-        <v>1.17</v>
+        <v>2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
       <c r="J17" t="n">
-        <v>29.3</v>
+        <v>15.2</v>
       </c>
       <c r="K17" t="n">
-        <v>39.9</v>
+        <v>75.7</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>27.2</v>
+        <v>37.6</v>
       </c>
       <c r="P17" t="n">
-        <v>30.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5911,129 +5911,129 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="H18" t="n">
-        <v>1.69</v>
+        <v>0.78</v>
       </c>
       <c r="I18" t="n">
-        <v>40.8</v>
+        <v>51.9</v>
       </c>
       <c r="J18" t="n">
-        <v>22.3</v>
+        <v>27.3</v>
       </c>
       <c r="K18" t="n">
-        <v>36.9</v>
+        <v>20.8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>12.6</v>
+        <v>4.7</v>
       </c>
       <c r="P18" t="n">
-        <v>36.9</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.66</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="n">
-        <v>0.92</v>
+        <v>1.83</v>
       </c>
       <c r="I19" t="n">
-        <v>54.9</v>
+        <v>11.5</v>
       </c>
       <c r="J19" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="K19" t="n">
-        <v>20.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>30.2</v>
+        <v>87.2</v>
       </c>
       <c r="P19" t="n">
-        <v>20.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6043,28 +6043,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H20" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="I20" t="n">
-        <v>33.9</v>
+        <v>14.5</v>
       </c>
       <c r="J20" t="n">
-        <v>30.6</v>
+        <v>22.1</v>
       </c>
       <c r="K20" t="n">
-        <v>35.5</v>
+        <v>63.4</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -6073,99 +6073,99 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P20" t="n">
-        <v>35.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.77</v>
+        <v>1.69</v>
       </c>
       <c r="H21" t="n">
-        <v>2.53</v>
+        <v>0.76</v>
       </c>
       <c r="I21" t="n">
-        <v>9.1</v>
+        <v>59.5</v>
       </c>
       <c r="J21" t="n">
-        <v>15.2</v>
+        <v>23.9</v>
       </c>
       <c r="K21" t="n">
-        <v>75.7</v>
+        <v>16.7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P21" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6175,129 +6175,129 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0.78</v>
+        <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>51.8</v>
+        <v>34.3</v>
       </c>
       <c r="J22" t="n">
-        <v>27.4</v>
+        <v>26.9</v>
       </c>
       <c r="K22" t="n">
-        <v>20.8</v>
+        <v>38.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="P22" t="n">
-        <v>51.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H23" t="n">
-        <v>1.83</v>
+        <v>2.97</v>
       </c>
       <c r="I23" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
-        <v>21.5</v>
+        <v>9.9</v>
       </c>
       <c r="K23" t="n">
-        <v>67</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P23" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6307,63 +6307,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="H24" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="I24" t="n">
-        <v>15.3</v>
+        <v>28.8</v>
       </c>
       <c r="J24" t="n">
-        <v>20.4</v>
+        <v>24.5</v>
       </c>
       <c r="K24" t="n">
-        <v>64.2</v>
+        <v>46.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>38.4</v>
+        <v>23.3</v>
       </c>
       <c r="P24" t="n">
-        <v>15.3</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>60.7</v>
+        <v>46.1</v>
       </c>
       <c r="J25" t="n">
-        <v>21.8</v>
+        <v>30.2</v>
       </c>
       <c r="K25" t="n">
-        <v>17.5</v>
+        <v>23.8</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -6403,283 +6403,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P25" t="n">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>69</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>27</v>
-      </c>
-      <c r="K26" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>70</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K27" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P27" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>71</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I28" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>72</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I29" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>41.1</v>
+        <v>46.1</v>
       </c>
     </row>
   </sheetData>
@@ -6800,17 +6536,17 @@
         <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2164</v>
+        <v>1.2174</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7469</v>
+        <v>0.7479</v>
       </c>
       <c r="M2" t="n">
         <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6582,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5212</v>
+        <v>1.5223</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -6856,7 +6592,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6892,17 +6628,17 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9683</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7879</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.5422</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6938,17 +6674,17 @@
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3184</v>
+        <v>1.3194</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7271</v>
+        <v>0.728</v>
       </c>
       <c r="M5" t="n">
         <v>0.7222</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6984,17 +6720,17 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5176</v>
+        <v>1.5188</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6834</v>
+        <v>0.6844</v>
       </c>
       <c r="M6" t="n">
         <v>0.6408</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7030,17 +6766,17 @@
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9705</v>
+        <v>0.9715</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0003</v>
+        <v>1.0013</v>
       </c>
       <c r="M7" t="n">
         <v>0.384</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7076,17 +6812,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4363</v>
+        <v>1.4374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>0.6761</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7122,17 +6858,17 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2254</v>
+        <v>1.2265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5695</v>
+        <v>0.5704</v>
       </c>
       <c r="M9" t="n">
         <v>0.6276</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7168,17 +6904,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0606</v>
+        <v>1.0615</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8112</v>
+        <v>0.8121</v>
       </c>
       <c r="M10" t="n">
         <v>0.4729</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7208,23 +6944,23 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.355</v>
+        <v>1.3012</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8556</v>
+        <v>0.7846</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6784</v>
+        <v>0.7178</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7260,17 +6996,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2335</v>
+        <v>1.1934</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0867</v>
+        <v>1.0016</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5662</v>
+        <v>0.6193</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7306,17 +7042,17 @@
         <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0937</v>
+        <v>1.0948</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2949</v>
+        <v>1.296</v>
       </c>
       <c r="M13" t="n">
         <v>0.3885</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7352,17 +7088,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1512</v>
+        <v>1.1522</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7116,7 @@
         <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
         <v>11</v>
@@ -7389,26 +7125,26 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8945</v>
+        <v>0.8198</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6387</v>
+        <v>0.646</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5734</v>
+        <v>0.4986</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7444,17 +7180,17 @@
         <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8046</v>
+        <v>0.8055</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5782</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0.5105</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7490,17 +7226,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0396</v>
+        <v>1.0407</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6852</v>
+        <v>0.6861</v>
       </c>
       <c r="M17" t="n">
         <v>0.6263</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7521,32 +7257,32 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J18" t="n">
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4191</v>
+        <v>1.2998</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6432</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8106</v>
+        <v>0.7464</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7582,17 +7318,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5266</v>
+        <v>1.5277</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7938</v>
       </c>
       <c r="M19" t="n">
         <v>0.8192</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7631,14 +7367,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8065</v>
+        <v>0.8075</v>
       </c>
       <c r="M20" t="n">
         <v>0.8933</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7656,13 +7392,13 @@
         <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>9</v>
@@ -7674,17 +7410,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7558</v>
+        <v>0.6839</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0822</v>
+        <v>0.9789</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2864</v>
+        <v>0.2939</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7720,17 +7456,17 @@
         <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>0.952</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9507</v>
+        <v>0.9517</v>
       </c>
       <c r="M22" t="n">
         <v>0.3494</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7766,17 +7502,17 @@
         <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1756</v>
+        <v>1.1767</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7812,17 +7548,17 @@
         <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7523</v>
+        <v>0.7532</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0772</v>
+        <v>1.0783</v>
       </c>
       <c r="M24" t="n">
         <v>0.4447</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7858,17 +7594,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1244</v>
+        <v>1.1255</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6825</v>
+        <v>0.6834</v>
       </c>
       <c r="M25" t="n">
         <v>0.6943</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7904,17 +7640,17 @@
         <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3105</v>
+        <v>1.3116</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6257</v>
+        <v>0.6266</v>
       </c>
       <c r="M26" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7950,17 +7686,17 @@
         <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8645</v>
+        <v>0.8655</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2812</v>
+        <v>1.2823</v>
       </c>
       <c r="M27" t="n">
         <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7732,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0769</v>
+        <v>1.0781</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -8006,7 +7742,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8042,7 +7778,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2961</v>
+        <v>1.2974</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -8052,7 +7788,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8088,17 +7824,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4947</v>
+        <v>1.4958</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8278</v>
+        <v>0.8287</v>
       </c>
       <c r="M30" t="n">
         <v>0.6559</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8134,17 +7870,17 @@
         <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2157</v>
+        <v>1.2168</v>
       </c>
       <c r="M31" t="n">
         <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8183,14 +7919,14 @@
         <v>1.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8249</v>
+        <v>0.8259</v>
       </c>
       <c r="M32" t="n">
         <v>0.7625999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8211,32 +7947,32 @@
         <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1119</v>
+        <v>1.0259</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0111</v>
+        <v>1.0045</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5132</v>
+        <v>0.448</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8272,17 +8008,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9986</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9066</v>
+        <v>0.9076</v>
       </c>
       <c r="M34" t="n">
         <v>0.5606</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8312,23 +8048,23 @@
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3068</v>
+        <v>1.4989</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7851</v>
+        <v>0.7199</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7025</v>
+        <v>0.7388</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8364,17 +8100,17 @@
         <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6887</v>
+        <v>0.6896</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2631</v>
+        <v>1.2641</v>
       </c>
       <c r="M36" t="n">
         <v>0.2428</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8410,17 +8146,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7703</v>
+        <v>0.7713</v>
       </c>
       <c r="L37" t="n">
-        <v>1.0478</v>
+        <v>1.0489</v>
       </c>
       <c r="M37" t="n">
         <v>0.3585</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8456,17 +8192,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1351</v>
+        <v>1.1362</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7562</v>
+        <v>0.7571</v>
       </c>
       <c r="M38" t="n">
         <v>0.5795</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8502,17 +8238,17 @@
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1745</v>
+        <v>1.1756</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9947</v>
+        <v>0.9958</v>
       </c>
       <c r="M39" t="n">
         <v>0.4583</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8548,17 +8284,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8087</v>
+        <v>0.8097</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8516</v>
+        <v>0.8526</v>
       </c>
       <c r="M40" t="n">
         <v>0.4009</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8594,17 +8330,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0428</v>
+        <v>1.0439</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7911</v>
+        <v>0.7921</v>
       </c>
       <c r="M41" t="n">
         <v>0.6054</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8640,17 +8376,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4562</v>
+        <v>1.4573</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6208</v>
+        <v>0.6217</v>
       </c>
       <c r="M42" t="n">
         <v>0.7209</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8686,17 +8422,17 @@
         <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3243</v>
+        <v>1.3254</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3559</v>
+        <v>1.3571</v>
       </c>
       <c r="M43" t="n">
         <v>0.4537</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8732,17 +8468,17 @@
         <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4103</v>
+        <v>1.4115</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8356</v>
+        <v>0.8365</v>
       </c>
       <c r="M44" t="n">
         <v>0.6069</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8778,17 +8514,17 @@
         <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7149</v>
+        <v>0.7158</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3974</v>
+        <v>1.3986</v>
       </c>
       <c r="M45" t="n">
         <v>0.2767</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8824,17 +8560,17 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1393</v>
+        <v>1.1404</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8512</v>
+        <v>0.8522</v>
       </c>
       <c r="M46" t="n">
         <v>0.63</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8870,17 +8606,17 @@
         <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3137</v>
+        <v>1.3149</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0607</v>
+        <v>1.0617</v>
       </c>
       <c r="M47" t="n">
         <v>0.6099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8916,17 +8652,17 @@
         <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8435</v>
+        <v>0.8445</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8527</v>
+        <v>0.8536</v>
       </c>
       <c r="M48" t="n">
         <v>0.4187</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8950,29 +8686,29 @@
         <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>1.0105</v>
+        <v>0.9424</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9372</v>
+        <v>1.1503</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4572</v>
+        <v>0.4067</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00:00+00:00</t>
+          <t>2026-06-24T01:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,19 +538,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="I2" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="J2" t="n">
-        <v>34.7</v>
+        <v>36.3</v>
       </c>
       <c r="K2" t="n">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
       <c r="L2" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -574,22 +574,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87.8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -598,97 +598,97 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="I3" t="n">
-        <v>38.2</v>
+        <v>42.7</v>
       </c>
       <c r="J3" t="n">
-        <v>25.3</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="L3" t="n">
-        <v>8.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1603.8</v>
+        <v>1617.8</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42.4</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>53.4</v>
+        <v>6.1</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>61.1</v>
+        <v>60.3</v>
       </c>
       <c r="I4" t="n">
-        <v>39.2</v>
+        <v>37.6</v>
       </c>
       <c r="J4" t="n">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="K4" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="L4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1617.8</v>
+        <v>1603.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="5">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -718,19 +718,19 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>72.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="J5" t="n">
-        <v>23.2</v>
+        <v>21.9</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="D6" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -778,19 +778,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>63.9</v>
+        <v>63.1</v>
       </c>
       <c r="I6" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="J6" t="n">
         <v>20.3</v>
       </c>
       <c r="K6" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="D7" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -838,19 +838,19 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>37.3</v>
+        <v>39.2</v>
       </c>
       <c r="J7" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="K7" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -898,23 +898,23 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>67.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.7</v>
+        <v>41.9</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="K8" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="D9" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>64.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="J9" t="n">
         <v>18.5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1006,31 +1006,31 @@
         <v>28.4</v>
       </c>
       <c r="D10" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
       <c r="E10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>91.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="H10" t="n">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="I10" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="J10" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="K10" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1054,19 +1054,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.8</v>
+        <v>59.2</v>
       </c>
       <c r="D11" t="n">
-        <v>25.2</v>
+        <v>40.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="I11" t="n">
-        <v>38.6</v>
+        <v>33.6</v>
       </c>
       <c r="J11" t="n">
-        <v>18.6</v>
+        <v>16.7</v>
       </c>
       <c r="K11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1544.6</v>
+        <v>1569.9</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="R11" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="12">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="D12" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1138,19 +1138,19 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>52.3</v>
+        <v>49.8</v>
       </c>
       <c r="I12" t="n">
-        <v>30.2</v>
+        <v>28.6</v>
       </c>
       <c r="J12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>63.4</v>
+        <v>50.4</v>
       </c>
       <c r="I13" t="n">
-        <v>32.3</v>
+        <v>25.3</v>
       </c>
       <c r="J13" t="n">
-        <v>16.9</v>
+        <v>13.1</v>
       </c>
       <c r="K13" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1218,38 +1218,38 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1569.9</v>
+        <v>1542.8</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39.2</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1258,94 +1258,94 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>46.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
       <c r="J14" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="K14" t="n">
         <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1571</v>
+        <v>1544.6</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="R14" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1</v>
+        <v>53.4</v>
       </c>
       <c r="D15" t="n">
-        <v>65.7</v>
+        <v>46.6</v>
       </c>
       <c r="E15" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>22.9</v>
+        <v>30.4</v>
       </c>
       <c r="J15" t="n">
-        <v>12.3</v>
+        <v>13.8</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1560</v>
+        <v>1541.7</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="R15" t="n">
         <v>0.72</v>
@@ -1354,58 +1354,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53.3</v>
+        <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>46.7</v>
+        <v>65.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>33.9</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>65.2</v>
+        <v>43.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28.2</v>
+        <v>22.8</v>
       </c>
       <c r="J16" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1541.7</v>
+        <v>1560</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="R16" t="n">
         <v>0.72</v>
@@ -1414,22 +1414,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.2</v>
+        <v>61.1</v>
       </c>
       <c r="D17" t="n">
-        <v>72.90000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1438,136 +1438,136 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>57.8</v>
+        <v>41.2</v>
       </c>
       <c r="I17" t="n">
-        <v>25.6</v>
+        <v>22.3</v>
       </c>
       <c r="J17" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1545.2</v>
+        <v>1571</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="R17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>34.1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>64.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>38.2</v>
+        <v>55.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20.4</v>
+        <v>29.1</v>
       </c>
       <c r="J18" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1573.4</v>
+        <v>1545.2</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>47.9</v>
+        <v>54.5</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>45.2</v>
+        <v>54.2</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>11.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.9</v>
@@ -1578,77 +1578,77 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1542.8</v>
+        <v>1560.9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>34.4</v>
       </c>
       <c r="E20" t="n">
-        <v>27.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>51.3</v>
+        <v>36.4</v>
       </c>
       <c r="I20" t="n">
-        <v>25.7</v>
+        <v>18.7</v>
       </c>
       <c r="J20" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1560.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="21">
@@ -1663,31 +1663,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="H21" t="n">
-        <v>40.6</v>
+        <v>40.1</v>
       </c>
       <c r="I21" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="J21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.6</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q21" t="n">
         <v>0.68</v>
@@ -1723,38 +1723,38 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="D22" t="n">
         <v>20.8</v>
       </c>
       <c r="E22" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="F22" t="n">
         <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>69.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="H22" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="I22" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="J22" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -1798,16 +1798,16 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>61.6</v>
+        <v>57.7</v>
       </c>
       <c r="I23" t="n">
-        <v>27.3</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>1.1</v>
@@ -1834,43 +1834,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.699999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="D24" t="n">
-        <v>21.7</v>
+        <v>37.4</v>
       </c>
       <c r="E24" t="n">
-        <v>67.7</v>
+        <v>38.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>90.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="H24" t="n">
-        <v>33.1</v>
+        <v>36.1</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="J24" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1878,17 +1878,17 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1521.6</v>
+        <v>1554.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="25">
@@ -1903,38 +1903,38 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3</v>
+        <v>80.8</v>
       </c>
       <c r="F25" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J25" t="n">
         <v>4.6</v>
       </c>
-      <c r="G25" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.4</v>
-      </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -1942,13 +1942,13 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="Q25" t="n">
         <v>0.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="26">
@@ -1966,28 +1966,28 @@
         <v>1.2</v>
       </c>
       <c r="D26" t="n">
-        <v>67.7</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
         <v>25.3</v>
       </c>
       <c r="F26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G26" t="n">
-        <v>90.5</v>
+        <v>91</v>
       </c>
       <c r="H26" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="I26" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
         <v>0.5</v>
@@ -2014,43 +2014,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>38.3</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>36.1</v>
+        <v>34.3</v>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2058,17 +2058,17 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1554.9</v>
+        <v>1514.3</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="28">
@@ -2089,28 +2089,28 @@
         <v>0.2</v>
       </c>
       <c r="E28" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="G28" t="n">
-        <v>49.3</v>
+        <v>46.2</v>
       </c>
       <c r="H28" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="I28" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2134,181 +2134,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>67.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>15.7</v>
+        <v>79.5</v>
       </c>
       <c r="F29" t="n">
-        <v>13.7</v>
+        <v>20.5</v>
       </c>
       <c r="G29" t="n">
-        <v>79.5</v>
+        <v>49.8</v>
       </c>
       <c r="H29" t="n">
-        <v>19.4</v>
+        <v>17.9</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L29" t="n">
         <v>0.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1494.5</v>
+        <v>1564.9</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="R29" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>67.2</v>
       </c>
       <c r="E30" t="n">
-        <v>79.3</v>
+        <v>15.6</v>
       </c>
       <c r="F30" t="n">
-        <v>20.7</v>
+        <v>13.9</v>
       </c>
       <c r="G30" t="n">
-        <v>48.9</v>
+        <v>79</v>
       </c>
       <c r="H30" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="I30" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.8</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1564.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>80.8</v>
       </c>
       <c r="E31" t="n">
-        <v>52.8</v>
+        <v>19.2</v>
       </c>
       <c r="F31" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>21.6</v>
+        <v>32.9</v>
       </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
         <v>0.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1519.6</v>
+        <v>1521.7</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G32" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="H32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K32" t="n">
         <v>0.5</v>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="F33" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="G33" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="H33" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I33" t="n">
         <v>2.7</v>
       </c>
       <c r="J33" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0.4</v>
@@ -2434,97 +2434,97 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D34" t="n">
-        <v>8.5</v>
+        <v>30.7</v>
       </c>
       <c r="E34" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="F34" t="n">
-        <v>39</v>
+        <v>16.1</v>
       </c>
       <c r="G34" t="n">
-        <v>21.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>8.199999999999999</v>
+        <v>20.7</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="J34" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
         <v>0.1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1534.2</v>
+        <v>1519.6</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="R34" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>55.8</v>
+        <v>36.4</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>10.4</v>
       </c>
       <c r="I35" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
         <v>0.3</v>
@@ -2538,17 +2538,17 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1514.3</v>
+        <v>1521.6</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="R35" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="36">
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>75.3</v>
@@ -2575,16 +2575,16 @@
         <v>7.7</v>
       </c>
       <c r="G36" t="n">
-        <v>36.3</v>
+        <v>33.1</v>
       </c>
       <c r="H36" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K36" t="n">
         <v>0.2</v>
@@ -2614,100 +2614,100 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>10.1</v>
+        <v>19.2</v>
       </c>
       <c r="E37" t="n">
-        <v>87.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="G37" t="n">
-        <v>84.8</v>
+        <v>19.1</v>
       </c>
       <c r="H37" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K37" t="n">
         <v>0.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1507.6</v>
+        <v>1534.2</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.36</v>
+        <v>0.87</v>
       </c>
       <c r="R37" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="D38" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="E38" t="n">
-        <v>58.9</v>
+        <v>88</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>99.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>19.7</v>
+        <v>17.8</v>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2718,53 +2718,53 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1467.7</v>
+        <v>1507.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.68</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.98</v>
+        <v>1.36</v>
       </c>
       <c r="R38" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="D39" t="n">
-        <v>19.5</v>
+        <v>31.1</v>
       </c>
       <c r="E39" t="n">
-        <v>24.2</v>
+        <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>56.3</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>23.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>7.2</v>
+        <v>19.3</v>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K39" t="n">
         <v>0.1</v>
@@ -2774,21 +2774,21 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1521.7</v>
+        <v>1467.7</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="R39" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="40">
@@ -2806,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="n">
         <v>13.9</v>
       </c>
       <c r="F40" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="H40" t="n">
         <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0.1</v>
@@ -2845,7 +2845,7 @@
         <v>1.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R40" t="n">
         <v>0.39</v>
@@ -2854,31 +2854,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="E41" t="n">
-        <v>20.7</v>
+        <v>4.4</v>
       </c>
       <c r="F41" t="n">
-        <v>79.3</v>
+        <v>89</v>
       </c>
       <c r="G41" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I41" t="n">
         <v>0.5</v>
@@ -2898,50 +2898,50 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1534.7</v>
+        <v>1518</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="R41" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>6.3</v>
+        <v>18.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="F42" t="n">
-        <v>89.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>8.9</v>
+        <v>20.8</v>
       </c>
       <c r="H42" t="n">
         <v>2.5</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0.1</v>
@@ -2958,53 +2958,53 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1518</v>
+        <v>1499.2</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="R42" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>78.5</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1499.2</v>
+        <v>1523</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3049,22 +3049,22 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="F44" t="n">
-        <v>76.5</v>
+        <v>79.5</v>
       </c>
       <c r="G44" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="H44" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3078,28 +3078,28 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1544.8</v>
+        <v>1534.7</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="R44" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="F45" t="n">
-        <v>99.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1523</v>
+        <v>1493.5</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.95</v>
+        <v>1.28</v>
       </c>
       <c r="R45" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3169,20 +3169,20 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="F46" t="n">
-        <v>98.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.2</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1493.5</v>
+        <v>1555</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3229,19 +3229,19 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3258,28 +3258,28 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="R47" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3289,19 +3289,19 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3318,28 +3318,28 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1484.3</v>
+        <v>1495</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="R48" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>76.3</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3378,17 +3378,17 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1495</v>
+        <v>1544.8</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="R49" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>23.3</v>
+        <v>80.8</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
+        <v>19.2</v>
       </c>
       <c r="G3" t="n">
-        <v>91.8</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="4">
@@ -3504,23 +3504,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8.5</v>
+        <v>80.8</v>
       </c>
       <c r="E4" t="n">
-        <v>52.5</v>
+        <v>19.2</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>21.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -3531,23 +3531,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>56.3</v>
+        <v>80.8</v>
       </c>
       <c r="G5" t="n">
-        <v>23.7</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="6">
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>25.2</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25.2</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>72.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3619,16 +3619,16 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>55.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -3649,13 +3649,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>53.4</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.9</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>67.7</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>90.59999999999999</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="13">
@@ -3757,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3808,16 +3808,16 @@
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>67.7</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>25.3</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>90.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -3828,23 +3828,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>52.8</v>
+        <v>21.7</v>
       </c>
       <c r="F16" t="n">
-        <v>16.1</v>
+        <v>78.3</v>
       </c>
       <c r="G16" t="n">
-        <v>73.7</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="17">
@@ -3855,23 +3855,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="E17" t="n">
-        <v>21.8</v>
+        <v>53.1</v>
       </c>
       <c r="F17" t="n">
-        <v>78.2</v>
+        <v>16.1</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D19" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="20">
@@ -3943,16 +3943,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G20" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -3970,16 +3970,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="n">
         <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="22">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="D22" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="E22" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60.6</v>
+        <v>61.1</v>
       </c>
       <c r="D23" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="E23" t="n">
         <v>0.2</v>
@@ -4048,19 +4048,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="E24" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>84.8</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -4105,16 +4105,16 @@
         <v>28.4</v>
       </c>
       <c r="D26" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
       <c r="E26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G26" t="n">
-        <v>91.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="27">
@@ -4129,13 +4129,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="D28" t="n">
         <v>20.8</v>
       </c>
       <c r="E28" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="F28" t="n">
         <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>69.40000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -4186,16 +4186,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="E29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F29" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="G29" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="E30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D31" t="n">
-        <v>67.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="E31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="F31" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="G31" t="n">
-        <v>79.5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>75.3</v>
@@ -4276,7 +4276,7 @@
         <v>7.7</v>
       </c>
       <c r="G32" t="n">
-        <v>36.3</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="33">
@@ -4294,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="E33" t="n">
         <v>3.1</v>
       </c>
       <c r="F33" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="34">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="D34" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="D35" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="F36" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="G36" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="37">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="F37" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="38">
@@ -4456,16 +4456,16 @@
         <v>0.1</v>
       </c>
       <c r="D39" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="E39" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4483,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="E40" t="n">
-        <v>64.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G40" t="n">
-        <v>82.5</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F41" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="42">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="D42" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="E42" t="n">
         <v>0.2</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="D43" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4594,13 +4594,13 @@
         <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="G44" t="n">
-        <v>49.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="45">
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="F45" t="n">
-        <v>76.5</v>
+        <v>76.3</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="46">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="D46" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E46" t="n">
         <v>0.3</v>
@@ -4669,16 +4669,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D47" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="E47" t="n">
         <v>38.3</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G47" t="n">
         <v>94.5</v>
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="D48" t="n">
         <v>31.1</v>
       </c>
       <c r="E48" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -4729,13 +4729,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F49" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,82 +4836,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T00:00:00Z</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
       <c r="J2" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>54.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>21.2</v>
+        <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>30.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-24T21:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,129 +4921,129 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>63.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>94.8</v>
+        <v>36.2</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T19:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.01</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>25.4</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="K4" t="n">
-        <v>48.7</v>
+        <v>50.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.6</v>
+        <v>33.1</v>
       </c>
       <c r="P4" t="n">
-        <v>48.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-24T18:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5053,195 +5053,195 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.59</v>
+        <v>2.59</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>55.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>25.1</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>19.1</v>
+        <v>12</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>68.2</v>
       </c>
       <c r="P5" t="n">
-        <v>19.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-25T22:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>19.2</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
-        <v>26.6</v>
+        <v>10.9</v>
       </c>
       <c r="K6" t="n">
-        <v>54.3</v>
+        <v>83.7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>39.6</v>
+        <v>76</v>
       </c>
       <c r="P6" t="n">
-        <v>19.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.78</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>39.9</v>
       </c>
       <c r="J7" t="n">
-        <v>30.1</v>
+        <v>23.6</v>
       </c>
       <c r="K7" t="n">
-        <v>45.9</v>
+        <v>36.5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>28.6</v>
+        <v>55.5</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T01:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5251,63 +5251,63 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H8" t="n">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>15.9</v>
+        <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>20.7</v>
+        <v>29.3</v>
       </c>
       <c r="K8" t="n">
-        <v>63.4</v>
+        <v>39.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>36.2</v>
+        <v>27.2</v>
       </c>
       <c r="P8" t="n">
-        <v>15.9</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5317,129 +5317,129 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>1.79</v>
       </c>
       <c r="H9" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>40.8</v>
       </c>
       <c r="J9" t="n">
-        <v>27.8</v>
+        <v>22.3</v>
       </c>
       <c r="K9" t="n">
-        <v>50.2</v>
+        <v>36.8</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>33.1</v>
+        <v>12.6</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="I10" t="n">
-        <v>72.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="J10" t="n">
-        <v>15.9</v>
+        <v>24.4</v>
       </c>
       <c r="K10" t="n">
-        <v>11.9</v>
+        <v>20.7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>68.2</v>
+        <v>30.2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.9</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5449,129 +5449,129 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>10.8</v>
+        <v>30.6</v>
       </c>
       <c r="K11" t="n">
-        <v>83.8</v>
+        <v>35.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>76</v>
+        <v>14.1</v>
       </c>
       <c r="P11" t="n">
-        <v>5.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>0.77</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>2.53</v>
       </c>
       <c r="I12" t="n">
-        <v>39.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>23.5</v>
+        <v>15.2</v>
       </c>
       <c r="K12" t="n">
-        <v>36.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>55.5</v>
+        <v>37.6</v>
       </c>
       <c r="P12" t="n">
-        <v>36.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5581,195 +5581,195 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.99</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>1.17</v>
+        <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>30.8</v>
+        <v>51.8</v>
       </c>
       <c r="J13" t="n">
-        <v>29.3</v>
+        <v>27.4</v>
       </c>
       <c r="K13" t="n">
-        <v>39.9</v>
+        <v>20.8</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>27.2</v>
+        <v>4.7</v>
       </c>
       <c r="P13" t="n">
-        <v>30.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.79</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>11.5</v>
       </c>
       <c r="J14" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="K14" t="n">
-        <v>36.9</v>
+        <v>67</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>12.6</v>
+        <v>87.2</v>
       </c>
       <c r="P14" t="n">
-        <v>36.9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.66</v>
+        <v>0.74</v>
       </c>
       <c r="H15" t="n">
-        <v>0.92</v>
+        <v>1.83</v>
       </c>
       <c r="I15" t="n">
-        <v>54.9</v>
+        <v>14.6</v>
       </c>
       <c r="J15" t="n">
-        <v>24.4</v>
+        <v>22.1</v>
       </c>
       <c r="K15" t="n">
-        <v>20.7</v>
+        <v>63.3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>30.2</v>
+        <v>38.4</v>
       </c>
       <c r="P15" t="n">
-        <v>20.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5779,129 +5779,129 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="H16" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>34</v>
+        <v>59.4</v>
       </c>
       <c r="J16" t="n">
-        <v>30.5</v>
+        <v>23.9</v>
       </c>
       <c r="K16" t="n">
-        <v>35.5</v>
+        <v>16.7</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>14.1</v>
+        <v>87.2</v>
       </c>
       <c r="P16" t="n">
-        <v>35.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.77</v>
+        <v>1.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>9.1</v>
+        <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>15.2</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>75.7</v>
+        <v>38.8</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>37.6</v>
+        <v>13.4</v>
       </c>
       <c r="P17" t="n">
-        <v>9.1</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5911,129 +5911,129 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.41</v>
+        <v>0.52</v>
       </c>
       <c r="H18" t="n">
-        <v>0.78</v>
+        <v>2.96</v>
       </c>
       <c r="I18" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>27.3</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>20.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>83.7</v>
       </c>
       <c r="P18" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="I19" t="n">
-        <v>11.5</v>
+        <v>28.8</v>
       </c>
       <c r="J19" t="n">
-        <v>21.4</v>
+        <v>24.5</v>
       </c>
       <c r="K19" t="n">
-        <v>67.09999999999999</v>
+        <v>46.6</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>87.2</v>
+        <v>23.3</v>
       </c>
       <c r="P19" t="n">
-        <v>11.5</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6043,379 +6043,49 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83</v>
+        <v>0.77</v>
       </c>
       <c r="I20" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="J20" t="n">
-        <v>22.1</v>
+        <v>30.2</v>
       </c>
       <c r="K20" t="n">
-        <v>63.4</v>
+        <v>23.8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>38.4</v>
+        <v>6.9</v>
       </c>
       <c r="P20" t="n">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>68</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-27T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I21" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>69</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>70</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>71</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I24" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>28.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>72</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I25" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -6536,17 +6206,17 @@
         <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2174</v>
+        <v>1.2162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7479</v>
+        <v>0.7478</v>
       </c>
       <c r="M2" t="n">
         <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6252,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5223</v>
+        <v>1.5203</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -6592,7 +6262,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6298,17 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7886</v>
       </c>
       <c r="M4" t="n">
         <v>0.5422</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3194</v>
+        <v>1.3179</v>
       </c>
       <c r="L5" t="n">
         <v>0.728</v>
@@ -6684,7 +6354,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6390,7 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5188</v>
+        <v>1.5168</v>
       </c>
       <c r="L6" t="n">
         <v>0.6844</v>
@@ -6730,7 +6400,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6751,32 +6421,32 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
+        <v>31</v>
+      </c>
+      <c r="J7" t="n">
         <v>29</v>
       </c>
-      <c r="J7" t="n">
-        <v>30</v>
-      </c>
       <c r="K7" t="n">
-        <v>0.9715</v>
+        <v>1.0651</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0013</v>
+        <v>0.9754</v>
       </c>
       <c r="M7" t="n">
-        <v>0.384</v>
+        <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6806,23 +6476,23 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4374</v>
+        <v>1.4915</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7536</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6761</v>
+        <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6513,32 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2265</v>
+        <v>1.1848</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5704</v>
+        <v>0.6333</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6276</v>
+        <v>0.5536</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6574,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0615</v>
+        <v>1.0607</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8121</v>
+        <v>0.8119</v>
       </c>
       <c r="M10" t="n">
         <v>0.4729</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6620,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3012</v>
+        <v>1.2997</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7846</v>
+        <v>0.7844</v>
       </c>
       <c r="M11" t="n">
         <v>0.7178</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6666,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1934</v>
+        <v>1.1922</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0016</v>
+        <v>1.0008</v>
       </c>
       <c r="M12" t="n">
         <v>0.6193</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +6712,17 @@
         <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0948</v>
+        <v>1.0938</v>
       </c>
       <c r="L13" t="n">
-        <v>1.296</v>
+        <v>1.2946</v>
       </c>
       <c r="M13" t="n">
         <v>0.3885</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +6758,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1522</v>
+        <v>1.1511</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +6804,17 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8198</v>
+        <v>0.8195</v>
       </c>
       <c r="L15" t="n">
-        <v>0.646</v>
+        <v>0.6461</v>
       </c>
       <c r="M15" t="n">
         <v>0.4986</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +6850,17 @@
         <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8055</v>
+        <v>0.8053</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5794</v>
       </c>
       <c r="M16" t="n">
         <v>0.5105</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7226,7 +6896,7 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0407</v>
+        <v>1.0399</v>
       </c>
       <c r="L17" t="n">
         <v>0.6861</v>
@@ -7236,7 +6906,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7272,17 +6942,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2998</v>
+        <v>1.2983</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5935</v>
       </c>
       <c r="M18" t="n">
         <v>0.7464</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7318,17 +6988,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5277</v>
+        <v>1.5257</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7938</v>
+        <v>0.7936</v>
       </c>
       <c r="M19" t="n">
         <v>0.8192</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7367,14 +7037,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8075</v>
+        <v>0.8072</v>
       </c>
       <c r="M20" t="n">
         <v>0.8933</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7410,17 +7080,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6839</v>
+        <v>0.6841</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9789</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.2939</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7441,32 +7111,32 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9571</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9517</v>
+        <v>1.1047</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3494</v>
+        <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7502,17 +7172,17 @@
         <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1767</v>
+        <v>1.1755</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7222</v>
       </c>
       <c r="M23" t="n">
         <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7548,17 +7218,17 @@
         <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7532</v>
+        <v>0.7531</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0783</v>
+        <v>1.0774</v>
       </c>
       <c r="M24" t="n">
         <v>0.4447</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7264,7 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1255</v>
+        <v>1.1244</v>
       </c>
       <c r="L25" t="n">
         <v>0.6834</v>
@@ -7604,7 +7274,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7640,17 +7310,17 @@
         <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3116</v>
+        <v>1.3101</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6266</v>
+        <v>0.6268</v>
       </c>
       <c r="M26" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7686,17 +7356,17 @@
         <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8655</v>
+        <v>0.8651</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2823</v>
+        <v>1.2809</v>
       </c>
       <c r="M27" t="n">
         <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7402,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0781</v>
+        <v>1.0771</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -7742,7 +7412,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7772,23 +7442,23 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2974</v>
+        <v>1.3781</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7856</v>
+        <v>0.8036</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7494,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4958</v>
+        <v>1.4939</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8287</v>
+        <v>0.8284</v>
       </c>
       <c r="M30" t="n">
         <v>0.6559</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7870,17 +7540,17 @@
         <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.964</v>
+        <v>0.9633</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2168</v>
+        <v>1.2156</v>
       </c>
       <c r="M31" t="n">
         <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7919,14 +7589,14 @@
         <v>1.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8259</v>
+        <v>0.8256</v>
       </c>
       <c r="M32" t="n">
         <v>0.7625999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7962,17 +7632,17 @@
         <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>1.0259</v>
+        <v>1.0251</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0045</v>
+        <v>1.0038</v>
       </c>
       <c r="M33" t="n">
         <v>0.448</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8008,17 +7678,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9988</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9076</v>
+        <v>0.9071</v>
       </c>
       <c r="M34" t="n">
         <v>0.5606</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8054,7 +7724,7 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4989</v>
+        <v>1.497</v>
       </c>
       <c r="L35" t="n">
         <v>0.7199</v>
@@ -8064,7 +7734,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8097,20 +7767,20 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6896</v>
+        <v>0.6917</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2641</v>
+        <v>1.3282</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2428</v>
+        <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8146,17 +7816,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7713</v>
+        <v>0.7711</v>
       </c>
       <c r="L37" t="n">
-        <v>1.0489</v>
+        <v>1.048</v>
       </c>
       <c r="M37" t="n">
         <v>0.3585</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8186,23 +7856,23 @@
         <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1362</v>
+        <v>1.0479</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7571</v>
+        <v>0.8625</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5795</v>
+        <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8238,17 +7908,17 @@
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1756</v>
+        <v>1.1745</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9958</v>
+        <v>0.995</v>
       </c>
       <c r="M39" t="n">
         <v>0.4583</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8278,23 +7948,23 @@
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8097</v>
+        <v>0.7937</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8526</v>
+        <v>0.7951</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4009</v>
+        <v>0.4588</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8318,29 +7988,29 @@
         <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J41" t="n">
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0439</v>
+        <v>0.9651</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7921</v>
+        <v>0.7864</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6054</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8376,17 +8046,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4573</v>
+        <v>1.4555</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6217</v>
+        <v>0.6219</v>
       </c>
       <c r="M42" t="n">
         <v>0.7209</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8422,17 +8092,17 @@
         <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3254</v>
+        <v>1.3239</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3571</v>
+        <v>1.3555</v>
       </c>
       <c r="M43" t="n">
         <v>0.4537</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8453,32 +8123,32 @@
         <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4115</v>
+        <v>1.4197</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8365</v>
+        <v>0.823</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6069</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8514,17 +8184,17 @@
         <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7158</v>
+        <v>0.7157</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3986</v>
+        <v>1.3969</v>
       </c>
       <c r="M45" t="n">
         <v>0.2767</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8560,17 +8230,17 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1404</v>
+        <v>1.1393</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8522</v>
+        <v>0.8518</v>
       </c>
       <c r="M46" t="n">
         <v>0.63</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8606,17 +8276,17 @@
         <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3149</v>
+        <v>1.3134</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0617</v>
+        <v>1.0609</v>
       </c>
       <c r="M47" t="n">
         <v>0.6099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8652,17 +8322,17 @@
         <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8445</v>
+        <v>0.8442</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8536</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0.4187</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8698,17 +8368,17 @@
         <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9424</v>
+        <v>0.9418</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1503</v>
+        <v>1.1492</v>
       </c>
       <c r="M49" t="n">
         <v>0.4067</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-24T01:00:00+00:00</t>
+          <t>2026-06-25T00:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,19 +538,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>53.4</v>
+        <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="K2" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
       <c r="L2" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -598,19 +598,19 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="I3" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="K3" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="L3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
         <v>6.1</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -658,16 +658,16 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="I4" t="n">
         <v>37.6</v>
       </c>
       <c r="J4" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="K4" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="L4" t="n">
         <v>8.199999999999999</v>
@@ -694,22 +694,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>99.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>31.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -718,58 +718,58 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>73.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="I5" t="n">
-        <v>42.4</v>
+        <v>34.7</v>
       </c>
       <c r="J5" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="K5" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1577.2</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="R5" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.2</v>
+        <v>47.2</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5</v>
+        <v>52.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,58 +778,58 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>63.1</v>
+        <v>71.8</v>
       </c>
       <c r="I6" t="n">
-        <v>34.9</v>
+        <v>39.7</v>
       </c>
       <c r="J6" t="n">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="L6" t="n">
         <v>5.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1565</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.6</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -838,48 +838,48 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I7" t="n">
-        <v>39.2</v>
+        <v>42.1</v>
       </c>
       <c r="J7" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="K7" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1565</v>
+        <v>1573.8</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -898,16 +898,16 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>71.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
       <c r="J8" t="n">
-        <v>21.3</v>
+        <v>19.7</v>
       </c>
       <c r="K8" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="L8" t="n">
         <v>5.2</v>
@@ -918,59 +918,59 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1573.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="R8" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.8</v>
+        <v>28.5</v>
       </c>
       <c r="D9" t="n">
-        <v>59.2</v>
+        <v>54.4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>65.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="I9" t="n">
-        <v>35.1</v>
+        <v>32.6</v>
       </c>
       <c r="J9" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="K9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -978,59 +978,59 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1582.5</v>
+        <v>1555.6</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.4</v>
+        <v>40.9</v>
       </c>
       <c r="D10" t="n">
-        <v>54.6</v>
+        <v>59.1</v>
       </c>
       <c r="E10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="I10" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="J10" t="n">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="K10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,17 +1038,17 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1555.6</v>
+        <v>1582.5</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="R10" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="D11" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1078,16 +1078,16 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="I11" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="J11" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>4.2</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>51.2</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1138,19 +1138,19 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>49.8</v>
+        <v>52.7</v>
       </c>
       <c r="I12" t="n">
-        <v>28.6</v>
+        <v>26.9</v>
       </c>
       <c r="J12" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="K12" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="L12" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1162,24 +1162,24 @@
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="R12" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,16 +1198,16 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>50.4</v>
+        <v>37.3</v>
       </c>
       <c r="I13" t="n">
-        <v>25.3</v>
+        <v>21.9</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L13" t="n">
         <v>2.9</v>
@@ -1218,17 +1218,17 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1542.8</v>
+        <v>1571</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="R13" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -1261,16 +1261,16 @@
         <v>65.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="J14" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1294,19 +1294,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.4</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>46.6</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1318,94 +1318,94 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>65.40000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="I15" t="n">
-        <v>30.4</v>
+        <v>23.4</v>
       </c>
       <c r="J15" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1541.7</v>
+        <v>1542.8</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1</v>
+        <v>52.8</v>
       </c>
       <c r="D16" t="n">
-        <v>65.5</v>
+        <v>47.2</v>
       </c>
       <c r="E16" t="n">
-        <v>33.9</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>43.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>22.8</v>
+        <v>30.3</v>
       </c>
       <c r="J16" t="n">
-        <v>12.1</v>
+        <v>13.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
         <v>2.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1560</v>
+        <v>1541.7</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="R16" t="n">
         <v>0.72</v>
@@ -1414,22 +1414,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>61.1</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38.6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1438,19 +1438,19 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>41.2</v>
+        <v>57.4</v>
       </c>
       <c r="I17" t="n">
-        <v>22.3</v>
+        <v>30.1</v>
       </c>
       <c r="J17" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1458,14 +1458,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1571</v>
+        <v>1545.2</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="R17" t="n">
         <v>0.66</v>
@@ -1474,82 +1474,82 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>55.8</v>
+        <v>38.4</v>
       </c>
       <c r="I18" t="n">
-        <v>29.1</v>
+        <v>20.1</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1545.2</v>
+        <v>1560</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="R18" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,214 +1558,214 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>54.2</v>
+        <v>45.1</v>
       </c>
       <c r="I19" t="n">
-        <v>27.5</v>
+        <v>21.2</v>
       </c>
       <c r="J19" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1560.9</v>
+        <v>1556.1</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>54.4</v>
       </c>
       <c r="D20" t="n">
-        <v>34.4</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>64.09999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>78.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>36.4</v>
+        <v>53.1</v>
       </c>
       <c r="I20" t="n">
-        <v>18.7</v>
+        <v>27.9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.9</v>
+        <v>11.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1573.4</v>
+        <v>1560.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>82.40000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.5</v>
       </c>
-      <c r="G21" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1556.1</v>
+        <v>1573.4</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58.7</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>34.9</v>
+        <v>42.8</v>
       </c>
       <c r="I22" t="n">
-        <v>16.5</v>
+        <v>20.3</v>
       </c>
       <c r="J22" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1546.8</v>
+        <v>1544.1</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.18</v>
+        <v>0.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="R22" t="n">
         <v>0.57</v>
@@ -1774,252 +1774,252 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>98.7</v>
+        <v>17.1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>58.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="H23" t="n">
-        <v>57.7</v>
+        <v>33.6</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1522.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.9</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>37.4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>36.1</v>
+        <v>56.7</v>
       </c>
       <c r="I24" t="n">
-        <v>13.1</v>
+        <v>24.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1554.9</v>
+        <v>1522.7</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>28.6</v>
+        <v>38.7</v>
       </c>
       <c r="I25" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1550.3</v>
+        <v>1546.8</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.2</v>
+        <v>22.1</v>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>37.6</v>
       </c>
       <c r="E26" t="n">
-        <v>25.3</v>
+        <v>37.9</v>
       </c>
       <c r="F26" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>91</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
         <v>0.5</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1546.8</v>
+        <v>1554.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2029,145 +2029,145 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="H27" t="n">
-        <v>34.3</v>
+        <v>20.2</v>
       </c>
       <c r="I27" t="n">
-        <v>12.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1514.3</v>
+        <v>1550.3</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="R27" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>76.09999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="F28" t="n">
-        <v>23.7</v>
+        <v>13.9</v>
       </c>
       <c r="G28" t="n">
-        <v>46.2</v>
+        <v>77.7</v>
       </c>
       <c r="H28" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L28" t="n">
         <v>0.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1537.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E29" t="n">
-        <v>79.5</v>
+        <v>76</v>
       </c>
       <c r="F29" t="n">
-        <v>20.5</v>
+        <v>23.8</v>
       </c>
       <c r="G29" t="n">
-        <v>49.8</v>
+        <v>45.9</v>
       </c>
       <c r="H29" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="n">
         <v>0.3</v>
@@ -2178,77 +2178,77 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1564.9</v>
+        <v>1537.9</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>67.2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>15.6</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>18.9</v>
+        <v>35.9</v>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>12.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
         <v>0.8</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1494.5</v>
+        <v>1514.3</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="R30" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
@@ -2284,10 +2284,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L31" t="n">
         <v>0.2</v>
@@ -2314,72 +2314,72 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>72.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>21.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>8.6</v>
+        <v>27.6</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L32" t="n">
         <v>0.2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1544.1</v>
+        <v>1519.6</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="R32" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2389,85 +2389,85 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>21.7</v>
+        <v>79.3</v>
       </c>
       <c r="F33" t="n">
-        <v>78.3</v>
+        <v>20.7</v>
       </c>
       <c r="G33" t="n">
-        <v>19.4</v>
+        <v>34.1</v>
       </c>
       <c r="H33" t="n">
-        <v>6.9</v>
+        <v>12.5</v>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1578.2</v>
+        <v>1564.9</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>30.7</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>53.1</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>71.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="I34" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L34" t="n">
         <v>0.1</v>
@@ -2478,350 +2478,350 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1519.6</v>
+        <v>1507.6</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.91</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="G35" t="n">
-        <v>36.4</v>
+        <v>19.1</v>
       </c>
       <c r="H35" t="n">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L35" t="n">
         <v>0.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1521.6</v>
+        <v>1534.2</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="R35" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>8.199999999999999</v>
+        <v>30.6</v>
       </c>
       <c r="E36" t="n">
-        <v>75.3</v>
+        <v>59.4</v>
       </c>
       <c r="F36" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>33.1</v>
+        <v>99.7</v>
       </c>
       <c r="H36" t="n">
-        <v>8.699999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0.8</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1516.6</v>
+        <v>1467.7</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="R36" t="n">
-        <v>0.42</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>19.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>75.2</v>
       </c>
       <c r="F37" t="n">
-        <v>80.8</v>
+        <v>7.9</v>
       </c>
       <c r="G37" t="n">
-        <v>19.1</v>
+        <v>31.2</v>
       </c>
       <c r="H37" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1534.2</v>
+        <v>1516.6</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="R37" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>82.40000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>17.8</v>
+        <v>2.7</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1507.6</v>
+        <v>1521.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.36</v>
+        <v>0.86</v>
       </c>
       <c r="R38" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>31.1</v>
+        <v>6.6</v>
       </c>
       <c r="E39" t="n">
-        <v>59</v>
+        <v>4.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="G39" t="n">
-        <v>99.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>19.3</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1467.7</v>
+        <v>1518</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="R39" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>18.6</v>
       </c>
       <c r="E40" t="n">
-        <v>13.9</v>
+        <v>3.1</v>
       </c>
       <c r="F40" t="n">
-        <v>73.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="G40" t="n">
-        <v>15.9</v>
+        <v>20.9</v>
       </c>
       <c r="H40" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0.1</v>
@@ -2838,53 +2838,53 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1519.9</v>
+        <v>1499.2</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2898,53 +2898,53 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1518</v>
+        <v>1519.9</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="R41" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>78.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2958,28 +2958,28 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1499.2</v>
+        <v>1523</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2989,16 +2989,16 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>79.3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1523</v>
+        <v>1534.7</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="R43" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3049,19 +3049,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>20.5</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>79.5</v>
+        <v>98</v>
       </c>
       <c r="G44" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3078,28 +3078,28 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1534.7</v>
+        <v>1493.5</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="R44" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,19 +3109,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="F45" t="n">
-        <v>97.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1493.5</v>
+        <v>1555</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3169,19 +3169,19 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="R46" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3258,28 +3258,28 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1484.3</v>
+        <v>1495</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3318,17 +3318,17 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1495</v>
+        <v>1578.2</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.72</v>
+        <v>1.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="R48" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="49">
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="F49" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="G49" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>19.2</v>
       </c>
       <c r="G3" t="n">
-        <v>75.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="4">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>36.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3805,19 +3805,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>21.7</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>19.4</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3855,23 +3855,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>30.7</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>53.1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16.1</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>71.09999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>82.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -3943,16 +3943,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>72.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>21.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -3970,16 +3970,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>73.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>15.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>51.2</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>61.1</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>38.6</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4048,19 +4048,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>82.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -4102,19 +4102,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="D26" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="E26" t="n">
         <v>9.4</v>
       </c>
       <c r="F26" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="G26" t="n">
-        <v>90.7</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -4129,19 +4129,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -4159,16 +4159,16 @@
         <v>17.1</v>
       </c>
       <c r="D28" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>58.7</v>
+        <v>58.4</v>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>66</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="29">
@@ -4189,13 +4189,13 @@
         <v>6.6</v>
       </c>
       <c r="E29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>88.8</v>
       </c>
       <c r="G29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="D30" t="n">
         <v>6.1</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4240,16 +4240,16 @@
         <v>3.3</v>
       </c>
       <c r="D31" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F31" t="n">
         <v>13.9</v>
       </c>
       <c r="G31" t="n">
-        <v>79</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="32">
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="F32" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="G32" t="n">
-        <v>33.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="33">
@@ -4294,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="E33" t="n">
         <v>3.1</v>
       </c>
       <c r="F33" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G33" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="34">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="D34" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="D35" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="F36" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="G36" t="n">
-        <v>49.8</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="37">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="F37" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="38">
@@ -4456,16 +4456,16 @@
         <v>0.1</v>
       </c>
       <c r="D39" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="F39" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>94.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4483,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="E40" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="F40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>78.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="41">
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="G41" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="D42" t="n">
-        <v>53.2</v>
+        <v>52.6</v>
       </c>
       <c r="E42" t="n">
         <v>0.2</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="D43" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4594,13 +4594,13 @@
         <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="F44" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G44" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="45">
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="F45" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="G45" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="E46" t="n">
         <v>0.3</v>
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="D47" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="E47" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="F47" t="n">
         <v>2.4</v>
       </c>
       <c r="G47" t="n">
-        <v>94.5</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4696,19 +4696,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="E48" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="49">
@@ -4735,7 +4735,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4876,7 +4876,7 @@
         <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4902,16 +4902,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,129 +4921,129 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>40.9</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="K3" t="n">
-        <v>63.3</v>
+        <v>36.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>France</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>36.2</v>
+        <v>12.6</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-25T19:00:00Z</t>
+          <t>2026-06-26T18:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1.37</v>
+        <v>0.92</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>54.9</v>
       </c>
       <c r="J4" t="n">
-        <v>27.8</v>
+        <v>24.4</v>
       </c>
       <c r="K4" t="n">
-        <v>50.2</v>
+        <v>20.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>33.1</v>
+        <v>30.2</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5053,94 +5053,94 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.59</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>72.09999999999999</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>30.5</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>35.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>68.2</v>
+        <v>14.1</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-25T22:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>10.9</v>
+        <v>15.2</v>
       </c>
       <c r="K6" t="n">
-        <v>83.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -5149,33 +5149,33 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>76</v>
+        <v>37.6</v>
       </c>
       <c r="P6" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5185,94 +5185,94 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="H7" t="n">
-        <v>1.54</v>
+        <v>0.78</v>
       </c>
       <c r="I7" t="n">
-        <v>39.9</v>
+        <v>51.8</v>
       </c>
       <c r="J7" t="n">
-        <v>23.6</v>
+        <v>27.3</v>
       </c>
       <c r="K7" t="n">
-        <v>36.5</v>
+        <v>20.9</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>55.5</v>
+        <v>4.7</v>
       </c>
       <c r="P7" t="n">
-        <v>36.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00Z</t>
+          <t>2026-06-26T23:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="I8" t="n">
-        <v>30.8</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
-        <v>29.3</v>
+        <v>21.5</v>
       </c>
       <c r="K8" t="n">
-        <v>39.9</v>
+        <v>67</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -5281,33 +5281,33 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>27.2</v>
+        <v>87.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5317,94 +5317,94 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.79</v>
+        <v>0.74</v>
       </c>
       <c r="H9" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>40.8</v>
+        <v>14.6</v>
       </c>
       <c r="J9" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="K9" t="n">
-        <v>36.8</v>
+        <v>63.3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>12.6</v>
+        <v>38.4</v>
       </c>
       <c r="P9" t="n">
-        <v>36.8</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="I10" t="n">
-        <v>54.9</v>
+        <v>59.4</v>
       </c>
       <c r="J10" t="n">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="K10" t="n">
-        <v>20.7</v>
+        <v>16.7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -5413,33 +5413,33 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>30.2</v>
+        <v>87.2</v>
       </c>
       <c r="P10" t="n">
-        <v>20.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5449,28 +5449,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="J11" t="n">
-        <v>30.6</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>35.5</v>
+        <v>38.8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -5479,64 +5479,64 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="P11" t="n">
-        <v>35.5</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="H12" t="n">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>15.2</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>75.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -5545,33 +5545,33 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>37.6</v>
+        <v>83.7</v>
       </c>
       <c r="P12" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5581,510 +5581,114 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="H13" t="n">
-        <v>0.78</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>51.8</v>
+        <v>28.8</v>
       </c>
       <c r="J13" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="K13" t="n">
-        <v>20.8</v>
+        <v>46.6</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4.7</v>
+        <v>23.3</v>
       </c>
       <c r="P13" t="n">
-        <v>51.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83</v>
+        <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="J14" t="n">
-        <v>21.5</v>
+        <v>30.2</v>
       </c>
       <c r="K14" t="n">
-        <v>67</v>
+        <v>23.8</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P14" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-27T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I15" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>68</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-27T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I16" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>69</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>70</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>71</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I19" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>28.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>72</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I20" t="n">
-        <v>46</v>
-      </c>
-      <c r="J20" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P20" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6206,17 +5810,17 @@
         <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2162</v>
+        <v>1.2161</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7478</v>
+        <v>0.7482</v>
       </c>
       <c r="M2" t="n">
         <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6252,7 +5856,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5203</v>
+        <v>1.5199</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -6262,7 +5866,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6283,32 +5887,32 @@
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9687</v>
+        <v>0.885</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7886</v>
+        <v>0.7269</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5422</v>
+        <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6344,17 +5948,17 @@
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3179</v>
+        <v>1.3177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.728</v>
+        <v>0.7285</v>
       </c>
       <c r="M5" t="n">
         <v>0.7222</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6390,17 +5994,17 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5168</v>
+        <v>1.5164</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6844</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>0.6408</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6436,17 +6040,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0651</v>
+        <v>1.0652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9754</v>
+        <v>0.9756</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6482,17 +6086,17 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4915</v>
+        <v>1.4912</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7536</v>
+        <v>0.7541</v>
       </c>
       <c r="M8" t="n">
         <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6528,17 +6132,17 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1848</v>
+        <v>1.1849</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6333</v>
+        <v>0.6338</v>
       </c>
       <c r="M9" t="n">
         <v>0.5536</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6574,17 +6178,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0607</v>
+        <v>1.0608</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8119</v>
+        <v>0.8123</v>
       </c>
       <c r="M10" t="n">
         <v>0.4729</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6620,17 +6224,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2997</v>
+        <v>1.2996</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7844</v>
+        <v>0.7849</v>
       </c>
       <c r="M11" t="n">
         <v>0.7178</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6666,17 +6270,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1922</v>
+        <v>1.1921</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0008</v>
+        <v>1.001</v>
       </c>
       <c r="M12" t="n">
         <v>0.6193</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6697,32 +6301,32 @@
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0938</v>
+        <v>0.9925</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2946</v>
+        <v>1.3135</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3885</v>
+        <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6758,17 +6362,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1511</v>
+        <v>1.1512</v>
       </c>
       <c r="L14" t="n">
-        <v>0.867</v>
+        <v>0.8673</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6804,17 +6408,17 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8195</v>
+        <v>0.8199</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6461</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>0.4986</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6835,32 +6439,32 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8053</v>
+        <v>0.8598</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5794</v>
+        <v>0.5942</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5105</v>
+        <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6896,17 +6500,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0399</v>
+        <v>1.04</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6861</v>
+        <v>0.6866</v>
       </c>
       <c r="M17" t="n">
         <v>0.6263</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6942,17 +6546,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2983</v>
+        <v>1.2982</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5935</v>
+        <v>0.5941</v>
       </c>
       <c r="M18" t="n">
         <v>0.7464</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6988,17 +6592,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5257</v>
+        <v>1.5253</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7936</v>
+        <v>0.794</v>
       </c>
       <c r="M19" t="n">
         <v>0.8192</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7019,32 +6623,32 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8072</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8933</v>
+        <v>0.7865</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7080,17 +6684,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6841</v>
+        <v>0.6846</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9785</v>
       </c>
       <c r="M21" t="n">
         <v>0.2939</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7126,17 +6730,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9571</v>
+        <v>0.9573</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1047</v>
+        <v>1.1048</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7175,14 +6779,14 @@
         <v>1.1755</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7222</v>
+        <v>0.7227</v>
       </c>
       <c r="M23" t="n">
         <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7218,17 +6822,17 @@
         <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7531</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0774</v>
+        <v>1.0775</v>
       </c>
       <c r="M24" t="n">
         <v>0.4447</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7264,17 +6868,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1244</v>
+        <v>1.1457</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6834</v>
+        <v>0.6363</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6943</v>
+        <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7295,32 +6899,32 @@
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3101</v>
+        <v>1.2508</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6268</v>
+        <v>0.6389</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7245</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7356,17 +6960,17 @@
         <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8651</v>
+        <v>0.8655</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2809</v>
+        <v>1.2808</v>
       </c>
       <c r="M27" t="n">
         <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7006,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0771</v>
+        <v>1.0772</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -7412,7 +7016,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7052,7 @@
         <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3781</v>
+        <v>1.378</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -7458,7 +7062,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7479,32 +7083,32 @@
         <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J30" t="n">
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4939</v>
+        <v>1.5496</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8284</v>
+        <v>0.8204</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6559</v>
+        <v>0.6995</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7540,17 +7144,17 @@
         <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9633</v>
+        <v>0.9636</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2156</v>
+        <v>1.2155</v>
       </c>
       <c r="M31" t="n">
         <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7589,14 +7193,14 @@
         <v>1.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8256</v>
+        <v>0.826</v>
       </c>
       <c r="M32" t="n">
         <v>0.7625999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7632,17 +7236,17 @@
         <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>1.0251</v>
+        <v>1.0253</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0038</v>
+        <v>1.004</v>
       </c>
       <c r="M33" t="n">
         <v>0.448</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7663,32 +7267,32 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9988</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9071</v>
+        <v>0.8364</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5606</v>
+        <v>0.5275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7724,17 +7328,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.497</v>
+        <v>1.4966</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7199</v>
+        <v>0.7204</v>
       </c>
       <c r="M35" t="n">
         <v>0.7388</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7770,17 +7374,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6917</v>
+        <v>0.6922</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3282</v>
+        <v>1.328</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7816,17 +7420,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7711</v>
+        <v>0.7715</v>
       </c>
       <c r="L37" t="n">
-        <v>1.048</v>
+        <v>1.0482</v>
       </c>
       <c r="M37" t="n">
         <v>0.3585</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7862,17 +7466,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0479</v>
+        <v>1.048</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8625</v>
+        <v>0.8629</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7911,14 +7515,14 @@
         <v>1.1745</v>
       </c>
       <c r="L39" t="n">
-        <v>0.995</v>
+        <v>0.9952</v>
       </c>
       <c r="M39" t="n">
         <v>0.4583</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7954,17 +7558,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7937</v>
+        <v>0.7941</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7951</v>
+        <v>0.7955</v>
       </c>
       <c r="M40" t="n">
         <v>0.4588</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8000,17 +7604,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9651</v>
+        <v>0.9654</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7864</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8046,17 +7650,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4555</v>
+        <v>1.4552</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6219</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.7209</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8086,23 +7690,23 @@
         <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J43" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.3239</v>
+        <v>1.2747</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3555</v>
+        <v>1.304</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4537</v>
+        <v>0.4405</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8138,17 +7742,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4197</v>
+        <v>1.4195</v>
       </c>
       <c r="L44" t="n">
-        <v>0.823</v>
+        <v>0.8233</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8172,29 +7776,29 @@
         <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7157</v>
+        <v>0.7161</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3969</v>
+        <v>1.4551</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2767</v>
+        <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8224,23 +7828,23 @@
         <v>5</v>
       </c>
       <c r="I46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1393</v>
+        <v>1.2215</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8518</v>
+        <v>0.903</v>
       </c>
       <c r="M46" t="n">
-        <v>0.63</v>
+        <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8270,23 +7874,23 @@
         <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3134</v>
+        <v>1.3307</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0609</v>
+        <v>1.1381</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6099</v>
+        <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8322,17 +7926,17 @@
         <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8442</v>
+        <v>0.8446</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8537</v>
       </c>
       <c r="M48" t="n">
         <v>0.4187</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -8368,7 +7972,7 @@
         <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9418</v>
+        <v>0.9421</v>
       </c>
       <c r="L49" t="n">
         <v>1.1492</v>
@@ -8378,7 +7982,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-25T00:00:00+00:00</t>
+          <t>2026-06-26T01:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,16 +538,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I2" t="n">
-        <v>53</v>
+        <v>51.8</v>
       </c>
       <c r="J2" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="K2" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="L2" t="n">
         <v>13.2</v>
@@ -598,19 +598,19 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="I3" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="J3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="K3" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -658,19 +658,19 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>60.5</v>
+        <v>62.3</v>
       </c>
       <c r="I4" t="n">
-        <v>37.6</v>
+        <v>39.5</v>
       </c>
       <c r="J4" t="n">
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
       <c r="K4" t="n">
-        <v>14.6</v>
+        <v>15.8</v>
       </c>
       <c r="L4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -682,13 +682,13 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="D5" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="E5" t="n">
         <v>0.3</v>
@@ -721,16 +721,16 @@
         <v>63.1</v>
       </c>
       <c r="I5" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="J5" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="K5" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.2</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>52.6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,58 +778,58 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>71.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>39.7</v>
+        <v>42</v>
       </c>
       <c r="J6" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="K6" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="L6" t="n">
         <v>5.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1565</v>
+        <v>1569.9</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="R6" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>46.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -838,48 +838,48 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>71.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
       <c r="J7" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="K7" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1573.8</v>
+        <v>1565</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -898,139 +898,139 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>73.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="I8" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="J8" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1577.2</v>
+        <v>1573.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.5</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>59</v>
+        <v>74.5</v>
       </c>
       <c r="I9" t="n">
-        <v>32.6</v>
+        <v>39.9</v>
       </c>
       <c r="J9" t="n">
-        <v>17.9</v>
+        <v>19.1</v>
       </c>
       <c r="K9" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1555.6</v>
+        <v>1577.2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40.9</v>
+        <v>28.5</v>
       </c>
       <c r="D10" t="n">
-        <v>59.1</v>
+        <v>54.4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>89.2</v>
       </c>
       <c r="H10" t="n">
-        <v>62.2</v>
+        <v>58.5</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>32.3</v>
       </c>
       <c r="J10" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="K10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,35 +1038,35 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1582.5</v>
+        <v>1555.6</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>40.9</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1078,55 +1078,55 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>63.2</v>
+        <v>52.6</v>
       </c>
       <c r="I11" t="n">
-        <v>34.2</v>
+        <v>28.9</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1569.9</v>
+        <v>1575.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1138,37 +1138,37 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>52.7</v>
+        <v>47.3</v>
       </c>
       <c r="I12" t="n">
-        <v>26.9</v>
+        <v>25.2</v>
       </c>
       <c r="J12" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1575.8</v>
+        <v>1542.8</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13">
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="I13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="J13" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1261,16 +1261,16 @@
         <v>65.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="J14" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1318,19 +1318,19 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>47.3</v>
+        <v>57.1</v>
       </c>
       <c r="I15" t="n">
-        <v>23.4</v>
+        <v>29.7</v>
       </c>
       <c r="J15" t="n">
-        <v>11.8</v>
+        <v>12.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1338,35 +1338,35 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1542.8</v>
+        <v>1545.2</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="R15" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>47.2</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1378,55 +1378,55 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>64.90000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="I16" t="n">
-        <v>30.3</v>
+        <v>24.4</v>
       </c>
       <c r="J16" t="n">
-        <v>13.9</v>
+        <v>12.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>2.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1541.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>53.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>46.9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1438,37 +1438,37 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>57.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="J17" t="n">
-        <v>12.5</v>
+        <v>13.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1545.2</v>
+        <v>1541.7</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="R17" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="18">
@@ -1495,22 +1495,22 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>84.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>38.4</v>
+        <v>33.4</v>
       </c>
       <c r="I18" t="n">
-        <v>20.1</v>
+        <v>17.6</v>
       </c>
       <c r="J18" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1534,121 +1534,121 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>54.4</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>45.1</v>
+        <v>52</v>
       </c>
       <c r="I19" t="n">
-        <v>21.2</v>
+        <v>27.1</v>
       </c>
       <c r="J19" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1556.1</v>
+        <v>1560.9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>53.1</v>
+        <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>27.9</v>
+        <v>21.3</v>
       </c>
       <c r="J20" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1560.9</v>
+        <v>1582.5</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="R20" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="21">
@@ -1669,28 +1669,28 @@
         <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="F21" t="n">
         <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>68.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>31.3</v>
+        <v>28.5</v>
       </c>
       <c r="I21" t="n">
-        <v>16.1</v>
+        <v>14.9</v>
       </c>
       <c r="J21" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="I22" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="J22" t="n">
         <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.3</v>
@@ -1795,22 +1795,22 @@
         <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>63.5</v>
+        <v>60.7</v>
       </c>
       <c r="H23" t="n">
-        <v>33.6</v>
+        <v>31.7</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="J23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1834,67 +1834,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="H24" t="n">
-        <v>56.7</v>
+        <v>38.6</v>
       </c>
       <c r="I24" t="n">
-        <v>24.1</v>
+        <v>18.4</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1522.7</v>
+        <v>1564.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="R24" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1918,157 +1918,157 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>38.7</v>
+        <v>56.2</v>
       </c>
       <c r="I25" t="n">
-        <v>12.2</v>
+        <v>23.9</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="K25" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1546.8</v>
+        <v>1522.7</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>37.6</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>37.9</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>89.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>34.2</v>
+        <v>39.1</v>
       </c>
       <c r="I26" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1554.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="R26" t="n">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>37.9</v>
       </c>
       <c r="E27" t="n">
-        <v>80.8</v>
+        <v>37.9</v>
       </c>
       <c r="F27" t="n">
-        <v>19.2</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>52.6</v>
+        <v>88.8</v>
       </c>
       <c r="H27" t="n">
-        <v>20.2</v>
+        <v>33.5</v>
       </c>
       <c r="I27" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1550.3</v>
+        <v>1554.9</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="28">
@@ -2083,34 +2083,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>67.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>77.7</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>18.9</v>
+        <v>23.6</v>
       </c>
       <c r="I28" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2122,13 +2122,13 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="R28" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="29">
@@ -2149,25 +2149,25 @@
         <v>0.2</v>
       </c>
       <c r="E29" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="G29" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="H29" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0.3</v>
@@ -2218,16 +2218,16 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>35.9</v>
+        <v>34.7</v>
       </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L30" t="n">
         <v>0.3</v>
@@ -2254,72 +2254,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>19.2</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>32.9</v>
+        <v>26.4</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1521.7</v>
+        <v>1519.6</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="R31" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2329,103 +2329,103 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="G32" t="n">
-        <v>99.09999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="H32" t="n">
-        <v>27.6</v>
+        <v>16.4</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>2.5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1519.6</v>
+        <v>1550.3</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="R32" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E33" t="n">
-        <v>79.3</v>
+        <v>19.2</v>
       </c>
       <c r="F33" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>34.1</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>12.5</v>
+        <v>32.6</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1564.9</v>
+        <v>1521.7</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R33" t="n">
         <v>0.46</v>
@@ -2458,16 +2458,16 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="I34" t="n">
         <v>6.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L34" t="n">
         <v>0.1</v>
@@ -2518,16 +2518,16 @@
         <v>19.1</v>
       </c>
       <c r="H35" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L35" t="n">
         <v>0.1</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="D36" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="E36" t="n">
         <v>59.4</v>
@@ -2575,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="H36" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0.8</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36" t="n">
         <v>0.98</v>
@@ -2614,61 +2614,61 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="E37" t="n">
-        <v>75.2</v>
+        <v>4.5</v>
       </c>
       <c r="F37" t="n">
-        <v>7.9</v>
+        <v>88.8</v>
       </c>
       <c r="G37" t="n">
-        <v>31.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1516.6</v>
+        <v>1518</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.85</v>
+        <v>1.22</v>
       </c>
       <c r="R37" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="38">
@@ -2695,16 +2695,16 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2734,37 +2734,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>88.8</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2778,53 +2778,53 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1518</v>
+        <v>1519.9</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="R39" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>78.2</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1499.2</v>
+        <v>1523</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2898,28 +2898,28 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1519.9</v>
+        <v>1534.7</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R41" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2958,28 +2958,28 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1523</v>
+        <v>1493.5</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2989,20 +2989,20 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>20.7</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>79.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="H43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.1</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1534.7</v>
+        <v>1555</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3049,16 +3049,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3078,28 +3078,28 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1493.5</v>
+        <v>1484.3</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="R44" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,19 +3109,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3138,28 +3138,28 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1555</v>
+        <v>1499.2</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="R45" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1484.3</v>
+        <v>1495</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="R46" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3258,28 +3258,28 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1495</v>
+        <v>1578.2</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>0.72</v>
+        <v>1.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.46</v>
+        <v>0.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3289,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3314,21 +3314,21 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1578.2</v>
+        <v>1516.6</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>1.22</v>
+        <v>0.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="R48" t="n">
-        <v>0.67</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="49">
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="F49" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>19.2</v>
       </c>
       <c r="G3" t="n">
-        <v>52.6</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="4">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4114,7 +4114,7 @@
         <v>7.7</v>
       </c>
       <c r="G26" t="n">
-        <v>89.90000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="27">
@@ -4168,7 +4168,7 @@
         <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>63.5</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="29">
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="E29" t="n">
         <v>4.5</v>
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D30" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>67.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>77.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -4260,23 +4260,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>75.2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>7.9</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4287,23 +4287,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3.1</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40.9</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4341,14 +4341,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>40.9</v>
+        <v>100</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>79.3</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>34.1</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="37">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>79.3</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4465,7 +4465,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>84.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4486,13 +4486,13 @@
         <v>34.5</v>
       </c>
       <c r="E40" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="F40" t="n">
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>68.2</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -4519,7 +4519,7 @@
         <v>98</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="D42" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="E42" t="n">
         <v>0.2</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52.8</v>
+        <v>53.1</v>
       </c>
       <c r="D43" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4594,13 +4594,13 @@
         <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="G44" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="F45" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="D46" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="E46" t="n">
         <v>0.3</v>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D47" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="E47" t="n">
         <v>37.9</v>
@@ -4681,7 +4681,7 @@
         <v>2.4</v>
       </c>
       <c r="G47" t="n">
-        <v>89.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="48">
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="D48" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="E48" t="n">
         <v>59.4</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="49">
@@ -4735,7 +4735,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4870,7 +4870,7 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="J2" t="n">
         <v>26.6</v>
@@ -4897,21 +4897,21 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,28 +4921,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.69</v>
+        <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>40.9</v>
+        <v>34</v>
       </c>
       <c r="J3" t="n">
-        <v>22.3</v>
+        <v>30.5</v>
       </c>
       <c r="K3" t="n">
-        <v>36.8</v>
+        <v>35.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4951,33 +4951,33 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>12.6</v>
+        <v>14.1</v>
       </c>
       <c r="P3" t="n">
-        <v>36.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-26T18:00:00Z</t>
+          <t>2026-06-27T02:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4987,63 +4987,63 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>0.77</v>
       </c>
       <c r="H4" t="n">
-        <v>0.92</v>
+        <v>2.53</v>
       </c>
       <c r="I4" t="n">
-        <v>54.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>24.4</v>
+        <v>15.2</v>
       </c>
       <c r="K4" t="n">
-        <v>20.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>30.2</v>
+        <v>37.6</v>
       </c>
       <c r="P4" t="n">
-        <v>20.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5053,129 +5053,129 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H5" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
-        <v>34</v>
+        <v>14.6</v>
       </c>
       <c r="J5" t="n">
-        <v>30.5</v>
+        <v>22.1</v>
       </c>
       <c r="K5" t="n">
-        <v>35.5</v>
+        <v>63.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P5" t="n">
-        <v>35.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.77</v>
+        <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.53</v>
+        <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>9.199999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="J6" t="n">
-        <v>15.2</v>
+        <v>23.9</v>
       </c>
       <c r="K6" t="n">
-        <v>75.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P6" t="n">
-        <v>9.199999999999999</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5185,129 +5185,129 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.78</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>51.8</v>
+        <v>34.3</v>
       </c>
       <c r="J7" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="K7" t="n">
-        <v>20.9</v>
+        <v>38.8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="P7" t="n">
-        <v>51.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>21.5</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P8" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5317,63 +5317,63 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.74</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>14.6</v>
+        <v>28.8</v>
       </c>
       <c r="J9" t="n">
-        <v>22.1</v>
+        <v>24.5</v>
       </c>
       <c r="K9" t="n">
-        <v>63.3</v>
+        <v>46.6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>38.4</v>
+        <v>23.3</v>
       </c>
       <c r="P9" t="n">
-        <v>14.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5383,28 +5383,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>59.4</v>
+        <v>46</v>
       </c>
       <c r="J10" t="n">
-        <v>23.9</v>
+        <v>30.2</v>
       </c>
       <c r="K10" t="n">
-        <v>16.7</v>
+        <v>23.8</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -5413,282 +5413,18 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>87.2</v>
+        <v>6.9</v>
       </c>
       <c r="P10" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>69</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>27</v>
-      </c>
-      <c r="K11" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>71</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>28.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>72</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I14" t="n">
-        <v>46</v>
-      </c>
-      <c r="J14" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P14" t="n">
         <v>46</v>
       </c>
     </row>
@@ -5810,17 +5546,17 @@
         <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2161</v>
+        <v>1.2159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7482</v>
+        <v>0.7486</v>
       </c>
       <c r="M2" t="n">
         <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5592,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5199</v>
+        <v>1.5193</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5866,7 +5602,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5902,17 +5638,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.885</v>
+        <v>0.8852</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7269</v>
+        <v>0.7272</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5948,17 +5684,17 @@
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3177</v>
+        <v>1.3173</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7285</v>
+        <v>0.7289</v>
       </c>
       <c r="M5" t="n">
         <v>0.7222</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5994,17 +5730,17 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5164</v>
+        <v>1.5159</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6854</v>
       </c>
       <c r="M6" t="n">
         <v>0.6408</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6043,14 +5779,14 @@
         <v>1.0652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9756</v>
+        <v>0.9757</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6086,17 +5822,17 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4912</v>
+        <v>1.4907</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7541</v>
+        <v>0.7544</v>
       </c>
       <c r="M8" t="n">
         <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6132,17 +5868,17 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1849</v>
+        <v>1.1847</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6338</v>
+        <v>0.6342</v>
       </c>
       <c r="M9" t="n">
         <v>0.5536</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6160,13 +5896,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -6178,17 +5914,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0608</v>
+        <v>0.9688</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8123</v>
+        <v>0.7421</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4729</v>
+        <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6224,17 +5960,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2996</v>
+        <v>1.2993</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7849</v>
+        <v>0.7852</v>
       </c>
       <c r="M11" t="n">
         <v>0.7178</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6270,17 +6006,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1921</v>
+        <v>1.192</v>
       </c>
       <c r="L12" t="n">
-        <v>1.001</v>
+        <v>1.0011</v>
       </c>
       <c r="M12" t="n">
         <v>0.6193</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6316,17 +6052,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9925</v>
+        <v>0.9926</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3135</v>
+        <v>1.3133</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6362,17 +6098,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1512</v>
+        <v>1.151</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8673</v>
+        <v>0.8675</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6408,17 +6144,17 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8199</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6471</v>
       </c>
       <c r="M15" t="n">
         <v>0.4986</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6454,17 +6190,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8598</v>
+        <v>0.86</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5942</v>
+        <v>0.5947</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6236,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.04</v>
+        <v>1.0401</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6866</v>
+        <v>0.6869</v>
       </c>
       <c r="M17" t="n">
         <v>0.6263</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6546,17 +6282,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2982</v>
+        <v>1.2979</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5941</v>
+        <v>0.5947</v>
       </c>
       <c r="M18" t="n">
         <v>0.7464</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6592,17 +6328,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5253</v>
+        <v>1.6224</v>
       </c>
       <c r="L19" t="n">
-        <v>0.794</v>
+        <v>0.7884</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8192</v>
+        <v>0.839</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6641,14 +6377,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8576</v>
       </c>
       <c r="M20" t="n">
         <v>0.7865</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6684,17 +6420,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6846</v>
+        <v>0.6851</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9785</v>
+        <v>0.9786</v>
       </c>
       <c r="M21" t="n">
         <v>0.2939</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6730,17 +6466,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9573</v>
+        <v>0.9574</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1048</v>
+        <v>1.1047</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6776,17 +6512,17 @@
         <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1755</v>
+        <v>1.1754</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7227</v>
+        <v>0.7231</v>
       </c>
       <c r="M23" t="n">
         <v>0.5686</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6807,32 +6543,32 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.6954</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0775</v>
+        <v>1.279</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4447</v>
+        <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6868,17 +6604,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1457</v>
+        <v>1.1456</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6363</v>
+        <v>0.6367</v>
       </c>
       <c r="M25" t="n">
         <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6914,17 +6650,17 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2508</v>
+        <v>1.2505</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6389</v>
+        <v>0.6394</v>
       </c>
       <c r="M26" t="n">
         <v>0.7245</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6960,17 +6696,17 @@
         <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8655</v>
+        <v>0.8657</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2808</v>
+        <v>1.2805</v>
       </c>
       <c r="M27" t="n">
         <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7016,7 +6752,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7052,7 +6788,7 @@
         <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.378</v>
+        <v>1.3777</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -7062,7 +6798,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7098,17 +6834,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5496</v>
+        <v>1.5491</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8204</v>
+        <v>0.8207</v>
       </c>
       <c r="M30" t="n">
         <v>0.6995</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7144,17 +6880,17 @@
         <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9636</v>
+        <v>0.9637</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2155</v>
+        <v>1.2153</v>
       </c>
       <c r="M31" t="n">
         <v>0.2416</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7175,32 +6911,32 @@
         <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J32" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>1.65</v>
+        <v>1.5921</v>
       </c>
       <c r="L32" t="n">
-        <v>0.826</v>
+        <v>0.9922</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.6701</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7246,7 +6982,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7282,17 +7018,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8364</v>
+        <v>0.8366</v>
       </c>
       <c r="M34" t="n">
         <v>0.5275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7328,17 +7064,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4966</v>
+        <v>1.4961</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7204</v>
+        <v>0.7208</v>
       </c>
       <c r="M35" t="n">
         <v>0.7388</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7374,17 +7110,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6922</v>
+        <v>0.6926</v>
       </c>
       <c r="L36" t="n">
-        <v>1.328</v>
+        <v>1.3276</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7405,32 +7141,32 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
         <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7715</v>
+        <v>0.7063</v>
       </c>
       <c r="L37" t="n">
-        <v>1.0482</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3585</v>
+        <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7469,14 +7205,14 @@
         <v>1.048</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8629</v>
+        <v>0.8631</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7506,23 +7242,23 @@
         <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1745</v>
+        <v>1.3274</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9952</v>
+        <v>0.9301</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4583</v>
+        <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7558,17 +7294,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7941</v>
+        <v>0.7944</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7955</v>
+        <v>0.7957</v>
       </c>
       <c r="M40" t="n">
         <v>0.4588</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7607,14 +7343,14 @@
         <v>0.9654</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7871</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7386,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4552</v>
+        <v>1.4004</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5774</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7209</v>
+        <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7696,17 +7432,17 @@
         <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2747</v>
+        <v>1.2745</v>
       </c>
       <c r="L43" t="n">
-        <v>1.304</v>
+        <v>1.3037</v>
       </c>
       <c r="M43" t="n">
         <v>0.4405</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7742,17 +7478,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4195</v>
+        <v>1.4191</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8233</v>
+        <v>0.8236</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7788,17 +7524,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7161</v>
+        <v>0.7164</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4551</v>
+        <v>1.4547</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7834,17 +7570,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2215</v>
+        <v>1.2213</v>
       </c>
       <c r="L46" t="n">
-        <v>0.903</v>
+        <v>0.9032</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7880,17 +7616,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3307</v>
+        <v>1.3304</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1381</v>
+        <v>1.138</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7914,29 +7650,29 @@
         <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8446</v>
+        <v>0.7745</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8537</v>
+        <v>0.8465</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4187</v>
+        <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7972,17 +7708,17 @@
         <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9421</v>
+        <v>0.9422</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1492</v>
+        <v>1.1491</v>
       </c>
       <c r="M49" t="n">
         <v>0.4067</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-26T01:00:00+00:00</t>
+          <t>2026-06-26T23:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,23 +538,23 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>51.8</v>
+        <v>54.3</v>
       </c>
       <c r="J2" t="n">
-        <v>35.1</v>
+        <v>36.9</v>
       </c>
       <c r="K2" t="n">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
       <c r="L2" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -601,16 +601,16 @@
         <v>62.9</v>
       </c>
       <c r="I3" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="J3" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="K3" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
       <c r="L3" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -658,19 +658,19 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="I4" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J4" t="n">
-        <v>27.5</v>
+        <v>25.1</v>
       </c>
       <c r="K4" t="n">
-        <v>15.8</v>
+        <v>14.6</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -694,22 +694,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.3</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -718,19 +718,19 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>63.1</v>
+        <v>67.7</v>
       </c>
       <c r="I5" t="n">
-        <v>34.2</v>
+        <v>49.9</v>
       </c>
       <c r="J5" t="n">
-        <v>20.5</v>
+        <v>26.6</v>
       </c>
       <c r="K5" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -738,38 +738,38 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1593.4</v>
+        <v>1555.6</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>68.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,58 +778,58 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>72.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I6" t="n">
-        <v>42</v>
+        <v>34.2</v>
       </c>
       <c r="J6" t="n">
-        <v>21.1</v>
+        <v>19.7</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.9</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -838,58 +838,58 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>71.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I7" t="n">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
       <c r="J7" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1565</v>
+        <v>1573.8</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>46.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>53.4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -898,48 +898,48 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>70</v>
+        <v>71.8</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6</v>
+        <v>20.3</v>
       </c>
       <c r="K8" t="n">
         <v>10.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1573.8</v>
+        <v>1565</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="R8" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>74.5</v>
+        <v>71.5</v>
       </c>
       <c r="I9" t="n">
-        <v>39.9</v>
+        <v>41.2</v>
       </c>
       <c r="J9" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="K9" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -978,77 +978,77 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1577.2</v>
+        <v>1569.9</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="R9" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.5</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>58.5</v>
+        <v>74.5</v>
       </c>
       <c r="I10" t="n">
-        <v>32.3</v>
+        <v>40.4</v>
       </c>
       <c r="J10" t="n">
-        <v>17.7</v>
+        <v>19.6</v>
       </c>
       <c r="K10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1555.6</v>
+        <v>1577.2</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="R10" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="11">
@@ -1084,13 +1084,13 @@
         <v>28.9</v>
       </c>
       <c r="J11" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1141,16 +1141,16 @@
         <v>47.3</v>
       </c>
       <c r="I12" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="I13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="I14" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="J14" t="n">
         <v>12.6</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="I15" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="J15" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="K15" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="L15" t="n">
         <v>2.5</v>
@@ -1381,13 +1381,13 @@
         <v>51.7</v>
       </c>
       <c r="I16" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="J16" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
         <v>2.5</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Q16" t="n">
         <v>0.64</v>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53.1</v>
+        <v>53.6</v>
       </c>
       <c r="D17" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1438,19 +1438,19 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="I17" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>0.72</v>
@@ -1474,43 +1474,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>33.4</v>
+        <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>17.6</v>
+        <v>21.5</v>
       </c>
       <c r="J18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1518,17 +1518,17 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1560</v>
+        <v>1582.5</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="R18" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="19">
@@ -1543,38 +1543,38 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>52</v>
+        <v>56.1</v>
       </c>
       <c r="I19" t="n">
-        <v>27.1</v>
+        <v>21.3</v>
       </c>
       <c r="J19" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1582,55 +1582,55 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Q19" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>33.6</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>76.7</v>
       </c>
       <c r="H20" t="n">
-        <v>48.2</v>
+        <v>29.9</v>
       </c>
       <c r="I20" t="n">
-        <v>21.3</v>
+        <v>15.5</v>
       </c>
       <c r="J20" t="n">
-        <v>10.1</v>
+        <v>7.8</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,59 +1638,59 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1582.5</v>
+        <v>1560</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="R20" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>63.9</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>28.5</v>
+        <v>40.8</v>
       </c>
       <c r="I21" t="n">
-        <v>14.9</v>
+        <v>18.9</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1698,28 +1698,28 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1573.4</v>
+        <v>1544.1</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.22</v>
+        <v>0.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="R21" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1735,22 +1735,22 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>42.3</v>
+        <v>35.7</v>
       </c>
       <c r="I22" t="n">
-        <v>20.1</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1758,56 +1758,56 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1544.1</v>
+        <v>1546.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="R22" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>58.4</v>
+        <v>64.5</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
       <c r="H23" t="n">
-        <v>31.7</v>
+        <v>25.2</v>
       </c>
       <c r="I23" t="n">
-        <v>15.2</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.2</v>
@@ -1818,17 +1818,17 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1546.8</v>
+        <v>1573.4</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="24">
@@ -1855,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>92.8</v>
+        <v>98</v>
       </c>
       <c r="H24" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="I24" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="K24" t="n">
         <v>2.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1918,43 +1918,43 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>56.2</v>
+        <v>43.8</v>
       </c>
       <c r="I25" t="n">
-        <v>23.9</v>
+        <v>13.8</v>
       </c>
       <c r="J25" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1522.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1978,79 +1978,79 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>39.1</v>
+        <v>56.5</v>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1546.8</v>
+        <v>1522.7</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="R26" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>37.9</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>37.9</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>88.8</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>33.5</v>
+        <v>23.5</v>
       </c>
       <c r="I27" t="n">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
         <v>1.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2058,77 +2058,77 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1554.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.19</v>
+        <v>0.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="R27" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>38.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>86.3</v>
       </c>
       <c r="H28" t="n">
-        <v>23.6</v>
+        <v>32.9</v>
       </c>
       <c r="I28" t="n">
-        <v>9.4</v>
+        <v>11.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L28" t="n">
         <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1494.5</v>
+        <v>1554.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="29">
@@ -2155,22 +2155,22 @@
         <v>23.7</v>
       </c>
       <c r="G29" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="H29" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2218,19 +2218,19 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>34.7</v>
+        <v>35.1</v>
       </c>
       <c r="I30" t="n">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Q30" t="n">
         <v>0.98</v>
@@ -2275,22 +2275,22 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="I31" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2326,55 +2326,55 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E32" t="n">
-        <v>80.8</v>
+        <v>19.2</v>
       </c>
       <c r="F32" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>41.5</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>16.4</v>
+        <v>31.4</v>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1550.3</v>
+        <v>1521.7</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2386,49 +2386,49 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>80.8</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>19.2</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="H33" t="n">
-        <v>32.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1521.7</v>
+        <v>1550.3</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Q33" t="n">
         <v>0.79</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0.8</v>
-      </c>
       <c r="R33" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="34">
@@ -2458,13 +2458,13 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="I34" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="J34" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K34" t="n">
         <v>0.3</v>
@@ -2518,10 +2518,10 @@
         <v>19.1</v>
       </c>
       <c r="H35" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0.8</v>
@@ -2566,25 +2566,25 @@
         <v>9.9</v>
       </c>
       <c r="D36" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="E36" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="I36" t="n">
         <v>3.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K36" t="n">
         <v>0.1</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="Q36" t="n">
         <v>0.98</v>
@@ -2614,37 +2614,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>88.8</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2658,23 +2658,23 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1518</v>
+        <v>1519.9</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="R37" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2689,22 +2689,22 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1521.6</v>
+        <v>1523</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="R38" t="n">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2778,28 +2778,28 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1519.9</v>
+        <v>1534.7</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R39" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1523</v>
+        <v>1493.5</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="R40" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2898,28 +2898,28 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1534.7</v>
+        <v>1518</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2929,20 +2929,20 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F42" t="n">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.1</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
@@ -2958,28 +2958,28 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1493.5</v>
+        <v>1555</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2989,19 +2989,19 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="R43" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3078,28 +3078,28 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1484.3</v>
+        <v>1499.2</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.33</v>
+        <v>0.98</v>
       </c>
       <c r="R44" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -3134,21 +3134,21 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1499.2</v>
+        <v>1521.6</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.71</v>
+        <v>1.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="R45" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
@@ -3477,23 +3477,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E3" t="n">
-        <v>80.8</v>
+        <v>19.2</v>
       </c>
       <c r="F3" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>41.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -3504,23 +3504,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>80.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>19.2</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3730,13 +3730,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3757,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -3774,14 +3774,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -4102,19 +4102,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.5</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -4129,19 +4129,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.4</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>58.4</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>60.7</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -4186,16 +4186,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>88.8</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>92.8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
@@ -4456,16 +4456,16 @@
         <v>0.1</v>
       </c>
       <c r="D39" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G39" t="n">
-        <v>81.40000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="40">
@@ -4483,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>63.9</v>
+        <v>64.5</v>
       </c>
       <c r="F40" t="n">
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>65.40000000000001</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="41">
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F41" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="42">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="D42" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="E42" t="n">
         <v>0.2</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.1</v>
+        <v>53.6</v>
       </c>
       <c r="D43" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4600,7 +4600,7 @@
         <v>23.7</v>
       </c>
       <c r="G44" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="45">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="D46" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E46" t="n">
         <v>0.3</v>
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="D47" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="E47" t="n">
-        <v>37.9</v>
+        <v>38.2</v>
       </c>
       <c r="F47" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="n">
-        <v>88.8</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="48">
@@ -4699,16 +4699,16 @@
         <v>9.9</v>
       </c>
       <c r="D48" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="E48" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -4729,13 +4729,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F49" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="G49" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4870,13 +4870,13 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="J2" t="n">
         <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4921,129 +4921,129 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>England</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="I3" t="n">
-        <v>34</v>
+        <v>14.6</v>
       </c>
       <c r="J3" t="n">
-        <v>30.5</v>
+        <v>22.2</v>
       </c>
       <c r="K3" t="n">
-        <v>35.5</v>
+        <v>63.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>14.1</v>
+        <v>38.4</v>
       </c>
       <c r="P3" t="n">
-        <v>35.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00Z</t>
+          <t>2026-06-27T20:00:00Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.77</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
-        <v>2.53</v>
+        <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>9.199999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="J4" t="n">
-        <v>15.2</v>
+        <v>23.9</v>
       </c>
       <c r="K4" t="n">
-        <v>75.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>37.6</v>
+        <v>87.2</v>
       </c>
       <c r="P4" t="n">
-        <v>9.199999999999999</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5053,63 +5053,63 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>14.6</v>
+        <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>22.1</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>63.3</v>
+        <v>38.8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>38.4</v>
+        <v>13.4</v>
       </c>
       <c r="P5" t="n">
-        <v>14.6</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-27T20:00:00Z</t>
+          <t>2026-06-28T01:00:00Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5119,63 +5119,63 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>0.52</v>
       </c>
       <c r="H6" t="n">
-        <v>0.76</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="n">
-        <v>59.4</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>23.9</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>16.7</v>
+        <v>86</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>87.2</v>
+        <v>83.7</v>
       </c>
       <c r="P6" t="n">
-        <v>16.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5185,28 +5185,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>34.3</v>
+        <v>28.8</v>
       </c>
       <c r="J7" t="n">
-        <v>26.9</v>
+        <v>24.6</v>
       </c>
       <c r="K7" t="n">
-        <v>38.8</v>
+        <v>46.6</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -5215,33 +5215,33 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13.4</v>
+        <v>23.3</v>
       </c>
       <c r="P7" t="n">
-        <v>38.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00Z</t>
+          <t>2026-06-27T22:30:00Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5251,180 +5251,48 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>30.2</v>
       </c>
       <c r="K8" t="n">
-        <v>86</v>
+        <v>23.8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>83.7</v>
+        <v>6.9</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>71</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I9" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>28.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>72</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I10" t="n">
-        <v>46</v>
-      </c>
-      <c r="J10" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P10" t="n">
         <v>46</v>
       </c>
     </row>
@@ -5546,17 +5414,17 @@
         <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2159</v>
+        <v>1.2151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7486</v>
+        <v>0.7483</v>
       </c>
       <c r="M2" t="n">
         <v>0.729</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5460,7 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5193</v>
+        <v>1.5182</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5602,7 +5470,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5638,17 +5506,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8852</v>
+        <v>0.8847</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7272</v>
+        <v>0.7269</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5684,17 +5552,17 @@
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3173</v>
+        <v>1.3165</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7289</v>
+        <v>0.7287</v>
       </c>
       <c r="M5" t="n">
         <v>0.7222</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5715,32 +5583,32 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5159</v>
+        <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6854</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6408</v>
+        <v>0.6862</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5776,17 +5644,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0652</v>
+        <v>1.0645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9757</v>
+        <v>0.9751</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5822,17 +5690,17 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4907</v>
+        <v>1.4896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7544</v>
+        <v>0.7541</v>
       </c>
       <c r="M8" t="n">
         <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5868,17 +5736,17 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1847</v>
+        <v>1.1839</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6342</v>
+        <v>0.634</v>
       </c>
       <c r="M9" t="n">
         <v>0.5536</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5914,17 +5782,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9688</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7421</v>
+        <v>0.7418</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5828,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2993</v>
+        <v>1.2984</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7852</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0.7178</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6006,17 +5874,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.192</v>
+        <v>1.1912</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0011</v>
+        <v>1.0005</v>
       </c>
       <c r="M12" t="n">
         <v>0.6193</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6052,17 +5920,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9926</v>
+        <v>0.992</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3133</v>
+        <v>1.3123</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6098,17 +5966,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.151</v>
+        <v>1.1503</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8675</v>
+        <v>0.8671</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6144,17 +6012,17 @@
         <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8198</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6471</v>
+        <v>0.6469</v>
       </c>
       <c r="M15" t="n">
         <v>0.4986</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6190,17 +6058,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.86</v>
+        <v>0.8596</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5947</v>
+        <v>0.5945</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6236,17 +6104,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0401</v>
+        <v>1.0189</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6869</v>
+        <v>0.6883</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6263</v>
+        <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6282,17 +6150,17 @@
         <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2979</v>
+        <v>1.297</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5947</v>
+        <v>0.5945</v>
       </c>
       <c r="M18" t="n">
         <v>0.7464</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6328,17 +6196,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6224</v>
+        <v>1.6212</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7884</v>
+        <v>0.788</v>
       </c>
       <c r="M19" t="n">
         <v>0.839</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6377,14 +6245,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8576</v>
+        <v>0.8572</v>
       </c>
       <c r="M20" t="n">
         <v>0.7865</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6420,17 +6288,17 @@
         <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6851</v>
+        <v>0.6849</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9786</v>
+        <v>0.9781</v>
       </c>
       <c r="M21" t="n">
         <v>0.2939</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6466,17 +6334,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9574</v>
+        <v>0.9569</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1047</v>
+        <v>1.104</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6497,32 +6365,32 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1754</v>
+        <v>1.1325</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7231</v>
+        <v>0.7174</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5686</v>
+        <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6558,17 +6426,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6954</v>
+        <v>0.6952</v>
       </c>
       <c r="L24" t="n">
-        <v>1.279</v>
+        <v>1.2781</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6604,17 +6472,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1456</v>
+        <v>1.1448</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6367</v>
+        <v>0.6365</v>
       </c>
       <c r="M25" t="n">
         <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6650,17 +6518,17 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2505</v>
+        <v>1.2497</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6394</v>
+        <v>0.6391</v>
       </c>
       <c r="M26" t="n">
         <v>0.7245</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6696,17 +6564,17 @@
         <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8657</v>
+        <v>0.8652</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2805</v>
+        <v>1.2796</v>
       </c>
       <c r="M27" t="n">
         <v>0.1768</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6610,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0772</v>
+        <v>1.0765</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6752,7 +6620,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6656,7 @@
         <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3777</v>
+        <v>1.3767</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6798,7 +6666,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6834,17 +6702,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5491</v>
+        <v>1.5479</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8207</v>
+        <v>0.8203</v>
       </c>
       <c r="M30" t="n">
         <v>0.6995</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6865,32 +6733,32 @@
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J31" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9637</v>
+        <v>0.9363</v>
       </c>
       <c r="L31" t="n">
-        <v>1.2153</v>
+        <v>1.4087</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2416</v>
+        <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6926,17 +6794,17 @@
         <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5921</v>
+        <v>1.5909</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9922</v>
+        <v>0.9916</v>
       </c>
       <c r="M32" t="n">
         <v>0.6701</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6972,17 +6840,17 @@
         <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>1.0253</v>
+        <v>1.0246</v>
       </c>
       <c r="L33" t="n">
-        <v>1.004</v>
+        <v>1.0034</v>
       </c>
       <c r="M33" t="n">
         <v>0.448</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7018,17 +6886,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.917</v>
+        <v>0.9165</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8366</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>0.5275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7064,17 +6932,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4961</v>
+        <v>1.495</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7208</v>
+        <v>0.7205</v>
       </c>
       <c r="M35" t="n">
         <v>0.7388</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7110,17 +6978,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6926</v>
+        <v>0.6924</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3276</v>
+        <v>1.3267</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7156,17 +7024,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7063</v>
+        <v>0.706</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9848</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7202,17 +7070,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.048</v>
+        <v>1.0474</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8631</v>
+        <v>0.8626</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7248,17 +7116,17 @@
         <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3274</v>
+        <v>1.3265</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9301</v>
+        <v>0.9296</v>
       </c>
       <c r="M39" t="n">
         <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7294,17 +7162,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7944</v>
+        <v>0.794</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7957</v>
+        <v>0.7953</v>
       </c>
       <c r="M40" t="n">
         <v>0.4588</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7340,17 +7208,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9654</v>
+        <v>0.9649</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7871</v>
+        <v>0.7867</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7386,17 +7254,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4004</v>
+        <v>1.3994</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5774</v>
+        <v>0.5772</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7432,17 +7300,17 @@
         <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2745</v>
+        <v>1.2736</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3037</v>
+        <v>1.3028</v>
       </c>
       <c r="M43" t="n">
         <v>0.4405</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7478,17 +7346,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4191</v>
+        <v>1.4181</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8236</v>
+        <v>0.8232</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7392,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7164</v>
+        <v>0.7161</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4547</v>
+        <v>1.4537</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7570,17 +7438,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2213</v>
+        <v>1.2205</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9032</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7616,17 +7484,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3304</v>
+        <v>1.3295</v>
       </c>
       <c r="L47" t="n">
-        <v>1.138</v>
+        <v>1.1373</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7530,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7745</v>
+        <v>0.7742</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8465</v>
+        <v>0.8461</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7708,17 +7576,17 @@
         <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9422</v>
+        <v>0.9417</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1491</v>
+        <v>1.1483</v>
       </c>
       <c r="M49" t="n">
         <v>0.4067</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-26T23:00:00+00:00</t>
+          <t>2026-06-27T02:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -538,19 +538,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>76.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I2" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
       <c r="J2" t="n">
-        <v>36.9</v>
+        <v>39.8</v>
       </c>
       <c r="K2" t="n">
-        <v>23.4</v>
+        <v>25.1</v>
       </c>
       <c r="L2" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -562,13 +562,13 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="3">
@@ -598,19 +598,19 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>62.9</v>
+        <v>62.6</v>
       </c>
       <c r="I3" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="J3" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="K3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="L3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -658,19 +658,19 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>62.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
       </c>
       <c r="J4" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
       <c r="K4" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="L4" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -718,19 +718,19 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>67.7</v>
+        <v>66.8</v>
       </c>
       <c r="I5" t="n">
-        <v>49.9</v>
+        <v>48.5</v>
       </c>
       <c r="J5" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>62.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>34.2</v>
+        <v>38.7</v>
       </c>
       <c r="J6" t="n">
-        <v>19.7</v>
+        <v>23.2</v>
       </c>
       <c r="K6" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -802,24 +802,24 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="R6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -838,58 +838,58 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>69.8</v>
+        <v>75.2</v>
       </c>
       <c r="I7" t="n">
-        <v>41.1</v>
+        <v>43.9</v>
       </c>
       <c r="J7" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="K7" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1573.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="R7" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46.4</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -898,48 +898,48 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>71.8</v>
+        <v>75.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38.1</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1565</v>
+        <v>1577.2</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="R8" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>71.5</v>
+        <v>68.7</v>
       </c>
       <c r="I9" t="n">
-        <v>41.2</v>
+        <v>36.3</v>
       </c>
       <c r="J9" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="K9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -978,35 +978,35 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1569.9</v>
+        <v>1573.8</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.79</v>
+        <v>0.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1018,37 +1018,37 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>74.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>40.4</v>
+        <v>31.5</v>
       </c>
       <c r="J10" t="n">
-        <v>19.6</v>
+        <v>17.6</v>
       </c>
       <c r="K10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1577.2</v>
+        <v>1565</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="R10" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>52.6</v>
+        <v>51.9</v>
       </c>
       <c r="I11" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="J11" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1138,48 +1138,48 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>47.3</v>
+        <v>78.8</v>
       </c>
       <c r="I12" t="n">
-        <v>24.9</v>
+        <v>40.2</v>
       </c>
       <c r="J12" t="n">
-        <v>12.7</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1542.8</v>
+        <v>1541.7</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>37.1</v>
+        <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>21.9</v>
+        <v>25.6</v>
       </c>
       <c r="J13" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1218,17 +1218,17 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1571</v>
+        <v>1542.8</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="14">
@@ -1258,13 +1258,13 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="J14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="K14" t="n">
         <v>5.7</v>
@@ -1318,16 +1318,16 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="I15" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="J15" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
         <v>2.5</v>
@@ -1354,19 +1354,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1378,55 +1378,55 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>51.7</v>
+        <v>37.3</v>
       </c>
       <c r="I16" t="n">
-        <v>24.5</v>
+        <v>22.2</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>2.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1556.1</v>
+        <v>1571</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="R16" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53.6</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>46.4</v>
+        <v>100</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1438,37 +1438,37 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>65.3</v>
+        <v>52.2</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>24.6</v>
       </c>
       <c r="J17" t="n">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1541.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="18">
@@ -1498,19 +1498,19 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
       <c r="I18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="J18" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="I19" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="J19" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.7</v>
@@ -1594,7 +1594,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1603,73 +1603,73 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>65.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>33.6</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>29.9</v>
+        <v>44.9</v>
       </c>
       <c r="I20" t="n">
-        <v>15.5</v>
+        <v>23.9</v>
       </c>
       <c r="J20" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1560</v>
+        <v>1573.4</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1678,48 +1678,48 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>40.8</v>
+        <v>34.5</v>
       </c>
       <c r="I21" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="J21" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1544.1</v>
+        <v>1560</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>0.86</v>
+        <v>1.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="R21" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1735,22 +1735,22 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>81.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>35.7</v>
+        <v>40.5</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>18.4</v>
       </c>
       <c r="J22" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1758,158 +1758,158 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1546.8</v>
+        <v>1544.1</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="R22" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>64.5</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>61.1</v>
+        <v>80.7</v>
       </c>
       <c r="H23" t="n">
-        <v>25.2</v>
+        <v>31.4</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1573.4</v>
+        <v>1564.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="R23" t="n">
-        <v>0.73</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>38.4</v>
+        <v>44.1</v>
       </c>
       <c r="I24" t="n">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="J24" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1564.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,37 +1918,37 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>43.8</v>
+        <v>33</v>
       </c>
       <c r="I25" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="J25" t="n">
         <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1546.8</v>
+        <v>1537.9</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1978,16 +1978,16 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>56.5</v>
+        <v>53.9</v>
       </c>
       <c r="I26" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="L26" t="n">
         <v>0.6</v>
@@ -2014,12 +2014,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2038,19 +2038,19 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>23.5</v>
+        <v>33.3</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2058,158 +2058,158 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1494.5</v>
+        <v>1554.9</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>86.3</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>32.9</v>
+        <v>22.2</v>
       </c>
       <c r="I28" t="n">
-        <v>11.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
         <v>0.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1554.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.19</v>
+        <v>0.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="R28" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>76.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>45.9</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>18.3</v>
+        <v>26.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1537.9</v>
+        <v>1519.6</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>19.2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2218,34 +2218,34 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>35.1</v>
+        <v>31.4</v>
       </c>
       <c r="I30" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L30" t="n">
         <v>0.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1514.3</v>
+        <v>1521.7</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.06</v>
+        <v>0.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="R30" t="n">
         <v>0.46</v>
@@ -2254,12 +2254,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2278,19 +2278,19 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>26.9</v>
+        <v>30.8</v>
       </c>
       <c r="I31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2298,38 +2298,38 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1519.6</v>
+        <v>1514.3</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="R31" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>19.2</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2338,43 +2338,43 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>31.4</v>
+        <v>22.8</v>
       </c>
       <c r="I32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1521.7</v>
+        <v>1507.6</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.79</v>
+        <v>1.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2386,60 +2386,60 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>80.8</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>19.2</v>
       </c>
-      <c r="G33" t="n">
-        <v>29</v>
-      </c>
       <c r="H33" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1550.3</v>
+        <v>1534.2</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.96</v>
+        <v>1.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="R33" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2458,19 +2458,19 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>22.5</v>
+        <v>21.1</v>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2478,59 +2478,59 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1507.6</v>
+        <v>1467.7</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2538,88 +2538,88 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1534.2</v>
+        <v>1519.9</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="R35" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1467.7</v>
+        <v>1523</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2629,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1519.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.31</v>
+        <v>0.72</v>
       </c>
       <c r="R37" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2718,28 +2718,28 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1523</v>
+        <v>1534.7</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2778,28 +2778,28 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1534.7</v>
+        <v>1493.5</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R39" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1493.5</v>
+        <v>1518</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="R40" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2898,28 +2898,28 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1518</v>
+        <v>1555</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="R41" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2929,19 +2929,19 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2958,28 +2958,28 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>1.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="R42" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3018,28 +3018,28 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1484.3</v>
+        <v>1499.2</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.33</v>
+        <v>0.98</v>
       </c>
       <c r="R43" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3049,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3074,32 +3074,32 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1499.2</v>
+        <v>1521.6</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.71</v>
+        <v>1.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="R44" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -3138,17 +3138,17 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1521.6</v>
+        <v>1550.3</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="R45" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="46">
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>76.3</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3382,13 +3382,13 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="R49" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -3504,23 +3504,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>80.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>19.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -3531,23 +3531,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F5" t="n">
         <v>19.2</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>80.8</v>
-      </c>
       <c r="G5" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4168,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>81.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>98</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="37">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -4449,23 +4449,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>65.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>33.6</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
@@ -4476,23 +4476,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E40" t="n">
-        <v>64.5</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>61.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>53.4</v>
+        <v>100</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.6</v>
+        <v>100</v>
       </c>
       <c r="D43" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4591,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>76.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>45.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -4621,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>76.3</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="D46" t="n">
-        <v>31.5</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>86.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>59.1</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -4729,13 +4729,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4898,402 +4898,6 @@
       </c>
       <c r="P2" t="n">
         <v>19.2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>67</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-27T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-27T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I4" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>27</v>
-      </c>
-      <c r="K5" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>70</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-28T01:00:00Z</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>86</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I7" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>28.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>72</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-27T22:30:00Z</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>46</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5399,32 +5003,32 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2151</v>
+        <v>1.2864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7483</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.729</v>
+        <v>0.6801</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5445,32 +5049,32 @@
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5182</v>
+        <v>1.5715</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9166</v>
+        <v>0.9344</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5110,7 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8847</v>
+        <v>0.8844</v>
       </c>
       <c r="L4" t="n">
         <v>0.7269</v>
@@ -5516,7 +5120,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5540,29 +5144,29 @@
         <v>13</v>
       </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3165</v>
+        <v>1.388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7287</v>
+        <v>0.8436</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7222</v>
+        <v>0.678</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5601,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6831</v>
       </c>
       <c r="M6" t="n">
         <v>0.6862</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5644,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0645</v>
+        <v>1.0639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9751</v>
+        <v>0.9746</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5690,17 +5294,17 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4896</v>
+        <v>1.4881</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7541</v>
+        <v>0.754</v>
       </c>
       <c r="M8" t="n">
         <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5736,17 +5340,17 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1839</v>
+        <v>1.183</v>
       </c>
       <c r="L9" t="n">
-        <v>0.634</v>
+        <v>0.6342</v>
       </c>
       <c r="M9" t="n">
         <v>0.5536</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5782,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9678</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7418</v>
+        <v>0.7419</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5816,29 +5420,29 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2984</v>
+        <v>1.202</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7229</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7178</v>
+        <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5874,17 +5478,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1912</v>
+        <v>1.2076</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0005</v>
+        <v>0.9789</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6193</v>
+        <v>0.6611</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5920,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.992</v>
+        <v>0.9915</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3123</v>
+        <v>1.3112</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5966,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1503</v>
+        <v>1.1495</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8671</v>
+        <v>0.8669</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5994,10 +5598,10 @@
         <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -6006,23 +5610,23 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8198</v>
+        <v>0.9234</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6469</v>
+        <v>0.6524</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4986</v>
+        <v>0.5572</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6058,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8596</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5945</v>
+        <v>0.5948</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6104,7 +5708,7 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0189</v>
+        <v>1.0183</v>
       </c>
       <c r="L17" t="n">
         <v>0.6883</v>
@@ -6114,7 +5718,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6135,32 +5739,32 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.297</v>
+        <v>1.3097</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5945</v>
+        <v>0.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7464</v>
+        <v>0.7831</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6196,17 +5800,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6212</v>
+        <v>1.6194</v>
       </c>
       <c r="L19" t="n">
-        <v>0.788</v>
+        <v>0.7879</v>
       </c>
       <c r="M19" t="n">
         <v>0.839</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6245,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8572</v>
+        <v>0.8569</v>
       </c>
       <c r="M20" t="n">
         <v>0.7865</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6270,7 +5874,7 @@
         <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -6279,26 +5883,26 @@
         <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6849</v>
+        <v>0.6876</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9781</v>
+        <v>1.0173</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2939</v>
+        <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6334,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9569</v>
+        <v>0.9564</v>
       </c>
       <c r="L22" t="n">
-        <v>1.104</v>
+        <v>1.1032</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6380,7 +5984,7 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1325</v>
+        <v>1.1317</v>
       </c>
       <c r="L23" t="n">
         <v>0.7174</v>
@@ -6390,7 +5994,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6429,14 +6033,14 @@
         <v>0.6952</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2781</v>
+        <v>1.277</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6472,17 +6076,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1448</v>
+        <v>1.144</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6365</v>
+        <v>0.6367</v>
       </c>
       <c r="M25" t="n">
         <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6518,17 +6122,17 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2497</v>
+        <v>1.2486</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6391</v>
+        <v>0.6394</v>
       </c>
       <c r="M26" t="n">
         <v>0.7245</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6552,29 +6156,29 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8652</v>
+        <v>0.8541</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2796</v>
+        <v>1.3499</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1768</v>
+        <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0765</v>
+        <v>1.0758</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6620,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6260,7 @@
         <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3767</v>
+        <v>1.3754</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6666,7 +6270,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6702,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5479</v>
+        <v>1.5463</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8203</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>0.6995</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6748,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9363</v>
+        <v>0.9359</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4087</v>
+        <v>1.4073</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6794,17 +6398,17 @@
         <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5909</v>
+        <v>1.5892</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9916</v>
+        <v>0.9911</v>
       </c>
       <c r="M32" t="n">
         <v>0.6701</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6825,32 +6429,32 @@
         <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>1.0246</v>
+        <v>0.9366</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0034</v>
+        <v>1.0464</v>
       </c>
       <c r="M33" t="n">
-        <v>0.448</v>
+        <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6886,17 +6490,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9165</v>
+        <v>0.9162</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8361</v>
       </c>
       <c r="M34" t="n">
         <v>0.5275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6917,32 +6521,32 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>1.495</v>
+        <v>1.3711</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7205</v>
+        <v>0.6635</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7388</v>
+        <v>0.6884</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6978,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6924</v>
+        <v>0.6925</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3267</v>
+        <v>1.3255</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7027,14 +6631,14 @@
         <v>0.706</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9848</v>
+        <v>0.9843</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7070,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0474</v>
+        <v>1.0467</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8626</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7116,17 +6720,17 @@
         <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3265</v>
+        <v>1.3253</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9296</v>
+        <v>0.9292</v>
       </c>
       <c r="M39" t="n">
         <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7162,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.794</v>
+        <v>0.7938</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7953</v>
+        <v>0.7952</v>
       </c>
       <c r="M40" t="n">
         <v>0.4588</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7208,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9649</v>
+        <v>0.9644</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7867</v>
+        <v>0.7866</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7254,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3994</v>
+        <v>1.3981</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5772</v>
+        <v>0.5775</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7300,17 +6904,17 @@
         <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2736</v>
+        <v>1.2725</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3028</v>
+        <v>1.3017</v>
       </c>
       <c r="M43" t="n">
         <v>0.4405</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7346,17 +6950,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4181</v>
+        <v>1.4167</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8232</v>
+        <v>0.823</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7395,14 +6999,14 @@
         <v>0.7161</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4537</v>
+        <v>1.4522</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7438,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2205</v>
+        <v>1.2195</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.9024</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7484,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3295</v>
+        <v>1.3283</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1373</v>
+        <v>1.1365</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7533,14 +7137,14 @@
         <v>0.7742</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8461</v>
+        <v>0.846</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7165,32 @@
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9417</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>1.1483</v>
+        <v>1.2319</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4067</v>
+        <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00:00+00:00</t>
+          <t>2026-06-28T01:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,16 +538,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="J2" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="K2" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
         <v>15.1</v>
@@ -598,19 +598,19 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="I3" t="n">
-        <v>43.2</v>
+        <v>39.3</v>
       </c>
       <c r="J3" t="n">
-        <v>27.5</v>
+        <v>24.9</v>
       </c>
       <c r="K3" t="n">
-        <v>16.5</v>
+        <v>15.2</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -658,19 +658,19 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="J4" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="K4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>48.5</v>
       </c>
       <c r="J5" t="n">
-        <v>25.8</v>
+        <v>26.1</v>
       </c>
       <c r="K5" t="n">
         <v>13.9</v>
@@ -778,19 +778,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="I6" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J6" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="K6" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -838,19 +838,19 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>75.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="J7" t="n">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="K7" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -898,16 +898,16 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>75.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>41</v>
+        <v>36.2</v>
       </c>
       <c r="J8" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="K8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L8" t="n">
         <v>4.9</v>
@@ -918,28 +918,28 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1577.2</v>
+        <v>1573.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>68.7</v>
+        <v>75.7</v>
       </c>
       <c r="I9" t="n">
-        <v>36.3</v>
+        <v>41.3</v>
       </c>
       <c r="J9" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="K9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -978,28 +978,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1573.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1018,19 +1018,19 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>66.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>31.5</v>
+        <v>41.6</v>
       </c>
       <c r="J10" t="n">
-        <v>17.6</v>
+        <v>20.3</v>
       </c>
       <c r="K10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,28 +1038,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1565</v>
+        <v>1544.6</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1078,55 +1078,55 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>51.9</v>
+        <v>67</v>
       </c>
       <c r="I11" t="n">
-        <v>28.3</v>
+        <v>31.8</v>
       </c>
       <c r="J11" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1575.8</v>
+        <v>1565</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="R11" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1138,48 +1138,48 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>78.8</v>
+        <v>52.2</v>
       </c>
       <c r="I12" t="n">
-        <v>40.2</v>
+        <v>28.6</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="K12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1541.7</v>
+        <v>1575.8</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.72</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,55 +1198,55 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>48</v>
+        <v>78.5</v>
       </c>
       <c r="I13" t="n">
-        <v>25.6</v>
+        <v>40.3</v>
       </c>
       <c r="J13" t="n">
-        <v>12.4</v>
+        <v>16.8</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1542.8</v>
+        <v>1541.7</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1258,37 +1258,37 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>65.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="I14" t="n">
-        <v>26.1</v>
+        <v>25.1</v>
       </c>
       <c r="J14" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1544.6</v>
+        <v>1542.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -1318,10 +1318,10 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="I15" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -1330,7 +1330,7 @@
         <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1354,19 +1354,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1378,55 +1378,55 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>37.3</v>
+        <v>51.8</v>
       </c>
       <c r="I16" t="n">
-        <v>22.2</v>
+        <v>24.6</v>
       </c>
       <c r="J16" t="n">
         <v>11.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1571</v>
+        <v>1556.1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1438,48 +1438,48 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>52.2</v>
+        <v>36.9</v>
       </c>
       <c r="I17" t="n">
-        <v>24.6</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1556.1</v>
+        <v>1571</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1498,19 +1498,19 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>47.7</v>
+        <v>55.8</v>
       </c>
       <c r="I18" t="n">
-        <v>21.4</v>
+        <v>20.2</v>
       </c>
       <c r="J18" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1518,28 +1518,28 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1582.5</v>
+        <v>1560.9</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1558,16 +1558,16 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>55.8</v>
+        <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.7</v>
@@ -1578,17 +1578,17 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1560.9</v>
+        <v>1582.5</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="20">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="J20" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="J21" t="n">
         <v>8</v>
@@ -1690,7 +1690,7 @@
         <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="I22" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="J22" t="n">
         <v>7.4</v>
@@ -1765,7 +1765,7 @@
         <v>0.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="R22" t="n">
         <v>0.57</v>
@@ -1774,12 +1774,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1795,19 +1795,19 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>80.7</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>31.4</v>
+        <v>32.9</v>
       </c>
       <c r="I23" t="n">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="J23" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L23" t="n">
         <v>0.8</v>
@@ -1818,98 +1818,98 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1564.9</v>
+        <v>1537.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H24" t="n">
-        <v>44.1</v>
+        <v>31.8</v>
       </c>
       <c r="I24" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="K24" t="n">
         <v>2.1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1546.8</v>
+        <v>1564.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="R24" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,37 +1918,37 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>44.1</v>
       </c>
       <c r="I25" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="L25" t="n">
         <v>0.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1537.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
@@ -1978,13 +1978,13 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>53.9</v>
+        <v>53.3</v>
       </c>
       <c r="I26" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="J26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
         <v>1.7</v>
@@ -2014,12 +2014,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2038,19 +2038,19 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
       <c r="I27" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
         <v>1.3</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2058,28 +2058,28 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1554.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.21</v>
+        <v>0.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="R27" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2098,10 +2098,10 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>22.2</v>
+        <v>32.9</v>
       </c>
       <c r="I28" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
         <v>3.9</v>
@@ -2118,17 +2118,17 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1494.5</v>
+        <v>1554.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="R28" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="29">
@@ -2161,16 +2161,16 @@
         <v>26.4</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K29" t="n">
         <v>0.7</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2194,22 +2194,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>19.2</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2221,10 +2221,10 @@
         <v>31.4</v>
       </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="J30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K30" t="n">
         <v>0.6</v>
@@ -2234,18 +2234,18 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1521.7</v>
+        <v>1514.3</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="R30" t="n">
         <v>0.46</v>
@@ -2254,12 +2254,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2278,19 +2278,19 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>30.8</v>
+        <v>22.9</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2298,28 +2298,28 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1514.3</v>
+        <v>1507.6</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.97</v>
+        <v>1.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2338,19 +2338,19 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>22.8</v>
+        <v>21.4</v>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2358,23 +2358,23 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1507.6</v>
+        <v>1467.7</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="R32" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2386,60 +2386,60 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="E33" t="n">
         <v>19.2</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>19.2</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1534.2</v>
+        <v>1521.7</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="R33" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2449,73 +2449,73 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1467.7</v>
+        <v>1519.9</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="R34" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2538,17 +2538,17 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R35" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="36">
@@ -3520,7 +3520,7 @@
         <v>80.8</v>
       </c>
       <c r="G4" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="5">
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="37">
@@ -4870,13 +4870,13 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="J2" t="n">
         <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
     </row>
   </sheetData>
@@ -5018,17 +5018,17 @@
         <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2864</v>
+        <v>1.2867</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8629</v>
       </c>
       <c r="M2" t="n">
         <v>0.6801</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5715</v>
+        <v>1.5718</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8844</v>
+        <v>0.8849</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7269</v>
+        <v>0.7275</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.388</v>
+        <v>1.3883</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8436</v>
+        <v>0.8441</v>
       </c>
       <c r="M5" t="n">
         <v>0.678</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6831</v>
+        <v>0.6836</v>
       </c>
       <c r="M6" t="n">
         <v>0.6862</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0639</v>
+        <v>1.0643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9746</v>
+        <v>0.9751</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4881</v>
+        <v>1.4884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.754</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>0.7115</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5334,23 +5334,23 @@
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.183</v>
+        <v>1.1275</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6342</v>
+        <v>0.5789</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5536</v>
+        <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9678</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7419</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.202</v>
+        <v>1.2024</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7229</v>
+        <v>0.7234</v>
       </c>
       <c r="M11" t="n">
         <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2076</v>
+        <v>1.208</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9789</v>
+        <v>0.9794</v>
       </c>
       <c r="M12" t="n">
         <v>0.6611</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9915</v>
+        <v>0.9919</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3112</v>
+        <v>1.3115</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1495</v>
+        <v>1.1499</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8669</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9234</v>
+        <v>0.9238</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6524</v>
+        <v>0.6529</v>
       </c>
       <c r="M15" t="n">
         <v>0.5572</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8598</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5948</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0183</v>
+        <v>1.0188</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6883</v>
+        <v>0.6888</v>
       </c>
       <c r="M17" t="n">
         <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3097</v>
+        <v>1.31</v>
       </c>
       <c r="L18" t="n">
         <v>0.55</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6194</v>
+        <v>1.6197</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7879</v>
+        <v>0.7884</v>
       </c>
       <c r="M19" t="n">
         <v>0.839</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8569</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>0.7865</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6876</v>
+        <v>0.6882</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0173</v>
+        <v>1.0177</v>
       </c>
       <c r="M21" t="n">
         <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9564</v>
+        <v>0.9569</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1032</v>
+        <v>1.1037</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1317</v>
+        <v>1.1322</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7174</v>
+        <v>0.7179</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6952</v>
+        <v>0.6958</v>
       </c>
       <c r="L24" t="n">
-        <v>1.277</v>
+        <v>1.2774</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.144</v>
+        <v>1.1444</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6367</v>
+        <v>0.6372</v>
       </c>
       <c r="M25" t="n">
         <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2486</v>
+        <v>1.249</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6394</v>
+        <v>0.6399</v>
       </c>
       <c r="M26" t="n">
         <v>0.7245</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8541</v>
+        <v>0.8546</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3499</v>
+        <v>1.3502</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0758</v>
+        <v>1.0763</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3754</v>
+        <v>1.3758</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5463</v>
+        <v>1.5466</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8206</v>
       </c>
       <c r="M30" t="n">
         <v>0.6995</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9359</v>
+        <v>0.9363</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4073</v>
+        <v>1.4077</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5892</v>
+        <v>1.5895</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9911</v>
+        <v>0.9916</v>
       </c>
       <c r="M32" t="n">
         <v>0.6701</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9366</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0464</v>
+        <v>1.0468</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9162</v>
+        <v>0.9166</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8361</v>
+        <v>0.8365</v>
       </c>
       <c r="M34" t="n">
         <v>0.5275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3711</v>
+        <v>1.3715</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6635</v>
+        <v>0.664</v>
       </c>
       <c r="M35" t="n">
         <v>0.6884</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6925</v>
+        <v>0.6931</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3255</v>
+        <v>1.3258</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.706</v>
+        <v>0.7066</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9843</v>
+        <v>0.9847</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0467</v>
+        <v>1.0472</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8629</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3253</v>
+        <v>1.3257</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9292</v>
+        <v>0.9296</v>
       </c>
       <c r="M39" t="n">
         <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7938</v>
+        <v>0.749</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7952</v>
+        <v>0.791</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4588</v>
+        <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9644</v>
+        <v>0.9649</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7866</v>
+        <v>0.7871</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3981</v>
+        <v>1.3984</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5775</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2725</v>
+        <v>1.2729</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3017</v>
+        <v>1.302</v>
       </c>
       <c r="M43" t="n">
         <v>0.4405</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4167</v>
+        <v>1.417</v>
       </c>
       <c r="L44" t="n">
-        <v>0.823</v>
+        <v>0.8235</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7161</v>
+        <v>0.7166</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4522</v>
+        <v>1.4526</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2195</v>
+        <v>1.2199</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9024</v>
+        <v>0.9028</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3283</v>
+        <v>1.3287</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1365</v>
+        <v>1.1369</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7742</v>
+        <v>0.7746</v>
       </c>
       <c r="L48" t="n">
-        <v>0.846</v>
+        <v>0.8464</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9273</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2319</v>
+        <v>1.2323</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-28T01:00:00+00:00</t>
+          <t>2026-06-28T18:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,16 +538,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="J2" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="L2" t="n">
         <v>15.1</v>
@@ -598,23 +598,23 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>39.3</v>
+        <v>61.4</v>
       </c>
       <c r="J3" t="n">
-        <v>24.9</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="L3" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -622,13 +622,13 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4">
@@ -658,7 +658,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="I4" t="n">
         <v>41.2</v>
@@ -670,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -694,12 +694,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -718,19 +718,19 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>48.5</v>
+        <v>39.1</v>
       </c>
       <c r="J5" t="n">
-        <v>26.1</v>
+        <v>23.7</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="L5" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1555.6</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -778,16 +778,16 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>67</v>
+        <v>66.7</v>
       </c>
       <c r="I6" t="n">
-        <v>38.8</v>
+        <v>48.6</v>
       </c>
       <c r="J6" t="n">
-        <v>23.3</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="L6" t="n">
         <v>7.4</v>
@@ -798,17 +798,17 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1555.6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R6" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -838,23 +838,23 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>74.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="I7" t="n">
-        <v>43.3</v>
+        <v>55.7</v>
       </c>
       <c r="J7" t="n">
-        <v>21.2</v>
+        <v>25.8</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -874,12 +874,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -898,19 +898,19 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>36.2</v>
+        <v>52.1</v>
       </c>
       <c r="J8" t="n">
-        <v>19.1</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>9.9</v>
+        <v>12.2</v>
       </c>
       <c r="L8" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -918,35 +918,35 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1573.8</v>
+        <v>1542.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,55 +958,55 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>41.3</v>
+        <v>38.5</v>
       </c>
       <c r="J9" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1577.2</v>
+        <v>1544.6</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1018,37 +1018,37 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>41.6</v>
+        <v>36.4</v>
       </c>
       <c r="J10" t="n">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="K10" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="L10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1544.6</v>
+        <v>1573.8</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0.59</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>31.8</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1114,19 +1114,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1138,48 +1138,48 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>52.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>28.6</v>
+        <v>39.7</v>
       </c>
       <c r="J12" t="n">
-        <v>14.3</v>
+        <v>16.8</v>
       </c>
       <c r="K12" t="n">
         <v>7.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1575.8</v>
+        <v>1541.7</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,55 +1198,55 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>78.5</v>
+        <v>57.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40.3</v>
+        <v>33.5</v>
       </c>
       <c r="J13" t="n">
-        <v>16.8</v>
+        <v>14.1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1541.7</v>
+        <v>1545.2</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="R13" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1258,55 +1258,55 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>47.7</v>
+        <v>52.1</v>
       </c>
       <c r="I14" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="J14" t="n">
         <v>12.2</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1542.8</v>
+        <v>1556.1</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1318,58 +1318,58 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>57.4</v>
+        <v>47.8</v>
       </c>
       <c r="I15" t="n">
-        <v>33.2</v>
+        <v>22.2</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1545.2</v>
+        <v>1582.5</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="R15" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1378,55 +1378,55 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>51.8</v>
+        <v>45.1</v>
       </c>
       <c r="I16" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="J16" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1556.1</v>
+        <v>1573.4</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="R16" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1438,48 +1438,48 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9</v>
+        <v>56.1</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>20.4</v>
       </c>
       <c r="J17" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1571</v>
+        <v>1560.9</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1498,19 +1498,19 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>55.8</v>
+        <v>34.7</v>
       </c>
       <c r="I18" t="n">
-        <v>20.2</v>
+        <v>16.8</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1518,38 +1518,38 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1560.9</v>
+        <v>1560</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,48 +1558,48 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>48.1</v>
+        <v>121.4</v>
       </c>
       <c r="I19" t="n">
-        <v>21.5</v>
+        <v>42.9</v>
       </c>
       <c r="J19" t="n">
-        <v>9.5</v>
+        <v>11.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 16强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1582.5</v>
+        <v>1519.6</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>0.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.99</v>
+        <v>0.83</v>
       </c>
       <c r="R19" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>45</v>
+        <v>40.5</v>
       </c>
       <c r="I20" t="n">
-        <v>24.1</v>
+        <v>18.4</v>
       </c>
       <c r="J20" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1573.4</v>
+        <v>1544.1</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1678,58 +1678,58 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>34.8</v>
+        <v>32.8</v>
       </c>
       <c r="I21" t="n">
-        <v>16.8</v>
+        <v>13.3</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1560</v>
+        <v>1537.9</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.39</v>
+        <v>0.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1738,48 +1738,48 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>40.8</v>
+        <v>43.8</v>
       </c>
       <c r="I22" t="n">
-        <v>18.7</v>
+        <v>13.6</v>
       </c>
       <c r="J22" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1544.1</v>
+        <v>1546.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="R22" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1795,22 +1795,22 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H23" t="n">
-        <v>32.9</v>
+        <v>31.7</v>
       </c>
       <c r="I23" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="J23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1818,88 +1818,88 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1537.9</v>
+        <v>1564.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>31.8</v>
+        <v>53.1</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>17.4</v>
       </c>
       <c r="J24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1564.9</v>
+        <v>1522.7</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1918,19 +1918,19 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>44.1</v>
+        <v>32.9</v>
       </c>
       <c r="I25" t="n">
-        <v>13.7</v>
+        <v>10.1</v>
       </c>
       <c r="J25" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1938,35 +1938,35 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1546.8</v>
+        <v>1554.9</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.88</v>
+        <v>1.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="R25" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1978,58 +1978,58 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>53.3</v>
+        <v>22.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17.6</v>
+        <v>9.6</v>
       </c>
       <c r="J26" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1522.7</v>
+        <v>1494.5</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.33</v>
+        <v>0.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.14</v>
+        <v>0.74</v>
       </c>
       <c r="R26" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2038,58 +2038,58 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>22.3</v>
+        <v>16.6</v>
       </c>
       <c r="I27" t="n">
-        <v>9.9</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1494.5</v>
+        <v>1514.3</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2098,48 +2098,48 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>32.9</v>
+        <v>19.9</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1554.9</v>
+        <v>1507.6</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.98</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2158,19 +2158,19 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>26.4</v>
+        <v>21.3</v>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2178,38 +2178,38 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1519.6</v>
+        <v>1467.7</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="R29" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>19.2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2218,48 +2218,48 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>31.4</v>
+        <v>2.8</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1514.3</v>
+        <v>1521.7</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="R30" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2269,127 +2269,127 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1507.6</v>
+        <v>1519.9</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.27</v>
+        <v>0.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R31" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
       <c r="H32" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1467.7</v>
+        <v>1534.2</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
       <c r="R32" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2398,48 +2398,48 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1521.7</v>
+        <v>1577.2</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.75</v>
+        <v>1.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2478,44 +2478,44 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1519.9</v>
+        <v>1523</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2534,32 +2534,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1534.2</v>
+        <v>1546.8</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="R35" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2598,44 +2598,44 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1523</v>
+        <v>1534.7</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1546.8</v>
+        <v>1575.8</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="R37" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2718,32 +2718,32 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1534.7</v>
+        <v>1493.5</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2774,21 +2774,21 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1493.5</v>
+        <v>1571</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.85</v>
+        <v>1.49</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R39" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="40">
@@ -3025,7 +3025,7 @@
         <v>0.71</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="R43" t="n">
         <v>0.34</v>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Q45" t="n">
         <v>0.79</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="Q48" t="n">
         <v>0.85</v>
@@ -3774,17 +3774,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -3882,14 +3882,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3946,13 +3946,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3976,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -3990,17 +3990,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4017,14 +4017,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4044,17 +4044,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -5018,17 +5018,17 @@
         <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2867</v>
+        <v>1.2868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8629</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0.6801</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5718</v>
+        <v>1.5714</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8849</v>
+        <v>0.8853</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7275</v>
+        <v>0.7281</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3883</v>
+        <v>1.3882</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8441</v>
+        <v>0.8446</v>
       </c>
       <c r="M5" t="n">
         <v>0.678</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6836</v>
+        <v>0.6843</v>
       </c>
       <c r="M6" t="n">
         <v>0.6862</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0643</v>
+        <v>1.0646</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9751</v>
+        <v>0.9754</v>
       </c>
       <c r="M7" t="n">
         <v>0.4603</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5288,23 +5288,23 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4884</v>
+        <v>1.476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7564</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7115</v>
+        <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1275</v>
+        <v>1.1278</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5789</v>
+        <v>0.5796</v>
       </c>
       <c r="M9" t="n">
         <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9686</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2024</v>
+        <v>1.2025</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7234</v>
+        <v>0.724</v>
       </c>
       <c r="M11" t="n">
         <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.208</v>
+        <v>1.2081</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9794</v>
+        <v>0.9797</v>
       </c>
       <c r="M12" t="n">
         <v>0.6611</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9919</v>
+        <v>0.9923</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3115</v>
+        <v>1.3116</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1499</v>
+        <v>1.15</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8678</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9238</v>
+        <v>0.9242</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6529</v>
+        <v>0.6536</v>
       </c>
       <c r="M15" t="n">
         <v>0.5572</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8598</v>
+        <v>0.8603</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5961</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0188</v>
+        <v>1.0191</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6888</v>
+        <v>0.6895</v>
       </c>
       <c r="M17" t="n">
         <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6197</v>
+        <v>1.6193</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7884</v>
+        <v>0.789</v>
       </c>
       <c r="M19" t="n">
         <v>0.839</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5831,10 +5831,10 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
@@ -5843,20 +5843,20 @@
         <v>53</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.852</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7865</v>
+        <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6882</v>
+        <v>0.6889</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0177</v>
+        <v>1.018</v>
       </c>
       <c r="M21" t="n">
         <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9569</v>
+        <v>0.9573</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1037</v>
+        <v>1.1039</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1322</v>
+        <v>1.1324</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7179</v>
+        <v>0.7186</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6958</v>
+        <v>0.6964</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2774</v>
+        <v>1.2775</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1444</v>
+        <v>1.1446</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6372</v>
+        <v>0.6379</v>
       </c>
       <c r="M25" t="n">
         <v>0.7252</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6107,32 +6107,32 @@
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.249</v>
+        <v>1.2024</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6399</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7245</v>
+        <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8546</v>
+        <v>0.8551</v>
       </c>
       <c r="L27" t="n">
         <v>1.3502</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0763</v>
+        <v>1.0765</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6245,32 +6245,32 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3758</v>
+        <v>1.3329</v>
       </c>
       <c r="L29" t="n">
-        <v>0.55</v>
+        <v>0.5523</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8036</v>
+        <v>0.7594</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6294,29 +6294,29 @@
         <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J30" t="n">
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.5466</v>
+        <v>1.493</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8206</v>
+        <v>0.8137</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6995</v>
+        <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9363</v>
+        <v>0.9367</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4077</v>
+        <v>1.4076</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5895</v>
+        <v>1.5892</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9916</v>
+        <v>0.9919</v>
       </c>
       <c r="M32" t="n">
         <v>0.6701</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9375</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0468</v>
+        <v>1.0471</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6484,23 +6484,23 @@
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9166</v>
+        <v>0.9065</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8365</v>
+        <v>0.8323</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5275</v>
+        <v>0.5065</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3715</v>
+        <v>1.3714</v>
       </c>
       <c r="L35" t="n">
-        <v>0.664</v>
+        <v>0.6647</v>
       </c>
       <c r="M35" t="n">
         <v>0.6884</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6931</v>
+        <v>0.6938</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3258</v>
+        <v>1.3257</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7066</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9847</v>
+        <v>0.9851</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0472</v>
+        <v>1.0475</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8629</v>
+        <v>0.8633</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3257</v>
+        <v>1.3258</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9296</v>
+        <v>0.9301</v>
       </c>
       <c r="M39" t="n">
         <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.749</v>
+        <v>0.7496</v>
       </c>
       <c r="L40" t="n">
-        <v>0.791</v>
+        <v>0.7915</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9649</v>
+        <v>0.9653</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7871</v>
+        <v>0.7877</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3984</v>
+        <v>1.3983</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5789</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.417</v>
+        <v>1.4169</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8235</v>
+        <v>0.824</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7166</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4526</v>
+        <v>1.4525</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2199</v>
+        <v>1.22</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9028</v>
+        <v>0.9033</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7091,14 +7091,14 @@
         <v>1.3287</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1369</v>
+        <v>1.1371</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7746</v>
+        <v>0.7753</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8464</v>
+        <v>0.847</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9273</v>
+        <v>0.9278</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2323</v>
+        <v>1.2324</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-28T18:00:00+00:00</t>
+          <t>2026-06-30T00:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,16 +538,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="J2" t="n">
         <v>39.9</v>
       </c>
       <c r="K2" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="L2" t="n">
         <v>15.1</v>
@@ -601,16 +601,16 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
       <c r="J3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>24.3</v>
+        <v>21.9</v>
       </c>
       <c r="L3" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -634,12 +634,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -658,48 +658,48 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>65.2</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>41.2</v>
+        <v>75.8</v>
       </c>
       <c r="J4" t="n">
-        <v>26.2</v>
+        <v>37.8</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>20.9</v>
       </c>
       <c r="L4" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1603.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="R4" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -718,19 +718,19 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>67.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="I5" t="n">
-        <v>39.1</v>
+        <v>41.3</v>
       </c>
       <c r="J5" t="n">
-        <v>23.7</v>
+        <v>26.4</v>
       </c>
       <c r="K5" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1593.4</v>
+        <v>1603.8</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="R5" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -778,16 +778,16 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>66.7</v>
+        <v>67.2</v>
       </c>
       <c r="I6" t="n">
-        <v>48.6</v>
+        <v>38.7</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>23.7</v>
       </c>
       <c r="K6" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="L6" t="n">
         <v>7.4</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1555.6</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -838,37 +838,37 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>75.5</v>
+        <v>66.5</v>
       </c>
       <c r="I7" t="n">
-        <v>55.7</v>
+        <v>48.2</v>
       </c>
       <c r="J7" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1569.9</v>
+        <v>1555.6</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="R7" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -901,16 +901,16 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="K8" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,55 +958,55 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>38.5</v>
+        <v>36.9</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>19.9</v>
       </c>
       <c r="K9" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>4.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1544.6</v>
+        <v>1573.8</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0.59</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1018,48 +1018,48 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>36.4</v>
+        <v>47.9</v>
       </c>
       <c r="J10" t="n">
-        <v>19.3</v>
+        <v>21.8</v>
       </c>
       <c r="K10" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1573.8</v>
+        <v>1582.5</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>67.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>31.8</v>
+        <v>38.7</v>
       </c>
       <c r="J11" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="K11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,23 +1098,23 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1565</v>
+        <v>1544.6</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1138,48 +1138,48 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>78.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I12" t="n">
-        <v>39.7</v>
+        <v>31.8</v>
       </c>
       <c r="J12" t="n">
-        <v>16.8</v>
+        <v>17.6</v>
       </c>
       <c r="K12" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1541.7</v>
+        <v>1565</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,55 +1198,55 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>57.4</v>
+        <v>78.5</v>
       </c>
       <c r="I13" t="n">
-        <v>33.5</v>
+        <v>40.3</v>
       </c>
       <c r="J13" t="n">
-        <v>14.1</v>
+        <v>16.9</v>
       </c>
       <c r="K13" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1545.2</v>
+        <v>1541.7</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1258,48 +1258,48 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>52.1</v>
+        <v>58.2</v>
       </c>
       <c r="I14" t="n">
-        <v>25.6</v>
+        <v>33.5</v>
       </c>
       <c r="J14" t="n">
-        <v>12.2</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1556.1</v>
+        <v>1545.2</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="R14" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1318,19 +1318,19 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>47.8</v>
+        <v>56.1</v>
       </c>
       <c r="I15" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="J15" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1338,17 +1338,17 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1582.5</v>
+        <v>1560.9</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -1378,19 +1378,19 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="I16" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="J16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1414,12 +1414,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1438,19 +1438,19 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>56.1</v>
+        <v>34.2</v>
       </c>
       <c r="I17" t="n">
-        <v>20.4</v>
+        <v>16.4</v>
       </c>
       <c r="J17" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1458,38 +1458,38 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1560.9</v>
+        <v>1560</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1498,48 +1498,48 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>34.7</v>
+        <v>40.6</v>
       </c>
       <c r="I18" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="J18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1560</v>
+        <v>1544.1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>0.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1555,51 +1555,51 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H19" t="n">
-        <v>121.4</v>
+        <v>31.7</v>
       </c>
       <c r="I19" t="n">
-        <v>42.9</v>
+        <v>14.5</v>
       </c>
       <c r="J19" t="n">
-        <v>11.7</v>
+        <v>5.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第3 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1519.6</v>
+        <v>1564.9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0.91</v>
+        <v>1.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>40.5</v>
+        <v>32.7</v>
       </c>
       <c r="I20" t="n">
-        <v>18.4</v>
+        <v>13.2</v>
       </c>
       <c r="J20" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1544.1</v>
+        <v>1537.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1678,43 +1678,43 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>32.8</v>
+        <v>43.8</v>
       </c>
       <c r="I21" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="J21" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1537.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1738,34 +1738,34 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>43.8</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>13.6</v>
+        <v>24.1</v>
       </c>
       <c r="J22" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1546.8</v>
+        <v>1519.6</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="R22" t="n">
         <v>0.51</v>
@@ -1774,79 +1774,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>31.7</v>
+        <v>54.4</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1564.9</v>
+        <v>1522.7</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1858,37 +1858,37 @@
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>53.1</v>
+        <v>22.3</v>
       </c>
       <c r="I24" t="n">
-        <v>17.4</v>
+        <v>9.9</v>
       </c>
       <c r="J24" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1522.7</v>
+        <v>1494.5</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.33</v>
+        <v>0.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.14</v>
+        <v>0.74</v>
       </c>
       <c r="R24" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="25">
@@ -1918,16 +1918,16 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>32.9</v>
+        <v>33.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L25" t="n">
         <v>0.4</v>
@@ -1954,22 +1954,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1978,48 +1978,48 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>22.2</v>
+        <v>16.4</v>
       </c>
       <c r="I26" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1494.5</v>
+        <v>1514.3</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="R26" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2038,19 +2038,19 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>16.6</v>
+        <v>21.4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2058,17 +2058,17 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1514.3</v>
+        <v>1467.7</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="R27" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -2098,19 +2098,19 @@
         <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>19.9</v>
+        <v>14.1</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2122,34 +2122,34 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="R28" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>19.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2158,73 +2158,73 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>21.3</v>
+        <v>2.8</v>
       </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1467.7</v>
+        <v>1521.7</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="R29" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2234,48 +2234,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1521.7</v>
+        <v>1519.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.79</v>
+        <v>1.31</v>
       </c>
       <c r="R30" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2298,44 +2298,44 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R31" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,36 +2354,36 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1534.2</v>
+        <v>1577.2</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1577.2</v>
+        <v>1523</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>0.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0.74</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2474,32 +2474,32 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1523</v>
+        <v>1546.8</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2509,10 +2509,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2534,48 +2534,48 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1546.8</v>
+        <v>1534.7</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.72</v>
+        <v>1.28</v>
       </c>
       <c r="R35" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2594,21 +2594,21 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1534.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R36" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="37">
@@ -3025,7 +3025,7 @@
         <v>0.71</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="R43" t="n">
         <v>0.34</v>
@@ -3774,17 +3774,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3882,17 +3882,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3919,13 +3919,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3936,11 +3936,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2868</v>
+        <v>1.2863</v>
       </c>
       <c r="L2" t="n">
         <v>0.8633999999999999</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5714</v>
+        <v>1.5706</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8853</v>
+        <v>0.8854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7281</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3882</v>
+        <v>1.3876</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8446</v>
+        <v>0.8447</v>
       </c>
       <c r="M5" t="n">
         <v>0.678</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6843</v>
+        <v>0.6846</v>
       </c>
       <c r="M6" t="n">
         <v>0.6862</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0646</v>
+        <v>1.0644</v>
       </c>
       <c r="L7" t="n">
         <v>0.9754</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.476</v>
+        <v>1.4753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7564</v>
+        <v>0.7565</v>
       </c>
       <c r="M8" t="n">
         <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1278</v>
+        <v>1.1275</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5796</v>
+        <v>0.58</v>
       </c>
       <c r="M9" t="n">
         <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9686</v>
+        <v>0.9685</v>
       </c>
       <c r="L10" t="n">
-        <v>0.743</v>
+        <v>0.7433</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2025</v>
+        <v>1.2021</v>
       </c>
       <c r="L11" t="n">
-        <v>0.724</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2081</v>
+        <v>1.2078</v>
       </c>
       <c r="L12" t="n">
         <v>0.9797</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923</v>
+        <v>0.9922</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3116</v>
+        <v>1.3111</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.15</v>
+        <v>1.1497</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8678</v>
+        <v>0.8679</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5619,14 +5619,14 @@
         <v>0.9242</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6536</v>
+        <v>0.6539</v>
       </c>
       <c r="M15" t="n">
         <v>0.5572</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8603</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5961</v>
+        <v>0.5965</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0191</v>
+        <v>1.019</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6895</v>
+        <v>0.6897</v>
       </c>
       <c r="M17" t="n">
         <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.31</v>
+        <v>1.3096</v>
       </c>
       <c r="L18" t="n">
         <v>0.55</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5794,23 +5794,23 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6193</v>
+        <v>1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0.789</v>
+        <v>0.7307</v>
       </c>
       <c r="M19" t="n">
-        <v>0.839</v>
+        <v>0.8551</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.852</v>
+        <v>0.8521</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6889</v>
+        <v>0.6892</v>
       </c>
       <c r="L21" t="n">
-        <v>1.018</v>
+        <v>1.0179</v>
       </c>
       <c r="M21" t="n">
         <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9573</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1039</v>
+        <v>1.1037</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1324</v>
+        <v>1.1321</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7186</v>
+        <v>0.7188</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6964</v>
+        <v>0.6967</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2775</v>
+        <v>1.277</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6061,32 +6061,32 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1446</v>
+        <v>1.1049</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6379</v>
+        <v>0.6936</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7252</v>
+        <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2024</v>
+        <v>1.2021</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7003</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8551</v>
+        <v>0.8552</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3502</v>
+        <v>1.3497</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0765</v>
+        <v>1.0764</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3329</v>
+        <v>1.3324</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5523</v>
+        <v>0.5526</v>
       </c>
       <c r="M29" t="n">
         <v>0.7594</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.493</v>
+        <v>1.4923</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8137</v>
+        <v>0.8138</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6355,14 +6355,14 @@
         <v>0.9367</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4076</v>
+        <v>1.407</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6383,32 +6383,32 @@
         <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5892</v>
+        <v>1.5813</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9919</v>
+        <v>0.9567</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6701</v>
+        <v>0.7113</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9375</v>
+        <v>0.9374</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0471</v>
+        <v>1.047</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6493,14 +6493,14 @@
         <v>0.9065</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8323</v>
+        <v>0.8324</v>
       </c>
       <c r="M34" t="n">
         <v>0.5065</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3714</v>
+        <v>1.3709</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6647</v>
+        <v>0.665</v>
       </c>
       <c r="M35" t="n">
         <v>0.6884</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6938</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3257</v>
+        <v>1.3252</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.7074</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9851</v>
+        <v>0.985</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0475</v>
+        <v>1.0473</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8633</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3258</v>
+        <v>1.3253</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9301</v>
+        <v>0.93</v>
       </c>
       <c r="M39" t="n">
         <v>0.5009</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7496</v>
+        <v>0.7498</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7915</v>
+        <v>0.7917</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9653</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7877</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3983</v>
+        <v>1.3977</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5789</v>
+        <v>0.5793</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
         <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
         <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2729</v>
+        <v>1.1725</v>
       </c>
       <c r="L43" t="n">
-        <v>1.302</v>
+        <v>1.3717</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4405</v>
+        <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4169</v>
+        <v>1.4163</v>
       </c>
       <c r="L44" t="n">
-        <v>0.824</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>0.6588000000000001</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7174</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4525</v>
+        <v>1.4519</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.22</v>
+        <v>1.2196</v>
       </c>
       <c r="L46" t="n">
         <v>0.9033</v>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3287</v>
+        <v>1.3282</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1371</v>
+        <v>1.1368</v>
       </c>
       <c r="M47" t="n">
         <v>0.5548</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7753</v>
+        <v>0.7755</v>
       </c>
       <c r="L48" t="n">
-        <v>0.847</v>
+        <v>0.8471</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9278</v>
+        <v>0.9277</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2324</v>
+        <v>1.232</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-30T00:00:00+00:00</t>
+          <t>2026-06-30T20:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,19 +538,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I2" t="n">
         <v>56</v>
       </c>
       <c r="J2" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="K2" t="n">
-        <v>25.5</v>
+        <v>24.3</v>
       </c>
       <c r="L2" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>61.2</v>
+        <v>60.9</v>
       </c>
       <c r="J3" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="K3" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="L3" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -634,12 +634,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -661,45 +661,45 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>75.8</v>
+        <v>58.3</v>
       </c>
       <c r="J4" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="K4" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="L4" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -718,48 +718,48 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>65.7</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>41.3</v>
+        <v>76.2</v>
       </c>
       <c r="J5" t="n">
-        <v>26.4</v>
+        <v>38.4</v>
       </c>
       <c r="K5" t="n">
-        <v>14.4</v>
+        <v>20.9</v>
       </c>
       <c r="L5" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1603.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -778,48 +778,48 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>67.2</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>38.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>23.7</v>
+        <v>34.8</v>
       </c>
       <c r="K6" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="L6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1555.6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -838,19 +838,19 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>66.5</v>
+        <v>65.2</v>
       </c>
       <c r="I7" t="n">
-        <v>48.2</v>
+        <v>40.8</v>
       </c>
       <c r="J7" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -858,17 +858,17 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1555.6</v>
+        <v>1603.8</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -904,13 +904,13 @@
         <v>52</v>
       </c>
       <c r="J8" t="n">
-        <v>24.6</v>
+        <v>22.9</v>
       </c>
       <c r="K8" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="L8" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0.76</v>
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="I9" t="n">
-        <v>36.9</v>
+        <v>33.1</v>
       </c>
       <c r="J9" t="n">
-        <v>19.9</v>
+        <v>17.8</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1024,13 +1024,13 @@
         <v>47.9</v>
       </c>
       <c r="J10" t="n">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="L10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1054,12 +1054,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>38.7</v>
+        <v>31.9</v>
       </c>
       <c r="J11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,28 +1098,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1544.6</v>
+        <v>1565</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1138,19 +1138,19 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>66.5</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>31.8</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1158,17 +1158,17 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1565</v>
+        <v>1544.6</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="13">
@@ -1198,16 +1198,16 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="I13" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="J13" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="L13" t="n">
         <v>2.9</v>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>58.2</v>
+        <v>59.1</v>
       </c>
       <c r="I14" t="n">
-        <v>33.5</v>
+        <v>34.1</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>1.6</v>
@@ -1354,22 +1354,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1378,37 +1378,37 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>44.7</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>24.1</v>
+        <v>32.8</v>
       </c>
       <c r="J16" t="n">
-        <v>9.9</v>
+        <v>11.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1573.4</v>
+        <v>1522.7</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="R16" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="17">
@@ -1438,16 +1438,16 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
       <c r="I17" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="J17" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -1474,22 +1474,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1498,48 +1498,48 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>40.6</v>
+        <v>43.9</v>
       </c>
       <c r="I18" t="n">
-        <v>18.6</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1544.1</v>
+        <v>1546.8</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="R18" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1555,22 +1555,22 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>31.7</v>
+        <v>19.4</v>
       </c>
       <c r="I19" t="n">
-        <v>14.5</v>
+        <v>10.7</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1578,28 +1578,28 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1564.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>32.7</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>13.2</v>
+        <v>23.7</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,38 +1638,38 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1537.9</v>
+        <v>1519.6</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1678,58 +1678,58 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>43.8</v>
+        <v>24.8</v>
       </c>
       <c r="I21" t="n">
-        <v>13.7</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1546.8</v>
+        <v>1544.1</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1738,55 +1738,55 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>22.4</v>
       </c>
       <c r="I22" t="n">
-        <v>24.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1519.6</v>
+        <v>1494.5</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="R22" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1798,103 +1798,103 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>54.4</v>
+        <v>33</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>10.4</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1522.7</v>
+        <v>1554.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="R23" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H24" t="n">
-        <v>22.3</v>
+        <v>17.1</v>
       </c>
       <c r="I24" t="n">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1494.5</v>
+        <v>1564.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.97</v>
+        <v>1.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1906,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,48 +1918,48 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>33.4</v>
+        <v>21.2</v>
       </c>
       <c r="I25" t="n">
-        <v>10.3</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1554.9</v>
+        <v>1467.7</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1978,19 +1978,19 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>16.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1998,28 +1998,28 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1514.3</v>
+        <v>1507.6</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.98</v>
+        <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2038,16 +2038,16 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2058,28 +2058,28 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1467.7</v>
+        <v>1514.3</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2089,52 +2089,52 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1507.6</v>
+        <v>1519.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2146,25 +2146,25 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>80.8</v>
       </c>
-      <c r="E29" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
       <c r="H29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2174,32 +2174,32 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1521.7</v>
+        <v>1534.2</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.75</v>
+        <v>1.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="R29" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2209,13 +2209,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2234,48 +2234,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1519.9</v>
+        <v>1537.9</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
       <c r="R30" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2294,36 +2294,36 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1534.2</v>
+        <v>1577.2</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="R31" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2332,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,32 +2354,32 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1577.2</v>
+        <v>1523</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>0.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.74</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2389,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1523</v>
+        <v>1546.8</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2474,48 +2474,48 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1546.8</v>
+        <v>1534.7</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.72</v>
+        <v>1.28</v>
       </c>
       <c r="R34" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2534,32 +2534,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1534.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R35" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2598,44 +2598,44 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1556.1</v>
+        <v>1575.8</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2654,36 +2654,36 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1575.8</v>
+        <v>1493.5</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="R37" t="n">
-        <v>0.64</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2692,10 +2692,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2714,36 +2714,36 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1493.5</v>
+        <v>1571</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.86</v>
+        <v>1.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2774,32 +2774,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1571</v>
+        <v>1518</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="R39" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1518</v>
+        <v>1555</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2898,28 +2898,28 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="R41" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2958,28 +2958,28 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1484.3</v>
+        <v>1499.2</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.33</v>
+        <v>0.98</v>
       </c>
       <c r="R42" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2989,10 +2989,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3014,48 +3014,48 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1499.2</v>
+        <v>1521.6</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.71</v>
+        <v>1.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="R43" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="E44" t="n">
-        <v>100</v>
+        <v>19.2</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -3074,21 +3074,21 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1521.6</v>
+        <v>1521.7</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="45">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="Q45" t="n">
         <v>0.79</v>
@@ -3477,23 +3477,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>80.8</v>
       </c>
-      <c r="E3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="4">
@@ -3504,23 +3504,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="E4" t="n">
         <v>19.2</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -3774,14 +3774,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -5018,17 +5018,17 @@
         <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2863</v>
+        <v>1.2854</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8633</v>
       </c>
       <c r="M2" t="n">
         <v>0.6801</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5706</v>
+        <v>1.5691</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8854</v>
+        <v>0.8852</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7285</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3876</v>
+        <v>1.3864</v>
       </c>
       <c r="L5" t="n">
         <v>0.8447</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5187,16 +5187,16 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J6" t="n">
         <v>19</v>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6846</v>
+        <v>0.7362</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6862</v>
+        <v>0.7259</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0644</v>
+        <v>0.99</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9754</v>
+        <v>1.0064</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4603</v>
+        <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4753</v>
+        <v>1.474</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7565</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1275</v>
+        <v>1.1269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.58</v>
+        <v>0.5803</v>
       </c>
       <c r="M9" t="n">
         <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9685</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7433</v>
+        <v>0.7435</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2021</v>
+        <v>1.2013</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7244</v>
       </c>
       <c r="M11" t="n">
         <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2078</v>
+        <v>1.207</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9797</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>0.6611</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9922</v>
+        <v>0.9918</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3111</v>
+        <v>1.3101</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1497</v>
+        <v>1.149</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8679</v>
+        <v>0.8678</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5601,32 +5601,32 @@
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9242</v>
+        <v>0.9095</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6539</v>
+        <v>0.7144</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5572</v>
+        <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8603</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5965</v>
+        <v>0.5969</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.019</v>
+        <v>1.0186</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6897</v>
+        <v>0.6899</v>
       </c>
       <c r="M17" t="n">
         <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5748,23 +5748,23 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" t="n">
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3096</v>
+        <v>1.3127</v>
       </c>
       <c r="L18" t="n">
-        <v>0.55</v>
+        <v>0.5567</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7831</v>
+        <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5803,14 +5803,14 @@
         <v>1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7307</v>
+        <v>0.7308</v>
       </c>
       <c r="M19" t="n">
         <v>0.8551</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8521</v>
+        <v>0.852</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6892</v>
+        <v>0.6895</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0179</v>
+        <v>1.0175</v>
       </c>
       <c r="M21" t="n">
         <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9569</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1037</v>
+        <v>1.1031</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1321</v>
+        <v>1.1315</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7188</v>
+        <v>0.719</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6967</v>
+        <v>0.6969</v>
       </c>
       <c r="L24" t="n">
-        <v>1.277</v>
+        <v>1.2761</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1049</v>
+        <v>1.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6936</v>
+        <v>0.6938</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2021</v>
+        <v>1.2013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7003</v>
+        <v>0.7005</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8552</v>
+        <v>0.8551</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3497</v>
+        <v>1.3486</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0764</v>
+        <v>1.0758</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3324</v>
+        <v>1.3314</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5526</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>0.7594</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4923</v>
+        <v>1.491</v>
       </c>
       <c r="L30" t="n">
         <v>0.8138</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9367</v>
+        <v>0.9365</v>
       </c>
       <c r="L31" t="n">
-        <v>1.407</v>
+        <v>1.4058</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5813</v>
+        <v>1.5798</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9567</v>
+        <v>0.9563</v>
       </c>
       <c r="M32" t="n">
         <v>0.7113</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9374</v>
+        <v>0.9371</v>
       </c>
       <c r="L33" t="n">
-        <v>1.047</v>
+        <v>1.0465</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9065</v>
+        <v>0.9063</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8324</v>
+        <v>0.8323</v>
       </c>
       <c r="M34" t="n">
         <v>0.5065</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3709</v>
+        <v>1.3698</v>
       </c>
       <c r="L35" t="n">
-        <v>0.665</v>
+        <v>0.6653</v>
       </c>
       <c r="M35" t="n">
         <v>0.6884</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6944</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3252</v>
+        <v>1.3241</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7074</v>
+        <v>0.7076</v>
       </c>
       <c r="L37" t="n">
-        <v>0.985</v>
+        <v>0.9847</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0473</v>
+        <v>1.0468</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8633</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6708,29 +6708,29 @@
         <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3253</v>
+        <v>1.3494</v>
       </c>
       <c r="L39" t="n">
-        <v>0.93</v>
+        <v>1.023</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5009</v>
+        <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7498</v>
+        <v>0.7499</v>
       </c>
       <c r="L40" t="n">
         <v>0.7917</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9649</v>
       </c>
       <c r="L41" t="n">
         <v>0.7877999999999999</v>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3977</v>
+        <v>1.3965</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5793</v>
+        <v>0.5798</v>
       </c>
       <c r="M42" t="n">
         <v>0.7514</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1725</v>
+        <v>1.1718</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3717</v>
+        <v>1.3706</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4163</v>
+        <v>1.4151</v>
       </c>
       <c r="L44" t="n">
         <v>0.8241000000000001</v>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7174</v>
+        <v>0.7176</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4519</v>
+        <v>1.4506</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2196</v>
+        <v>1.2188</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9033</v>
+        <v>0.9031</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
         <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J47" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3282</v>
+        <v>1.3527</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1368</v>
+        <v>1.0298</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5548</v>
+        <v>0.6123</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7755</v>
+        <v>0.7756</v>
       </c>
       <c r="L48" t="n">
         <v>0.8471</v>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9277</v>
+        <v>0.9275</v>
       </c>
       <c r="L49" t="n">
-        <v>1.232</v>
+        <v>1.2312</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-30T20:00:00+00:00</t>
+          <t>2026-07-01T23:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -541,16 +541,16 @@
         <v>77.5</v>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="J2" t="n">
-        <v>39.7</v>
+        <v>38.7</v>
       </c>
       <c r="K2" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="L2" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -601,52 +601,52 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>60.9</v>
+        <v>60.2</v>
       </c>
       <c r="J3" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="K3" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1617.8</v>
+        <v>1603.8</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
         <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -661,45 +661,45 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>58.3</v>
+        <v>61.3</v>
       </c>
       <c r="J4" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="K4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="L4" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1593.4</v>
+        <v>1617.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -721,45 +721,45 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>76.2</v>
+        <v>57.6</v>
       </c>
       <c r="J5" t="n">
-        <v>38.4</v>
+        <v>35.3</v>
       </c>
       <c r="K5" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -781,45 +781,45 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>67.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="J6" t="n">
-        <v>34.8</v>
+        <v>37.8</v>
       </c>
       <c r="K6" t="n">
-        <v>17.3</v>
+        <v>19.1</v>
       </c>
       <c r="L6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1555.6</v>
+        <v>1569.9</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="R6" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -838,48 +838,48 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>65.2</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>40.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>30.2</v>
       </c>
       <c r="K7" t="n">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1603.8</v>
+        <v>1555.6</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -901,16 +901,16 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>60.6</v>
       </c>
       <c r="J8" t="n">
-        <v>22.9</v>
+        <v>27.3</v>
       </c>
       <c r="K8" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="L8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -918,28 +918,28 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1542.8</v>
+        <v>1545.2</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
         <v>0.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -958,19 +958,19 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>33.1</v>
+        <v>52.3</v>
       </c>
       <c r="J9" t="n">
-        <v>17.8</v>
+        <v>23.1</v>
       </c>
       <c r="K9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -978,28 +978,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1573.8</v>
+        <v>1542.8</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1021,16 +1021,16 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>47.9</v>
+        <v>39.7</v>
       </c>
       <c r="J10" t="n">
-        <v>20.3</v>
+        <v>21.2</v>
       </c>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,35 +1038,35 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1582.5</v>
+        <v>1565</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1078,37 +1078,37 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>66.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="I11" t="n">
-        <v>31.9</v>
+        <v>33.6</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1565</v>
+        <v>1573.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -1141,13 +1141,13 @@
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="J12" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="K12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>3.9</v>
@@ -1174,19 +1174,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1198,48 +1198,48 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>78.7</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>40.4</v>
+        <v>47.6</v>
       </c>
       <c r="J13" t="n">
-        <v>17.1</v>
+        <v>20.1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1541.7</v>
+        <v>1582.5</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="R13" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1258,37 +1258,37 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>59.1</v>
+        <v>78.3</v>
       </c>
       <c r="I14" t="n">
-        <v>34.1</v>
+        <v>35.6</v>
       </c>
       <c r="J14" t="n">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
       <c r="K14" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1545.2</v>
+        <v>1541.7</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="R14" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="15">
@@ -1318,19 +1318,19 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
       <c r="I15" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="J15" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1384,13 +1384,13 @@
         <v>32.8</v>
       </c>
       <c r="J16" t="n">
-        <v>11.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1414,12 +1414,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1438,19 +1438,19 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>34.7</v>
+        <v>43.6</v>
       </c>
       <c r="I17" t="n">
-        <v>16.8</v>
+        <v>13.3</v>
       </c>
       <c r="J17" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1458,23 +1458,23 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1560</v>
+        <v>1546.8</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>0.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="R17" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1498,34 +1498,34 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>43.9</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>23.9</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1546.8</v>
+        <v>1519.6</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="R18" t="n">
         <v>0.51</v>
@@ -1534,22 +1534,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,48 +1558,48 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>19.4</v>
+        <v>22.4</v>
       </c>
       <c r="I19" t="n">
-        <v>10.7</v>
+        <v>9.9</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1573.4</v>
+        <v>1494.5</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.29</v>
+        <v>0.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="R19" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>14.6</v>
       </c>
       <c r="I20" t="n">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1519.6</v>
+        <v>1544.1</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.83</v>
+        <v>0.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1675,22 +1675,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H21" t="n">
-        <v>24.8</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1698,38 +1698,38 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1544.1</v>
+        <v>1564.9</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>0.86</v>
+        <v>1.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1738,58 +1738,58 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="I22" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1494.5</v>
+        <v>1467.7</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1798,48 +1798,48 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>33</v>
+        <v>5.1</v>
       </c>
       <c r="I23" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>0.1</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1554.9</v>
+        <v>1507.6</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.98</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1855,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1878,38 +1878,38 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1564.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="R24" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,48 +1918,48 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1467.7</v>
+        <v>1560</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="R25" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1978,13 +1978,13 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1998,38 +1998,38 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1507.6</v>
+        <v>1514.3</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2054,21 +2054,21 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1514.3</v>
+        <v>1554.9</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="Q27" t="n">
         <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -3558,14 +3558,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3585,14 +3585,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -4665,17 +4665,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -4692,17 +4692,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -5003,32 +5003,32 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2854</v>
+        <v>1.185</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8633</v>
+        <v>0.9099</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6801</v>
+        <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5691</v>
+        <v>1.5684</v>
       </c>
       <c r="L3" t="n">
         <v>0.55</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8852</v>
+        <v>0.8855</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7285</v>
+        <v>0.7289</v>
       </c>
       <c r="M4" t="n">
         <v>0.5133</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5141,32 +5141,32 @@
         <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3864</v>
+        <v>1.2681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8447</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.678</v>
+        <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7362</v>
+        <v>0.7366</v>
       </c>
       <c r="M6" t="n">
         <v>0.7259</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.99</v>
+        <v>0.9901</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0064</v>
+        <v>1.0065</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.474</v>
+        <v>1.4736</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="M8" t="n">
         <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1269</v>
+        <v>1.1268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5803</v>
+        <v>0.5809</v>
       </c>
       <c r="M9" t="n">
         <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9684</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7435</v>
+        <v>0.7439</v>
       </c>
       <c r="M10" t="n">
         <v>0.454</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2013</v>
+        <v>1.2012</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7244</v>
+        <v>0.7249</v>
       </c>
       <c r="M11" t="n">
         <v>0.6786</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5466,29 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.207</v>
+        <v>1.1646</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9792999999999999</v>
+        <v>1.0064</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6611</v>
+        <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9918</v>
+        <v>0.9919</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3101</v>
+        <v>1.3098</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.149</v>
+        <v>1.1489</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8678</v>
+        <v>0.8681</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9095</v>
+        <v>0.9097</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7144</v>
+        <v>0.7149</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8603</v>
+        <v>0.8606</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5969</v>
+        <v>0.5976</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0186</v>
+        <v>1.0187</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6899</v>
+        <v>0.6903</v>
       </c>
       <c r="M17" t="n">
         <v>0.6004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3127</v>
+        <v>1.3125</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5567</v>
+        <v>0.5574</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5803,14 +5803,14 @@
         <v>1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7308</v>
+        <v>0.7312</v>
       </c>
       <c r="M19" t="n">
         <v>0.8551</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.852</v>
+        <v>0.8522</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6895</v>
+        <v>0.6901</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0175</v>
+        <v>1.0176</v>
       </c>
       <c r="M21" t="n">
         <v>0.2527</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9569</v>
+        <v>0.9571</v>
       </c>
       <c r="L22" t="n">
         <v>1.1031</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1315</v>
+        <v>1.1314</v>
       </c>
       <c r="L23" t="n">
-        <v>0.719</v>
+        <v>0.7194</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6969</v>
+        <v>0.6974</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2761</v>
+        <v>1.2758</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6079,14 +6079,14 @@
         <v>1.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6938</v>
+        <v>0.6942</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2013</v>
+        <v>1.2011</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7005</v>
+        <v>0.701</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8551</v>
+        <v>0.8554</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3486</v>
+        <v>1.3483</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3314</v>
+        <v>1.3312</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5535</v>
       </c>
       <c r="M29" t="n">
         <v>0.7594</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.491</v>
+        <v>1.4905</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8138</v>
+        <v>0.8141</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9365</v>
+        <v>0.9366</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4058</v>
+        <v>1.4053</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5798</v>
+        <v>1.5792</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9563</v>
+        <v>0.9565</v>
       </c>
       <c r="M32" t="n">
         <v>0.7113</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9371</v>
+        <v>0.9373</v>
       </c>
       <c r="L33" t="n">
         <v>1.0465</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9063</v>
+        <v>0.9065</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8323</v>
+        <v>0.8327</v>
       </c>
       <c r="M34" t="n">
         <v>0.5065</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6521,32 +6521,32 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3698</v>
+        <v>1.3814</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6653</v>
+        <v>0.6731</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6884</v>
+        <v>0.7251</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6944</v>
+        <v>0.6949</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3241</v>
+        <v>1.3238</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7076</v>
+        <v>0.708</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9847</v>
+        <v>0.9848</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0468</v>
+        <v>1.0469</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8633</v>
+        <v>0.8636</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3494</v>
+        <v>1.3491</v>
       </c>
       <c r="L39" t="n">
-        <v>1.023</v>
+        <v>1.0231</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7499</v>
+        <v>0.7502</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7917</v>
+        <v>0.792</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9649</v>
+        <v>0.965</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7882</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3965</v>
+        <v>1.4477</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5798</v>
+        <v>0.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7514</v>
+        <v>0.7765</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1718</v>
+        <v>1.1717</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3706</v>
+        <v>1.3702</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6935,10 +6935,10 @@
         <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -6947,20 +6947,20 @@
         <v>46</v>
       </c>
       <c r="J44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4151</v>
+        <v>1.4155</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6988</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7176</v>
+        <v>0.718</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4506</v>
+        <v>1.4502</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2188</v>
+        <v>1.2186</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9031</v>
+        <v>0.9033</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3527</v>
+        <v>1.3523</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0298</v>
+        <v>1.0299</v>
       </c>
       <c r="M47" t="n">
         <v>0.6123</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7756</v>
+        <v>0.776</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8471</v>
+        <v>0.8474</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9275</v>
+        <v>0.9277</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2312</v>
+        <v>1.231</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-01T23:00:00+00:00</t>
+          <t>2026-07-03T02:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -538,23 +538,23 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>56.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>38.7</v>
+        <v>48.5</v>
       </c>
       <c r="K2" t="n">
-        <v>23.7</v>
+        <v>30.3</v>
       </c>
       <c r="L2" t="n">
-        <v>13.8</v>
+        <v>17.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -562,13 +562,13 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
         <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3">
@@ -601,16 +601,16 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="J3" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="K3" t="n">
         <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -661,16 +661,16 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="J4" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="L4" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -721,16 +721,16 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="J5" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="K5" t="n">
-        <v>20.1</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -784,13 +784,13 @@
         <v>76</v>
       </c>
       <c r="J6" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="K6" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="L6" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -841,16 +841,16 @@
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="J7" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="K7" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -874,19 +874,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -901,34 +901,34 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>60.6</v>
+        <v>39.8</v>
       </c>
       <c r="J8" t="n">
-        <v>27.3</v>
+        <v>21.1</v>
       </c>
       <c r="K8" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1545.2</v>
+        <v>1565</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="9">
@@ -961,16 +961,16 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="J9" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="K9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="L9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1021,34 +1021,34 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>39.7</v>
+        <v>52.6</v>
       </c>
       <c r="J10" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="K10" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1565</v>
+        <v>1545.2</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="R10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="I11" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="K11" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1141,16 +1141,16 @@
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="J12" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="K12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1201,16 +1201,16 @@
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="J13" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="K13" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="L13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>35.6</v>
+        <v>47.3</v>
       </c>
       <c r="J14" t="n">
-        <v>14.7</v>
+        <v>17.8</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1282,13 +1282,13 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -1318,23 +1318,23 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>56.3</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>20.1</v>
+        <v>28.8</v>
       </c>
       <c r="J15" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1342,13 +1342,13 @@
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -1381,13 +1381,13 @@
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="J16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.1</v>
@@ -1414,7 +1414,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1426,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1438,34 +1438,34 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>43.6</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>13.3</v>
+        <v>23.9</v>
       </c>
       <c r="J17" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1546.8</v>
+        <v>1519.6</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="R17" t="n">
         <v>0.51</v>
@@ -1474,12 +1474,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1498,19 +1498,19 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="I18" t="n">
-        <v>23.9</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1518,88 +1518,88 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1519.6</v>
+        <v>1544.1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.83</v>
+        <v>0.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H19" t="n">
-        <v>22.4</v>
+        <v>9.4</v>
       </c>
       <c r="I19" t="n">
-        <v>9.9</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1494.5</v>
+        <v>1564.9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0.97</v>
+        <v>1.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1618,19 +1618,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>14.6</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1544.1</v>
+        <v>1507.6</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="R20" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1675,22 +1675,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1698,38 +1698,38 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1564.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="R21" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1738,58 +1738,58 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1467.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="R22" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1814,32 +1814,32 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1507.6</v>
+        <v>1560</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.37</v>
+        <v>0.95</v>
       </c>
       <c r="R23" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1878,28 +1878,28 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1573.4</v>
+        <v>1514.3</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1938,38 +1938,38 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1560</v>
+        <v>1494.5</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1994,48 +1994,48 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1514.3</v>
+        <v>1554.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
       </c>
       <c r="R26" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2054,48 +2054,48 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1554.9</v>
+        <v>1519.9</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R27" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2118,44 +2118,44 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R28" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2174,42 +2174,42 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1534.2</v>
+        <v>1537.9</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="R29" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2234,42 +2234,42 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1537.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.91</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2294,21 +2294,21 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1577.2</v>
+        <v>1467.7</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.65</v>
+        <v>0.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="R31" t="n">
-        <v>0.74</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="32">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Q41" t="n">
         <v>1.32</v>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Q45" t="n">
         <v>0.79</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4665,17 +4665,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -4692,17 +4692,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.185</v>
+        <v>1.1849</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9099</v>
+        <v>0.9101</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5049,32 +5049,32 @@
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5684</v>
+        <v>1.6166</v>
       </c>
       <c r="L3" t="n">
-        <v>0.55</v>
+        <v>0.5543</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9344</v>
+        <v>0.9467</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8855</v>
+        <v>0.8737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7289</v>
+        <v>0.7282</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5133</v>
+        <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2681</v>
+        <v>1.2679</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9523</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7366</v>
+        <v>0.7369</v>
       </c>
       <c r="M6" t="n">
         <v>0.7259</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9901</v>
+        <v>0.9902</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0065</v>
+        <v>1.0066</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4736</v>
+        <v>1.4732</v>
       </c>
       <c r="L8" t="n">
-        <v>0.757</v>
+        <v>0.7574</v>
       </c>
       <c r="M8" t="n">
         <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5343,14 +5343,14 @@
         <v>1.1268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5809</v>
+        <v>0.5814</v>
       </c>
       <c r="M9" t="n">
         <v>0.5903</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -5377,26 +5377,26 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
       <c r="K10" t="n">
-        <v>0.9684</v>
+        <v>1.0057</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7439</v>
+        <v>0.8575</v>
       </c>
       <c r="M10" t="n">
-        <v>0.454</v>
+        <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5426,23 +5426,23 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2012</v>
+        <v>1.1552</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7249</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6786</v>
+        <v>0.711</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1646</v>
+        <v>1.1645</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0064</v>
+        <v>1.0065</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9919</v>
+        <v>0.992</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3098</v>
+        <v>1.3096</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1489</v>
+        <v>1.1488</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8681</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9097</v>
+        <v>0.9099</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7149</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8606</v>
+        <v>0.8608</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5976</v>
+        <v>0.5981</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0187</v>
+        <v>1.0004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6903</v>
+        <v>0.6921</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6004</v>
+        <v>0.5783</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3125</v>
+        <v>1.3122</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5574</v>
+        <v>0.5579</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5803,14 +5803,14 @@
         <v>1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7312</v>
+        <v>0.7316</v>
       </c>
       <c r="M19" t="n">
         <v>0.8551</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8522</v>
+        <v>0.8525</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
         <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -5883,26 +5883,26 @@
         <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
         <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6901</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0176</v>
+        <v>0.9926</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2527</v>
+        <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9571</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1031</v>
+        <v>1.103</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1314</v>
+        <v>1.1313</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7194</v>
+        <v>0.7198</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6974</v>
+        <v>0.6978</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2758</v>
+        <v>1.2756</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6079,14 +6079,14 @@
         <v>1.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6942</v>
+        <v>0.6946</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2011</v>
+        <v>1.201</v>
       </c>
       <c r="L26" t="n">
-        <v>0.701</v>
+        <v>0.7014</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8554</v>
+        <v>0.8556</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3483</v>
+        <v>1.348</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0758</v>
+        <v>1.0759</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3312</v>
+        <v>1.331</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5535</v>
+        <v>0.554</v>
       </c>
       <c r="M29" t="n">
         <v>0.7594</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4905</v>
+        <v>1.4901</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8141</v>
+        <v>0.8144</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9366</v>
+        <v>0.9368</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4053</v>
+        <v>1.405</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5792</v>
+        <v>1.5787</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9565</v>
+        <v>0.9566</v>
       </c>
       <c r="M32" t="n">
         <v>0.7113</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9373</v>
+        <v>0.9375</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0465</v>
+        <v>1.0466</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9065</v>
+        <v>0.9067</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8327</v>
+        <v>0.8329</v>
       </c>
       <c r="M34" t="n">
         <v>0.5065</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3814</v>
+        <v>1.3811</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6731</v>
+        <v>0.6736</v>
       </c>
       <c r="M35" t="n">
         <v>0.7251</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6949</v>
+        <v>0.6954</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3238</v>
+        <v>1.3235</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.708</v>
+        <v>0.7084</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9848</v>
+        <v>0.9849</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6677,14 +6677,14 @@
         <v>1.0469</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8636</v>
+        <v>0.8638</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3491</v>
+        <v>1.3489</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0231</v>
+        <v>1.0232</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7502</v>
+        <v>0.7506</v>
       </c>
       <c r="L40" t="n">
-        <v>0.792</v>
+        <v>0.7923</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.965</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7882</v>
+        <v>0.7885</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4477</v>
+        <v>1.4473</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1717</v>
+        <v>1.1716</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3702</v>
+        <v>1.37</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4155</v>
+        <v>1.4152</v>
       </c>
       <c r="L44" t="n">
-        <v>0.759</v>
+        <v>0.7594</v>
       </c>
       <c r="M44" t="n">
         <v>0.6988</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.718</v>
+        <v>0.7184</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4502</v>
+        <v>1.4499</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2186</v>
+        <v>1.2185</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9033</v>
+        <v>0.9035</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
         <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3523</v>
+        <v>1.3521</v>
       </c>
       <c r="L47" t="n">
         <v>1.0299</v>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.776</v>
+        <v>0.7764</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8474</v>
+        <v>0.8476</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9277</v>
+        <v>0.9278</v>
       </c>
       <c r="L49" t="n">
-        <v>1.231</v>
+        <v>1.2309</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00:00+00:00</t>
+          <t>2026-07-04T00:30:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,19 +514,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -541,45 +541,45 @@
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>71.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>48.5</v>
+        <v>55.7</v>
       </c>
       <c r="K2" t="n">
-        <v>30.3</v>
+        <v>31.6</v>
       </c>
       <c r="L2" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1577.2</v>
+        <v>1617.8</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="Q2" t="n">
         <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -601,16 +601,16 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>60.1</v>
+        <v>71.3</v>
       </c>
       <c r="J3" t="n">
-        <v>38.4</v>
+        <v>48.6</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>30.5</v>
       </c>
       <c r="L3" t="n">
-        <v>12.8</v>
+        <v>17.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -618,35 +618,35 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1603.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
         <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -661,45 +661,45 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.8</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>37</v>
+        <v>44.2</v>
       </c>
       <c r="K4" t="n">
-        <v>20.5</v>
+        <v>23.1</v>
       </c>
       <c r="L4" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1617.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R4" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -721,16 +721,16 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.8</v>
+        <v>60.2</v>
       </c>
       <c r="J5" t="n">
-        <v>35.2</v>
+        <v>38.6</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>20.2</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1593.4</v>
+        <v>1603.8</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -781,34 +781,34 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>76</v>
+        <v>58.2</v>
       </c>
       <c r="J6" t="n">
-        <v>37.6</v>
+        <v>35.1</v>
       </c>
       <c r="K6" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="L6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -841,16 +841,16 @@
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>67.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="K7" t="n">
-        <v>15.2</v>
+        <v>13.1</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -901,16 +901,16 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>52.8</v>
+        <v>52.1</v>
       </c>
       <c r="J9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="K9" t="n">
         <v>10.4</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1021,16 +1021,16 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="J10" t="n">
         <v>20.6</v>
       </c>
       <c r="K10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J11" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="K11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1141,16 +1141,16 @@
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>39.1</v>
+        <v>47.8</v>
       </c>
       <c r="J12" t="n">
-        <v>18.8</v>
+        <v>20.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1158,35 +1158,35 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1544.6</v>
+        <v>1582.5</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="R12" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1201,31 +1201,31 @@
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="J13" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="K13" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1582.5</v>
+        <v>1541.7</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.96</v>
+        <v>0.68</v>
       </c>
       <c r="R13" t="n">
         <v>0.71</v>
@@ -1234,19 +1234,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1261,52 +1261,52 @@
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>47.3</v>
+        <v>28.6</v>
       </c>
       <c r="J14" t="n">
-        <v>17.8</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1541.7</v>
+        <v>1560.9</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1321,55 +1321,55 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1560.9</v>
+        <v>1522.7</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="R15" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1378,48 +1378,48 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>14.8</v>
       </c>
       <c r="I16" t="n">
-        <v>32.7</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>9.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1522.7</v>
+        <v>1544.1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.35</v>
+        <v>0.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1435,22 +1435,22 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>23.9</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1458,28 +1458,28 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1519.6</v>
+        <v>1564.9</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0.91</v>
+        <v>1.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1498,19 +1498,19 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1518,28 +1518,28 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1544.1</v>
+        <v>1507.6</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1555,22 +1555,22 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1578,38 +1578,38 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1564.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="R19" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1618,13 +1618,13 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1634,27 +1634,27 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1507.6</v>
+        <v>1546.8</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.37</v>
+        <v>0.73</v>
       </c>
       <c r="R20" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1666,10 +1666,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1694,18 +1694,18 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1573.4</v>
+        <v>1560</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="R21" t="n">
         <v>0.6</v>
@@ -1714,22 +1714,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1754,32 +1754,32 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1546.8</v>
+        <v>1514.3</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1798,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1814,42 +1814,42 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1560</v>
+        <v>1544.6</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1874,32 +1874,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1514.3</v>
+        <v>1494.5</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="R24" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1938,44 +1938,44 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1494.5</v>
+        <v>1554.9</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.86</v>
-      </c>
       <c r="R25" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1994,48 +1994,48 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1554.9</v>
+        <v>1519.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R26" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2058,44 +2058,44 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R27" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2114,42 +2114,42 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1534.2</v>
+        <v>1537.9</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="R28" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2174,42 +2174,42 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1537.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.91</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="R29" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2234,32 +2234,32 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1577.2</v>
+        <v>1467.7</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.65</v>
+        <v>0.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="R30" t="n">
-        <v>0.74</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2269,13 +2269,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2294,32 +2294,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1467.7</v>
+        <v>1523</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2329,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2354,32 +2354,32 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1523</v>
+        <v>1546.8</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2389,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2414,48 +2414,48 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1546.8</v>
+        <v>1534.7</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.72</v>
+        <v>1.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2474,32 +2474,32 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1534.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.28</v>
-      </c>
       <c r="R34" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2538,44 +2538,44 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1556.1</v>
+        <v>1575.8</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2594,36 +2594,36 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1575.8</v>
+        <v>1493.5</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="R36" t="n">
-        <v>0.64</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2632,10 +2632,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2654,36 +2654,36 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1493.5</v>
+        <v>1571</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.86</v>
+        <v>1.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R37" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2692,10 +2692,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1571</v>
+        <v>1518</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="R38" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2778,28 +2778,28 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1518</v>
+        <v>1555</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="R39" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2809,16 +2809,16 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2834,21 +2834,21 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 16强</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1555</v>
+        <v>1519.6</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="R40" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="41">
@@ -2965,7 +2965,7 @@
         <v>0.71</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="R42" t="n">
         <v>0.34</v>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3612,17 +3612,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1849</v>
+        <v>1.1852</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9101</v>
+        <v>0.9105</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6166</v>
+        <v>1.6167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5543</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>0.9467</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8737</v>
+        <v>0.8741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7282</v>
+        <v>0.7287</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2679</v>
+        <v>1.2682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9523</v>
+        <v>0.9527</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7369</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>0.7259</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9902</v>
+        <v>0.9906</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0066</v>
+        <v>1.007</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4732</v>
+        <v>1.4734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7574</v>
+        <v>0.7578</v>
       </c>
       <c r="M8" t="n">
         <v>0.7403</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5328,29 +5328,29 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>31</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1268</v>
+        <v>1.0645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5814</v>
+        <v>0.696</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5903</v>
+        <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0057</v>
+        <v>1.0061</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8575</v>
+        <v>0.8579</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1552</v>
+        <v>1.1555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6754</v>
       </c>
       <c r="M11" t="n">
         <v>0.711</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1645</v>
+        <v>1.1649</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0065</v>
+        <v>1.0069</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.992</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3096</v>
+        <v>1.3098</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1488</v>
+        <v>1.1491</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8688</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9099</v>
+        <v>0.9103</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7157</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8608</v>
+        <v>0.8613</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5981</v>
+        <v>0.5987</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0004</v>
+        <v>1.0008</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6921</v>
+        <v>0.6926</v>
       </c>
       <c r="M17" t="n">
         <v>0.5783</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3122</v>
+        <v>1.3125</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5579</v>
+        <v>0.5585</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5785,32 +5785,32 @@
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.65</v>
+        <v>1.5992</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7316</v>
+        <v>0.6848</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8551</v>
+        <v>0.874</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8525</v>
+        <v>0.8529</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6342</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9926</v>
+        <v>0.993</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9576</v>
       </c>
       <c r="L22" t="n">
-        <v>1.103</v>
+        <v>1.1034</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1313</v>
+        <v>1.1317</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7198</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6978</v>
+        <v>0.6983</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2756</v>
+        <v>1.2759</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1043</v>
+        <v>1.1047</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6946</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.201</v>
+        <v>1.2013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7014</v>
+        <v>0.7019</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8556</v>
+        <v>0.8561</v>
       </c>
       <c r="L27" t="n">
-        <v>1.348</v>
+        <v>1.3482</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0759</v>
+        <v>1.0762</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6254,23 +6254,23 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J29" t="n">
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.331</v>
+        <v>1.3884</v>
       </c>
       <c r="L29" t="n">
-        <v>0.554</v>
+        <v>0.55</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7594</v>
+        <v>0.7756</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4901</v>
+        <v>1.4903</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8144</v>
+        <v>0.8149</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9368</v>
+        <v>0.9372</v>
       </c>
       <c r="L31" t="n">
-        <v>1.405</v>
+        <v>1.4052</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5787</v>
+        <v>1.5789</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9566</v>
+        <v>0.9571</v>
       </c>
       <c r="M32" t="n">
         <v>0.7113</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9375</v>
+        <v>0.9379</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0466</v>
+        <v>1.047</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6475,32 +6475,32 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9067</v>
+        <v>0.837</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8329</v>
+        <v>0.8252</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5065</v>
+        <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3811</v>
+        <v>1.3813</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6736</v>
+        <v>0.6741</v>
       </c>
       <c r="M35" t="n">
         <v>0.7251</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6954</v>
+        <v>0.6959</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3235</v>
+        <v>1.3237</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7084</v>
+        <v>0.7089</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9849</v>
+        <v>0.9853</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0469</v>
+        <v>1.0473</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8638</v>
+        <v>0.8643</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3489</v>
+        <v>1.3492</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0232</v>
+        <v>1.0236</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7506</v>
+        <v>0.7511</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7923</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9656</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7885</v>
+        <v>0.789</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4473</v>
+        <v>1.4476</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1716</v>
+        <v>1.1719</v>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>1.3702</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4152</v>
+        <v>1.4154</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7594</v>
+        <v>0.7599</v>
       </c>
       <c r="M44" t="n">
         <v>0.6988</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7184</v>
+        <v>0.7189</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4499</v>
+        <v>1.4501</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2185</v>
+        <v>1.2187</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9035</v>
+        <v>0.904</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3521</v>
+        <v>1.3524</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0299</v>
+        <v>1.0303</v>
       </c>
       <c r="M47" t="n">
         <v>0.6123</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7764</v>
+        <v>0.7769</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8476</v>
+        <v>0.8481</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9278</v>
+        <v>0.9283</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2309</v>
+        <v>1.2312</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-04T00:30:00+00:00</t>
+          <t>2026-07-04T20:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -544,13 +544,13 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>55.7</v>
+        <v>55.5</v>
       </c>
       <c r="K2" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="L2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="K3" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="L3" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R3" t="n">
         <v>0.95</v>
@@ -634,12 +634,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,13 +664,13 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>44.2</v>
+        <v>60.8</v>
       </c>
       <c r="K4" t="n">
-        <v>23.1</v>
+        <v>31.7</v>
       </c>
       <c r="L4" t="n">
-        <v>12.2</v>
+        <v>15.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -721,45 +721,45 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>60.2</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
       <c r="K5" t="n">
-        <v>20.2</v>
+        <v>23.1</v>
       </c>
       <c r="L5" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1603.8</v>
+        <v>1569.9</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -781,16 +781,16 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>58.2</v>
+        <v>60.2</v>
       </c>
       <c r="J6" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
       </c>
       <c r="K6" t="n">
-        <v>18.7</v>
+        <v>19.9</v>
       </c>
       <c r="L6" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -798,17 +798,17 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1603.8</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
@@ -844,13 +844,13 @@
         <v>66.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="K7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -901,52 +901,52 @@
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>39.7</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>21.2</v>
+        <v>39.1</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>16.1</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1565</v>
+        <v>1582.5</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -961,34 +961,34 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>52.1</v>
+        <v>39.7</v>
       </c>
       <c r="J9" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="K9" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1542.8</v>
+        <v>1565</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="R9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="10">
@@ -1021,16 +1021,16 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="J10" t="n">
         <v>20.6</v>
       </c>
       <c r="K10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q10" t="n">
         <v>0.76</v>
@@ -1054,12 +1054,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1078,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>70.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>33.3</v>
+        <v>47.5</v>
       </c>
       <c r="J11" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="K11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,28 +1098,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1573.8</v>
+        <v>1541.7</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="R11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1141,16 +1141,16 @@
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>47.8</v>
+        <v>28.5</v>
       </c>
       <c r="J12" t="n">
-        <v>20.5</v>
+        <v>12.8</v>
       </c>
       <c r="K12" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1158,28 +1158,28 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1582.5</v>
+        <v>1560.9</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1201,16 +1201,16 @@
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>47.2</v>
+        <v>33</v>
       </c>
       <c r="J13" t="n">
-        <v>17.5</v>
+        <v>9.9</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1218,38 +1218,38 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1541.7</v>
+        <v>1522.7</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="R13" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1258,43 +1258,43 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1560.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="R14" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1318,58 +1318,58 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1522.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.35</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1378,48 +1378,48 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1544.1</v>
+        <v>1560</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>0.86</v>
+        <v>1.27</v>
       </c>
       <c r="Q16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1435,22 +1435,22 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1458,38 +1458,38 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1564.9</v>
+        <v>1514.3</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.35</v>
+        <v>0.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1498,13 +1498,13 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1514,42 +1514,42 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1507.6</v>
+        <v>1542.8</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1574,32 +1574,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1573.4</v>
+        <v>1544.6</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1546.8</v>
+        <v>1494.5</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1698,28 +1698,28 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1560</v>
+        <v>1554.9</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1729,13 +1729,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1754,51 +1754,51 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1514.3</v>
+        <v>1519.9</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R22" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>22.4</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1814,42 +1814,42 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1544.6</v>
+        <v>1534.2</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="R23" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1874,42 +1874,42 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1494.5</v>
+        <v>1537.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1934,27 +1934,27 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1554.9</v>
+        <v>1544.1</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>0.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1994,48 +1994,48 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1519.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.99</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.31</v>
+        <v>0.85</v>
       </c>
       <c r="R26" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1534.2</v>
+        <v>1467.7</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.15</v>
+        <v>0.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="R27" t="n">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2114,48 +2114,48 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1537.9</v>
+        <v>1523</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.72</v>
+        <v>1.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2174,32 +2174,32 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1577.2</v>
+        <v>1546.8</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="R29" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2209,13 +2209,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2234,48 +2234,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1467.7</v>
+        <v>1534.7</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.99</v>
+        <v>1.27</v>
       </c>
       <c r="R30" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2294,48 +2294,48 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1523</v>
+        <v>1556.1</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,32 +2354,32 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1546.8</v>
+        <v>1575.8</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2418,35 +2418,35 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1534.7</v>
+        <v>1493.5</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2474,27 +2474,27 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1556.1</v>
+        <v>1573.8</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="R34" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -2534,32 +2534,32 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1575.8</v>
+        <v>1571</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R35" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2598,32 +2598,32 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1493.5</v>
+        <v>1518</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2632,10 +2632,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1571</v>
+        <v>1555</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 16强</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1518</v>
+        <v>1519.6</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.41</v>
+        <v>0.82</v>
       </c>
       <c r="R38" t="n">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2778,28 +2778,28 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="R39" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2809,16 +2809,16 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2834,32 +2834,32 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>小组第3 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1519.6</v>
+        <v>1499.2</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="R40" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2869,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2894,32 +2894,32 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1484.3</v>
+        <v>1521.6</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.32</v>
+        <v>0.86</v>
       </c>
       <c r="R41" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2954,48 +2954,48 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1499.2</v>
+        <v>1564.9</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.71</v>
+        <v>1.35</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="R42" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="E43" t="n">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -3014,27 +3014,27 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1521.6</v>
+        <v>1521.7</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="R43" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3046,16 +3046,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>19.2</v>
+        <v>77.5</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -3074,32 +3074,32 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1521.7</v>
+        <v>1550.3</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="Q44" t="n">
         <v>0.79</v>
       </c>
       <c r="R44" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3134,21 +3134,21 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1550.3</v>
+        <v>1507.6</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="R45" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="46">
@@ -3450,23 +3450,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="3">
@@ -3477,23 +3477,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>80.8</v>
+        <v>77.5</v>
       </c>
       <c r="E4" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>80.8</v>
+        <v>77.5</v>
       </c>
       <c r="F5" t="n">
-        <v>19.2</v>
+        <v>22.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3919,13 +3919,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -3990,17 +3990,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4017,14 +4017,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4044,17 +4044,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>80.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="38">
@@ -4864,19 +4864,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>19.1</v>
+        <v>22.5</v>
       </c>
       <c r="J2" t="n">
-        <v>26.6</v>
+        <v>26.1</v>
       </c>
       <c r="K2" t="n">
-        <v>54.3</v>
+        <v>51.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1852</v>
+        <v>1.1842</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9105</v>
+        <v>0.9101</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6167</v>
+        <v>1.6147</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5553</v>
       </c>
       <c r="M3" t="n">
         <v>0.9467</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8741</v>
+        <v>0.8738</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7287</v>
+        <v>0.7288</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2682</v>
+        <v>1.267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9527</v>
+        <v>0.9522</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9906</v>
+        <v>0.9901</v>
       </c>
       <c r="L7" t="n">
-        <v>1.007</v>
+        <v>1.0064</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5282,29 +5282,29 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4734</v>
+        <v>1.4225</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7578</v>
+        <v>0.8055</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7403</v>
+        <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0645</v>
+        <v>1.0638</v>
       </c>
       <c r="L9" t="n">
         <v>0.696</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0061</v>
+        <v>1.0055</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8579</v>
+        <v>0.8577</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1555</v>
+        <v>1.1546</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6754</v>
+        <v>0.6756</v>
       </c>
       <c r="M11" t="n">
         <v>0.711</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1649</v>
+        <v>1.1639</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0069</v>
+        <v>1.0063</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9919</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3098</v>
+        <v>1.3085</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1491</v>
+        <v>1.1482</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8688</v>
+        <v>0.8686</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9103</v>
+        <v>0.9099</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7157</v>
+        <v>0.7158</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8613</v>
+        <v>0.861</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5987</v>
+        <v>0.599</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0008</v>
+        <v>1.0002</v>
       </c>
       <c r="L17" t="n">
         <v>0.6926</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5751,20 +5751,20 @@
         <v>47</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3125</v>
+        <v>1.3648</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5585</v>
+        <v>0.6234</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8048</v>
+        <v>0.8227</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5992</v>
+        <v>1.5973</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6848</v>
+        <v>0.6849</v>
       </c>
       <c r="M19" t="n">
         <v>0.874</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.65</v>
+        <v>1.6486</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8529</v>
+        <v>0.8527</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6342</v>
+        <v>0.6345</v>
       </c>
       <c r="L21" t="n">
-        <v>0.993</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9576</v>
+        <v>0.9571</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1034</v>
+        <v>1.1026</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1317</v>
+        <v>1.1308</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7204</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6983</v>
+        <v>0.6984</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2759</v>
+        <v>1.2747</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1047</v>
+        <v>1.1038</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6952</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2013</v>
+        <v>1.2003</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7019</v>
+        <v>0.702</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8561</v>
+        <v>0.8558</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3482</v>
+        <v>1.3468</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6202,29 +6202,29 @@
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0762</v>
+        <v>1.1151</v>
       </c>
       <c r="L28" t="n">
-        <v>0.55</v>
+        <v>0.6595</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7476</v>
+        <v>0.6807</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3884</v>
+        <v>1.387</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4903</v>
+        <v>1.4887</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8149</v>
+        <v>0.8147</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9372</v>
+        <v>0.9368</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4052</v>
+        <v>1.4037</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6392,23 +6392,23 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J32" t="n">
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5789</v>
+        <v>1.5589</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9571</v>
+        <v>0.9408</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7113</v>
+        <v>0.7378</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9379</v>
+        <v>0.9374</v>
       </c>
       <c r="L33" t="n">
-        <v>1.047</v>
+        <v>1.0463</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.837</v>
+        <v>0.8368</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8252</v>
+        <v>0.825</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3813</v>
+        <v>1.3799</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6741</v>
+        <v>0.6742</v>
       </c>
       <c r="M35" t="n">
         <v>0.7251</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6959</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3237</v>
+        <v>1.3223</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7089</v>
+        <v>0.709</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9853</v>
+        <v>0.9847</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0473</v>
+        <v>1.0466</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8643</v>
+        <v>0.864</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3492</v>
+        <v>1.3479</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0236</v>
+        <v>1.0229</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7511</v>
+        <v>0.751</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7926</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9656</v>
+        <v>0.9651</v>
       </c>
       <c r="L41" t="n">
-        <v>0.789</v>
+        <v>0.7889</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4476</v>
+        <v>1.446</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1719</v>
+        <v>1.171</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3702</v>
+        <v>1.3688</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4154</v>
+        <v>1.4139</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7599</v>
+        <v>0.7598</v>
       </c>
       <c r="M44" t="n">
         <v>0.6988</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6999,14 +6999,14 @@
         <v>0.7189</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4501</v>
+        <v>1.4485</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2187</v>
+        <v>1.2177</v>
       </c>
       <c r="L46" t="n">
-        <v>0.904</v>
+        <v>0.9036</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3524</v>
+        <v>1.351</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0303</v>
+        <v>1.0297</v>
       </c>
       <c r="M47" t="n">
         <v>0.6123</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7137,14 +7137,14 @@
         <v>0.7769</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8481</v>
+        <v>0.8479</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9283</v>
+        <v>0.9278</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2312</v>
+        <v>1.2301</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-04T20:00:00+00:00</t>
+          <t>2026-07-05T23:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -544,13 +544,13 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
       <c r="K2" t="n">
-        <v>31.9</v>
+        <v>30.4</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         <v>48.5</v>
       </c>
       <c r="K3" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="L3" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -634,12 +634,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,13 +664,13 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>60.8</v>
+        <v>57.8</v>
       </c>
       <c r="K4" t="n">
-        <v>31.7</v>
+        <v>29.9</v>
       </c>
       <c r="L4" t="n">
-        <v>15.5</v>
+        <v>16.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -678,17 +678,17 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1593.4</v>
+        <v>1603.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -724,13 +724,13 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="K5" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="L5" t="n">
-        <v>12.3</v>
+        <v>11.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>0.87</v>
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -781,16 +781,16 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>60.2</v>
+        <v>57.6</v>
       </c>
       <c r="J6" t="n">
-        <v>38.4</v>
+        <v>35.9</v>
       </c>
       <c r="K6" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="L6" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -798,17 +798,17 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1603.8</v>
+        <v>1593.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -841,16 +841,16 @@
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>66.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>30.2</v>
+        <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>18.1</v>
       </c>
       <c r="L7" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>0.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="8">
@@ -904,13 +904,13 @@
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>39.1</v>
+        <v>42.6</v>
       </c>
       <c r="K8" t="n">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="L8" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -961,45 +961,45 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>39.7</v>
+        <v>52.9</v>
       </c>
       <c r="J9" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1565</v>
+        <v>1545.2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1018,19 +1018,19 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>70.7</v>
       </c>
       <c r="I10" t="n">
-        <v>52.4</v>
+        <v>33.7</v>
       </c>
       <c r="J10" t="n">
-        <v>20.6</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,17 +1038,17 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1545.2</v>
+        <v>1573.8</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.76</v>
+        <v>0.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1081,16 +1081,16 @@
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>47.5</v>
+        <v>47</v>
       </c>
       <c r="J11" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1144,13 +1144,13 @@
         <v>28.5</v>
       </c>
       <c r="J12" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1174,22 +1174,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1198,48 +1198,48 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>14.8</v>
       </c>
       <c r="I13" t="n">
-        <v>33</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>9.9</v>
+        <v>2.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1522.7</v>
+        <v>1544.1</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.35</v>
+        <v>0.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1255,22 +1255,22 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1573.4</v>
+        <v>1564.9</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1546.8</v>
+        <v>1507.6</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.73</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1366,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1394,18 +1394,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1560</v>
+        <v>1573.4</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="R16" t="n">
         <v>0.6</v>
@@ -1414,22 +1414,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1454,39 +1454,39 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1514.3</v>
+        <v>1546.8</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>0.73</v>
       </c>
       <c r="R17" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1514,27 +1514,27 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1542.8</v>
+        <v>1560</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1546,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1574,39 +1574,39 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1544.6</v>
+        <v>1514.3</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1634,32 +1634,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1494.5</v>
+        <v>1542.8</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1678,7 +1678,7 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1554.9</v>
+        <v>1544.6</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1754,48 +1754,48 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1519.9</v>
+        <v>1494.5</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.31</v>
+        <v>0.86</v>
       </c>
       <c r="R22" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>77.5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>22.4</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1814,32 +1814,32 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1534.2</v>
+        <v>1554.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1849,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1874,51 +1874,51 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1537.9</v>
+        <v>1519.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>1.31</v>
       </c>
       <c r="R24" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
       <c r="H25" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1934,42 +1934,42 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1544.1</v>
+        <v>1534.2</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="R25" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1994,42 +1994,42 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1577.2</v>
+        <v>1537.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>0.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="R26" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1467.7</v>
+        <v>1577.2</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>0.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="R27" t="n">
-        <v>0.22</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2114,32 +2114,32 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1523</v>
+        <v>1467.7</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.96</v>
+        <v>0.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2174,32 +2174,32 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1546.8</v>
+        <v>1523</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.72</v>
+        <v>1.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2234,48 +2234,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1534.7</v>
+        <v>1546.8</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
       <c r="R30" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2294,32 +2294,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1556.1</v>
+        <v>1534.7</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.7</v>
+        <v>1.27</v>
       </c>
       <c r="R31" t="n">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2358,44 +2358,44 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1575.8</v>
+        <v>1556.1</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q32" t="n">
         <v>0.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2414,36 +2414,36 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1493.5</v>
+        <v>1575.8</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.35</v>
+        <v>0.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>67.7</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2474,21 +2474,21 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1573.8</v>
+        <v>1493.5</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.12</v>
+        <v>0.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.66</v>
+        <v>1.35</v>
       </c>
       <c r="R34" t="n">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="35">
@@ -2545,7 +2545,7 @@
         <v>1.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="R35" t="n">
         <v>0.67</v>
@@ -2725,7 +2725,7 @@
         <v>0.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="R38" t="n">
         <v>0.45</v>
@@ -2734,31 +2734,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2774,32 +2774,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1484.3</v>
+        <v>1565</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>0.7</v>
+        <v>1.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.32</v>
+        <v>0.68</v>
       </c>
       <c r="R39" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1499.2</v>
+        <v>1484.3</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.98</v>
+        <v>1.32</v>
       </c>
       <c r="R40" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2869,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2894,32 +2894,32 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1521.6</v>
+        <v>1499.2</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="R41" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>77.5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2954,21 +2954,21 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1564.9</v>
+        <v>1521.6</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="R42" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="43">
@@ -2986,10 +2986,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>77.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>77.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3134,32 +3134,32 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1507.6</v>
+        <v>1495</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.17</v>
+        <v>0.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="R45" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3198,23 +3198,23 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1495</v>
+        <v>1578.2</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>0.72</v>
+        <v>1.22</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.45</v>
+        <v>0.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -3232,13 +3232,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3254,21 +3254,21 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1578.2</v>
+        <v>1522.7</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
       <c r="R47" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="48">
@@ -3450,23 +3450,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>77.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>22.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -3477,23 +3477,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="4">
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>77.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>77.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3774,14 +3774,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3855,11 +3855,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3868,10 +3868,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3919,13 +3919,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3990,17 +3990,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4017,14 +4017,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4044,17 +4044,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="37">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>77.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -4557,17 +4557,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -4584,17 +4584,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4864,19 +4864,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="J2" t="n">
-        <v>26.1</v>
+        <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>51.4</v>
+        <v>54.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
     </row>
   </sheetData>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1842</v>
+        <v>1.1845</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9101</v>
+        <v>0.9106</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
         <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6147</v>
+        <v>1.6148</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5553</v>
+        <v>0.556</v>
       </c>
       <c r="M3" t="n">
         <v>0.9467</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8738</v>
+        <v>0.8744</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7288</v>
+        <v>0.7294</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.267</v>
+        <v>1.2672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9522</v>
+        <v>0.9527</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5187,16 +5187,16 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J6" t="n">
         <v>19</v>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7365</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7259</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9901</v>
+        <v>0.9905</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0064</v>
+        <v>1.0068</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4225</v>
+        <v>1.4227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8055</v>
+        <v>0.806</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0638</v>
+        <v>1.0642</v>
       </c>
       <c r="L9" t="n">
-        <v>0.696</v>
+        <v>0.6966</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0055</v>
+        <v>1.0059</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8577</v>
+        <v>0.8582</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1546</v>
+        <v>1.1549</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6756</v>
+        <v>0.6762</v>
       </c>
       <c r="M11" t="n">
         <v>0.711</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1639</v>
+        <v>1.1642</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0063</v>
+        <v>1.0068</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9919</v>
+        <v>0.9923</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3085</v>
+        <v>1.3088</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1482</v>
+        <v>1.1485</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8686</v>
+        <v>0.8691</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9099</v>
+        <v>0.9104</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7158</v>
+        <v>0.7164</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.861</v>
+        <v>0.8615</v>
       </c>
       <c r="L16" t="n">
-        <v>0.599</v>
+        <v>0.5997</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0002</v>
+        <v>1.0006</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6926</v>
+        <v>0.6932</v>
       </c>
       <c r="M17" t="n">
         <v>0.5783</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5751,20 +5751,20 @@
         <v>47</v>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3648</v>
+        <v>1.3115</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6234</v>
+        <v>0.5596</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8227</v>
+        <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5973</v>
+        <v>1.5974</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6849</v>
+        <v>0.6855</v>
       </c>
       <c r="M19" t="n">
         <v>0.874</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5849,14 +5849,14 @@
         <v>1.6486</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8527</v>
+        <v>0.8532</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6345</v>
+        <v>0.6352</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9928</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9571</v>
+        <v>0.9576</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1026</v>
+        <v>1.1029</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1308</v>
+        <v>1.1312</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7204</v>
+        <v>0.721</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6984</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2747</v>
+        <v>1.275</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1038</v>
+        <v>1.1042</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6952</v>
+        <v>0.6958</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2003</v>
+        <v>1.2006</v>
       </c>
       <c r="L26" t="n">
-        <v>0.702</v>
+        <v>0.7026</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8558</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3468</v>
+        <v>1.3471</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6202,29 +6202,29 @@
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.1151</v>
+        <v>1.0759</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6595</v>
+        <v>0.55</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6807</v>
+        <v>0.7476</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.387</v>
+        <v>1.3873</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4887</v>
+        <v>1.4888</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8147</v>
+        <v>0.8153</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9368</v>
+        <v>0.9373</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4037</v>
+        <v>1.4038</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5589</v>
+        <v>1.559</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9408</v>
+        <v>0.9413</v>
       </c>
       <c r="M32" t="n">
         <v>0.7378</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9374</v>
+        <v>0.9379</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0463</v>
+        <v>1.0467</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8368</v>
+        <v>0.8373</v>
       </c>
       <c r="L34" t="n">
-        <v>0.825</v>
+        <v>0.8255</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6521,32 +6521,32 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J35" t="n">
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.3799</v>
+        <v>1.2698</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6742</v>
+        <v>0.6774</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7251</v>
+        <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6967</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3223</v>
+        <v>1.3225</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.709</v>
+        <v>0.7096</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9847</v>
+        <v>0.9852</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0466</v>
+        <v>1.047</v>
       </c>
       <c r="L38" t="n">
-        <v>0.864</v>
+        <v>0.8645</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3479</v>
+        <v>1.3482</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0229</v>
+        <v>1.0234</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.751</v>
+        <v>0.7516</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7926</v>
+        <v>0.7932</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9651</v>
+        <v>0.9655</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7889</v>
+        <v>0.7895</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6852,23 +6852,23 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>1.446</v>
+        <v>1.3944</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7765</v>
+        <v>0.7971</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.171</v>
+        <v>1.1713</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3688</v>
+        <v>1.369</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4139</v>
+        <v>1.4141</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7598</v>
+        <v>0.7604</v>
       </c>
       <c r="M44" t="n">
         <v>0.6988</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7189</v>
+        <v>0.7195</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4485</v>
+        <v>1.4487</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2177</v>
+        <v>1.218</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9036</v>
+        <v>0.9041</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
         <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J47" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.351</v>
+        <v>1.2777</v>
       </c>
       <c r="L47" t="n">
-        <v>1.0297</v>
+        <v>1.1708</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6123</v>
+        <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7769</v>
+        <v>0.7775</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8479</v>
+        <v>0.8485</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9278</v>
+        <v>0.9283</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2301</v>
+        <v>1.2304</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-05T23:00:00+00:00</t>
+          <t>2026-07-06T23:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,19 +514,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -544,49 +544,49 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>55.9</v>
+        <v>64.5</v>
       </c>
       <c r="K2" t="n">
-        <v>30.4</v>
+        <v>39.4</v>
       </c>
       <c r="L2" t="n">
-        <v>17.6</v>
+        <v>20.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1617.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="R2" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -601,34 +601,34 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>48.5</v>
+        <v>55.3</v>
       </c>
       <c r="K3" t="n">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1577.2</v>
+        <v>1617.8</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="4">
@@ -667,10 +667,10 @@
         <v>57.8</v>
       </c>
       <c r="K4" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="L4" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -724,13 +724,13 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="K5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="L5" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="J6" t="n">
         <v>35.9</v>
       </c>
       <c r="K6" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="L6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -874,19 +874,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -904,49 +904,49 @@
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>42.6</v>
+        <v>35.4</v>
       </c>
       <c r="K8" t="n">
-        <v>17.8</v>
+        <v>16.3</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1582.5</v>
+        <v>1545.2</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="R8" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -961,34 +961,34 @@
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>42.6</v>
       </c>
       <c r="K9" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1545.2</v>
+        <v>1582.5</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="10">
@@ -1018,19 +1018,19 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="I10" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J10" t="n">
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1054,22 +1054,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1078,108 +1078,108 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I11" t="n">
-        <v>47</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>17.7</v>
+        <v>2.1</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1541.7</v>
+        <v>1544.1</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>12.7</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1560.9</v>
+        <v>1564.9</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>14.8</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1218,28 +1218,28 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1544.1</v>
+        <v>1507.6</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1255,22 +1255,22 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1278,38 +1278,38 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1564.9</v>
+        <v>1573.4</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="R14" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1334,27 +1334,27 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1507.6</v>
+        <v>1546.8</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.37</v>
+        <v>0.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1366,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1394,18 +1394,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1573.4</v>
+        <v>1560</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="R16" t="n">
         <v>0.6</v>
@@ -1414,22 +1414,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1454,39 +1454,39 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1546.8</v>
+        <v>1514.3</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1514,27 +1514,27 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1560</v>
+        <v>1542.8</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1546,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1574,39 +1574,39 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1514.3</v>
+        <v>1544.6</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1634,39 +1634,39 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1542.8</v>
+        <v>1494.5</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1544.6</v>
+        <v>1541.7</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="R21" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1758,44 +1758,44 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1494.5</v>
+        <v>1554.9</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0.86</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1814,48 +1814,48 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1554.9</v>
+        <v>1519.9</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R23" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1878,44 +1878,44 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R24" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>80.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1934,42 +1934,42 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1534.2</v>
+        <v>1537.9</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="R25" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1994,21 +1994,21 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1537.9</v>
+        <v>1560.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="27">
@@ -4876,7 +4876,7 @@
         <v>26.6</v>
       </c>
       <c r="K2" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -5021,14 +5021,14 @@
         <v>1.1845</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9106</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5058,23 +5058,23 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6148</v>
+        <v>1.6383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.556</v>
+        <v>0.6223</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9467</v>
+        <v>0.9518</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8744</v>
+        <v>0.8746</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7294</v>
+        <v>0.7297</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2672</v>
+        <v>1.2671</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9527</v>
+        <v>0.9528</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7365</v>
+        <v>0.7368</v>
       </c>
       <c r="M6" t="n">
         <v>0.7596000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9905</v>
+        <v>0.9907</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0068</v>
+        <v>1.0069</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4227</v>
+        <v>1.4226</v>
       </c>
       <c r="L8" t="n">
-        <v>0.806</v>
+        <v>0.8063</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0642</v>
+        <v>1.0643</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6966</v>
+        <v>0.697</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0059</v>
+        <v>1.006</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8582</v>
+        <v>0.8585</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5420,29 +5420,29 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1549</v>
+        <v>1.0715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6762</v>
+        <v>0.62</v>
       </c>
       <c r="M11" t="n">
-        <v>0.711</v>
+        <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1642</v>
+        <v>1.1643</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0068</v>
+        <v>1.0069</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3088</v>
+        <v>1.3086</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5573,14 +5573,14 @@
         <v>1.1485</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8691</v>
+        <v>0.8694</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9104</v>
+        <v>0.9106</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7164</v>
+        <v>0.7168</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8615</v>
+        <v>0.8618</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5997</v>
+        <v>0.6002</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5693,32 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
         <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0006</v>
+        <v>1.0326</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6932</v>
+        <v>0.7968</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5783</v>
+        <v>0.519</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3115</v>
+        <v>1.3114</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5596</v>
+        <v>0.5601</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5974</v>
+        <v>1.5972</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6855</v>
+        <v>0.6859</v>
       </c>
       <c r="M19" t="n">
         <v>0.874</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6486</v>
+        <v>1.6483</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8532</v>
+        <v>0.8535</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6352</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9928</v>
+        <v>0.993</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9576</v>
+        <v>0.9578</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1029</v>
+        <v>1.103</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5987,14 +5987,14 @@
         <v>1.1312</v>
       </c>
       <c r="L23" t="n">
-        <v>0.721</v>
+        <v>0.7214</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6995</v>
       </c>
       <c r="L24" t="n">
-        <v>1.275</v>
+        <v>1.2749</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1042</v>
+        <v>1.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6958</v>
+        <v>0.6962</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6125,14 +6125,14 @@
         <v>1.2006</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7026</v>
+        <v>0.703</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8566</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3471</v>
+        <v>1.3469</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0759</v>
+        <v>1.076</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3873</v>
+        <v>1.3872</v>
       </c>
       <c r="L29" t="n">
         <v>0.55</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4888</v>
+        <v>1.4886</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8153</v>
+        <v>0.8155</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9373</v>
+        <v>0.9375</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4038</v>
+        <v>1.4036</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.559</v>
+        <v>1.5588</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9413</v>
+        <v>0.9415</v>
       </c>
       <c r="M32" t="n">
         <v>0.7378</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9379</v>
+        <v>0.9381</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0467</v>
+        <v>1.0468</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8373</v>
+        <v>0.8376</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8255</v>
+        <v>0.8258</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2698</v>
+        <v>1.2697</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6774</v>
+        <v>0.6778</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6967</v>
+        <v>0.6972</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3225</v>
+        <v>1.3223</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7096</v>
+        <v>0.71</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9852</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.047</v>
+        <v>1.0471</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8645</v>
+        <v>0.8648</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3482</v>
+        <v>1.3481</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0234</v>
+        <v>1.0235</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7516</v>
+        <v>0.7519</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7932</v>
+        <v>0.7935</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9655</v>
+        <v>0.9657</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7895</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3944</v>
+        <v>1.3943</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6907,14 +6907,14 @@
         <v>1.1713</v>
       </c>
       <c r="L43" t="n">
-        <v>1.369</v>
+        <v>1.3689</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6944,23 +6944,23 @@
         <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.4141</v>
+        <v>1.3174</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7604</v>
+        <v>0.7069</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6988</v>
+        <v>0.6649</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7195</v>
+        <v>0.7199</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4487</v>
+        <v>1.4485</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.218</v>
+        <v>1.2179</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9041</v>
+        <v>0.9043</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7775</v>
+        <v>0.7778</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8485</v>
+        <v>0.8488</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9283</v>
+        <v>0.9285</v>
       </c>
       <c r="L49" t="n">
         <v>1.2304</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-06T23:00:00+00:00</t>
+          <t>2026-07-07T19:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -544,49 +544,49 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>64.5</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>39.4</v>
+        <v>50.4</v>
       </c>
       <c r="L2" t="n">
-        <v>20.5</v>
+        <v>27.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 4强</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1577.2</v>
+        <v>1569.9</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -604,31 +604,31 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>55.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>30.2</v>
+        <v>39.1</v>
       </c>
       <c r="L3" t="n">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1617.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4">
@@ -664,13 +664,13 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="K4" t="n">
-        <v>29.7</v>
+        <v>30.7</v>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -694,12 +694,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -721,45 +721,45 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>57.4</v>
       </c>
       <c r="J5" t="n">
-        <v>44.6</v>
+        <v>35.2</v>
       </c>
       <c r="K5" t="n">
-        <v>21.6</v>
+        <v>18.5</v>
       </c>
       <c r="L5" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1569.9</v>
+        <v>1593.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -781,52 +781,52 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>35.9</v>
+        <v>42.3</v>
       </c>
       <c r="K6" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1593.4</v>
+        <v>1555.6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -844,31 +844,31 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="K7" t="n">
-        <v>18.3</v>
+        <v>16.9</v>
       </c>
       <c r="L7" t="n">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1555.6</v>
+        <v>1582.5</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.74</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.76</v>
       </c>
     </row>
     <row r="8">
@@ -904,10 +904,10 @@
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="K8" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>6.1</v>
@@ -934,19 +934,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -958,58 +958,58 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>70.8</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>33.7</v>
       </c>
       <c r="J9" t="n">
-        <v>42.6</v>
+        <v>18.2</v>
       </c>
       <c r="K9" t="n">
-        <v>16.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1582.5</v>
+        <v>1573.8</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1018,48 +1018,48 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>70.3</v>
+        <v>14.8</v>
       </c>
       <c r="I10" t="n">
-        <v>33.6</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>2.1</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1573.8</v>
+        <v>1544.1</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>0.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1075,22 +1075,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H11" t="n">
-        <v>14.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,28 +1098,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1544.1</v>
+        <v>1564.9</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>0.86</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1135,22 +1135,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1158,28 +1158,28 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1564.9</v>
+        <v>1507.6</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1198,13 +1198,13 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1218,38 +1218,38 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1507.6</v>
+        <v>1573.4</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>0.91</v>
       </c>
       <c r="R13" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1573.4</v>
+        <v>1546.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1338,38 +1338,38 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1546.8</v>
+        <v>1560</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1394,42 +1394,42 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1560</v>
+        <v>1514.3</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1.27</v>
+        <v>0.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1454,39 +1454,39 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1514.3</v>
+        <v>1542.8</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0.41</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1514,32 +1514,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1542.8</v>
+        <v>1544.6</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1558,7 +1558,7 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1574,39 +1574,39 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1544.6</v>
+        <v>1494.5</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1634,39 +1634,39 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1494.5</v>
+        <v>1541.7</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1541.7</v>
+        <v>1554.9</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1754,48 +1754,48 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1554.9</v>
+        <v>1519.9</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R22" t="n">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1818,44 +1818,44 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1519.9</v>
+        <v>1534.2</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.31</v>
+        <v>0.87</v>
       </c>
       <c r="R23" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>80.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1874,42 +1874,42 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1534.2</v>
+        <v>1537.9</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.15</v>
+        <v>0.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1934,39 +1934,39 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1537.9</v>
+        <v>1560.9</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1994,42 +1994,42 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1560.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="R26" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1577.2</v>
+        <v>1467.7</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>0.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="R27" t="n">
-        <v>0.74</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2114,32 +2114,32 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1467.7</v>
+        <v>1523</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2174,32 +2174,32 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1523</v>
+        <v>1546.8</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2234,48 +2234,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1546.8</v>
+        <v>1534.7</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.72</v>
+        <v>1.27</v>
       </c>
       <c r="R30" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2294,32 +2294,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1534.7</v>
+        <v>1556.1</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.27</v>
-      </c>
       <c r="R31" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2358,44 +2358,44 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1556.1</v>
+        <v>1575.8</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2414,54 +2414,54 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1575.8</v>
+        <v>1493.5</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0.64</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2474,21 +2474,21 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1493.5</v>
+        <v>1617.8</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>0.86</v>
+        <v>1.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.35</v>
+        <v>0.59</v>
       </c>
       <c r="R34" t="n">
-        <v>0.15</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="35">
@@ -2965,7 +2965,7 @@
         <v>1.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="R42" t="n">
         <v>0.52</v>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3693,11 +3693,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3706,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3720,23 +3720,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -4873,7 +4873,7 @@
         <v>19.1</v>
       </c>
       <c r="J2" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="K2" t="n">
         <v>54.4</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1845</v>
+        <v>1.1843</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9112</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
         <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6383</v>
+        <v>1.6372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6223</v>
+        <v>0.6233</v>
       </c>
       <c r="M3" t="n">
         <v>0.9518</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8746</v>
+        <v>0.8751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7297</v>
+        <v>0.7305</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2671</v>
+        <v>1.2667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9528</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7368</v>
+        <v>0.7375</v>
       </c>
       <c r="M6" t="n">
         <v>0.7596000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9907</v>
+        <v>0.9909</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0069</v>
+        <v>1.0071</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4226</v>
+        <v>1.4219</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8063</v>
+        <v>0.8069</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0643</v>
+        <v>1.0644</v>
       </c>
       <c r="L9" t="n">
-        <v>0.697</v>
+        <v>0.6978</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.006</v>
+        <v>1.0062</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8585</v>
+        <v>0.859</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5435,14 +5435,14 @@
         <v>1.0715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.62</v>
+        <v>0.6209</v>
       </c>
       <c r="M11" t="n">
         <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1643</v>
+        <v>1.1641</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0069</v>
+        <v>1.0071</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9927</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3086</v>
+        <v>1.3081</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1485</v>
+        <v>1.1483</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8694</v>
+        <v>0.8699</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9106</v>
+        <v>0.911</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7168</v>
+        <v>0.7176</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8618</v>
+        <v>0.8623</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6002</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0326</v>
+        <v>1.0327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7968</v>
+        <v>0.7974</v>
       </c>
       <c r="M17" t="n">
         <v>0.519</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3114</v>
+        <v>1.3109</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5601</v>
+        <v>0.5612</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5794,23 +5794,23 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5972</v>
+        <v>1.5819</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6859</v>
+        <v>0.6405</v>
       </c>
       <c r="M19" t="n">
-        <v>0.874</v>
+        <v>0.8847</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6483</v>
+        <v>1.6471</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8535</v>
+        <v>0.854</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6367</v>
       </c>
       <c r="L21" t="n">
-        <v>0.993</v>
+        <v>0.9932</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9578</v>
+        <v>0.9581</v>
       </c>
       <c r="L22" t="n">
         <v>1.103</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1312</v>
+        <v>1.1311</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7214</v>
+        <v>0.7222</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6995</v>
+        <v>0.7003</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2749</v>
+        <v>1.2744</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6079,14 +6079,14 @@
         <v>1.1043</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6962</v>
+        <v>0.697</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2006</v>
+        <v>1.2004</v>
       </c>
       <c r="L26" t="n">
-        <v>0.703</v>
+        <v>0.7039</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8566</v>
+        <v>0.8571</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3469</v>
+        <v>1.3463</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6245,32 +6245,32 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3872</v>
+        <v>1.3155</v>
       </c>
       <c r="L29" t="n">
-        <v>0.55</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7756</v>
+        <v>0.7085</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4886</v>
+        <v>1.4877</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8155</v>
+        <v>0.8161</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9375</v>
+        <v>0.9378</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4036</v>
+        <v>1.4029</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5588</v>
+        <v>1.5579</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9415</v>
+        <v>0.9418</v>
       </c>
       <c r="M32" t="n">
         <v>0.7378</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9381</v>
+        <v>0.9384</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0468</v>
+        <v>1.0469</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8376</v>
+        <v>0.8381</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8258</v>
+        <v>0.8264</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2697</v>
+        <v>1.2694</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6778</v>
+        <v>0.6786</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6972</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3223</v>
+        <v>1.3216</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.71</v>
+        <v>0.7108</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9856</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0471</v>
+        <v>1.0472</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8648</v>
+        <v>0.8653</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3481</v>
+        <v>1.3476</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0235</v>
+        <v>1.0237</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7519</v>
+        <v>0.7526</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7935</v>
+        <v>0.7941</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9657</v>
+        <v>0.966</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7905</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3943</v>
+        <v>1.3937</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1713</v>
+        <v>1.1711</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3689</v>
+        <v>1.3683</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.3174</v>
+        <v>1.317</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7069</v>
+        <v>0.7076</v>
       </c>
       <c r="M44" t="n">
         <v>0.6649</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7199</v>
+        <v>0.7207</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4485</v>
+        <v>1.4477</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2179</v>
+        <v>1.2176</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9043</v>
+        <v>0.9048</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2777</v>
+        <v>1.2773</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1708</v>
+        <v>1.1707</v>
       </c>
       <c r="M47" t="n">
         <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7778</v>
+        <v>0.7786</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8488</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9285</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2304</v>
+        <v>1.2301</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-07T19:00:00+00:00</t>
+          <t>2026-07-09T19:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -547,10 +547,10 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>50.4</v>
+        <v>52.8</v>
       </c>
       <c r="L2" t="n">
-        <v>27.2</v>
+        <v>29.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -558,28 +558,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1569.9</v>
+        <v>1603.8</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -604,42 +604,42 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>64.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>39.1</v>
+        <v>47.1</v>
       </c>
       <c r="L3" t="n">
-        <v>20.7</v>
+        <v>25.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 4强</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1577.2</v>
+        <v>1569.9</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,13 +664,13 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>57.6</v>
+        <v>65</v>
       </c>
       <c r="K4" t="n">
-        <v>30.7</v>
+        <v>39.6</v>
       </c>
       <c r="L4" t="n">
-        <v>17.3</v>
+        <v>20.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -678,17 +678,17 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1603.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5">
@@ -721,16 +721,16 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="J5" t="n">
-        <v>35.2</v>
+        <v>35.9</v>
       </c>
       <c r="K5" t="n">
         <v>18.5</v>
       </c>
       <c r="L5" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -754,12 +754,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -784,13 +784,13 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>42.3</v>
+        <v>34.9</v>
       </c>
       <c r="K6" t="n">
-        <v>18.8</v>
+        <v>16.1</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -798,17 +798,17 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1555.6</v>
+        <v>1545.2</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="R6" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="7">
@@ -844,13 +844,13 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>43.1</v>
+        <v>42.4</v>
       </c>
       <c r="K7" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="L7" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -898,58 +898,58 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>33.5</v>
       </c>
       <c r="J8" t="n">
-        <v>35.3</v>
+        <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1545.2</v>
+        <v>1573.8</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -958,48 +958,48 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>70.8</v>
+        <v>14.8</v>
       </c>
       <c r="I9" t="n">
-        <v>33.7</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="K9" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1573.8</v>
+        <v>1544.1</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>0.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="H10" t="n">
-        <v>14.8</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,28 +1038,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1544.1</v>
+        <v>1564.9</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.86</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1075,22 +1075,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1098,28 +1098,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1564.9</v>
+        <v>1507.6</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1138,13 +1138,13 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1158,38 +1158,38 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1507.6</v>
+        <v>1573.4</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>0.91</v>
       </c>
       <c r="R12" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1214,32 +1214,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1573.4</v>
+        <v>1546.8</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1278,35 +1278,35 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1546.8</v>
+        <v>1560</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>0.88</v>
+        <v>1.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1334,21 +1334,21 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1560</v>
+        <v>1555.6</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1843</v>
+        <v>1.1841</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9112</v>
+        <v>0.9113</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
         <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6372</v>
+        <v>1.6364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6233</v>
+        <v>0.6237</v>
       </c>
       <c r="M3" t="n">
         <v>0.9518</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8751</v>
+        <v>0.8752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7305</v>
+        <v>0.7308</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2667</v>
+        <v>1.2663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9532</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5196,23 +5196,23 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7375</v>
+        <v>0.7843</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.6945</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4219</v>
+        <v>1.4214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8069</v>
+        <v>0.8071</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0644</v>
+        <v>1.0643</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6978</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5389,14 +5389,14 @@
         <v>1.0062</v>
       </c>
       <c r="L10" t="n">
-        <v>0.859</v>
+        <v>0.8592</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0715</v>
+        <v>1.0714</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6209</v>
+        <v>0.6213</v>
       </c>
       <c r="M11" t="n">
         <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1641</v>
+        <v>1.1638</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0071</v>
+        <v>1.007</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9927</v>
+        <v>0.9926</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3081</v>
+        <v>1.3077</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1483</v>
+        <v>1.148</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8699</v>
+        <v>0.87</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.911</v>
+        <v>0.9111</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7176</v>
+        <v>0.7179</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8623</v>
+        <v>0.8625</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6018</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5711,14 +5711,14 @@
         <v>1.0327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7974</v>
+        <v>0.7975</v>
       </c>
       <c r="M17" t="n">
         <v>0.519</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3109</v>
+        <v>1.3105</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5612</v>
+        <v>0.5617</v>
       </c>
       <c r="M18" t="n">
         <v>0.8048</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5819</v>
+        <v>1.5812</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6405</v>
+        <v>0.6408</v>
       </c>
       <c r="M19" t="n">
         <v>0.8847</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6471</v>
+        <v>1.6462</v>
       </c>
       <c r="L20" t="n">
-        <v>0.854</v>
+        <v>0.8541</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6367</v>
+        <v>0.6371</v>
       </c>
       <c r="L21" t="n">
         <v>0.9932</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5941,14 +5941,14 @@
         <v>0.9581</v>
       </c>
       <c r="L22" t="n">
-        <v>1.103</v>
+        <v>1.1028</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1311</v>
+        <v>1.1309</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7222</v>
+        <v>0.7225</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7003</v>
+        <v>0.7007</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2744</v>
+        <v>1.274</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1043</v>
+        <v>1.1041</v>
       </c>
       <c r="L25" t="n">
-        <v>0.697</v>
+        <v>0.6973</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2004</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7039</v>
+        <v>0.7042</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8571</v>
+        <v>0.8573</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3463</v>
+        <v>1.3458</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.076</v>
+        <v>1.0758</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3155</v>
+        <v>1.3151</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5925</v>
       </c>
       <c r="M29" t="n">
         <v>0.7085</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4877</v>
+        <v>1.4871</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8161</v>
+        <v>0.8163</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6355,14 +6355,14 @@
         <v>0.9378</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4029</v>
+        <v>1.4023</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5579</v>
+        <v>1.5572</v>
       </c>
       <c r="L32" t="n">
         <v>0.9418</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9384</v>
+        <v>0.9385</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0469</v>
+        <v>1.0468</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8381</v>
+        <v>0.8383</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8264</v>
+        <v>0.8266</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2694</v>
+        <v>1.269</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6786</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6985</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3216</v>
+        <v>1.3211</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7108</v>
+        <v>0.7111</v>
       </c>
       <c r="L37" t="n">
         <v>0.9856</v>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0472</v>
+        <v>1.047</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8653</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3476</v>
+        <v>1.3472</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0237</v>
+        <v>1.0236</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7526</v>
+        <v>0.7529</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7941</v>
+        <v>0.7943</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6815,14 +6815,14 @@
         <v>0.966</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7905</v>
+        <v>0.7907</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6852,23 +6852,23 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3937</v>
+        <v>1.3914</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7971</v>
+        <v>0.8144</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1711</v>
+        <v>1.1709</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3683</v>
+        <v>1.3678</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.317</v>
+        <v>1.3166</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7076</v>
+        <v>0.7079</v>
       </c>
       <c r="M44" t="n">
         <v>0.6649</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7207</v>
+        <v>0.721</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4477</v>
+        <v>1.4471</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2176</v>
+        <v>1.2172</v>
       </c>
       <c r="L46" t="n">
         <v>0.9048</v>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2773</v>
+        <v>1.277</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1707</v>
+        <v>1.1705</v>
       </c>
       <c r="M47" t="n">
         <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7786</v>
+        <v>0.7789</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8495</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7183,14 +7183,14 @@
         <v>0.9288999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2301</v>
+        <v>1.2298</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-09T19:00:00+00:00</t>
+          <t>2026-07-10T18:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -547,10 +547,10 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="L2" t="n">
-        <v>29.9</v>
+        <v>27.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -574,12 +574,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -607,10 +607,10 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>47.1</v>
+        <v>53.4</v>
       </c>
       <c r="L3" t="n">
-        <v>25.4</v>
+        <v>27.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -618,28 +618,28 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1569.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -664,31 +664,31 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>39.6</v>
+        <v>47</v>
       </c>
       <c r="L4" t="n">
-        <v>20.4</v>
+        <v>23</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第1 → 4强</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1577.2</v>
+        <v>1569.9</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="5">
@@ -721,20 +721,20 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.8</v>
+        <v>56.7</v>
       </c>
       <c r="J5" t="n">
-        <v>35.9</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>18.5</v>
+        <v>46.5</v>
       </c>
       <c r="L5" t="n">
-        <v>8.9</v>
+        <v>22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第1 → 4强</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -745,31 +745,31 @@
         <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -778,48 +778,48 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>34.9</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1545.2</v>
+        <v>1573.4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="R6" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -838,55 +838,55 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1582.5</v>
+        <v>1546.8</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>0.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="R7" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -898,58 +898,58 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>70.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1573.8</v>
+        <v>1560</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -958,48 +958,48 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>14.8</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1544.1</v>
+        <v>1555.6</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>0.86</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1038,38 +1038,38 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1564.9</v>
+        <v>1514.3</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>0.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1094,42 +1094,42 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1507.6</v>
+        <v>1542.8</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1138,7 +1138,7 @@
         <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1154,32 +1154,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1573.4</v>
+        <v>1544.6</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1218,35 +1218,35 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1546.8</v>
+        <v>1494.5</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1274,39 +1274,39 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1560</v>
+        <v>1541.7</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>小组第1 → 8强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1555.6</v>
+        <v>1554.9</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.78</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1369,13 +1369,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1394,51 +1394,51 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1514.3</v>
+        <v>1519.9</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R16" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1454,42 +1454,42 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1542.8</v>
+        <v>1534.2</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="R17" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1514,42 +1514,42 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1544.6</v>
+        <v>1537.9</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="R18" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1574,39 +1574,39 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1494.5</v>
+        <v>1544.1</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1634,39 +1634,39 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>小组第1 → 16强</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1541.7</v>
+        <v>1560.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1554.9</v>
+        <v>1577.2</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="R21" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1729,13 +1729,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1754,48 +1754,48 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1519.9</v>
+        <v>1467.7</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0.99</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.31</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>80.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1818,28 +1818,28 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1534.2</v>
+        <v>1523</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1874,51 +1874,51 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1537.9</v>
+        <v>1546.8</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>0.91</v>
+        <v>1.13</v>
       </c>
       <c r="Q24" t="n">
         <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1934,27 +1934,27 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1560.9</v>
+        <v>1534.7</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.03</v>
+        <v>0.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="R25" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1994,42 +1994,42 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1577.2</v>
+        <v>1556.1</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>小组第3 → 32强</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1467.7</v>
+        <v>1575.8</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.64</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2118,50 +2118,50 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1523</v>
+        <v>1493.5</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2174,54 +2174,54 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第1 → 16强</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1546.8</v>
+        <v>1573.8</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="R29" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2234,39 +2234,39 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1534.7</v>
+        <v>1617.8</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0.7</v>
+        <v>1.31</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.27</v>
+        <v>0.59</v>
       </c>
       <c r="R30" t="n">
-        <v>0.39</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2294,48 +2294,48 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第1 → 32强</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1556.1</v>
+        <v>1571</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.1</v>
+        <v>1.49</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="R31" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,54 +2354,54 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1575.8</v>
+        <v>1518</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2414,54 +2414,54 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 8强</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1493.5</v>
+        <v>1582.5</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.86</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.35</v>
+        <v>0.98</v>
       </c>
       <c r="R33" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2474,42 +2474,42 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>小组第2 → 8强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1617.8</v>
+        <v>1555</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.59</v>
+        <v>1.05</v>
       </c>
       <c r="R34" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2534,51 +2534,51 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>小组第1 → 32强</t>
+          <t>小组第3 → 16强</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1571</v>
+        <v>1519.6</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.49</v>
+        <v>0.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="R35" t="n">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2594,32 +2594,32 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 16强</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1518</v>
+        <v>1565</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.4</v>
+        <v>0.68</v>
       </c>
       <c r="R36" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1555</v>
+        <v>1484.3</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="R37" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2689,16 +2689,16 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2714,51 +2714,51 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>小组第3 → 16强</t>
+          <t>小组第4 → 小组赛</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1519.6</v>
+        <v>1499.2</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="R38" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2774,32 +2774,32 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>小组第2 → 16强</t>
+          <t>小组第3 → 小组赛</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1565</v>
+        <v>1521.6</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.68</v>
+        <v>0.87</v>
       </c>
       <c r="R39" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2809,19 +2809,19 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2834,48 +2834,48 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1484.3</v>
+        <v>1564.9</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="R40" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2894,32 +2894,32 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>小组第4 → 小组赛</t>
+          <t>小组第2 → 32强</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1499.2</v>
+        <v>1521.7</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="R41" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2929,10 +2929,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2958,38 +2958,38 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1521.6</v>
+        <v>1550.3</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="R42" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>80.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3014,54 +3014,54 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>小组第2 → 32强</t>
+          <t>小组第3 → 32强</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1521.7</v>
+        <v>1507.6</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="R43" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>80.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3074,21 +3074,21 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>小组第3 → 小组赛</t>
+          <t>小组第1 → 8强</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1550.3</v>
+        <v>1545.2</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="R44" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="45">
@@ -3450,23 +3450,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="3">
@@ -3477,23 +3477,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>80.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>19.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3639,11 +3639,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3652,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3919,13 +3919,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -3990,17 +3990,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4017,14 +4017,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4044,17 +4044,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -4341,23 +4341,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4368,23 +4368,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4405,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="38">
@@ -4873,7 +4873,7 @@
         <v>19.1</v>
       </c>
       <c r="J2" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="K2" t="n">
         <v>54.4</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1841</v>
+        <v>1.1834</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9113</v>
+        <v>0.9111</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5049,32 +5049,32 @@
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6364</v>
+        <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6237</v>
+        <v>0.6258</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9518</v>
+        <v>0.9638</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8752</v>
+        <v>0.8751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7308</v>
+        <v>0.731</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2663</v>
+        <v>1.2654</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9532</v>
+        <v>0.9529</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7843</v>
+        <v>0.7844</v>
       </c>
       <c r="M6" t="n">
         <v>0.6945</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9909</v>
+        <v>0.9905</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0071</v>
+        <v>1.0067</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4214</v>
+        <v>1.4202</v>
       </c>
       <c r="L8" t="n">
         <v>0.8071</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0643</v>
+        <v>1.0638</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6983</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0062</v>
+        <v>1.0058</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8592</v>
+        <v>0.8591</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0714</v>
+        <v>1.0709</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6213</v>
+        <v>0.6217</v>
       </c>
       <c r="M11" t="n">
         <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1638</v>
+        <v>1.1632</v>
       </c>
       <c r="L12" t="n">
-        <v>1.007</v>
+        <v>1.0067</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9926</v>
+        <v>0.9923</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3077</v>
+        <v>1.3067</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.148</v>
+        <v>1.1474</v>
       </c>
       <c r="L14" t="n">
         <v>0.87</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9111</v>
+        <v>0.9109</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7179</v>
+        <v>0.7181</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8625</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6018</v>
+        <v>0.6024</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
         <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0327</v>
+        <v>1.0322</v>
       </c>
       <c r="L17" t="n">
         <v>0.7975</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5748,23 +5748,23 @@
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3105</v>
+        <v>1.3131</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5617</v>
+        <v>0.5764</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8048</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5812</v>
+        <v>1.5797</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6408</v>
+        <v>0.6411</v>
       </c>
       <c r="M19" t="n">
         <v>0.8847</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6462</v>
+        <v>1.6445</v>
       </c>
       <c r="L20" t="n">
         <v>0.8541</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6371</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9932</v>
+        <v>0.9929</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9581</v>
+        <v>0.9578</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1028</v>
+        <v>1.1022</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1309</v>
+        <v>1.1303</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7225</v>
+        <v>0.7228</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7007</v>
+        <v>0.701</v>
       </c>
       <c r="L24" t="n">
-        <v>1.274</v>
+        <v>1.2731</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1041</v>
+        <v>1.1036</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6973</v>
+        <v>0.6975</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>1.1993</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7042</v>
+        <v>0.7045</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6171,14 +6171,14 @@
         <v>0.8573</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3458</v>
+        <v>1.3447</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0758</v>
+        <v>1.0754</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3151</v>
+        <v>1.3142</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5925</v>
+        <v>0.5929</v>
       </c>
       <c r="M29" t="n">
         <v>0.7085</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4871</v>
+        <v>1.4857</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8163</v>
+        <v>0.8164</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9378</v>
+        <v>0.9376</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4023</v>
+        <v>1.4011</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6383,32 +6383,32 @@
         <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5572</v>
+        <v>1.4878</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9418</v>
+        <v>0.9796</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7378</v>
+        <v>0.6666</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9385</v>
+        <v>0.9382</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0468</v>
+        <v>1.0464</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.269</v>
+        <v>1.2681</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6792</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6985</v>
+        <v>0.6989</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3211</v>
+        <v>1.3201</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7111</v>
+        <v>0.7113</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9856</v>
+        <v>0.9852</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.047</v>
+        <v>1.0466</v>
       </c>
       <c r="L38" t="n">
         <v>0.8653999999999999</v>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3472</v>
+        <v>1.3462</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0236</v>
+        <v>1.0232</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7529</v>
+        <v>0.753</v>
       </c>
       <c r="L40" t="n">
         <v>0.7943</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.966</v>
+        <v>0.9657</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7907</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3914</v>
+        <v>1.3903</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1709</v>
+        <v>1.1702</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3678</v>
+        <v>1.3667</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6944,23 +6944,23 @@
         <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J44" t="n">
         <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.3166</v>
+        <v>1.2743</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7079</v>
+        <v>0.797</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6649</v>
+        <v>0.6076</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.721</v>
+        <v>0.7212</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4471</v>
+        <v>1.4459</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2172</v>
+        <v>1.2165</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9048</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.277</v>
+        <v>1.2761</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1705</v>
+        <v>1.1698</v>
       </c>
       <c r="M47" t="n">
         <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7789</v>
+        <v>0.7791</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8495</v>
+        <v>0.8496</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9287</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2298</v>
+        <v>1.229</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-10T18:00:00+00:00</t>
+          <t>2026-07-12T00:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -547,39 +547,39 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>27.6</v>
+        <v>51.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>小组第1 → 4强</t>
+          <t>小组第1 → 冠军</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1603.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -607,10 +607,10 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>53.4</v>
+        <v>53</v>
       </c>
       <c r="L3" t="n">
-        <v>27.4</v>
+        <v>26.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -618,17 +618,17 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1577.2</v>
+        <v>1603.8</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -667,10 +667,10 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -721,16 +721,16 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>56.7</v>
+        <v>53.1</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -742,13 +742,13 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R5" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="6">
@@ -922,7 +922,7 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
         <v>0.95</v>
@@ -985,7 +985,7 @@
         <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="R9" t="n">
         <v>0.6899999999999999</v>
@@ -1558,10 +1558,10 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>1.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="R27" t="n">
         <v>0.64</v>
@@ -2158,10 +2158,10 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>34.5</v>
+        <v>37.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q29" t="n">
         <v>0.55</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
         <v>0.82</v>
@@ -2818,10 +2818,10 @@
         <v>80.8</v>
       </c>
       <c r="H40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q40" t="n">
         <v>1.02</v>
@@ -2905,7 +2905,7 @@
         <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="R41" t="n">
         <v>0.42</v>
@@ -2998,10 +2998,10 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>1.17</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R43" t="n">
         <v>0.39</v>
@@ -3145,7 +3145,7 @@
         <v>0.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R45" t="n">
         <v>0.25</v>
@@ -3205,7 +3205,7 @@
         <v>1.22</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="R46" t="n">
         <v>0.67</v>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q47" t="n">
         <v>1.17</v>
@@ -4870,10 +4870,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="K2" t="n">
         <v>54.4</v>
@@ -4897,7 +4897,7 @@
         <v>39.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1834</v>
+        <v>1.1825</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9111</v>
+        <v>0.9115</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5058,23 +5058,23 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6258</v>
+        <v>0.6362</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9638</v>
+        <v>0.9668</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8751</v>
+        <v>0.8756</v>
       </c>
       <c r="L4" t="n">
-        <v>0.731</v>
+        <v>0.7322</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2654</v>
+        <v>1.2641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9529</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7844</v>
+        <v>0.7852</v>
       </c>
       <c r="M6" t="n">
         <v>0.6945</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5251,14 +5251,14 @@
         <v>0.9905</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0067</v>
+        <v>1.0066</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4202</v>
+        <v>1.4183</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8071</v>
+        <v>0.8079</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0638</v>
+        <v>1.0635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6983</v>
+        <v>0.6995</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0058</v>
+        <v>1.0057</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8591</v>
+        <v>0.8598</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0709</v>
+        <v>1.0705</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6217</v>
+        <v>0.6233</v>
       </c>
       <c r="M11" t="n">
         <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1632</v>
+        <v>1.1624</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0067</v>
+        <v>1.0066</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5527,14 +5527,14 @@
         <v>0.9923</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3067</v>
+        <v>1.3051</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1474</v>
+        <v>1.1465</v>
       </c>
       <c r="L14" t="n">
-        <v>0.87</v>
+        <v>0.8707</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9109</v>
+        <v>0.9113</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7181</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8631</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6024</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0322</v>
+        <v>1.0321</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7975</v>
+        <v>0.7983</v>
       </c>
       <c r="M17" t="n">
         <v>0.519</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5739,32 +5739,32 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3131</v>
+        <v>1.2587</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5764</v>
+        <v>0.639</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.7439</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5800,17 +5800,17 @@
         <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5797</v>
+        <v>1.5773</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6411</v>
+        <v>0.6425</v>
       </c>
       <c r="M19" t="n">
         <v>0.8847</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6445</v>
+        <v>1.6415</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8541</v>
+        <v>0.8547</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6394</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9929</v>
+        <v>0.9928</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9578</v>
+        <v>0.958</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1022</v>
+        <v>1.1017</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1303</v>
+        <v>1.1296</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7228</v>
+        <v>0.7241</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.701</v>
+        <v>0.7024</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2731</v>
+        <v>1.2717</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1036</v>
+        <v>1.1031</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6975</v>
+        <v>0.6988</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1993</v>
+        <v>1.1983</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7045</v>
+        <v>0.7058</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8573</v>
+        <v>0.8579</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3447</v>
+        <v>1.343</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0754</v>
+        <v>1.075</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3142</v>
+        <v>1.313</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5929</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0.7085</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4857</v>
+        <v>1.4834</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8164</v>
+        <v>0.8172</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9376</v>
+        <v>0.9379</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4011</v>
+        <v>1.399</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>1.4878</v>
+        <v>1.4857</v>
       </c>
       <c r="L32" t="n">
         <v>0.9796</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9382</v>
+        <v>0.9385</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0464</v>
+        <v>1.0461</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8383</v>
+        <v>0.839</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8266</v>
+        <v>0.8273</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2681</v>
+        <v>1.2669</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6792</v>
+        <v>0.6806</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6989</v>
+        <v>0.7005</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3201</v>
+        <v>1.3183</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7113</v>
+        <v>0.7126</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9852</v>
+        <v>0.9853</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0466</v>
+        <v>1.0463</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3462</v>
+        <v>1.3447</v>
       </c>
       <c r="L39" t="n">
-        <v>1.0232</v>
+        <v>1.023</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7943</v>
+        <v>0.7952</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9657</v>
+        <v>0.9658</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3903</v>
+        <v>1.3886</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1702</v>
+        <v>1.1693</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3667</v>
+        <v>1.3649</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.2743</v>
+        <v>1.2731</v>
       </c>
       <c r="L44" t="n">
-        <v>0.797</v>
+        <v>0.7977</v>
       </c>
       <c r="M44" t="n">
         <v>0.6076</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6996,17 +6996,17 @@
         <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7212</v>
+        <v>0.7225</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4459</v>
+        <v>1.4437</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2165</v>
+        <v>1.2153</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9051</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2761</v>
+        <v>1.2749</v>
       </c>
       <c r="L47" t="n">
-        <v>1.1698</v>
+        <v>1.169</v>
       </c>
       <c r="M47" t="n">
         <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7791</v>
+        <v>0.7803</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8496</v>
+        <v>0.8504</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9287</v>
+        <v>0.929</v>
       </c>
       <c r="L49" t="n">
-        <v>1.229</v>
+        <v>1.2279</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-12T00:00:00+00:00</t>
+          <t>2026-07-15T18:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -550,7 +550,7 @@
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>51.2</v>
+        <v>54.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>53</v>
+        <v>61.6</v>
       </c>
       <c r="L3" t="n">
-        <v>26.7</v>
+        <v>31</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q3" t="n">
         <v>0.55</v>
@@ -667,10 +667,10 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>46.9</v>
+        <v>38.3</v>
       </c>
       <c r="L4" t="n">
-        <v>22.1</v>
+        <v>14.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -682,13 +682,13 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="R4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
@@ -721,7 +721,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>53.1</v>
+        <v>51.2</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -742,13 +742,13 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6">
@@ -862,7 +862,7 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0.73</v>
@@ -985,7 +985,7 @@
         <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="R9" t="n">
         <v>0.6899999999999999</v>
@@ -1045,7 +1045,7 @@
         <v>0.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0.41</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0.8100000000000001</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0.86</v>
@@ -1345,7 +1345,7 @@
         <v>1.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0.59</v>
@@ -1405,7 +1405,7 @@
         <v>0.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
         <v>0.34</v>
@@ -1426,13 +1426,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G17" t="n">
         <v>19.1</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Q17" t="n">
         <v>0.87</v>
@@ -1558,10 +1558,10 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>0.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="R19" t="n">
         <v>0.57</v>
@@ -2158,10 +2158,10 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>70.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I29" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2365,7 +2365,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R32" t="n">
         <v>0.21</v>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q33" t="n">
         <v>0.98</v>
@@ -2485,7 +2485,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R34" t="n">
         <v>0.39</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q36" t="n">
         <v>0.68</v>
@@ -2665,7 +2665,7 @@
         <v>0.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R37" t="n">
         <v>0.21</v>
@@ -2725,7 +2725,7 @@
         <v>0.71</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="R38" t="n">
         <v>0.34</v>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q39" t="n">
         <v>0.87</v>
@@ -2818,10 +2818,10 @@
         <v>80.8</v>
       </c>
       <c r="H40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="E41" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="R41" t="n">
         <v>0.42</v>
@@ -2929,10 +2929,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="F42" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="Q42" t="n">
         <v>0.79</v>
@@ -2998,10 +2998,10 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3202,10 +3202,10 @@
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="R46" t="n">
         <v>0.67</v>
@@ -3385,7 +3385,7 @@
         <v>0.93</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R49" t="n">
         <v>0.36</v>
@@ -3457,13 +3457,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G2" t="n">
         <v>19.1</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="E4" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="F5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="K2" t="n">
         <v>54.4</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1825</v>
+        <v>1.1796</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9115</v>
+        <v>0.9103</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5067,14 +5067,14 @@
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6362</v>
+        <v>0.6365</v>
       </c>
       <c r="M3" t="n">
         <v>0.9668</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8756</v>
+        <v>0.8747</v>
       </c>
       <c r="L4" t="n">
         <v>0.7322</v>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2641</v>
+        <v>1.2607</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9518</v>
       </c>
       <c r="M5" t="n">
         <v>0.5955</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5205,14 +5205,14 @@
         <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7852</v>
+        <v>0.7847</v>
       </c>
       <c r="M6" t="n">
         <v>0.6945</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5248,17 +5248,17 @@
         <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9905</v>
+        <v>0.9889</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0066</v>
+        <v>1.0049</v>
       </c>
       <c r="M7" t="n">
         <v>0.4138</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5294,17 +5294,17 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4183</v>
+        <v>1.414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8079</v>
+        <v>0.8073</v>
       </c>
       <c r="M8" t="n">
         <v>0.6693</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5340,17 +5340,17 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0635</v>
+        <v>1.0613</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6995</v>
+        <v>0.6996</v>
       </c>
       <c r="M9" t="n">
         <v>0.5385</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5386,17 +5386,17 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0057</v>
+        <v>1.004</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8598</v>
+        <v>0.8591</v>
       </c>
       <c r="M10" t="n">
         <v>0.3984</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5432,17 @@
         <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0705</v>
+        <v>1.0683</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6233</v>
+        <v>0.6239</v>
       </c>
       <c r="M11" t="n">
         <v>0.679</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5478,17 +5478,17 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1624</v>
+        <v>1.1596</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0066</v>
+        <v>1.0048</v>
       </c>
       <c r="M12" t="n">
         <v>0.5918</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
         <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923</v>
+        <v>0.9907</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3051</v>
+        <v>1.3015</v>
       </c>
       <c r="M13" t="n">
         <v>0.338</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5570,17 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1465</v>
+        <v>1.1439</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8707</v>
+        <v>0.87</v>
       </c>
       <c r="M14" t="n">
         <v>0.5483</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9113</v>
+        <v>0.9101</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7194</v>
       </c>
       <c r="M15" t="n">
         <v>0.4947</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5662,17 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8631</v>
+        <v>0.8623</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5708,17 @@
         <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0321</v>
+        <v>1.03</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7983</v>
+        <v>0.7976</v>
       </c>
       <c r="M17" t="n">
         <v>0.519</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5748,23 +5748,23 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2587</v>
+        <v>1.4487</v>
       </c>
       <c r="L18" t="n">
-        <v>0.639</v>
+        <v>0.7872</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7439</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5794,23 +5794,23 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5773</v>
+        <v>1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6425</v>
+        <v>0.8718</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8847</v>
+        <v>0.8162</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6415</v>
+        <v>1.6356</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8547</v>
+        <v>0.8539</v>
       </c>
       <c r="M20" t="n">
         <v>0.7357</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5892,17 +5892,17 @@
         <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6394</v>
+        <v>0.6402</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9928</v>
+        <v>0.9913</v>
       </c>
       <c r="M21" t="n">
         <v>0.221</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5938,17 +5938,17 @@
         <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>0.958</v>
+        <v>0.9566</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1017</v>
+        <v>1.0993</v>
       </c>
       <c r="M22" t="n">
         <v>0.3031</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5984,17 +5984,17 @@
         <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1296</v>
+        <v>1.127</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7241</v>
+        <v>0.7242</v>
       </c>
       <c r="M23" t="n">
         <v>0.5376</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6030,17 @@
         <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7024</v>
+        <v>0.7027</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2717</v>
+        <v>1.2682</v>
       </c>
       <c r="M24" t="n">
         <v>0.3878</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1031</v>
+        <v>1.1007</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6988</v>
+        <v>0.6989</v>
       </c>
       <c r="M25" t="n">
         <v>0.6505</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6122,17 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1983</v>
+        <v>1.1953</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7058</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0.641</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
         <v>32</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8579</v>
+        <v>0.8572</v>
       </c>
       <c r="L27" t="n">
-        <v>1.343</v>
+        <v>1.339</v>
       </c>
       <c r="M27" t="n">
         <v>0.1547</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>1.075</v>
+        <v>1.0728</v>
       </c>
       <c r="L28" t="n">
         <v>0.55</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6260,17 +6260,17 @@
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>1.313</v>
+        <v>1.3093</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5947</v>
       </c>
       <c r="M29" t="n">
         <v>0.7085</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4834</v>
+        <v>1.4786</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8172</v>
+        <v>0.8166</v>
       </c>
       <c r="M30" t="n">
         <v>0.6656</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6352,17 +6352,17 @@
         <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9379</v>
+        <v>0.9367</v>
       </c>
       <c r="L31" t="n">
-        <v>1.399</v>
+        <v>1.3947</v>
       </c>
       <c r="M31" t="n">
         <v>0.2061</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
         <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>1.4857</v>
+        <v>1.4811</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9796</v>
+        <v>0.9779</v>
       </c>
       <c r="M32" t="n">
         <v>0.6666</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6444,17 +6444,17 @@
         <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9385</v>
+        <v>0.9371</v>
       </c>
       <c r="L33" t="n">
-        <v>1.0461</v>
+        <v>1.0441</v>
       </c>
       <c r="M33" t="n">
         <v>0.3925</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6490,17 +6490,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0.839</v>
+        <v>0.8383</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8273</v>
+        <v>0.8267</v>
       </c>
       <c r="M34" t="n">
         <v>0.4483</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2669</v>
+        <v>1.2635</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6806</v>
+        <v>0.6807</v>
       </c>
       <c r="M35" t="n">
         <v>0.6502</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6582,17 +6582,17 @@
         <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7005</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3183</v>
+        <v>1.3145</v>
       </c>
       <c r="M36" t="n">
         <v>0.2125</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
         <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7126</v>
+        <v>0.7128</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9853</v>
+        <v>0.9836</v>
       </c>
       <c r="M37" t="n">
         <v>0.3434</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6674,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0463</v>
+        <v>1.0444</v>
       </c>
       <c r="L38" t="n">
-        <v>0.866</v>
+        <v>0.8653</v>
       </c>
       <c r="M38" t="n">
         <v>0.5163</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6720,17 @@
         <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3447</v>
+        <v>1.3408</v>
       </c>
       <c r="L39" t="n">
-        <v>1.023</v>
+        <v>1.0211</v>
       </c>
       <c r="M39" t="n">
         <v>0.458</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6766,17 +6766,17 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>0.754</v>
+        <v>0.7538</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7952</v>
+        <v>0.7947</v>
       </c>
       <c r="M40" t="n">
         <v>0.4219</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6812,17 @@
         <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9658</v>
+        <v>0.9644</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7915</v>
       </c>
       <c r="M41" t="n">
         <v>0.5397999999999999</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3886</v>
+        <v>1.3845</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,17 @@
         <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1693</v>
+        <v>1.1665</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3649</v>
+        <v>1.3609</v>
       </c>
       <c r="M43" t="n">
         <v>0.3881</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
         <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>1.2731</v>
+        <v>1.2697</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7977</v>
+        <v>0.7971</v>
       </c>
       <c r="M44" t="n">
         <v>0.6076</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -6999,14 +6999,14 @@
         <v>0.7225</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4437</v>
+        <v>1.4392</v>
       </c>
       <c r="M45" t="n">
         <v>0.2471</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7042,17 @@
         <v>26</v>
       </c>
       <c r="K46" t="n">
-        <v>1.2153</v>
+        <v>1.2122</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9051</v>
+        <v>0.9041</v>
       </c>
       <c r="M46" t="n">
         <v>0.6705</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,17 +7088,17 @@
         <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2749</v>
+        <v>1.2714</v>
       </c>
       <c r="L47" t="n">
-        <v>1.169</v>
+        <v>1.1662</v>
       </c>
       <c r="M47" t="n">
         <v>0.545</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7137,14 +7137,14 @@
         <v>0.7803</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8504</v>
+        <v>0.8499</v>
       </c>
       <c r="M48" t="n">
         <v>0.3601</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -7180,17 +7180,17 @@
         <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>0.929</v>
+        <v>0.9277</v>
       </c>
       <c r="L49" t="n">
-        <v>1.2279</v>
+        <v>1.2247</v>
       </c>
       <c r="M49" t="n">
         <v>0.3551</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-07-15T18:00:00+00:00</t>
+          <t>2026-07-18T20:00:00+00:00</t>
         </is>
       </c>
     </row>

--- a/worldcup-schedule/output/worldcup_prediction_model.xlsx
+++ b/worldcup-schedule/output/worldcup_prediction_model.xlsx
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -547,10 +547,10 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>60.3</v>
       </c>
       <c r="L2" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -558,28 +558,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1577.2</v>
+        <v>1603.8</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -607,28 +607,28 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>61.6</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>小组第1 → 4强</t>
+          <t>小组第1 → 亚军</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1603.8</v>
+        <v>1577.2</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="4">
@@ -667,10 +667,10 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>38.3</v>
+        <v>39.6</v>
       </c>
       <c r="L4" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>51.2</v>
+        <v>51.8</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0.73</v>
@@ -985,7 +985,7 @@
         <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="R9" t="n">
         <v>0.6899999999999999</v>
@@ -1045,7 +1045,7 @@
         <v>0.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0.41</v>
@@ -1345,7 +1345,7 @@
         <v>1.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0.59</v>
@@ -1558,10 +1558,10 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2158,10 +2158,10 @@
         <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>70.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>1.31</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="R30" t="n">
         <v>0.71</v>
@@ -2818,10 +2818,10 @@
         <v>80.8</v>
       </c>
       <c r="H40" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="R41" t="n">
         <v>0.42</v>
@@ -2998,10 +2998,10 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0.93</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R49" t="n">
         <v>0.36</v>
@@ -5018,17 +5018,17 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9103</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>0.6042</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00+00:00</t>
+          <t>2026-07-19T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5049,32 +5049,32 @@
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>1.65</v>
+        <v>1.5602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6365</v>
+        <v>0.6469</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9668</v>
+        <v>0.8853</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00+00:00</t>
+          <t>2026-07-19T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5110,17 @@
         <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8747</v>
+        <v>0.8752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7322</v>
+        <v>0.7328</v>
       </c>
       <c r="M4" t="n">
         <v>0.4951</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-18T20:00:00+00:00</t>
+          <t>2026-07-19T18:00:00+00:00</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2607</v>
+        <v>1.2609</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9518</v>
+        <v>0.9522</v>
       